--- a/Part-Supplier Risk Model/Supplier_Scorecard.xlsx
+++ b/Part-Supplier Risk Model/Supplier_Scorecard.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Read Me" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Score Log" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Dashboard" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="PART_RISK" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Risk Suggestions" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Suppliers" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Rubric" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Settings" sheetId="7" state="visible" r:id="rId9"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="147">
   <si>
     <t xml:space="preserve">Supplier Scorecard — how to use</t>
   </si>
@@ -255,145 +255,46 @@
     <t xml:space="preserve">Rows mirror the process list in Settings (first 20); columns mirror the first 10 suppliers. Blank = no projects yet for that pairing.</t>
   </si>
   <si>
-    <t xml:space="preserve">PART-SUPPLIER RISK - SCORECARD OUTPUT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same columns A-T as the PART_RISK tab of Part_Supplier_Risk_Model - rows copy straight across (paste as values). Supplier comes from this workbook's Suppliers tab. Qty_per_Quarter, Supplier_Stability, External_Factors and Supplier_Flags are hard entries here - the master model computes them. Columns U-W pull this scorecard's own performance data: Suggested_Risk = 6 - average Overall, a starting point when scoring Quality_Compliance. Score 1 (low risk) to 5 (high risk).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. IDENTIFY THE PART</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. VOLUME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. SCORE THE PART (1-5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. SUPPLIER SCORES (manual here)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. IMPACT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPPLIER FLAGS (manual)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESULT (auto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. ACTIONS &amp; REVIEW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCORECARD LINK (auto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIRRORED FROM MASTER MODEL (editable)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part_Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part_Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part_Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qty_per_Model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qty_per_Quarter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sourcing_Backup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality_Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capacity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supplier_Stability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">External_Factors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impact (1-5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supplier_Flags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Likelihood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Risk_Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Risk_Band</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top_Driver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitigation / Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last_Reviewed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scorecard_Overall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suggested_Risk (6-Overall)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projects_Logged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sourcing weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capacity weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stability weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">External weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total (=100%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRITICAL &gt;=</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MONITOR &gt;=</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Driver names:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sourcing &amp; Backup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality &amp; Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supplier Stability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">External Factors</t>
+    <t xml:space="preserve">Risk Suggestions - feed for the Part-Supplier Risk Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fully automatic, one row per supplier. Translation: risk = 6 - average performance (scorecard 5 = excellent -&gt; risk 1 = low), rounded to the nearest whole score and clamped to 1-5. Type the suggested values into the PART_RISK tab of Part_Supplier_Risk_Model - they are a starting point, not an override; adjust with judgment and with what the scorecard cannot see.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUPPLIER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCORECARD PERFORMANCE (auto, 5 = excellent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUGGESTED RISK ENTRIES FOR PART_RISK (1 = low risk ... 5 = high)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality_Compliance (suggest)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacity (suggest)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplier_Stability (suggest)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOW THE TRANSLATION WORKS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality_Compliance  &lt;-  6 - avg Quality.  What they actually delivered is direct evidence for the part's quality risk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacity  &lt;-  6 - avg Lead time.  Observed delivery performance is the visible side of capacity; sanity-check against On-time %.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplier_Stability  &lt;-  6 - average(Responsiveness, Cost).  Cost has no part-level column in the risk register, but erratic pricing and poor cost transparency - like slow communication - are evidence about the supplier as a business, so both feed the Stability suggestion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No scorecard equivalent - score these by judgment in the master model:  Sourcing_Backup (do alternatives exist?),  External_Factors (location, logistics, borders),  Impact (what the part means to the model),  Qty_per_Model / volume.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggestions round to the nearest whole score and clamp to 1-5. A supplier with few projects logged (see Projects column) is thin evidence - weigh it accordingly.</t>
   </si>
   <si>
     <t xml:space="preserve">Supplier directory</t>
@@ -585,8 +486,8 @@
     <numFmt numFmtId="168" formatCode="#,##0"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="0%"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
-    <numFmt numFmtId="172" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="171" formatCode="General"/>
+    <numFmt numFmtId="172" formatCode="0.0"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -726,14 +627,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -770,7 +672,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -803,14 +705,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF6DC"/>
-        <bgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF6DC"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -880,7 +776,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="55">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1017,63 +913,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="171" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="20" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1081,20 +949,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="19" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1125,11 +981,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="24" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1151,7 +1007,7 @@
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
     <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1256,48 +1112,6 @@
         <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
         <color rgb="FFFFFFFF"/>
         <sz val="10"/>
       </font>
@@ -1315,20 +1129,20 @@
       <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFF2CC"/>
+      <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF9C0006"/>
-      <rgbColor rgb="FF006100"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF9C6500"/>
+      <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF6DC"/>
+      <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFF8696B"/>
@@ -1344,12 +1158,12 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFD9E2F3"/>
-      <rgbColor rgb="FFC6EFCE"/>
-      <rgbColor rgb="FFFFEB9C"/>
       <rgbColor rgb="FFF9F9F9"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFC7CE"/>
+      <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -1539,11 +1353,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="49612605"/>
-        <c:axId val="55727902"/>
+        <c:axId val="29834272"/>
+        <c:axId val="67701022"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="49612605"/>
+        <c:axId val="29834272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1575,7 +1389,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55727902"/>
+        <c:crossAx val="67701022"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1583,7 +1397,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="55727902"/>
+        <c:axId val="67701022"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -1627,7 +1441,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49612605"/>
+        <c:crossAx val="29834272"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11907,33 +11721,18 @@
     <tabColor rgb="FFC00000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Z104"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11946,4837 +11745,1554 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34" t="s">
+      <c r="B3" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34" t="s">
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34" t="s">
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+    </row>
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="L3" s="34"/>
-      <c r="M3" s="35" t="s">
+      <c r="J4" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="N3" s="35" t="s">
+      <c r="K4" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="34" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="37" t="str">
+        <f aca="false">IF(Suppliers!A3="","",Suppliers!A3)</f>
+        <v>Fictiv</v>
+      </c>
+      <c r="B5" s="38" t="n">
+        <f aca="false">IF($A5="","",COUNTIF('Score Log'!$C$4:$C$203,$A5))</f>
+        <v>1</v>
+      </c>
+      <c r="C5" s="39" t="n">
+        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A5),1),"-"))</f>
+        <v>4</v>
+      </c>
+      <c r="D5" s="39" t="n">
+        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A5),1),"-"))</f>
+        <v>5</v>
+      </c>
+      <c r="E5" s="39" t="n">
+        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A5),1),"-"))</f>
+        <v>4</v>
+      </c>
+      <c r="F5" s="39" t="n">
+        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A5),1),"-"))</f>
+        <v>5</v>
+      </c>
+      <c r="G5" s="39" t="n">
+        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A5),1),"-"))</f>
+        <v>4.5</v>
+      </c>
+      <c r="H5" s="40" t="n">
+        <f aca="false">IF($A5="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A5,'Score Log'!$U$4:$U$203,"Yes")/$B5,"-"))</f>
+        <v>1</v>
+      </c>
+      <c r="I5" s="41" t="n">
+        <f aca="false">IF($A5="","",IF(ISNUMBER($D5),MAX(1,MIN(5,ROUND(6-$D5,0))),"-"))</f>
+        <v>1</v>
+      </c>
+      <c r="J5" s="41" t="n">
+        <f aca="false">IF($A5="","",IF(ISNUMBER($E5),MAX(1,MIN(5,ROUND(6-$E5,0))),"-"))</f>
+        <v>2</v>
+      </c>
+      <c r="K5" s="41" t="n">
+        <f aca="false">IF($A5="","",IF(AND(ISNUMBER($F5),ISNUMBER($C5)),MAX(1,MIN(5,ROUND(6-AVERAGE($F5,$C5),0))),IF(ISNUMBER($F5),MAX(1,MIN(5,ROUND(6-$F5,0))),"-")))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="37" t="str">
+        <f aca="false">IF(Suppliers!A4="","",Suppliers!A4)</f>
+        <v>Advanced Plastiform</v>
+      </c>
+      <c r="B6" s="38" t="n">
+        <f aca="false">IF($A6="","",COUNTIF('Score Log'!$C$4:$C$203,$A6))</f>
+        <v>1</v>
+      </c>
+      <c r="C6" s="39" t="str">
+        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A6),1),"-"))</f>
+        <v>-</v>
+      </c>
+      <c r="D6" s="39" t="str">
+        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A6),1),"-"))</f>
+        <v>-</v>
+      </c>
+      <c r="E6" s="39" t="str">
+        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A6),1),"-"))</f>
+        <v>-</v>
+      </c>
+      <c r="F6" s="39" t="str">
+        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A6),1),"-"))</f>
+        <v>-</v>
+      </c>
+      <c r="G6" s="39" t="str">
+        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A6),1),"-"))</f>
+        <v>-</v>
+      </c>
+      <c r="H6" s="40" t="n">
+        <f aca="false">IF($A6="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A6,'Score Log'!$U$4:$U$203,"Yes")/$B6,"-"))</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="41" t="str">
+        <f aca="false">IF($A6="","",IF(ISNUMBER($D6),MAX(1,MIN(5,ROUND(6-$D6,0))),"-"))</f>
+        <v>-</v>
+      </c>
+      <c r="J6" s="41" t="str">
+        <f aca="false">IF($A6="","",IF(ISNUMBER($E6),MAX(1,MIN(5,ROUND(6-$E6,0))),"-"))</f>
+        <v>-</v>
+      </c>
+      <c r="K6" s="41" t="str">
+        <f aca="false">IF($A6="","",IF(AND(ISNUMBER($F6),ISNUMBER($C6)),MAX(1,MIN(5,ROUND(6-AVERAGE($F6,$C6),0))),IF(ISNUMBER($F6),MAX(1,MIN(5,ROUND(6-$F6,0))),"-")))</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="37" t="str">
+        <f aca="false">IF(Suppliers!A5="","",Suppliers!A5)</f>
+        <v/>
+      </c>
+      <c r="B7" s="38" t="str">
+        <f aca="false">IF($A7="","",COUNTIF('Score Log'!$C$4:$C$203,$A7))</f>
+        <v/>
+      </c>
+      <c r="C7" s="39" t="str">
+        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A7),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D7" s="39" t="str">
+        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A7),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E7" s="39" t="str">
+        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A7),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F7" s="39" t="str">
+        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A7),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G7" s="39" t="str">
+        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A7),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H7" s="40" t="str">
+        <f aca="false">IF($A7="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A7,'Score Log'!$U$4:$U$203,"Yes")/$B7,"-"))</f>
+        <v/>
+      </c>
+      <c r="I7" s="41" t="str">
+        <f aca="false">IF($A7="","",IF(ISNUMBER($D7),MAX(1,MIN(5,ROUND(6-$D7,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J7" s="41" t="str">
+        <f aca="false">IF($A7="","",IF(ISNUMBER($E7),MAX(1,MIN(5,ROUND(6-$E7,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K7" s="41" t="str">
+        <f aca="false">IF($A7="","",IF(AND(ISNUMBER($F7),ISNUMBER($C7)),MAX(1,MIN(5,ROUND(6-AVERAGE($F7,$C7),0))),IF(ISNUMBER($F7),MAX(1,MIN(5,ROUND(6-$F7,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="37" t="str">
+        <f aca="false">IF(Suppliers!A6="","",Suppliers!A6)</f>
+        <v/>
+      </c>
+      <c r="B8" s="38" t="str">
+        <f aca="false">IF($A8="","",COUNTIF('Score Log'!$C$4:$C$203,$A8))</f>
+        <v/>
+      </c>
+      <c r="C8" s="39" t="str">
+        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A8),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D8" s="39" t="str">
+        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A8),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E8" s="39" t="str">
+        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A8),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F8" s="39" t="str">
+        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A8),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G8" s="39" t="str">
+        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A8),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H8" s="40" t="str">
+        <f aca="false">IF($A8="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A8,'Score Log'!$U$4:$U$203,"Yes")/$B8,"-"))</f>
+        <v/>
+      </c>
+      <c r="I8" s="41" t="str">
+        <f aca="false">IF($A8="","",IF(ISNUMBER($D8),MAX(1,MIN(5,ROUND(6-$D8,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J8" s="41" t="str">
+        <f aca="false">IF($A8="","",IF(ISNUMBER($E8),MAX(1,MIN(5,ROUND(6-$E8,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K8" s="41" t="str">
+        <f aca="false">IF($A8="","",IF(AND(ISNUMBER($F8),ISNUMBER($C8)),MAX(1,MIN(5,ROUND(6-AVERAGE($F8,$C8),0))),IF(ISNUMBER($F8),MAX(1,MIN(5,ROUND(6-$F8,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="37" t="str">
+        <f aca="false">IF(Suppliers!A7="","",Suppliers!A7)</f>
+        <v/>
+      </c>
+      <c r="B9" s="38" t="str">
+        <f aca="false">IF($A9="","",COUNTIF('Score Log'!$C$4:$C$203,$A9))</f>
+        <v/>
+      </c>
+      <c r="C9" s="39" t="str">
+        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A9),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D9" s="39" t="str">
+        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A9),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E9" s="39" t="str">
+        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A9),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F9" s="39" t="str">
+        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A9),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G9" s="39" t="str">
+        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A9),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H9" s="40" t="str">
+        <f aca="false">IF($A9="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A9,'Score Log'!$U$4:$U$203,"Yes")/$B9,"-"))</f>
+        <v/>
+      </c>
+      <c r="I9" s="41" t="str">
+        <f aca="false">IF($A9="","",IF(ISNUMBER($D9),MAX(1,MIN(5,ROUND(6-$D9,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J9" s="41" t="str">
+        <f aca="false">IF($A9="","",IF(ISNUMBER($E9),MAX(1,MIN(5,ROUND(6-$E9,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K9" s="41" t="str">
+        <f aca="false">IF($A9="","",IF(AND(ISNUMBER($F9),ISNUMBER($C9)),MAX(1,MIN(5,ROUND(6-AVERAGE($F9,$C9),0))),IF(ISNUMBER($F9),MAX(1,MIN(5,ROUND(6-$F9,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="37" t="str">
+        <f aca="false">IF(Suppliers!A8="","",Suppliers!A8)</f>
+        <v/>
+      </c>
+      <c r="B10" s="38" t="str">
+        <f aca="false">IF($A10="","",COUNTIF('Score Log'!$C$4:$C$203,$A10))</f>
+        <v/>
+      </c>
+      <c r="C10" s="39" t="str">
+        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A10),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D10" s="39" t="str">
+        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A10),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E10" s="39" t="str">
+        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A10),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F10" s="39" t="str">
+        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A10),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G10" s="39" t="str">
+        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A10),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H10" s="40" t="str">
+        <f aca="false">IF($A10="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A10,'Score Log'!$U$4:$U$203,"Yes")/$B10,"-"))</f>
+        <v/>
+      </c>
+      <c r="I10" s="41" t="str">
+        <f aca="false">IF($A10="","",IF(ISNUMBER($D10),MAX(1,MIN(5,ROUND(6-$D10,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J10" s="41" t="str">
+        <f aca="false">IF($A10="","",IF(ISNUMBER($E10),MAX(1,MIN(5,ROUND(6-$E10,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K10" s="41" t="str">
+        <f aca="false">IF($A10="","",IF(AND(ISNUMBER($F10),ISNUMBER($C10)),MAX(1,MIN(5,ROUND(6-AVERAGE($F10,$C10),0))),IF(ISNUMBER($F10),MAX(1,MIN(5,ROUND(6-$F10,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="37" t="str">
+        <f aca="false">IF(Suppliers!A9="","",Suppliers!A9)</f>
+        <v/>
+      </c>
+      <c r="B11" s="38" t="str">
+        <f aca="false">IF($A11="","",COUNTIF('Score Log'!$C$4:$C$203,$A11))</f>
+        <v/>
+      </c>
+      <c r="C11" s="39" t="str">
+        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A11),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D11" s="39" t="str">
+        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A11),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E11" s="39" t="str">
+        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A11),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F11" s="39" t="str">
+        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A11),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G11" s="39" t="str">
+        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A11),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H11" s="40" t="str">
+        <f aca="false">IF($A11="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A11,'Score Log'!$U$4:$U$203,"Yes")/$B11,"-"))</f>
+        <v/>
+      </c>
+      <c r="I11" s="41" t="str">
+        <f aca="false">IF($A11="","",IF(ISNUMBER($D11),MAX(1,MIN(5,ROUND(6-$D11,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J11" s="41" t="str">
+        <f aca="false">IF($A11="","",IF(ISNUMBER($E11),MAX(1,MIN(5,ROUND(6-$E11,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K11" s="41" t="str">
+        <f aca="false">IF($A11="","",IF(AND(ISNUMBER($F11),ISNUMBER($C11)),MAX(1,MIN(5,ROUND(6-AVERAGE($F11,$C11),0))),IF(ISNUMBER($F11),MAX(1,MIN(5,ROUND(6-$F11,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="37" t="str">
+        <f aca="false">IF(Suppliers!A10="","",Suppliers!A10)</f>
+        <v/>
+      </c>
+      <c r="B12" s="38" t="str">
+        <f aca="false">IF($A12="","",COUNTIF('Score Log'!$C$4:$C$203,$A12))</f>
+        <v/>
+      </c>
+      <c r="C12" s="39" t="str">
+        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A12),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D12" s="39" t="str">
+        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A12),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E12" s="39" t="str">
+        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A12),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F12" s="39" t="str">
+        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A12),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G12" s="39" t="str">
+        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A12),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H12" s="40" t="str">
+        <f aca="false">IF($A12="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A12,'Score Log'!$U$4:$U$203,"Yes")/$B12,"-"))</f>
+        <v/>
+      </c>
+      <c r="I12" s="41" t="str">
+        <f aca="false">IF($A12="","",IF(ISNUMBER($D12),MAX(1,MIN(5,ROUND(6-$D12,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J12" s="41" t="str">
+        <f aca="false">IF($A12="","",IF(ISNUMBER($E12),MAX(1,MIN(5,ROUND(6-$E12,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K12" s="41" t="str">
+        <f aca="false">IF($A12="","",IF(AND(ISNUMBER($F12),ISNUMBER($C12)),MAX(1,MIN(5,ROUND(6-AVERAGE($F12,$C12),0))),IF(ISNUMBER($F12),MAX(1,MIN(5,ROUND(6-$F12,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="37" t="str">
+        <f aca="false">IF(Suppliers!A11="","",Suppliers!A11)</f>
+        <v/>
+      </c>
+      <c r="B13" s="38" t="str">
+        <f aca="false">IF($A13="","",COUNTIF('Score Log'!$C$4:$C$203,$A13))</f>
+        <v/>
+      </c>
+      <c r="C13" s="39" t="str">
+        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A13),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D13" s="39" t="str">
+        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A13),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E13" s="39" t="str">
+        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A13),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F13" s="39" t="str">
+        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A13),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G13" s="39" t="str">
+        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A13),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H13" s="40" t="str">
+        <f aca="false">IF($A13="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A13,'Score Log'!$U$4:$U$203,"Yes")/$B13,"-"))</f>
+        <v/>
+      </c>
+      <c r="I13" s="41" t="str">
+        <f aca="false">IF($A13="","",IF(ISNUMBER($D13),MAX(1,MIN(5,ROUND(6-$D13,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J13" s="41" t="str">
+        <f aca="false">IF($A13="","",IF(ISNUMBER($E13),MAX(1,MIN(5,ROUND(6-$E13,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K13" s="41" t="str">
+        <f aca="false">IF($A13="","",IF(AND(ISNUMBER($F13),ISNUMBER($C13)),MAX(1,MIN(5,ROUND(6-AVERAGE($F13,$C13),0))),IF(ISNUMBER($F13),MAX(1,MIN(5,ROUND(6-$F13,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="37" t="str">
+        <f aca="false">IF(Suppliers!A12="","",Suppliers!A12)</f>
+        <v/>
+      </c>
+      <c r="B14" s="38" t="str">
+        <f aca="false">IF($A14="","",COUNTIF('Score Log'!$C$4:$C$203,$A14))</f>
+        <v/>
+      </c>
+      <c r="C14" s="39" t="str">
+        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A14),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D14" s="39" t="str">
+        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A14),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E14" s="39" t="str">
+        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A14),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F14" s="39" t="str">
+        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A14),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G14" s="39" t="str">
+        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A14),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H14" s="40" t="str">
+        <f aca="false">IF($A14="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A14,'Score Log'!$U$4:$U$203,"Yes")/$B14,"-"))</f>
+        <v/>
+      </c>
+      <c r="I14" s="41" t="str">
+        <f aca="false">IF($A14="","",IF(ISNUMBER($D14),MAX(1,MIN(5,ROUND(6-$D14,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J14" s="41" t="str">
+        <f aca="false">IF($A14="","",IF(ISNUMBER($E14),MAX(1,MIN(5,ROUND(6-$E14,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K14" s="41" t="str">
+        <f aca="false">IF($A14="","",IF(AND(ISNUMBER($F14),ISNUMBER($C14)),MAX(1,MIN(5,ROUND(6-AVERAGE($F14,$C14),0))),IF(ISNUMBER($F14),MAX(1,MIN(5,ROUND(6-$F14,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="37" t="str">
+        <f aca="false">IF(Suppliers!A13="","",Suppliers!A13)</f>
+        <v/>
+      </c>
+      <c r="B15" s="38" t="str">
+        <f aca="false">IF($A15="","",COUNTIF('Score Log'!$C$4:$C$203,$A15))</f>
+        <v/>
+      </c>
+      <c r="C15" s="39" t="str">
+        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A15),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D15" s="39" t="str">
+        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A15),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E15" s="39" t="str">
+        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A15),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F15" s="39" t="str">
+        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A15),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="39" t="str">
+        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A15),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H15" s="40" t="str">
+        <f aca="false">IF($A15="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A15,'Score Log'!$U$4:$U$203,"Yes")/$B15,"-"))</f>
+        <v/>
+      </c>
+      <c r="I15" s="41" t="str">
+        <f aca="false">IF($A15="","",IF(ISNUMBER($D15),MAX(1,MIN(5,ROUND(6-$D15,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J15" s="41" t="str">
+        <f aca="false">IF($A15="","",IF(ISNUMBER($E15),MAX(1,MIN(5,ROUND(6-$E15,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K15" s="41" t="str">
+        <f aca="false">IF($A15="","",IF(AND(ISNUMBER($F15),ISNUMBER($C15)),MAX(1,MIN(5,ROUND(6-AVERAGE($F15,$C15),0))),IF(ISNUMBER($F15),MAX(1,MIN(5,ROUND(6-$F15,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="37" t="str">
+        <f aca="false">IF(Suppliers!A14="","",Suppliers!A14)</f>
+        <v/>
+      </c>
+      <c r="B16" s="38" t="str">
+        <f aca="false">IF($A16="","",COUNTIF('Score Log'!$C$4:$C$203,$A16))</f>
+        <v/>
+      </c>
+      <c r="C16" s="39" t="str">
+        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A16),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D16" s="39" t="str">
+        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A16),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E16" s="39" t="str">
+        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A16),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F16" s="39" t="str">
+        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A16),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G16" s="39" t="str">
+        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A16),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H16" s="40" t="str">
+        <f aca="false">IF($A16="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A16,'Score Log'!$U$4:$U$203,"Yes")/$B16,"-"))</f>
+        <v/>
+      </c>
+      <c r="I16" s="41" t="str">
+        <f aca="false">IF($A16="","",IF(ISNUMBER($D16),MAX(1,MIN(5,ROUND(6-$D16,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J16" s="41" t="str">
+        <f aca="false">IF($A16="","",IF(ISNUMBER($E16),MAX(1,MIN(5,ROUND(6-$E16,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K16" s="41" t="str">
+        <f aca="false">IF($A16="","",IF(AND(ISNUMBER($F16),ISNUMBER($C16)),MAX(1,MIN(5,ROUND(6-AVERAGE($F16,$C16),0))),IF(ISNUMBER($F16),MAX(1,MIN(5,ROUND(6-$F16,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="37" t="str">
+        <f aca="false">IF(Suppliers!A15="","",Suppliers!A15)</f>
+        <v/>
+      </c>
+      <c r="B17" s="38" t="str">
+        <f aca="false">IF($A17="","",COUNTIF('Score Log'!$C$4:$C$203,$A17))</f>
+        <v/>
+      </c>
+      <c r="C17" s="39" t="str">
+        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A17),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D17" s="39" t="str">
+        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A17),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E17" s="39" t="str">
+        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A17),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F17" s="39" t="str">
+        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A17),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G17" s="39" t="str">
+        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A17),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H17" s="40" t="str">
+        <f aca="false">IF($A17="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A17,'Score Log'!$U$4:$U$203,"Yes")/$B17,"-"))</f>
+        <v/>
+      </c>
+      <c r="I17" s="41" t="str">
+        <f aca="false">IF($A17="","",IF(ISNUMBER($D17),MAX(1,MIN(5,ROUND(6-$D17,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J17" s="41" t="str">
+        <f aca="false">IF($A17="","",IF(ISNUMBER($E17),MAX(1,MIN(5,ROUND(6-$E17,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K17" s="41" t="str">
+        <f aca="false">IF($A17="","",IF(AND(ISNUMBER($F17),ISNUMBER($C17)),MAX(1,MIN(5,ROUND(6-AVERAGE($F17,$C17),0))),IF(ISNUMBER($F17),MAX(1,MIN(5,ROUND(6-$F17,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="37" t="str">
+        <f aca="false">IF(Suppliers!A16="","",Suppliers!A16)</f>
+        <v/>
+      </c>
+      <c r="B18" s="38" t="str">
+        <f aca="false">IF($A18="","",COUNTIF('Score Log'!$C$4:$C$203,$A18))</f>
+        <v/>
+      </c>
+      <c r="C18" s="39" t="str">
+        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A18),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D18" s="39" t="str">
+        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A18),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E18" s="39" t="str">
+        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A18),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F18" s="39" t="str">
+        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A18),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G18" s="39" t="str">
+        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A18),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H18" s="40" t="str">
+        <f aca="false">IF($A18="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A18,'Score Log'!$U$4:$U$203,"Yes")/$B18,"-"))</f>
+        <v/>
+      </c>
+      <c r="I18" s="41" t="str">
+        <f aca="false">IF($A18="","",IF(ISNUMBER($D18),MAX(1,MIN(5,ROUND(6-$D18,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J18" s="41" t="str">
+        <f aca="false">IF($A18="","",IF(ISNUMBER($E18),MAX(1,MIN(5,ROUND(6-$E18,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K18" s="41" t="str">
+        <f aca="false">IF($A18="","",IF(AND(ISNUMBER($F18),ISNUMBER($C18)),MAX(1,MIN(5,ROUND(6-AVERAGE($F18,$C18),0))),IF(ISNUMBER($F18),MAX(1,MIN(5,ROUND(6-$F18,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="37" t="str">
+        <f aca="false">IF(Suppliers!A17="","",Suppliers!A17)</f>
+        <v/>
+      </c>
+      <c r="B19" s="38" t="str">
+        <f aca="false">IF($A19="","",COUNTIF('Score Log'!$C$4:$C$203,$A19))</f>
+        <v/>
+      </c>
+      <c r="C19" s="39" t="str">
+        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A19),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D19" s="39" t="str">
+        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A19),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E19" s="39" t="str">
+        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A19),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F19" s="39" t="str">
+        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A19),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G19" s="39" t="str">
+        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A19),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H19" s="40" t="str">
+        <f aca="false">IF($A19="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A19,'Score Log'!$U$4:$U$203,"Yes")/$B19,"-"))</f>
+        <v/>
+      </c>
+      <c r="I19" s="41" t="str">
+        <f aca="false">IF($A19="","",IF(ISNUMBER($D19),MAX(1,MIN(5,ROUND(6-$D19,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J19" s="41" t="str">
+        <f aca="false">IF($A19="","",IF(ISNUMBER($E19),MAX(1,MIN(5,ROUND(6-$E19,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K19" s="41" t="str">
+        <f aca="false">IF($A19="","",IF(AND(ISNUMBER($F19),ISNUMBER($C19)),MAX(1,MIN(5,ROUND(6-AVERAGE($F19,$C19),0))),IF(ISNUMBER($F19),MAX(1,MIN(5,ROUND(6-$F19,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="37" t="str">
+        <f aca="false">IF(Suppliers!A18="","",Suppliers!A18)</f>
+        <v/>
+      </c>
+      <c r="B20" s="38" t="str">
+        <f aca="false">IF($A20="","",COUNTIF('Score Log'!$C$4:$C$203,$A20))</f>
+        <v/>
+      </c>
+      <c r="C20" s="39" t="str">
+        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A20),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D20" s="39" t="str">
+        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A20),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E20" s="39" t="str">
+        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A20),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F20" s="39" t="str">
+        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A20),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G20" s="39" t="str">
+        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A20),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H20" s="40" t="str">
+        <f aca="false">IF($A20="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A20,'Score Log'!$U$4:$U$203,"Yes")/$B20,"-"))</f>
+        <v/>
+      </c>
+      <c r="I20" s="41" t="str">
+        <f aca="false">IF($A20="","",IF(ISNUMBER($D20),MAX(1,MIN(5,ROUND(6-$D20,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J20" s="41" t="str">
+        <f aca="false">IF($A20="","",IF(ISNUMBER($E20),MAX(1,MIN(5,ROUND(6-$E20,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K20" s="41" t="str">
+        <f aca="false">IF($A20="","",IF(AND(ISNUMBER($F20),ISNUMBER($C20)),MAX(1,MIN(5,ROUND(6-AVERAGE($F20,$C20),0))),IF(ISNUMBER($F20),MAX(1,MIN(5,ROUND(6-$F20,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="37" t="str">
+        <f aca="false">IF(Suppliers!A19="","",Suppliers!A19)</f>
+        <v/>
+      </c>
+      <c r="B21" s="38" t="str">
+        <f aca="false">IF($A21="","",COUNTIF('Score Log'!$C$4:$C$203,$A21))</f>
+        <v/>
+      </c>
+      <c r="C21" s="39" t="str">
+        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A21),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D21" s="39" t="str">
+        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A21),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E21" s="39" t="str">
+        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A21),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F21" s="39" t="str">
+        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A21),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G21" s="39" t="str">
+        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A21),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H21" s="40" t="str">
+        <f aca="false">IF($A21="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A21,'Score Log'!$U$4:$U$203,"Yes")/$B21,"-"))</f>
+        <v/>
+      </c>
+      <c r="I21" s="41" t="str">
+        <f aca="false">IF($A21="","",IF(ISNUMBER($D21),MAX(1,MIN(5,ROUND(6-$D21,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J21" s="41" t="str">
+        <f aca="false">IF($A21="","",IF(ISNUMBER($E21),MAX(1,MIN(5,ROUND(6-$E21,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K21" s="41" t="str">
+        <f aca="false">IF($A21="","",IF(AND(ISNUMBER($F21),ISNUMBER($C21)),MAX(1,MIN(5,ROUND(6-AVERAGE($F21,$C21),0))),IF(ISNUMBER($F21),MAX(1,MIN(5,ROUND(6-$F21,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="37" t="str">
+        <f aca="false">IF(Suppliers!A20="","",Suppliers!A20)</f>
+        <v/>
+      </c>
+      <c r="B22" s="38" t="str">
+        <f aca="false">IF($A22="","",COUNTIF('Score Log'!$C$4:$C$203,$A22))</f>
+        <v/>
+      </c>
+      <c r="C22" s="39" t="str">
+        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A22),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D22" s="39" t="str">
+        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A22),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E22" s="39" t="str">
+        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A22),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F22" s="39" t="str">
+        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A22),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G22" s="39" t="str">
+        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A22),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H22" s="40" t="str">
+        <f aca="false">IF($A22="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A22,'Score Log'!$U$4:$U$203,"Yes")/$B22,"-"))</f>
+        <v/>
+      </c>
+      <c r="I22" s="41" t="str">
+        <f aca="false">IF($A22="","",IF(ISNUMBER($D22),MAX(1,MIN(5,ROUND(6-$D22,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J22" s="41" t="str">
+        <f aca="false">IF($A22="","",IF(ISNUMBER($E22),MAX(1,MIN(5,ROUND(6-$E22,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K22" s="41" t="str">
+        <f aca="false">IF($A22="","",IF(AND(ISNUMBER($F22),ISNUMBER($C22)),MAX(1,MIN(5,ROUND(6-AVERAGE($F22,$C22),0))),IF(ISNUMBER($F22),MAX(1,MIN(5,ROUND(6-$F22,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="37" t="str">
+        <f aca="false">IF(Suppliers!A21="","",Suppliers!A21)</f>
+        <v/>
+      </c>
+      <c r="B23" s="38" t="str">
+        <f aca="false">IF($A23="","",COUNTIF('Score Log'!$C$4:$C$203,$A23))</f>
+        <v/>
+      </c>
+      <c r="C23" s="39" t="str">
+        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A23),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D23" s="39" t="str">
+        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A23),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E23" s="39" t="str">
+        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A23),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F23" s="39" t="str">
+        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A23),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G23" s="39" t="str">
+        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A23),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H23" s="40" t="str">
+        <f aca="false">IF($A23="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A23,'Score Log'!$U$4:$U$203,"Yes")/$B23,"-"))</f>
+        <v/>
+      </c>
+      <c r="I23" s="41" t="str">
+        <f aca="false">IF($A23="","",IF(ISNUMBER($D23),MAX(1,MIN(5,ROUND(6-$D23,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J23" s="41" t="str">
+        <f aca="false">IF($A23="","",IF(ISNUMBER($E23),MAX(1,MIN(5,ROUND(6-$E23,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K23" s="41" t="str">
+        <f aca="false">IF($A23="","",IF(AND(ISNUMBER($F23),ISNUMBER($C23)),MAX(1,MIN(5,ROUND(6-AVERAGE($F23,$C23),0))),IF(ISNUMBER($F23),MAX(1,MIN(5,ROUND(6-$F23,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="37" t="str">
+        <f aca="false">IF(Suppliers!A22="","",Suppliers!A22)</f>
+        <v/>
+      </c>
+      <c r="B24" s="38" t="str">
+        <f aca="false">IF($A24="","",COUNTIF('Score Log'!$C$4:$C$203,$A24))</f>
+        <v/>
+      </c>
+      <c r="C24" s="39" t="str">
+        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A24),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D24" s="39" t="str">
+        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A24),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E24" s="39" t="str">
+        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A24),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F24" s="39" t="str">
+        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A24),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G24" s="39" t="str">
+        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A24),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H24" s="40" t="str">
+        <f aca="false">IF($A24="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A24,'Score Log'!$U$4:$U$203,"Yes")/$B24,"-"))</f>
+        <v/>
+      </c>
+      <c r="I24" s="41" t="str">
+        <f aca="false">IF($A24="","",IF(ISNUMBER($D24),MAX(1,MIN(5,ROUND(6-$D24,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J24" s="41" t="str">
+        <f aca="false">IF($A24="","",IF(ISNUMBER($E24),MAX(1,MIN(5,ROUND(6-$E24,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K24" s="41" t="str">
+        <f aca="false">IF($A24="","",IF(AND(ISNUMBER($F24),ISNUMBER($C24)),MAX(1,MIN(5,ROUND(6-AVERAGE($F24,$C24),0))),IF(ISNUMBER($F24),MAX(1,MIN(5,ROUND(6-$F24,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="37" t="str">
+        <f aca="false">IF(Suppliers!A23="","",Suppliers!A23)</f>
+        <v/>
+      </c>
+      <c r="B25" s="38" t="str">
+        <f aca="false">IF($A25="","",COUNTIF('Score Log'!$C$4:$C$203,$A25))</f>
+        <v/>
+      </c>
+      <c r="C25" s="39" t="str">
+        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A25),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D25" s="39" t="str">
+        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A25),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E25" s="39" t="str">
+        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A25),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F25" s="39" t="str">
+        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A25),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G25" s="39" t="str">
+        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A25),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H25" s="40" t="str">
+        <f aca="false">IF($A25="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A25,'Score Log'!$U$4:$U$203,"Yes")/$B25,"-"))</f>
+        <v/>
+      </c>
+      <c r="I25" s="41" t="str">
+        <f aca="false">IF($A25="","",IF(ISNUMBER($D25),MAX(1,MIN(5,ROUND(6-$D25,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J25" s="41" t="str">
+        <f aca="false">IF($A25="","",IF(ISNUMBER($E25),MAX(1,MIN(5,ROUND(6-$E25,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K25" s="41" t="str">
+        <f aca="false">IF($A25="","",IF(AND(ISNUMBER($F25),ISNUMBER($C25)),MAX(1,MIN(5,ROUND(6-AVERAGE($F25,$C25),0))),IF(ISNUMBER($F25),MAX(1,MIN(5,ROUND(6-$F25,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="37" t="str">
+        <f aca="false">IF(Suppliers!A24="","",Suppliers!A24)</f>
+        <v/>
+      </c>
+      <c r="B26" s="38" t="str">
+        <f aca="false">IF($A26="","",COUNTIF('Score Log'!$C$4:$C$203,$A26))</f>
+        <v/>
+      </c>
+      <c r="C26" s="39" t="str">
+        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A26),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D26" s="39" t="str">
+        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A26),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E26" s="39" t="str">
+        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A26),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F26" s="39" t="str">
+        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A26),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G26" s="39" t="str">
+        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A26),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H26" s="40" t="str">
+        <f aca="false">IF($A26="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A26,'Score Log'!$U$4:$U$203,"Yes")/$B26,"-"))</f>
+        <v/>
+      </c>
+      <c r="I26" s="41" t="str">
+        <f aca="false">IF($A26="","",IF(ISNUMBER($D26),MAX(1,MIN(5,ROUND(6-$D26,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J26" s="41" t="str">
+        <f aca="false">IF($A26="","",IF(ISNUMBER($E26),MAX(1,MIN(5,ROUND(6-$E26,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K26" s="41" t="str">
+        <f aca="false">IF($A26="","",IF(AND(ISNUMBER($F26),ISNUMBER($C26)),MAX(1,MIN(5,ROUND(6-AVERAGE($F26,$C26),0))),IF(ISNUMBER($F26),MAX(1,MIN(5,ROUND(6-$F26,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="37" t="str">
+        <f aca="false">IF(Suppliers!A25="","",Suppliers!A25)</f>
+        <v/>
+      </c>
+      <c r="B27" s="38" t="str">
+        <f aca="false">IF($A27="","",COUNTIF('Score Log'!$C$4:$C$203,$A27))</f>
+        <v/>
+      </c>
+      <c r="C27" s="39" t="str">
+        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A27),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D27" s="39" t="str">
+        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A27),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E27" s="39" t="str">
+        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A27),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F27" s="39" t="str">
+        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A27),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G27" s="39" t="str">
+        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A27),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H27" s="40" t="str">
+        <f aca="false">IF($A27="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A27,'Score Log'!$U$4:$U$203,"Yes")/$B27,"-"))</f>
+        <v/>
+      </c>
+      <c r="I27" s="41" t="str">
+        <f aca="false">IF($A27="","",IF(ISNUMBER($D27),MAX(1,MIN(5,ROUND(6-$D27,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J27" s="41" t="str">
+        <f aca="false">IF($A27="","",IF(ISNUMBER($E27),MAX(1,MIN(5,ROUND(6-$E27,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K27" s="41" t="str">
+        <f aca="false">IF($A27="","",IF(AND(ISNUMBER($F27),ISNUMBER($C27)),MAX(1,MIN(5,ROUND(6-AVERAGE($F27,$C27),0))),IF(ISNUMBER($F27),MAX(1,MIN(5,ROUND(6-$F27,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="37" t="str">
+        <f aca="false">IF(Suppliers!A26="","",Suppliers!A26)</f>
+        <v/>
+      </c>
+      <c r="B28" s="38" t="str">
+        <f aca="false">IF($A28="","",COUNTIF('Score Log'!$C$4:$C$203,$A28))</f>
+        <v/>
+      </c>
+      <c r="C28" s="39" t="str">
+        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A28),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D28" s="39" t="str">
+        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A28),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E28" s="39" t="str">
+        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A28),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F28" s="39" t="str">
+        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A28),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G28" s="39" t="str">
+        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A28),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H28" s="40" t="str">
+        <f aca="false">IF($A28="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A28,'Score Log'!$U$4:$U$203,"Yes")/$B28,"-"))</f>
+        <v/>
+      </c>
+      <c r="I28" s="41" t="str">
+        <f aca="false">IF($A28="","",IF(ISNUMBER($D28),MAX(1,MIN(5,ROUND(6-$D28,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J28" s="41" t="str">
+        <f aca="false">IF($A28="","",IF(ISNUMBER($E28),MAX(1,MIN(5,ROUND(6-$E28,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K28" s="41" t="str">
+        <f aca="false">IF($A28="","",IF(AND(ISNUMBER($F28),ISNUMBER($C28)),MAX(1,MIN(5,ROUND(6-AVERAGE($F28,$C28),0))),IF(ISNUMBER($F28),MAX(1,MIN(5,ROUND(6-$F28,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="37" t="str">
+        <f aca="false">IF(Suppliers!A27="","",Suppliers!A27)</f>
+        <v/>
+      </c>
+      <c r="B29" s="38" t="str">
+        <f aca="false">IF($A29="","",COUNTIF('Score Log'!$C$4:$C$203,$A29))</f>
+        <v/>
+      </c>
+      <c r="C29" s="39" t="str">
+        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A29),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D29" s="39" t="str">
+        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A29),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E29" s="39" t="str">
+        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A29),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F29" s="39" t="str">
+        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A29),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G29" s="39" t="str">
+        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A29),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H29" s="40" t="str">
+        <f aca="false">IF($A29="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A29,'Score Log'!$U$4:$U$203,"Yes")/$B29,"-"))</f>
+        <v/>
+      </c>
+      <c r="I29" s="41" t="str">
+        <f aca="false">IF($A29="","",IF(ISNUMBER($D29),MAX(1,MIN(5,ROUND(6-$D29,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J29" s="41" t="str">
+        <f aca="false">IF($A29="","",IF(ISNUMBER($E29),MAX(1,MIN(5,ROUND(6-$E29,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K29" s="41" t="str">
+        <f aca="false">IF($A29="","",IF(AND(ISNUMBER($F29),ISNUMBER($C29)),MAX(1,MIN(5,ROUND(6-AVERAGE($F29,$C29),0))),IF(ISNUMBER($F29),MAX(1,MIN(5,ROUND(6-$F29,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="37" t="str">
+        <f aca="false">IF(Suppliers!A28="","",Suppliers!A28)</f>
+        <v/>
+      </c>
+      <c r="B30" s="38" t="str">
+        <f aca="false">IF($A30="","",COUNTIF('Score Log'!$C$4:$C$203,$A30))</f>
+        <v/>
+      </c>
+      <c r="C30" s="39" t="str">
+        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A30),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D30" s="39" t="str">
+        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A30),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E30" s="39" t="str">
+        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A30),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F30" s="39" t="str">
+        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A30),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G30" s="39" t="str">
+        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A30),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H30" s="40" t="str">
+        <f aca="false">IF($A30="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A30,'Score Log'!$U$4:$U$203,"Yes")/$B30,"-"))</f>
+        <v/>
+      </c>
+      <c r="I30" s="41" t="str">
+        <f aca="false">IF($A30="","",IF(ISNUMBER($D30),MAX(1,MIN(5,ROUND(6-$D30,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J30" s="41" t="str">
+        <f aca="false">IF($A30="","",IF(ISNUMBER($E30),MAX(1,MIN(5,ROUND(6-$E30,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K30" s="41" t="str">
+        <f aca="false">IF($A30="","",IF(AND(ISNUMBER($F30),ISNUMBER($C30)),MAX(1,MIN(5,ROUND(6-AVERAGE($F30,$C30),0))),IF(ISNUMBER($F30),MAX(1,MIN(5,ROUND(6-$F30,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="37" t="str">
+        <f aca="false">IF(Suppliers!A29="","",Suppliers!A29)</f>
+        <v/>
+      </c>
+      <c r="B31" s="38" t="str">
+        <f aca="false">IF($A31="","",COUNTIF('Score Log'!$C$4:$C$203,$A31))</f>
+        <v/>
+      </c>
+      <c r="C31" s="39" t="str">
+        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A31),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D31" s="39" t="str">
+        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A31),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E31" s="39" t="str">
+        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A31),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F31" s="39" t="str">
+        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A31),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G31" s="39" t="str">
+        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A31),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H31" s="40" t="str">
+        <f aca="false">IF($A31="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A31,'Score Log'!$U$4:$U$203,"Yes")/$B31,"-"))</f>
+        <v/>
+      </c>
+      <c r="I31" s="41" t="str">
+        <f aca="false">IF($A31="","",IF(ISNUMBER($D31),MAX(1,MIN(5,ROUND(6-$D31,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J31" s="41" t="str">
+        <f aca="false">IF($A31="","",IF(ISNUMBER($E31),MAX(1,MIN(5,ROUND(6-$E31,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K31" s="41" t="str">
+        <f aca="false">IF($A31="","",IF(AND(ISNUMBER($F31),ISNUMBER($C31)),MAX(1,MIN(5,ROUND(6-AVERAGE($F31,$C31),0))),IF(ISNUMBER($F31),MAX(1,MIN(5,ROUND(6-$F31,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="37" t="str">
+        <f aca="false">IF(Suppliers!A30="","",Suppliers!A30)</f>
+        <v/>
+      </c>
+      <c r="B32" s="38" t="str">
+        <f aca="false">IF($A32="","",COUNTIF('Score Log'!$C$4:$C$203,$A32))</f>
+        <v/>
+      </c>
+      <c r="C32" s="39" t="str">
+        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A32),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D32" s="39" t="str">
+        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A32),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E32" s="39" t="str">
+        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A32),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F32" s="39" t="str">
+        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A32),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G32" s="39" t="str">
+        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A32),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H32" s="40" t="str">
+        <f aca="false">IF($A32="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A32,'Score Log'!$U$4:$U$203,"Yes")/$B32,"-"))</f>
+        <v/>
+      </c>
+      <c r="I32" s="41" t="str">
+        <f aca="false">IF($A32="","",IF(ISNUMBER($D32),MAX(1,MIN(5,ROUND(6-$D32,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J32" s="41" t="str">
+        <f aca="false">IF($A32="","",IF(ISNUMBER($E32),MAX(1,MIN(5,ROUND(6-$E32,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K32" s="41" t="str">
+        <f aca="false">IF($A32="","",IF(AND(ISNUMBER($F32),ISNUMBER($C32)),MAX(1,MIN(5,ROUND(6-AVERAGE($F32,$C32),0))),IF(ISNUMBER($F32),MAX(1,MIN(5,ROUND(6-$F32,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="37" t="str">
+        <f aca="false">IF(Suppliers!A31="","",Suppliers!A31)</f>
+        <v/>
+      </c>
+      <c r="B33" s="38" t="str">
+        <f aca="false">IF($A33="","",COUNTIF('Score Log'!$C$4:$C$203,$A33))</f>
+        <v/>
+      </c>
+      <c r="C33" s="39" t="str">
+        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A33),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D33" s="39" t="str">
+        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A33),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E33" s="39" t="str">
+        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A33),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F33" s="39" t="str">
+        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A33),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G33" s="39" t="str">
+        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A33),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H33" s="40" t="str">
+        <f aca="false">IF($A33="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A33,'Score Log'!$U$4:$U$203,"Yes")/$B33,"-"))</f>
+        <v/>
+      </c>
+      <c r="I33" s="41" t="str">
+        <f aca="false">IF($A33="","",IF(ISNUMBER($D33),MAX(1,MIN(5,ROUND(6-$D33,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J33" s="41" t="str">
+        <f aca="false">IF($A33="","",IF(ISNUMBER($E33),MAX(1,MIN(5,ROUND(6-$E33,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K33" s="41" t="str">
+        <f aca="false">IF($A33="","",IF(AND(ISNUMBER($F33),ISNUMBER($C33)),MAX(1,MIN(5,ROUND(6-AVERAGE($F33,$C33),0))),IF(ISNUMBER($F33),MAX(1,MIN(5,ROUND(6-$F33,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="37" t="str">
+        <f aca="false">IF(Suppliers!A32="","",Suppliers!A32)</f>
+        <v/>
+      </c>
+      <c r="B34" s="38" t="str">
+        <f aca="false">IF($A34="","",COUNTIF('Score Log'!$C$4:$C$203,$A34))</f>
+        <v/>
+      </c>
+      <c r="C34" s="39" t="str">
+        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A34),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="D34" s="39" t="str">
+        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A34),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="E34" s="39" t="str">
+        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A34),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F34" s="39" t="str">
+        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A34),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G34" s="39" t="str">
+        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A34),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H34" s="40" t="str">
+        <f aca="false">IF($A34="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A34,'Score Log'!$U$4:$U$203,"Yes")/$B34,"-"))</f>
+        <v/>
+      </c>
+      <c r="I34" s="41" t="str">
+        <f aca="false">IF($A34="","",IF(ISNUMBER($D34),MAX(1,MIN(5,ROUND(6-$D34,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="J34" s="41" t="str">
+        <f aca="false">IF($A34="","",IF(ISNUMBER($E34),MAX(1,MIN(5,ROUND(6-$E34,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="K34" s="41" t="str">
+        <f aca="false">IF($A34="","",IF(AND(ISNUMBER($F34),ISNUMBER($C34)),MAX(1,MIN(5,ROUND(6-AVERAGE($F34,$C34),0))),IF(ISNUMBER($F34),MAX(1,MIN(5,ROUND(6-$F34,0))),"-")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="34"/>
-      <c r="R3" s="34"/>
-      <c r="S3" s="34" t="s">
+    </row>
+    <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="T3" s="34"/>
-      <c r="U3" s="34" t="s">
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+    </row>
+    <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="V3" s="34"/>
-      <c r="W3" s="34"/>
-      <c r="Y3" s="36" t="s">
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+    </row>
+    <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="43" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="37" t="s">
+      <c r="B40" s="43"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+    </row>
+    <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B41" s="43"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+    </row>
+    <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E4" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="G4" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="H4" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="I4" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="J4" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="K4" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="L4" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="M4" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="N4" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="O4" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="P4" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q4" s="37" t="s">
-        <v>101</v>
-      </c>
-      <c r="R4" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="S4" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="T4" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="U4" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="V4" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="W4" s="37" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="38"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="42" t="str">
-        <f aca="false">IF(COUNT($H5:$L5)&lt;5,"",ROUND($H5*$Z$5+$I5*$Z$6+$J5*$Z$7+$K5*$Z$8+$L5*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P5" s="43" t="str">
-        <f aca="false">IF(OR($O5="",$M5=""),"",ROUND($O5*$M5,1))</f>
-        <v/>
-      </c>
-      <c r="Q5" s="44" t="str">
-        <f aca="false">IF($E5="","",IF(OR($O5="",$M5=""),"NOT SCORED",IF($P5&gt;=$Z$11,"CRITICAL",IF($P5&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R5" s="45" t="str">
-        <f aca="false">IF($O5="","",INDEX($Y$15:$Y$19,MATCH(MAX($H5:$L5),$H5:$L5,0)))</f>
-        <v/>
-      </c>
-      <c r="S5" s="40"/>
-      <c r="T5" s="46"/>
-      <c r="U5" s="47" t="str">
-        <f aca="false">IF($E5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E5),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V5" s="42" t="str">
-        <f aca="false">IF($E5="","",IF(ISNUMBER($U5),ROUND(6-$U5,1),""))</f>
-        <v/>
-      </c>
-      <c r="W5" s="48" t="str">
-        <f aca="false">IF($E5="","",COUNTIF('Score Log'!$C$4:$C$203,$E5))</f>
-        <v/>
-      </c>
-      <c r="Y5" s="49" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z5" s="50" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="38"/>
-      <c r="B6" s="39"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="42" t="str">
-        <f aca="false">IF(COUNT($H6:$L6)&lt;5,"",ROUND($H6*$Z$5+$I6*$Z$6+$J6*$Z$7+$K6*$Z$8+$L6*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P6" s="43" t="str">
-        <f aca="false">IF(OR($O6="",$M6=""),"",ROUND($O6*$M6,1))</f>
-        <v/>
-      </c>
-      <c r="Q6" s="44" t="str">
-        <f aca="false">IF($E6="","",IF(OR($O6="",$M6=""),"NOT SCORED",IF($P6&gt;=$Z$11,"CRITICAL",IF($P6&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R6" s="45" t="str">
-        <f aca="false">IF($O6="","",INDEX($Y$15:$Y$19,MATCH(MAX($H6:$L6),$H6:$L6,0)))</f>
-        <v/>
-      </c>
-      <c r="S6" s="40"/>
-      <c r="T6" s="46"/>
-      <c r="U6" s="47" t="str">
-        <f aca="false">IF($E6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E6),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V6" s="42" t="str">
-        <f aca="false">IF($E6="","",IF(ISNUMBER($U6),ROUND(6-$U6,1),""))</f>
-        <v/>
-      </c>
-      <c r="W6" s="48" t="str">
-        <f aca="false">IF($E6="","",COUNTIF('Score Log'!$C$4:$C$203,$E6))</f>
-        <v/>
-      </c>
-      <c r="Y6" s="49" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z6" s="50" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="42" t="str">
-        <f aca="false">IF(COUNT($H7:$L7)&lt;5,"",ROUND($H7*$Z$5+$I7*$Z$6+$J7*$Z$7+$K7*$Z$8+$L7*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P7" s="43" t="str">
-        <f aca="false">IF(OR($O7="",$M7=""),"",ROUND($O7*$M7,1))</f>
-        <v/>
-      </c>
-      <c r="Q7" s="44" t="str">
-        <f aca="false">IF($E7="","",IF(OR($O7="",$M7=""),"NOT SCORED",IF($P7&gt;=$Z$11,"CRITICAL",IF($P7&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R7" s="45" t="str">
-        <f aca="false">IF($O7="","",INDEX($Y$15:$Y$19,MATCH(MAX($H7:$L7),$H7:$L7,0)))</f>
-        <v/>
-      </c>
-      <c r="S7" s="40"/>
-      <c r="T7" s="46"/>
-      <c r="U7" s="47" t="str">
-        <f aca="false">IF($E7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E7),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V7" s="42" t="str">
-        <f aca="false">IF($E7="","",IF(ISNUMBER($U7),ROUND(6-$U7,1),""))</f>
-        <v/>
-      </c>
-      <c r="W7" s="48" t="str">
-        <f aca="false">IF($E7="","",COUNTIF('Score Log'!$C$4:$C$203,$E7))</f>
-        <v/>
-      </c>
-      <c r="Y7" s="49" t="s">
-        <v>110</v>
-      </c>
-      <c r="Z7" s="50" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="38"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="42" t="str">
-        <f aca="false">IF(COUNT($H8:$L8)&lt;5,"",ROUND($H8*$Z$5+$I8*$Z$6+$J8*$Z$7+$K8*$Z$8+$L8*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P8" s="43" t="str">
-        <f aca="false">IF(OR($O8="",$M8=""),"",ROUND($O8*$M8,1))</f>
-        <v/>
-      </c>
-      <c r="Q8" s="44" t="str">
-        <f aca="false">IF($E8="","",IF(OR($O8="",$M8=""),"NOT SCORED",IF($P8&gt;=$Z$11,"CRITICAL",IF($P8&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R8" s="45" t="str">
-        <f aca="false">IF($O8="","",INDEX($Y$15:$Y$19,MATCH(MAX($H8:$L8),$H8:$L8,0)))</f>
-        <v/>
-      </c>
-      <c r="S8" s="40"/>
-      <c r="T8" s="46"/>
-      <c r="U8" s="47" t="str">
-        <f aca="false">IF($E8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E8),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V8" s="42" t="str">
-        <f aca="false">IF($E8="","",IF(ISNUMBER($U8),ROUND(6-$U8,1),""))</f>
-        <v/>
-      </c>
-      <c r="W8" s="48" t="str">
-        <f aca="false">IF($E8="","",COUNTIF('Score Log'!$C$4:$C$203,$E8))</f>
-        <v/>
-      </c>
-      <c r="Y8" s="49" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z8" s="50" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="38"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="39"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="42" t="str">
-        <f aca="false">IF(COUNT($H9:$L9)&lt;5,"",ROUND($H9*$Z$5+$I9*$Z$6+$J9*$Z$7+$K9*$Z$8+$L9*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P9" s="43" t="str">
-        <f aca="false">IF(OR($O9="",$M9=""),"",ROUND($O9*$M9,1))</f>
-        <v/>
-      </c>
-      <c r="Q9" s="44" t="str">
-        <f aca="false">IF($E9="","",IF(OR($O9="",$M9=""),"NOT SCORED",IF($P9&gt;=$Z$11,"CRITICAL",IF($P9&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R9" s="45" t="str">
-        <f aca="false">IF($O9="","",INDEX($Y$15:$Y$19,MATCH(MAX($H9:$L9),$H9:$L9,0)))</f>
-        <v/>
-      </c>
-      <c r="S9" s="40"/>
-      <c r="T9" s="46"/>
-      <c r="U9" s="47" t="str">
-        <f aca="false">IF($E9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E9),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V9" s="42" t="str">
-        <f aca="false">IF($E9="","",IF(ISNUMBER($U9),ROUND(6-$U9,1),""))</f>
-        <v/>
-      </c>
-      <c r="W9" s="48" t="str">
-        <f aca="false">IF($E9="","",COUNTIF('Score Log'!$C$4:$C$203,$E9))</f>
-        <v/>
-      </c>
-      <c r="Y9" s="49" t="s">
-        <v>112</v>
-      </c>
-      <c r="Z9" s="50" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="38"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39"/>
-      <c r="N10" s="38"/>
-      <c r="O10" s="42" t="str">
-        <f aca="false">IF(COUNT($H10:$L10)&lt;5,"",ROUND($H10*$Z$5+$I10*$Z$6+$J10*$Z$7+$K10*$Z$8+$L10*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P10" s="43" t="str">
-        <f aca="false">IF(OR($O10="",$M10=""),"",ROUND($O10*$M10,1))</f>
-        <v/>
-      </c>
-      <c r="Q10" s="44" t="str">
-        <f aca="false">IF($E10="","",IF(OR($O10="",$M10=""),"NOT SCORED",IF($P10&gt;=$Z$11,"CRITICAL",IF($P10&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R10" s="45" t="str">
-        <f aca="false">IF($O10="","",INDEX($Y$15:$Y$19,MATCH(MAX($H10:$L10),$H10:$L10,0)))</f>
-        <v/>
-      </c>
-      <c r="S10" s="40"/>
-      <c r="T10" s="46"/>
-      <c r="U10" s="47" t="str">
-        <f aca="false">IF($E10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E10),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V10" s="42" t="str">
-        <f aca="false">IF($E10="","",IF(ISNUMBER($U10),ROUND(6-$U10,1),""))</f>
-        <v/>
-      </c>
-      <c r="W10" s="48" t="str">
-        <f aca="false">IF($E10="","",COUNTIF('Score Log'!$C$4:$C$203,$E10))</f>
-        <v/>
-      </c>
-      <c r="Y10" s="49" t="s">
-        <v>113</v>
-      </c>
-      <c r="Z10" s="51" t="n">
-        <f aca="false">SUM(Z5:Z9)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="38"/>
-      <c r="B11" s="39"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="42" t="str">
-        <f aca="false">IF(COUNT($H11:$L11)&lt;5,"",ROUND($H11*$Z$5+$I11*$Z$6+$J11*$Z$7+$K11*$Z$8+$L11*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P11" s="43" t="str">
-        <f aca="false">IF(OR($O11="",$M11=""),"",ROUND($O11*$M11,1))</f>
-        <v/>
-      </c>
-      <c r="Q11" s="44" t="str">
-        <f aca="false">IF($E11="","",IF(OR($O11="",$M11=""),"NOT SCORED",IF($P11&gt;=$Z$11,"CRITICAL",IF($P11&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R11" s="45" t="str">
-        <f aca="false">IF($O11="","",INDEX($Y$15:$Y$19,MATCH(MAX($H11:$L11),$H11:$L11,0)))</f>
-        <v/>
-      </c>
-      <c r="S11" s="40"/>
-      <c r="T11" s="46"/>
-      <c r="U11" s="47" t="str">
-        <f aca="false">IF($E11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E11),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V11" s="42" t="str">
-        <f aca="false">IF($E11="","",IF(ISNUMBER($U11),ROUND(6-$U11,1),""))</f>
-        <v/>
-      </c>
-      <c r="W11" s="48" t="str">
-        <f aca="false">IF($E11="","",COUNTIF('Score Log'!$C$4:$C$203,$E11))</f>
-        <v/>
-      </c>
-      <c r="Y11" s="49" t="s">
-        <v>114</v>
-      </c>
-      <c r="Z11" s="52" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="38"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="42" t="str">
-        <f aca="false">IF(COUNT($H12:$L12)&lt;5,"",ROUND($H12*$Z$5+$I12*$Z$6+$J12*$Z$7+$K12*$Z$8+$L12*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P12" s="43" t="str">
-        <f aca="false">IF(OR($O12="",$M12=""),"",ROUND($O12*$M12,1))</f>
-        <v/>
-      </c>
-      <c r="Q12" s="44" t="str">
-        <f aca="false">IF($E12="","",IF(OR($O12="",$M12=""),"NOT SCORED",IF($P12&gt;=$Z$11,"CRITICAL",IF($P12&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R12" s="45" t="str">
-        <f aca="false">IF($O12="","",INDEX($Y$15:$Y$19,MATCH(MAX($H12:$L12),$H12:$L12,0)))</f>
-        <v/>
-      </c>
-      <c r="S12" s="40"/>
-      <c r="T12" s="46"/>
-      <c r="U12" s="47" t="str">
-        <f aca="false">IF($E12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E12),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V12" s="42" t="str">
-        <f aca="false">IF($E12="","",IF(ISNUMBER($U12),ROUND(6-$U12,1),""))</f>
-        <v/>
-      </c>
-      <c r="W12" s="48" t="str">
-        <f aca="false">IF($E12="","",COUNTIF('Score Log'!$C$4:$C$203,$E12))</f>
-        <v/>
-      </c>
-      <c r="Y12" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z12" s="52" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="38"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="42" t="str">
-        <f aca="false">IF(COUNT($H13:$L13)&lt;5,"",ROUND($H13*$Z$5+$I13*$Z$6+$J13*$Z$7+$K13*$Z$8+$L13*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P13" s="43" t="str">
-        <f aca="false">IF(OR($O13="",$M13=""),"",ROUND($O13*$M13,1))</f>
-        <v/>
-      </c>
-      <c r="Q13" s="44" t="str">
-        <f aca="false">IF($E13="","",IF(OR($O13="",$M13=""),"NOT SCORED",IF($P13&gt;=$Z$11,"CRITICAL",IF($P13&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R13" s="45" t="str">
-        <f aca="false">IF($O13="","",INDEX($Y$15:$Y$19,MATCH(MAX($H13:$L13),$H13:$L13,0)))</f>
-        <v/>
-      </c>
-      <c r="S13" s="40"/>
-      <c r="T13" s="46"/>
-      <c r="U13" s="47" t="str">
-        <f aca="false">IF($E13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E13),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V13" s="42" t="str">
-        <f aca="false">IF($E13="","",IF(ISNUMBER($U13),ROUND(6-$U13,1),""))</f>
-        <v/>
-      </c>
-      <c r="W13" s="48" t="str">
-        <f aca="false">IF($E13="","",COUNTIF('Score Log'!$C$4:$C$203,$E13))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="38"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="42" t="str">
-        <f aca="false">IF(COUNT($H14:$L14)&lt;5,"",ROUND($H14*$Z$5+$I14*$Z$6+$J14*$Z$7+$K14*$Z$8+$L14*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P14" s="43" t="str">
-        <f aca="false">IF(OR($O14="",$M14=""),"",ROUND($O14*$M14,1))</f>
-        <v/>
-      </c>
-      <c r="Q14" s="44" t="str">
-        <f aca="false">IF($E14="","",IF(OR($O14="",$M14=""),"NOT SCORED",IF($P14&gt;=$Z$11,"CRITICAL",IF($P14&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R14" s="45" t="str">
-        <f aca="false">IF($O14="","",INDEX($Y$15:$Y$19,MATCH(MAX($H14:$L14),$H14:$L14,0)))</f>
-        <v/>
-      </c>
-      <c r="S14" s="40"/>
-      <c r="T14" s="46"/>
-      <c r="U14" s="47" t="str">
-        <f aca="false">IF($E14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E14),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V14" s="42" t="str">
-        <f aca="false">IF($E14="","",IF(ISNUMBER($U14),ROUND(6-$U14,1),""))</f>
-        <v/>
-      </c>
-      <c r="W14" s="48" t="str">
-        <f aca="false">IF($E14="","",COUNTIF('Score Log'!$C$4:$C$203,$E14))</f>
-        <v/>
-      </c>
-      <c r="Y14" s="49" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="38"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="39"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="42" t="str">
-        <f aca="false">IF(COUNT($H15:$L15)&lt;5,"",ROUND($H15*$Z$5+$I15*$Z$6+$J15*$Z$7+$K15*$Z$8+$L15*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P15" s="43" t="str">
-        <f aca="false">IF(OR($O15="",$M15=""),"",ROUND($O15*$M15,1))</f>
-        <v/>
-      </c>
-      <c r="Q15" s="44" t="str">
-        <f aca="false">IF($E15="","",IF(OR($O15="",$M15=""),"NOT SCORED",IF($P15&gt;=$Z$11,"CRITICAL",IF($P15&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R15" s="45" t="str">
-        <f aca="false">IF($O15="","",INDEX($Y$15:$Y$19,MATCH(MAX($H15:$L15),$H15:$L15,0)))</f>
-        <v/>
-      </c>
-      <c r="S15" s="40"/>
-      <c r="T15" s="46"/>
-      <c r="U15" s="47" t="str">
-        <f aca="false">IF($E15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E15),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V15" s="42" t="str">
-        <f aca="false">IF($E15="","",IF(ISNUMBER($U15),ROUND(6-$U15,1),""))</f>
-        <v/>
-      </c>
-      <c r="W15" s="48" t="str">
-        <f aca="false">IF($E15="","",COUNTIF('Score Log'!$C$4:$C$203,$E15))</f>
-        <v/>
-      </c>
-      <c r="Y15" s="53" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="38"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="42" t="str">
-        <f aca="false">IF(COUNT($H16:$L16)&lt;5,"",ROUND($H16*$Z$5+$I16*$Z$6+$J16*$Z$7+$K16*$Z$8+$L16*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P16" s="43" t="str">
-        <f aca="false">IF(OR($O16="",$M16=""),"",ROUND($O16*$M16,1))</f>
-        <v/>
-      </c>
-      <c r="Q16" s="44" t="str">
-        <f aca="false">IF($E16="","",IF(OR($O16="",$M16=""),"NOT SCORED",IF($P16&gt;=$Z$11,"CRITICAL",IF($P16&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R16" s="45" t="str">
-        <f aca="false">IF($O16="","",INDEX($Y$15:$Y$19,MATCH(MAX($H16:$L16),$H16:$L16,0)))</f>
-        <v/>
-      </c>
-      <c r="S16" s="40"/>
-      <c r="T16" s="46"/>
-      <c r="U16" s="47" t="str">
-        <f aca="false">IF($E16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E16),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V16" s="42" t="str">
-        <f aca="false">IF($E16="","",IF(ISNUMBER($U16),ROUND(6-$U16,1),""))</f>
-        <v/>
-      </c>
-      <c r="W16" s="48" t="str">
-        <f aca="false">IF($E16="","",COUNTIF('Score Log'!$C$4:$C$203,$E16))</f>
-        <v/>
-      </c>
-      <c r="Y16" s="53" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="38"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="39"/>
-      <c r="M17" s="39"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="42" t="str">
-        <f aca="false">IF(COUNT($H17:$L17)&lt;5,"",ROUND($H17*$Z$5+$I17*$Z$6+$J17*$Z$7+$K17*$Z$8+$L17*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P17" s="43" t="str">
-        <f aca="false">IF(OR($O17="",$M17=""),"",ROUND($O17*$M17,1))</f>
-        <v/>
-      </c>
-      <c r="Q17" s="44" t="str">
-        <f aca="false">IF($E17="","",IF(OR($O17="",$M17=""),"NOT SCORED",IF($P17&gt;=$Z$11,"CRITICAL",IF($P17&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R17" s="45" t="str">
-        <f aca="false">IF($O17="","",INDEX($Y$15:$Y$19,MATCH(MAX($H17:$L17),$H17:$L17,0)))</f>
-        <v/>
-      </c>
-      <c r="S17" s="40"/>
-      <c r="T17" s="46"/>
-      <c r="U17" s="47" t="str">
-        <f aca="false">IF($E17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E17),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V17" s="42" t="str">
-        <f aca="false">IF($E17="","",IF(ISNUMBER($U17),ROUND(6-$U17,1),""))</f>
-        <v/>
-      </c>
-      <c r="W17" s="48" t="str">
-        <f aca="false">IF($E17="","",COUNTIF('Score Log'!$C$4:$C$203,$E17))</f>
-        <v/>
-      </c>
-      <c r="Y17" s="53" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="38"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="39"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="42" t="str">
-        <f aca="false">IF(COUNT($H18:$L18)&lt;5,"",ROUND($H18*$Z$5+$I18*$Z$6+$J18*$Z$7+$K18*$Z$8+$L18*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P18" s="43" t="str">
-        <f aca="false">IF(OR($O18="",$M18=""),"",ROUND($O18*$M18,1))</f>
-        <v/>
-      </c>
-      <c r="Q18" s="44" t="str">
-        <f aca="false">IF($E18="","",IF(OR($O18="",$M18=""),"NOT SCORED",IF($P18&gt;=$Z$11,"CRITICAL",IF($P18&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R18" s="45" t="str">
-        <f aca="false">IF($O18="","",INDEX($Y$15:$Y$19,MATCH(MAX($H18:$L18),$H18:$L18,0)))</f>
-        <v/>
-      </c>
-      <c r="S18" s="40"/>
-      <c r="T18" s="46"/>
-      <c r="U18" s="47" t="str">
-        <f aca="false">IF($E18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E18),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V18" s="42" t="str">
-        <f aca="false">IF($E18="","",IF(ISNUMBER($U18),ROUND(6-$U18,1),""))</f>
-        <v/>
-      </c>
-      <c r="W18" s="48" t="str">
-        <f aca="false">IF($E18="","",COUNTIF('Score Log'!$C$4:$C$203,$E18))</f>
-        <v/>
-      </c>
-      <c r="Y18" s="53" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="38"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="39"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="42" t="str">
-        <f aca="false">IF(COUNT($H19:$L19)&lt;5,"",ROUND($H19*$Z$5+$I19*$Z$6+$J19*$Z$7+$K19*$Z$8+$L19*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P19" s="43" t="str">
-        <f aca="false">IF(OR($O19="",$M19=""),"",ROUND($O19*$M19,1))</f>
-        <v/>
-      </c>
-      <c r="Q19" s="44" t="str">
-        <f aca="false">IF($E19="","",IF(OR($O19="",$M19=""),"NOT SCORED",IF($P19&gt;=$Z$11,"CRITICAL",IF($P19&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R19" s="45" t="str">
-        <f aca="false">IF($O19="","",INDEX($Y$15:$Y$19,MATCH(MAX($H19:$L19),$H19:$L19,0)))</f>
-        <v/>
-      </c>
-      <c r="S19" s="40"/>
-      <c r="T19" s="46"/>
-      <c r="U19" s="47" t="str">
-        <f aca="false">IF($E19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E19),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V19" s="42" t="str">
-        <f aca="false">IF($E19="","",IF(ISNUMBER($U19),ROUND(6-$U19,1),""))</f>
-        <v/>
-      </c>
-      <c r="W19" s="48" t="str">
-        <f aca="false">IF($E19="","",COUNTIF('Score Log'!$C$4:$C$203,$E19))</f>
-        <v/>
-      </c>
-      <c r="Y19" s="53" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="38"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="39"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="42" t="str">
-        <f aca="false">IF(COUNT($H20:$L20)&lt;5,"",ROUND($H20*$Z$5+$I20*$Z$6+$J20*$Z$7+$K20*$Z$8+$L20*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P20" s="43" t="str">
-        <f aca="false">IF(OR($O20="",$M20=""),"",ROUND($O20*$M20,1))</f>
-        <v/>
-      </c>
-      <c r="Q20" s="44" t="str">
-        <f aca="false">IF($E20="","",IF(OR($O20="",$M20=""),"NOT SCORED",IF($P20&gt;=$Z$11,"CRITICAL",IF($P20&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R20" s="45" t="str">
-        <f aca="false">IF($O20="","",INDEX($Y$15:$Y$19,MATCH(MAX($H20:$L20),$H20:$L20,0)))</f>
-        <v/>
-      </c>
-      <c r="S20" s="40"/>
-      <c r="T20" s="46"/>
-      <c r="U20" s="47" t="str">
-        <f aca="false">IF($E20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E20),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V20" s="42" t="str">
-        <f aca="false">IF($E20="","",IF(ISNUMBER($U20),ROUND(6-$U20,1),""))</f>
-        <v/>
-      </c>
-      <c r="W20" s="48" t="str">
-        <f aca="false">IF($E20="","",COUNTIF('Score Log'!$C$4:$C$203,$E20))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="38"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="39"/>
-      <c r="L21" s="39"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="42" t="str">
-        <f aca="false">IF(COUNT($H21:$L21)&lt;5,"",ROUND($H21*$Z$5+$I21*$Z$6+$J21*$Z$7+$K21*$Z$8+$L21*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P21" s="43" t="str">
-        <f aca="false">IF(OR($O21="",$M21=""),"",ROUND($O21*$M21,1))</f>
-        <v/>
-      </c>
-      <c r="Q21" s="44" t="str">
-        <f aca="false">IF($E21="","",IF(OR($O21="",$M21=""),"NOT SCORED",IF($P21&gt;=$Z$11,"CRITICAL",IF($P21&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R21" s="45" t="str">
-        <f aca="false">IF($O21="","",INDEX($Y$15:$Y$19,MATCH(MAX($H21:$L21),$H21:$L21,0)))</f>
-        <v/>
-      </c>
-      <c r="S21" s="40"/>
-      <c r="T21" s="46"/>
-      <c r="U21" s="47" t="str">
-        <f aca="false">IF($E21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E21),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V21" s="42" t="str">
-        <f aca="false">IF($E21="","",IF(ISNUMBER($U21),ROUND(6-$U21,1),""))</f>
-        <v/>
-      </c>
-      <c r="W21" s="48" t="str">
-        <f aca="false">IF($E21="","",COUNTIF('Score Log'!$C$4:$C$203,$E21))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="38"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="42" t="str">
-        <f aca="false">IF(COUNT($H22:$L22)&lt;5,"",ROUND($H22*$Z$5+$I22*$Z$6+$J22*$Z$7+$K22*$Z$8+$L22*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P22" s="43" t="str">
-        <f aca="false">IF(OR($O22="",$M22=""),"",ROUND($O22*$M22,1))</f>
-        <v/>
-      </c>
-      <c r="Q22" s="44" t="str">
-        <f aca="false">IF($E22="","",IF(OR($O22="",$M22=""),"NOT SCORED",IF($P22&gt;=$Z$11,"CRITICAL",IF($P22&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R22" s="45" t="str">
-        <f aca="false">IF($O22="","",INDEX($Y$15:$Y$19,MATCH(MAX($H22:$L22),$H22:$L22,0)))</f>
-        <v/>
-      </c>
-      <c r="S22" s="40"/>
-      <c r="T22" s="46"/>
-      <c r="U22" s="47" t="str">
-        <f aca="false">IF($E22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E22),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V22" s="42" t="str">
-        <f aca="false">IF($E22="","",IF(ISNUMBER($U22),ROUND(6-$U22,1),""))</f>
-        <v/>
-      </c>
-      <c r="W22" s="48" t="str">
-        <f aca="false">IF($E22="","",COUNTIF('Score Log'!$C$4:$C$203,$E22))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="38"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="42" t="str">
-        <f aca="false">IF(COUNT($H23:$L23)&lt;5,"",ROUND($H23*$Z$5+$I23*$Z$6+$J23*$Z$7+$K23*$Z$8+$L23*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P23" s="43" t="str">
-        <f aca="false">IF(OR($O23="",$M23=""),"",ROUND($O23*$M23,1))</f>
-        <v/>
-      </c>
-      <c r="Q23" s="44" t="str">
-        <f aca="false">IF($E23="","",IF(OR($O23="",$M23=""),"NOT SCORED",IF($P23&gt;=$Z$11,"CRITICAL",IF($P23&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R23" s="45" t="str">
-        <f aca="false">IF($O23="","",INDEX($Y$15:$Y$19,MATCH(MAX($H23:$L23),$H23:$L23,0)))</f>
-        <v/>
-      </c>
-      <c r="S23" s="40"/>
-      <c r="T23" s="46"/>
-      <c r="U23" s="47" t="str">
-        <f aca="false">IF($E23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E23),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V23" s="42" t="str">
-        <f aca="false">IF($E23="","",IF(ISNUMBER($U23),ROUND(6-$U23,1),""))</f>
-        <v/>
-      </c>
-      <c r="W23" s="48" t="str">
-        <f aca="false">IF($E23="","",COUNTIF('Score Log'!$C$4:$C$203,$E23))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="38"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="42" t="str">
-        <f aca="false">IF(COUNT($H24:$L24)&lt;5,"",ROUND($H24*$Z$5+$I24*$Z$6+$J24*$Z$7+$K24*$Z$8+$L24*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P24" s="43" t="str">
-        <f aca="false">IF(OR($O24="",$M24=""),"",ROUND($O24*$M24,1))</f>
-        <v/>
-      </c>
-      <c r="Q24" s="44" t="str">
-        <f aca="false">IF($E24="","",IF(OR($O24="",$M24=""),"NOT SCORED",IF($P24&gt;=$Z$11,"CRITICAL",IF($P24&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R24" s="45" t="str">
-        <f aca="false">IF($O24="","",INDEX($Y$15:$Y$19,MATCH(MAX($H24:$L24),$H24:$L24,0)))</f>
-        <v/>
-      </c>
-      <c r="S24" s="40"/>
-      <c r="T24" s="46"/>
-      <c r="U24" s="47" t="str">
-        <f aca="false">IF($E24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E24),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V24" s="42" t="str">
-        <f aca="false">IF($E24="","",IF(ISNUMBER($U24),ROUND(6-$U24,1),""))</f>
-        <v/>
-      </c>
-      <c r="W24" s="48" t="str">
-        <f aca="false">IF($E24="","",COUNTIF('Score Log'!$C$4:$C$203,$E24))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="38"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="42" t="str">
-        <f aca="false">IF(COUNT($H25:$L25)&lt;5,"",ROUND($H25*$Z$5+$I25*$Z$6+$J25*$Z$7+$K25*$Z$8+$L25*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P25" s="43" t="str">
-        <f aca="false">IF(OR($O25="",$M25=""),"",ROUND($O25*$M25,1))</f>
-        <v/>
-      </c>
-      <c r="Q25" s="44" t="str">
-        <f aca="false">IF($E25="","",IF(OR($O25="",$M25=""),"NOT SCORED",IF($P25&gt;=$Z$11,"CRITICAL",IF($P25&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R25" s="45" t="str">
-        <f aca="false">IF($O25="","",INDEX($Y$15:$Y$19,MATCH(MAX($H25:$L25),$H25:$L25,0)))</f>
-        <v/>
-      </c>
-      <c r="S25" s="40"/>
-      <c r="T25" s="46"/>
-      <c r="U25" s="47" t="str">
-        <f aca="false">IF($E25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E25),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V25" s="42" t="str">
-        <f aca="false">IF($E25="","",IF(ISNUMBER($U25),ROUND(6-$U25,1),""))</f>
-        <v/>
-      </c>
-      <c r="W25" s="48" t="str">
-        <f aca="false">IF($E25="","",COUNTIF('Score Log'!$C$4:$C$203,$E25))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="38"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="39"/>
-      <c r="K26" s="39"/>
-      <c r="L26" s="39"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="38"/>
-      <c r="O26" s="42" t="str">
-        <f aca="false">IF(COUNT($H26:$L26)&lt;5,"",ROUND($H26*$Z$5+$I26*$Z$6+$J26*$Z$7+$K26*$Z$8+$L26*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P26" s="43" t="str">
-        <f aca="false">IF(OR($O26="",$M26=""),"",ROUND($O26*$M26,1))</f>
-        <v/>
-      </c>
-      <c r="Q26" s="44" t="str">
-        <f aca="false">IF($E26="","",IF(OR($O26="",$M26=""),"NOT SCORED",IF($P26&gt;=$Z$11,"CRITICAL",IF($P26&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R26" s="45" t="str">
-        <f aca="false">IF($O26="","",INDEX($Y$15:$Y$19,MATCH(MAX($H26:$L26),$H26:$L26,0)))</f>
-        <v/>
-      </c>
-      <c r="S26" s="40"/>
-      <c r="T26" s="46"/>
-      <c r="U26" s="47" t="str">
-        <f aca="false">IF($E26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E26),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V26" s="42" t="str">
-        <f aca="false">IF($E26="","",IF(ISNUMBER($U26),ROUND(6-$U26,1),""))</f>
-        <v/>
-      </c>
-      <c r="W26" s="48" t="str">
-        <f aca="false">IF($E26="","",COUNTIF('Score Log'!$C$4:$C$203,$E26))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="38"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="39"/>
-      <c r="L27" s="39"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="38"/>
-      <c r="O27" s="42" t="str">
-        <f aca="false">IF(COUNT($H27:$L27)&lt;5,"",ROUND($H27*$Z$5+$I27*$Z$6+$J27*$Z$7+$K27*$Z$8+$L27*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P27" s="43" t="str">
-        <f aca="false">IF(OR($O27="",$M27=""),"",ROUND($O27*$M27,1))</f>
-        <v/>
-      </c>
-      <c r="Q27" s="44" t="str">
-        <f aca="false">IF($E27="","",IF(OR($O27="",$M27=""),"NOT SCORED",IF($P27&gt;=$Z$11,"CRITICAL",IF($P27&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R27" s="45" t="str">
-        <f aca="false">IF($O27="","",INDEX($Y$15:$Y$19,MATCH(MAX($H27:$L27),$H27:$L27,0)))</f>
-        <v/>
-      </c>
-      <c r="S27" s="40"/>
-      <c r="T27" s="46"/>
-      <c r="U27" s="47" t="str">
-        <f aca="false">IF($E27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E27),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V27" s="42" t="str">
-        <f aca="false">IF($E27="","",IF(ISNUMBER($U27),ROUND(6-$U27,1),""))</f>
-        <v/>
-      </c>
-      <c r="W27" s="48" t="str">
-        <f aca="false">IF($E27="","",COUNTIF('Score Log'!$C$4:$C$203,$E27))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="38"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="39"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="39"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="38"/>
-      <c r="O28" s="42" t="str">
-        <f aca="false">IF(COUNT($H28:$L28)&lt;5,"",ROUND($H28*$Z$5+$I28*$Z$6+$J28*$Z$7+$K28*$Z$8+$L28*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P28" s="43" t="str">
-        <f aca="false">IF(OR($O28="",$M28=""),"",ROUND($O28*$M28,1))</f>
-        <v/>
-      </c>
-      <c r="Q28" s="44" t="str">
-        <f aca="false">IF($E28="","",IF(OR($O28="",$M28=""),"NOT SCORED",IF($P28&gt;=$Z$11,"CRITICAL",IF($P28&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R28" s="45" t="str">
-        <f aca="false">IF($O28="","",INDEX($Y$15:$Y$19,MATCH(MAX($H28:$L28),$H28:$L28,0)))</f>
-        <v/>
-      </c>
-      <c r="S28" s="40"/>
-      <c r="T28" s="46"/>
-      <c r="U28" s="47" t="str">
-        <f aca="false">IF($E28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E28),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V28" s="42" t="str">
-        <f aca="false">IF($E28="","",IF(ISNUMBER($U28),ROUND(6-$U28,1),""))</f>
-        <v/>
-      </c>
-      <c r="W28" s="48" t="str">
-        <f aca="false">IF($E28="","",COUNTIF('Score Log'!$C$4:$C$203,$E28))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="38"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="39"/>
-      <c r="K29" s="39"/>
-      <c r="L29" s="39"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="38"/>
-      <c r="O29" s="42" t="str">
-        <f aca="false">IF(COUNT($H29:$L29)&lt;5,"",ROUND($H29*$Z$5+$I29*$Z$6+$J29*$Z$7+$K29*$Z$8+$L29*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P29" s="43" t="str">
-        <f aca="false">IF(OR($O29="",$M29=""),"",ROUND($O29*$M29,1))</f>
-        <v/>
-      </c>
-      <c r="Q29" s="44" t="str">
-        <f aca="false">IF($E29="","",IF(OR($O29="",$M29=""),"NOT SCORED",IF($P29&gt;=$Z$11,"CRITICAL",IF($P29&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R29" s="45" t="str">
-        <f aca="false">IF($O29="","",INDEX($Y$15:$Y$19,MATCH(MAX($H29:$L29),$H29:$L29,0)))</f>
-        <v/>
-      </c>
-      <c r="S29" s="40"/>
-      <c r="T29" s="46"/>
-      <c r="U29" s="47" t="str">
-        <f aca="false">IF($E29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E29),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V29" s="42" t="str">
-        <f aca="false">IF($E29="","",IF(ISNUMBER($U29),ROUND(6-$U29,1),""))</f>
-        <v/>
-      </c>
-      <c r="W29" s="48" t="str">
-        <f aca="false">IF($E29="","",COUNTIF('Score Log'!$C$4:$C$203,$E29))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="38"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="40"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="39"/>
-      <c r="J30" s="39"/>
-      <c r="K30" s="39"/>
-      <c r="L30" s="39"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="38"/>
-      <c r="O30" s="42" t="str">
-        <f aca="false">IF(COUNT($H30:$L30)&lt;5,"",ROUND($H30*$Z$5+$I30*$Z$6+$J30*$Z$7+$K30*$Z$8+$L30*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P30" s="43" t="str">
-        <f aca="false">IF(OR($O30="",$M30=""),"",ROUND($O30*$M30,1))</f>
-        <v/>
-      </c>
-      <c r="Q30" s="44" t="str">
-        <f aca="false">IF($E30="","",IF(OR($O30="",$M30=""),"NOT SCORED",IF($P30&gt;=$Z$11,"CRITICAL",IF($P30&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R30" s="45" t="str">
-        <f aca="false">IF($O30="","",INDEX($Y$15:$Y$19,MATCH(MAX($H30:$L30),$H30:$L30,0)))</f>
-        <v/>
-      </c>
-      <c r="S30" s="40"/>
-      <c r="T30" s="46"/>
-      <c r="U30" s="47" t="str">
-        <f aca="false">IF($E30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E30),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V30" s="42" t="str">
-        <f aca="false">IF($E30="","",IF(ISNUMBER($U30),ROUND(6-$U30,1),""))</f>
-        <v/>
-      </c>
-      <c r="W30" s="48" t="str">
-        <f aca="false">IF($E30="","",COUNTIF('Score Log'!$C$4:$C$203,$E30))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="38"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="39"/>
-      <c r="K31" s="39"/>
-      <c r="L31" s="39"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="38"/>
-      <c r="O31" s="42" t="str">
-        <f aca="false">IF(COUNT($H31:$L31)&lt;5,"",ROUND($H31*$Z$5+$I31*$Z$6+$J31*$Z$7+$K31*$Z$8+$L31*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P31" s="43" t="str">
-        <f aca="false">IF(OR($O31="",$M31=""),"",ROUND($O31*$M31,1))</f>
-        <v/>
-      </c>
-      <c r="Q31" s="44" t="str">
-        <f aca="false">IF($E31="","",IF(OR($O31="",$M31=""),"NOT SCORED",IF($P31&gt;=$Z$11,"CRITICAL",IF($P31&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R31" s="45" t="str">
-        <f aca="false">IF($O31="","",INDEX($Y$15:$Y$19,MATCH(MAX($H31:$L31),$H31:$L31,0)))</f>
-        <v/>
-      </c>
-      <c r="S31" s="40"/>
-      <c r="T31" s="46"/>
-      <c r="U31" s="47" t="str">
-        <f aca="false">IF($E31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E31),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V31" s="42" t="str">
-        <f aca="false">IF($E31="","",IF(ISNUMBER($U31),ROUND(6-$U31,1),""))</f>
-        <v/>
-      </c>
-      <c r="W31" s="48" t="str">
-        <f aca="false">IF($E31="","",COUNTIF('Score Log'!$C$4:$C$203,$E31))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="38"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="39"/>
-      <c r="J32" s="39"/>
-      <c r="K32" s="39"/>
-      <c r="L32" s="39"/>
-      <c r="M32" s="39"/>
-      <c r="N32" s="38"/>
-      <c r="O32" s="42" t="str">
-        <f aca="false">IF(COUNT($H32:$L32)&lt;5,"",ROUND($H32*$Z$5+$I32*$Z$6+$J32*$Z$7+$K32*$Z$8+$L32*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P32" s="43" t="str">
-        <f aca="false">IF(OR($O32="",$M32=""),"",ROUND($O32*$M32,1))</f>
-        <v/>
-      </c>
-      <c r="Q32" s="44" t="str">
-        <f aca="false">IF($E32="","",IF(OR($O32="",$M32=""),"NOT SCORED",IF($P32&gt;=$Z$11,"CRITICAL",IF($P32&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R32" s="45" t="str">
-        <f aca="false">IF($O32="","",INDEX($Y$15:$Y$19,MATCH(MAX($H32:$L32),$H32:$L32,0)))</f>
-        <v/>
-      </c>
-      <c r="S32" s="40"/>
-      <c r="T32" s="46"/>
-      <c r="U32" s="47" t="str">
-        <f aca="false">IF($E32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E32),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V32" s="42" t="str">
-        <f aca="false">IF($E32="","",IF(ISNUMBER($U32),ROUND(6-$U32,1),""))</f>
-        <v/>
-      </c>
-      <c r="W32" s="48" t="str">
-        <f aca="false">IF($E32="","",COUNTIF('Score Log'!$C$4:$C$203,$E32))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="38"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="39"/>
-      <c r="J33" s="39"/>
-      <c r="K33" s="39"/>
-      <c r="L33" s="39"/>
-      <c r="M33" s="39"/>
-      <c r="N33" s="38"/>
-      <c r="O33" s="42" t="str">
-        <f aca="false">IF(COUNT($H33:$L33)&lt;5,"",ROUND($H33*$Z$5+$I33*$Z$6+$J33*$Z$7+$K33*$Z$8+$L33*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P33" s="43" t="str">
-        <f aca="false">IF(OR($O33="",$M33=""),"",ROUND($O33*$M33,1))</f>
-        <v/>
-      </c>
-      <c r="Q33" s="44" t="str">
-        <f aca="false">IF($E33="","",IF(OR($O33="",$M33=""),"NOT SCORED",IF($P33&gt;=$Z$11,"CRITICAL",IF($P33&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R33" s="45" t="str">
-        <f aca="false">IF($O33="","",INDEX($Y$15:$Y$19,MATCH(MAX($H33:$L33),$H33:$L33,0)))</f>
-        <v/>
-      </c>
-      <c r="S33" s="40"/>
-      <c r="T33" s="46"/>
-      <c r="U33" s="47" t="str">
-        <f aca="false">IF($E33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E33),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V33" s="42" t="str">
-        <f aca="false">IF($E33="","",IF(ISNUMBER($U33),ROUND(6-$U33,1),""))</f>
-        <v/>
-      </c>
-      <c r="W33" s="48" t="str">
-        <f aca="false">IF($E33="","",COUNTIF('Score Log'!$C$4:$C$203,$E33))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="38"/>
-      <c r="B34" s="39"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="39"/>
-      <c r="K34" s="39"/>
-      <c r="L34" s="39"/>
-      <c r="M34" s="39"/>
-      <c r="N34" s="38"/>
-      <c r="O34" s="42" t="str">
-        <f aca="false">IF(COUNT($H34:$L34)&lt;5,"",ROUND($H34*$Z$5+$I34*$Z$6+$J34*$Z$7+$K34*$Z$8+$L34*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P34" s="43" t="str">
-        <f aca="false">IF(OR($O34="",$M34=""),"",ROUND($O34*$M34,1))</f>
-        <v/>
-      </c>
-      <c r="Q34" s="44" t="str">
-        <f aca="false">IF($E34="","",IF(OR($O34="",$M34=""),"NOT SCORED",IF($P34&gt;=$Z$11,"CRITICAL",IF($P34&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R34" s="45" t="str">
-        <f aca="false">IF($O34="","",INDEX($Y$15:$Y$19,MATCH(MAX($H34:$L34),$H34:$L34,0)))</f>
-        <v/>
-      </c>
-      <c r="S34" s="40"/>
-      <c r="T34" s="46"/>
-      <c r="U34" s="47" t="str">
-        <f aca="false">IF($E34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E34),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V34" s="42" t="str">
-        <f aca="false">IF($E34="","",IF(ISNUMBER($U34),ROUND(6-$U34,1),""))</f>
-        <v/>
-      </c>
-      <c r="W34" s="48" t="str">
-        <f aca="false">IF($E34="","",COUNTIF('Score Log'!$C$4:$C$203,$E34))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="38"/>
-      <c r="B35" s="39"/>
-      <c r="C35" s="40"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="39"/>
-      <c r="J35" s="39"/>
-      <c r="K35" s="39"/>
-      <c r="L35" s="39"/>
-      <c r="M35" s="39"/>
-      <c r="N35" s="38"/>
-      <c r="O35" s="42" t="str">
-        <f aca="false">IF(COUNT($H35:$L35)&lt;5,"",ROUND($H35*$Z$5+$I35*$Z$6+$J35*$Z$7+$K35*$Z$8+$L35*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P35" s="43" t="str">
-        <f aca="false">IF(OR($O35="",$M35=""),"",ROUND($O35*$M35,1))</f>
-        <v/>
-      </c>
-      <c r="Q35" s="44" t="str">
-        <f aca="false">IF($E35="","",IF(OR($O35="",$M35=""),"NOT SCORED",IF($P35&gt;=$Z$11,"CRITICAL",IF($P35&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R35" s="45" t="str">
-        <f aca="false">IF($O35="","",INDEX($Y$15:$Y$19,MATCH(MAX($H35:$L35),$H35:$L35,0)))</f>
-        <v/>
-      </c>
-      <c r="S35" s="40"/>
-      <c r="T35" s="46"/>
-      <c r="U35" s="47" t="str">
-        <f aca="false">IF($E35="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E35),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V35" s="42" t="str">
-        <f aca="false">IF($E35="","",IF(ISNUMBER($U35),ROUND(6-$U35,1),""))</f>
-        <v/>
-      </c>
-      <c r="W35" s="48" t="str">
-        <f aca="false">IF($E35="","",COUNTIF('Score Log'!$C$4:$C$203,$E35))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="38"/>
-      <c r="B36" s="39"/>
-      <c r="C36" s="40"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="39"/>
-      <c r="J36" s="39"/>
-      <c r="K36" s="39"/>
-      <c r="L36" s="39"/>
-      <c r="M36" s="39"/>
-      <c r="N36" s="38"/>
-      <c r="O36" s="42" t="str">
-        <f aca="false">IF(COUNT($H36:$L36)&lt;5,"",ROUND($H36*$Z$5+$I36*$Z$6+$J36*$Z$7+$K36*$Z$8+$L36*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P36" s="43" t="str">
-        <f aca="false">IF(OR($O36="",$M36=""),"",ROUND($O36*$M36,1))</f>
-        <v/>
-      </c>
-      <c r="Q36" s="44" t="str">
-        <f aca="false">IF($E36="","",IF(OR($O36="",$M36=""),"NOT SCORED",IF($P36&gt;=$Z$11,"CRITICAL",IF($P36&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R36" s="45" t="str">
-        <f aca="false">IF($O36="","",INDEX($Y$15:$Y$19,MATCH(MAX($H36:$L36),$H36:$L36,0)))</f>
-        <v/>
-      </c>
-      <c r="S36" s="40"/>
-      <c r="T36" s="46"/>
-      <c r="U36" s="47" t="str">
-        <f aca="false">IF($E36="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E36),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V36" s="42" t="str">
-        <f aca="false">IF($E36="","",IF(ISNUMBER($U36),ROUND(6-$U36,1),""))</f>
-        <v/>
-      </c>
-      <c r="W36" s="48" t="str">
-        <f aca="false">IF($E36="","",COUNTIF('Score Log'!$C$4:$C$203,$E36))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="38"/>
-      <c r="B37" s="39"/>
-      <c r="C37" s="40"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="39"/>
-      <c r="I37" s="39"/>
-      <c r="J37" s="39"/>
-      <c r="K37" s="39"/>
-      <c r="L37" s="39"/>
-      <c r="M37" s="39"/>
-      <c r="N37" s="38"/>
-      <c r="O37" s="42" t="str">
-        <f aca="false">IF(COUNT($H37:$L37)&lt;5,"",ROUND($H37*$Z$5+$I37*$Z$6+$J37*$Z$7+$K37*$Z$8+$L37*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P37" s="43" t="str">
-        <f aca="false">IF(OR($O37="",$M37=""),"",ROUND($O37*$M37,1))</f>
-        <v/>
-      </c>
-      <c r="Q37" s="44" t="str">
-        <f aca="false">IF($E37="","",IF(OR($O37="",$M37=""),"NOT SCORED",IF($P37&gt;=$Z$11,"CRITICAL",IF($P37&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R37" s="45" t="str">
-        <f aca="false">IF($O37="","",INDEX($Y$15:$Y$19,MATCH(MAX($H37:$L37),$H37:$L37,0)))</f>
-        <v/>
-      </c>
-      <c r="S37" s="40"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="47" t="str">
-        <f aca="false">IF($E37="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E37),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V37" s="42" t="str">
-        <f aca="false">IF($E37="","",IF(ISNUMBER($U37),ROUND(6-$U37,1),""))</f>
-        <v/>
-      </c>
-      <c r="W37" s="48" t="str">
-        <f aca="false">IF($E37="","",COUNTIF('Score Log'!$C$4:$C$203,$E37))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="38"/>
-      <c r="B38" s="39"/>
-      <c r="C38" s="40"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="39"/>
-      <c r="K38" s="39"/>
-      <c r="L38" s="39"/>
-      <c r="M38" s="39"/>
-      <c r="N38" s="38"/>
-      <c r="O38" s="42" t="str">
-        <f aca="false">IF(COUNT($H38:$L38)&lt;5,"",ROUND($H38*$Z$5+$I38*$Z$6+$J38*$Z$7+$K38*$Z$8+$L38*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P38" s="43" t="str">
-        <f aca="false">IF(OR($O38="",$M38=""),"",ROUND($O38*$M38,1))</f>
-        <v/>
-      </c>
-      <c r="Q38" s="44" t="str">
-        <f aca="false">IF($E38="","",IF(OR($O38="",$M38=""),"NOT SCORED",IF($P38&gt;=$Z$11,"CRITICAL",IF($P38&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R38" s="45" t="str">
-        <f aca="false">IF($O38="","",INDEX($Y$15:$Y$19,MATCH(MAX($H38:$L38),$H38:$L38,0)))</f>
-        <v/>
-      </c>
-      <c r="S38" s="40"/>
-      <c r="T38" s="46"/>
-      <c r="U38" s="47" t="str">
-        <f aca="false">IF($E38="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E38),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V38" s="42" t="str">
-        <f aca="false">IF($E38="","",IF(ISNUMBER($U38),ROUND(6-$U38,1),""))</f>
-        <v/>
-      </c>
-      <c r="W38" s="48" t="str">
-        <f aca="false">IF($E38="","",COUNTIF('Score Log'!$C$4:$C$203,$E38))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="38"/>
-      <c r="B39" s="39"/>
-      <c r="C39" s="40"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="39"/>
-      <c r="I39" s="39"/>
-      <c r="J39" s="39"/>
-      <c r="K39" s="39"/>
-      <c r="L39" s="39"/>
-      <c r="M39" s="39"/>
-      <c r="N39" s="38"/>
-      <c r="O39" s="42" t="str">
-        <f aca="false">IF(COUNT($H39:$L39)&lt;5,"",ROUND($H39*$Z$5+$I39*$Z$6+$J39*$Z$7+$K39*$Z$8+$L39*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P39" s="43" t="str">
-        <f aca="false">IF(OR($O39="",$M39=""),"",ROUND($O39*$M39,1))</f>
-        <v/>
-      </c>
-      <c r="Q39" s="44" t="str">
-        <f aca="false">IF($E39="","",IF(OR($O39="",$M39=""),"NOT SCORED",IF($P39&gt;=$Z$11,"CRITICAL",IF($P39&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R39" s="45" t="str">
-        <f aca="false">IF($O39="","",INDEX($Y$15:$Y$19,MATCH(MAX($H39:$L39),$H39:$L39,0)))</f>
-        <v/>
-      </c>
-      <c r="S39" s="40"/>
-      <c r="T39" s="46"/>
-      <c r="U39" s="47" t="str">
-        <f aca="false">IF($E39="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E39),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V39" s="42" t="str">
-        <f aca="false">IF($E39="","",IF(ISNUMBER($U39),ROUND(6-$U39,1),""))</f>
-        <v/>
-      </c>
-      <c r="W39" s="48" t="str">
-        <f aca="false">IF($E39="","",COUNTIF('Score Log'!$C$4:$C$203,$E39))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="38"/>
-      <c r="B40" s="39"/>
-      <c r="C40" s="40"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="38"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="39"/>
-      <c r="I40" s="39"/>
-      <c r="J40" s="39"/>
-      <c r="K40" s="39"/>
-      <c r="L40" s="39"/>
-      <c r="M40" s="39"/>
-      <c r="N40" s="38"/>
-      <c r="O40" s="42" t="str">
-        <f aca="false">IF(COUNT($H40:$L40)&lt;5,"",ROUND($H40*$Z$5+$I40*$Z$6+$J40*$Z$7+$K40*$Z$8+$L40*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P40" s="43" t="str">
-        <f aca="false">IF(OR($O40="",$M40=""),"",ROUND($O40*$M40,1))</f>
-        <v/>
-      </c>
-      <c r="Q40" s="44" t="str">
-        <f aca="false">IF($E40="","",IF(OR($O40="",$M40=""),"NOT SCORED",IF($P40&gt;=$Z$11,"CRITICAL",IF($P40&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R40" s="45" t="str">
-        <f aca="false">IF($O40="","",INDEX($Y$15:$Y$19,MATCH(MAX($H40:$L40),$H40:$L40,0)))</f>
-        <v/>
-      </c>
-      <c r="S40" s="40"/>
-      <c r="T40" s="46"/>
-      <c r="U40" s="47" t="str">
-        <f aca="false">IF($E40="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E40),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V40" s="42" t="str">
-        <f aca="false">IF($E40="","",IF(ISNUMBER($U40),ROUND(6-$U40,1),""))</f>
-        <v/>
-      </c>
-      <c r="W40" s="48" t="str">
-        <f aca="false">IF($E40="","",COUNTIF('Score Log'!$C$4:$C$203,$E40))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="38"/>
-      <c r="B41" s="39"/>
-      <c r="C41" s="40"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="38"/>
-      <c r="F41" s="41"/>
-      <c r="G41" s="41"/>
-      <c r="H41" s="39"/>
-      <c r="I41" s="39"/>
-      <c r="J41" s="39"/>
-      <c r="K41" s="39"/>
-      <c r="L41" s="39"/>
-      <c r="M41" s="39"/>
-      <c r="N41" s="38"/>
-      <c r="O41" s="42" t="str">
-        <f aca="false">IF(COUNT($H41:$L41)&lt;5,"",ROUND($H41*$Z$5+$I41*$Z$6+$J41*$Z$7+$K41*$Z$8+$L41*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P41" s="43" t="str">
-        <f aca="false">IF(OR($O41="",$M41=""),"",ROUND($O41*$M41,1))</f>
-        <v/>
-      </c>
-      <c r="Q41" s="44" t="str">
-        <f aca="false">IF($E41="","",IF(OR($O41="",$M41=""),"NOT SCORED",IF($P41&gt;=$Z$11,"CRITICAL",IF($P41&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R41" s="45" t="str">
-        <f aca="false">IF($O41="","",INDEX($Y$15:$Y$19,MATCH(MAX($H41:$L41),$H41:$L41,0)))</f>
-        <v/>
-      </c>
-      <c r="S41" s="40"/>
-      <c r="T41" s="46"/>
-      <c r="U41" s="47" t="str">
-        <f aca="false">IF($E41="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E41),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V41" s="42" t="str">
-        <f aca="false">IF($E41="","",IF(ISNUMBER($U41),ROUND(6-$U41,1),""))</f>
-        <v/>
-      </c>
-      <c r="W41" s="48" t="str">
-        <f aca="false">IF($E41="","",COUNTIF('Score Log'!$C$4:$C$203,$E41))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="38"/>
-      <c r="B42" s="39"/>
-      <c r="C42" s="40"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="38"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="39"/>
-      <c r="I42" s="39"/>
-      <c r="J42" s="39"/>
-      <c r="K42" s="39"/>
-      <c r="L42" s="39"/>
-      <c r="M42" s="39"/>
-      <c r="N42" s="38"/>
-      <c r="O42" s="42" t="str">
-        <f aca="false">IF(COUNT($H42:$L42)&lt;5,"",ROUND($H42*$Z$5+$I42*$Z$6+$J42*$Z$7+$K42*$Z$8+$L42*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P42" s="43" t="str">
-        <f aca="false">IF(OR($O42="",$M42=""),"",ROUND($O42*$M42,1))</f>
-        <v/>
-      </c>
-      <c r="Q42" s="44" t="str">
-        <f aca="false">IF($E42="","",IF(OR($O42="",$M42=""),"NOT SCORED",IF($P42&gt;=$Z$11,"CRITICAL",IF($P42&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R42" s="45" t="str">
-        <f aca="false">IF($O42="","",INDEX($Y$15:$Y$19,MATCH(MAX($H42:$L42),$H42:$L42,0)))</f>
-        <v/>
-      </c>
-      <c r="S42" s="40"/>
-      <c r="T42" s="46"/>
-      <c r="U42" s="47" t="str">
-        <f aca="false">IF($E42="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E42),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V42" s="42" t="str">
-        <f aca="false">IF($E42="","",IF(ISNUMBER($U42),ROUND(6-$U42,1),""))</f>
-        <v/>
-      </c>
-      <c r="W42" s="48" t="str">
-        <f aca="false">IF($E42="","",COUNTIF('Score Log'!$C$4:$C$203,$E42))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="38"/>
-      <c r="B43" s="39"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="39"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="39"/>
-      <c r="I43" s="39"/>
-      <c r="J43" s="39"/>
-      <c r="K43" s="39"/>
-      <c r="L43" s="39"/>
-      <c r="M43" s="39"/>
-      <c r="N43" s="38"/>
-      <c r="O43" s="42" t="str">
-        <f aca="false">IF(COUNT($H43:$L43)&lt;5,"",ROUND($H43*$Z$5+$I43*$Z$6+$J43*$Z$7+$K43*$Z$8+$L43*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P43" s="43" t="str">
-        <f aca="false">IF(OR($O43="",$M43=""),"",ROUND($O43*$M43,1))</f>
-        <v/>
-      </c>
-      <c r="Q43" s="44" t="str">
-        <f aca="false">IF($E43="","",IF(OR($O43="",$M43=""),"NOT SCORED",IF($P43&gt;=$Z$11,"CRITICAL",IF($P43&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R43" s="45" t="str">
-        <f aca="false">IF($O43="","",INDEX($Y$15:$Y$19,MATCH(MAX($H43:$L43),$H43:$L43,0)))</f>
-        <v/>
-      </c>
-      <c r="S43" s="40"/>
-      <c r="T43" s="46"/>
-      <c r="U43" s="47" t="str">
-        <f aca="false">IF($E43="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E43),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V43" s="42" t="str">
-        <f aca="false">IF($E43="","",IF(ISNUMBER($U43),ROUND(6-$U43,1),""))</f>
-        <v/>
-      </c>
-      <c r="W43" s="48" t="str">
-        <f aca="false">IF($E43="","",COUNTIF('Score Log'!$C$4:$C$203,$E43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="38"/>
-      <c r="B44" s="39"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="39"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="39"/>
-      <c r="I44" s="39"/>
-      <c r="J44" s="39"/>
-      <c r="K44" s="39"/>
-      <c r="L44" s="39"/>
-      <c r="M44" s="39"/>
-      <c r="N44" s="38"/>
-      <c r="O44" s="42" t="str">
-        <f aca="false">IF(COUNT($H44:$L44)&lt;5,"",ROUND($H44*$Z$5+$I44*$Z$6+$J44*$Z$7+$K44*$Z$8+$L44*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P44" s="43" t="str">
-        <f aca="false">IF(OR($O44="",$M44=""),"",ROUND($O44*$M44,1))</f>
-        <v/>
-      </c>
-      <c r="Q44" s="44" t="str">
-        <f aca="false">IF($E44="","",IF(OR($O44="",$M44=""),"NOT SCORED",IF($P44&gt;=$Z$11,"CRITICAL",IF($P44&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R44" s="45" t="str">
-        <f aca="false">IF($O44="","",INDEX($Y$15:$Y$19,MATCH(MAX($H44:$L44),$H44:$L44,0)))</f>
-        <v/>
-      </c>
-      <c r="S44" s="40"/>
-      <c r="T44" s="46"/>
-      <c r="U44" s="47" t="str">
-        <f aca="false">IF($E44="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E44),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V44" s="42" t="str">
-        <f aca="false">IF($E44="","",IF(ISNUMBER($U44),ROUND(6-$U44,1),""))</f>
-        <v/>
-      </c>
-      <c r="W44" s="48" t="str">
-        <f aca="false">IF($E44="","",COUNTIF('Score Log'!$C$4:$C$203,$E44))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="38"/>
-      <c r="B45" s="39"/>
-      <c r="C45" s="40"/>
-      <c r="D45" s="39"/>
-      <c r="E45" s="38"/>
-      <c r="F45" s="41"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="39"/>
-      <c r="I45" s="39"/>
-      <c r="J45" s="39"/>
-      <c r="K45" s="39"/>
-      <c r="L45" s="39"/>
-      <c r="M45" s="39"/>
-      <c r="N45" s="38"/>
-      <c r="O45" s="42" t="str">
-        <f aca="false">IF(COUNT($H45:$L45)&lt;5,"",ROUND($H45*$Z$5+$I45*$Z$6+$J45*$Z$7+$K45*$Z$8+$L45*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P45" s="43" t="str">
-        <f aca="false">IF(OR($O45="",$M45=""),"",ROUND($O45*$M45,1))</f>
-        <v/>
-      </c>
-      <c r="Q45" s="44" t="str">
-        <f aca="false">IF($E45="","",IF(OR($O45="",$M45=""),"NOT SCORED",IF($P45&gt;=$Z$11,"CRITICAL",IF($P45&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R45" s="45" t="str">
-        <f aca="false">IF($O45="","",INDEX($Y$15:$Y$19,MATCH(MAX($H45:$L45),$H45:$L45,0)))</f>
-        <v/>
-      </c>
-      <c r="S45" s="40"/>
-      <c r="T45" s="46"/>
-      <c r="U45" s="47" t="str">
-        <f aca="false">IF($E45="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E45),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V45" s="42" t="str">
-        <f aca="false">IF($E45="","",IF(ISNUMBER($U45),ROUND(6-$U45,1),""))</f>
-        <v/>
-      </c>
-      <c r="W45" s="48" t="str">
-        <f aca="false">IF($E45="","",COUNTIF('Score Log'!$C$4:$C$203,$E45))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="38"/>
-      <c r="B46" s="39"/>
-      <c r="C46" s="40"/>
-      <c r="D46" s="39"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="41"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="39"/>
-      <c r="I46" s="39"/>
-      <c r="J46" s="39"/>
-      <c r="K46" s="39"/>
-      <c r="L46" s="39"/>
-      <c r="M46" s="39"/>
-      <c r="N46" s="38"/>
-      <c r="O46" s="42" t="str">
-        <f aca="false">IF(COUNT($H46:$L46)&lt;5,"",ROUND($H46*$Z$5+$I46*$Z$6+$J46*$Z$7+$K46*$Z$8+$L46*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P46" s="43" t="str">
-        <f aca="false">IF(OR($O46="",$M46=""),"",ROUND($O46*$M46,1))</f>
-        <v/>
-      </c>
-      <c r="Q46" s="44" t="str">
-        <f aca="false">IF($E46="","",IF(OR($O46="",$M46=""),"NOT SCORED",IF($P46&gt;=$Z$11,"CRITICAL",IF($P46&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R46" s="45" t="str">
-        <f aca="false">IF($O46="","",INDEX($Y$15:$Y$19,MATCH(MAX($H46:$L46),$H46:$L46,0)))</f>
-        <v/>
-      </c>
-      <c r="S46" s="40"/>
-      <c r="T46" s="46"/>
-      <c r="U46" s="47" t="str">
-        <f aca="false">IF($E46="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E46),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V46" s="42" t="str">
-        <f aca="false">IF($E46="","",IF(ISNUMBER($U46),ROUND(6-$U46,1),""))</f>
-        <v/>
-      </c>
-      <c r="W46" s="48" t="str">
-        <f aca="false">IF($E46="","",COUNTIF('Score Log'!$C$4:$C$203,$E46))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="38"/>
-      <c r="B47" s="39"/>
-      <c r="C47" s="40"/>
-      <c r="D47" s="39"/>
-      <c r="E47" s="38"/>
-      <c r="F47" s="41"/>
-      <c r="G47" s="41"/>
-      <c r="H47" s="39"/>
-      <c r="I47" s="39"/>
-      <c r="J47" s="39"/>
-      <c r="K47" s="39"/>
-      <c r="L47" s="39"/>
-      <c r="M47" s="39"/>
-      <c r="N47" s="38"/>
-      <c r="O47" s="42" t="str">
-        <f aca="false">IF(COUNT($H47:$L47)&lt;5,"",ROUND($H47*$Z$5+$I47*$Z$6+$J47*$Z$7+$K47*$Z$8+$L47*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P47" s="43" t="str">
-        <f aca="false">IF(OR($O47="",$M47=""),"",ROUND($O47*$M47,1))</f>
-        <v/>
-      </c>
-      <c r="Q47" s="44" t="str">
-        <f aca="false">IF($E47="","",IF(OR($O47="",$M47=""),"NOT SCORED",IF($P47&gt;=$Z$11,"CRITICAL",IF($P47&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R47" s="45" t="str">
-        <f aca="false">IF($O47="","",INDEX($Y$15:$Y$19,MATCH(MAX($H47:$L47),$H47:$L47,0)))</f>
-        <v/>
-      </c>
-      <c r="S47" s="40"/>
-      <c r="T47" s="46"/>
-      <c r="U47" s="47" t="str">
-        <f aca="false">IF($E47="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E47),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V47" s="42" t="str">
-        <f aca="false">IF($E47="","",IF(ISNUMBER($U47),ROUND(6-$U47,1),""))</f>
-        <v/>
-      </c>
-      <c r="W47" s="48" t="str">
-        <f aca="false">IF($E47="","",COUNTIF('Score Log'!$C$4:$C$203,$E47))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="38"/>
-      <c r="B48" s="39"/>
-      <c r="C48" s="40"/>
-      <c r="D48" s="39"/>
-      <c r="E48" s="38"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="41"/>
-      <c r="H48" s="39"/>
-      <c r="I48" s="39"/>
-      <c r="J48" s="39"/>
-      <c r="K48" s="39"/>
-      <c r="L48" s="39"/>
-      <c r="M48" s="39"/>
-      <c r="N48" s="38"/>
-      <c r="O48" s="42" t="str">
-        <f aca="false">IF(COUNT($H48:$L48)&lt;5,"",ROUND($H48*$Z$5+$I48*$Z$6+$J48*$Z$7+$K48*$Z$8+$L48*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P48" s="43" t="str">
-        <f aca="false">IF(OR($O48="",$M48=""),"",ROUND($O48*$M48,1))</f>
-        <v/>
-      </c>
-      <c r="Q48" s="44" t="str">
-        <f aca="false">IF($E48="","",IF(OR($O48="",$M48=""),"NOT SCORED",IF($P48&gt;=$Z$11,"CRITICAL",IF($P48&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R48" s="45" t="str">
-        <f aca="false">IF($O48="","",INDEX($Y$15:$Y$19,MATCH(MAX($H48:$L48),$H48:$L48,0)))</f>
-        <v/>
-      </c>
-      <c r="S48" s="40"/>
-      <c r="T48" s="46"/>
-      <c r="U48" s="47" t="str">
-        <f aca="false">IF($E48="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E48),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V48" s="42" t="str">
-        <f aca="false">IF($E48="","",IF(ISNUMBER($U48),ROUND(6-$U48,1),""))</f>
-        <v/>
-      </c>
-      <c r="W48" s="48" t="str">
-        <f aca="false">IF($E48="","",COUNTIF('Score Log'!$C$4:$C$203,$E48))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="38"/>
-      <c r="B49" s="39"/>
-      <c r="C49" s="40"/>
-      <c r="D49" s="39"/>
-      <c r="E49" s="38"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="39"/>
-      <c r="I49" s="39"/>
-      <c r="J49" s="39"/>
-      <c r="K49" s="39"/>
-      <c r="L49" s="39"/>
-      <c r="M49" s="39"/>
-      <c r="N49" s="38"/>
-      <c r="O49" s="42" t="str">
-        <f aca="false">IF(COUNT($H49:$L49)&lt;5,"",ROUND($H49*$Z$5+$I49*$Z$6+$J49*$Z$7+$K49*$Z$8+$L49*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P49" s="43" t="str">
-        <f aca="false">IF(OR($O49="",$M49=""),"",ROUND($O49*$M49,1))</f>
-        <v/>
-      </c>
-      <c r="Q49" s="44" t="str">
-        <f aca="false">IF($E49="","",IF(OR($O49="",$M49=""),"NOT SCORED",IF($P49&gt;=$Z$11,"CRITICAL",IF($P49&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R49" s="45" t="str">
-        <f aca="false">IF($O49="","",INDEX($Y$15:$Y$19,MATCH(MAX($H49:$L49),$H49:$L49,0)))</f>
-        <v/>
-      </c>
-      <c r="S49" s="40"/>
-      <c r="T49" s="46"/>
-      <c r="U49" s="47" t="str">
-        <f aca="false">IF($E49="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E49),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V49" s="42" t="str">
-        <f aca="false">IF($E49="","",IF(ISNUMBER($U49),ROUND(6-$U49,1),""))</f>
-        <v/>
-      </c>
-      <c r="W49" s="48" t="str">
-        <f aca="false">IF($E49="","",COUNTIF('Score Log'!$C$4:$C$203,$E49))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="38"/>
-      <c r="B50" s="39"/>
-      <c r="C50" s="40"/>
-      <c r="D50" s="39"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="39"/>
-      <c r="I50" s="39"/>
-      <c r="J50" s="39"/>
-      <c r="K50" s="39"/>
-      <c r="L50" s="39"/>
-      <c r="M50" s="39"/>
-      <c r="N50" s="38"/>
-      <c r="O50" s="42" t="str">
-        <f aca="false">IF(COUNT($H50:$L50)&lt;5,"",ROUND($H50*$Z$5+$I50*$Z$6+$J50*$Z$7+$K50*$Z$8+$L50*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P50" s="43" t="str">
-        <f aca="false">IF(OR($O50="",$M50=""),"",ROUND($O50*$M50,1))</f>
-        <v/>
-      </c>
-      <c r="Q50" s="44" t="str">
-        <f aca="false">IF($E50="","",IF(OR($O50="",$M50=""),"NOT SCORED",IF($P50&gt;=$Z$11,"CRITICAL",IF($P50&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R50" s="45" t="str">
-        <f aca="false">IF($O50="","",INDEX($Y$15:$Y$19,MATCH(MAX($H50:$L50),$H50:$L50,0)))</f>
-        <v/>
-      </c>
-      <c r="S50" s="40"/>
-      <c r="T50" s="46"/>
-      <c r="U50" s="47" t="str">
-        <f aca="false">IF($E50="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E50),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V50" s="42" t="str">
-        <f aca="false">IF($E50="","",IF(ISNUMBER($U50),ROUND(6-$U50,1),""))</f>
-        <v/>
-      </c>
-      <c r="W50" s="48" t="str">
-        <f aca="false">IF($E50="","",COUNTIF('Score Log'!$C$4:$C$203,$E50))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="38"/>
-      <c r="B51" s="39"/>
-      <c r="C51" s="40"/>
-      <c r="D51" s="39"/>
-      <c r="E51" s="38"/>
-      <c r="F51" s="41"/>
-      <c r="G51" s="41"/>
-      <c r="H51" s="39"/>
-      <c r="I51" s="39"/>
-      <c r="J51" s="39"/>
-      <c r="K51" s="39"/>
-      <c r="L51" s="39"/>
-      <c r="M51" s="39"/>
-      <c r="N51" s="38"/>
-      <c r="O51" s="42" t="str">
-        <f aca="false">IF(COUNT($H51:$L51)&lt;5,"",ROUND($H51*$Z$5+$I51*$Z$6+$J51*$Z$7+$K51*$Z$8+$L51*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P51" s="43" t="str">
-        <f aca="false">IF(OR($O51="",$M51=""),"",ROUND($O51*$M51,1))</f>
-        <v/>
-      </c>
-      <c r="Q51" s="44" t="str">
-        <f aca="false">IF($E51="","",IF(OR($O51="",$M51=""),"NOT SCORED",IF($P51&gt;=$Z$11,"CRITICAL",IF($P51&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R51" s="45" t="str">
-        <f aca="false">IF($O51="","",INDEX($Y$15:$Y$19,MATCH(MAX($H51:$L51),$H51:$L51,0)))</f>
-        <v/>
-      </c>
-      <c r="S51" s="40"/>
-      <c r="T51" s="46"/>
-      <c r="U51" s="47" t="str">
-        <f aca="false">IF($E51="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E51),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V51" s="42" t="str">
-        <f aca="false">IF($E51="","",IF(ISNUMBER($U51),ROUND(6-$U51,1),""))</f>
-        <v/>
-      </c>
-      <c r="W51" s="48" t="str">
-        <f aca="false">IF($E51="","",COUNTIF('Score Log'!$C$4:$C$203,$E51))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="38"/>
-      <c r="B52" s="39"/>
-      <c r="C52" s="40"/>
-      <c r="D52" s="39"/>
-      <c r="E52" s="38"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="39"/>
-      <c r="I52" s="39"/>
-      <c r="J52" s="39"/>
-      <c r="K52" s="39"/>
-      <c r="L52" s="39"/>
-      <c r="M52" s="39"/>
-      <c r="N52" s="38"/>
-      <c r="O52" s="42" t="str">
-        <f aca="false">IF(COUNT($H52:$L52)&lt;5,"",ROUND($H52*$Z$5+$I52*$Z$6+$J52*$Z$7+$K52*$Z$8+$L52*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P52" s="43" t="str">
-        <f aca="false">IF(OR($O52="",$M52=""),"",ROUND($O52*$M52,1))</f>
-        <v/>
-      </c>
-      <c r="Q52" s="44" t="str">
-        <f aca="false">IF($E52="","",IF(OR($O52="",$M52=""),"NOT SCORED",IF($P52&gt;=$Z$11,"CRITICAL",IF($P52&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R52" s="45" t="str">
-        <f aca="false">IF($O52="","",INDEX($Y$15:$Y$19,MATCH(MAX($H52:$L52),$H52:$L52,0)))</f>
-        <v/>
-      </c>
-      <c r="S52" s="40"/>
-      <c r="T52" s="46"/>
-      <c r="U52" s="47" t="str">
-        <f aca="false">IF($E52="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E52),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V52" s="42" t="str">
-        <f aca="false">IF($E52="","",IF(ISNUMBER($U52),ROUND(6-$U52,1),""))</f>
-        <v/>
-      </c>
-      <c r="W52" s="48" t="str">
-        <f aca="false">IF($E52="","",COUNTIF('Score Log'!$C$4:$C$203,$E52))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="38"/>
-      <c r="B53" s="39"/>
-      <c r="C53" s="40"/>
-      <c r="D53" s="39"/>
-      <c r="E53" s="38"/>
-      <c r="F53" s="41"/>
-      <c r="G53" s="41"/>
-      <c r="H53" s="39"/>
-      <c r="I53" s="39"/>
-      <c r="J53" s="39"/>
-      <c r="K53" s="39"/>
-      <c r="L53" s="39"/>
-      <c r="M53" s="39"/>
-      <c r="N53" s="38"/>
-      <c r="O53" s="42" t="str">
-        <f aca="false">IF(COUNT($H53:$L53)&lt;5,"",ROUND($H53*$Z$5+$I53*$Z$6+$J53*$Z$7+$K53*$Z$8+$L53*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P53" s="43" t="str">
-        <f aca="false">IF(OR($O53="",$M53=""),"",ROUND($O53*$M53,1))</f>
-        <v/>
-      </c>
-      <c r="Q53" s="44" t="str">
-        <f aca="false">IF($E53="","",IF(OR($O53="",$M53=""),"NOT SCORED",IF($P53&gt;=$Z$11,"CRITICAL",IF($P53&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R53" s="45" t="str">
-        <f aca="false">IF($O53="","",INDEX($Y$15:$Y$19,MATCH(MAX($H53:$L53),$H53:$L53,0)))</f>
-        <v/>
-      </c>
-      <c r="S53" s="40"/>
-      <c r="T53" s="46"/>
-      <c r="U53" s="47" t="str">
-        <f aca="false">IF($E53="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E53),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V53" s="42" t="str">
-        <f aca="false">IF($E53="","",IF(ISNUMBER($U53),ROUND(6-$U53,1),""))</f>
-        <v/>
-      </c>
-      <c r="W53" s="48" t="str">
-        <f aca="false">IF($E53="","",COUNTIF('Score Log'!$C$4:$C$203,$E53))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="38"/>
-      <c r="B54" s="39"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="39"/>
-      <c r="E54" s="38"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="41"/>
-      <c r="H54" s="39"/>
-      <c r="I54" s="39"/>
-      <c r="J54" s="39"/>
-      <c r="K54" s="39"/>
-      <c r="L54" s="39"/>
-      <c r="M54" s="39"/>
-      <c r="N54" s="38"/>
-      <c r="O54" s="42" t="str">
-        <f aca="false">IF(COUNT($H54:$L54)&lt;5,"",ROUND($H54*$Z$5+$I54*$Z$6+$J54*$Z$7+$K54*$Z$8+$L54*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P54" s="43" t="str">
-        <f aca="false">IF(OR($O54="",$M54=""),"",ROUND($O54*$M54,1))</f>
-        <v/>
-      </c>
-      <c r="Q54" s="44" t="str">
-        <f aca="false">IF($E54="","",IF(OR($O54="",$M54=""),"NOT SCORED",IF($P54&gt;=$Z$11,"CRITICAL",IF($P54&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R54" s="45" t="str">
-        <f aca="false">IF($O54="","",INDEX($Y$15:$Y$19,MATCH(MAX($H54:$L54),$H54:$L54,0)))</f>
-        <v/>
-      </c>
-      <c r="S54" s="40"/>
-      <c r="T54" s="46"/>
-      <c r="U54" s="47" t="str">
-        <f aca="false">IF($E54="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E54),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V54" s="42" t="str">
-        <f aca="false">IF($E54="","",IF(ISNUMBER($U54),ROUND(6-$U54,1),""))</f>
-        <v/>
-      </c>
-      <c r="W54" s="48" t="str">
-        <f aca="false">IF($E54="","",COUNTIF('Score Log'!$C$4:$C$203,$E54))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="38"/>
-      <c r="B55" s="39"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="39"/>
-      <c r="E55" s="38"/>
-      <c r="F55" s="41"/>
-      <c r="G55" s="41"/>
-      <c r="H55" s="39"/>
-      <c r="I55" s="39"/>
-      <c r="J55" s="39"/>
-      <c r="K55" s="39"/>
-      <c r="L55" s="39"/>
-      <c r="M55" s="39"/>
-      <c r="N55" s="38"/>
-      <c r="O55" s="42" t="str">
-        <f aca="false">IF(COUNT($H55:$L55)&lt;5,"",ROUND($H55*$Z$5+$I55*$Z$6+$J55*$Z$7+$K55*$Z$8+$L55*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P55" s="43" t="str">
-        <f aca="false">IF(OR($O55="",$M55=""),"",ROUND($O55*$M55,1))</f>
-        <v/>
-      </c>
-      <c r="Q55" s="44" t="str">
-        <f aca="false">IF($E55="","",IF(OR($O55="",$M55=""),"NOT SCORED",IF($P55&gt;=$Z$11,"CRITICAL",IF($P55&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R55" s="45" t="str">
-        <f aca="false">IF($O55="","",INDEX($Y$15:$Y$19,MATCH(MAX($H55:$L55),$H55:$L55,0)))</f>
-        <v/>
-      </c>
-      <c r="S55" s="40"/>
-      <c r="T55" s="46"/>
-      <c r="U55" s="47" t="str">
-        <f aca="false">IF($E55="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E55),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V55" s="42" t="str">
-        <f aca="false">IF($E55="","",IF(ISNUMBER($U55),ROUND(6-$U55,1),""))</f>
-        <v/>
-      </c>
-      <c r="W55" s="48" t="str">
-        <f aca="false">IF($E55="","",COUNTIF('Score Log'!$C$4:$C$203,$E55))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="38"/>
-      <c r="B56" s="39"/>
-      <c r="C56" s="40"/>
-      <c r="D56" s="39"/>
-      <c r="E56" s="38"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="41"/>
-      <c r="H56" s="39"/>
-      <c r="I56" s="39"/>
-      <c r="J56" s="39"/>
-      <c r="K56" s="39"/>
-      <c r="L56" s="39"/>
-      <c r="M56" s="39"/>
-      <c r="N56" s="38"/>
-      <c r="O56" s="42" t="str">
-        <f aca="false">IF(COUNT($H56:$L56)&lt;5,"",ROUND($H56*$Z$5+$I56*$Z$6+$J56*$Z$7+$K56*$Z$8+$L56*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P56" s="43" t="str">
-        <f aca="false">IF(OR($O56="",$M56=""),"",ROUND($O56*$M56,1))</f>
-        <v/>
-      </c>
-      <c r="Q56" s="44" t="str">
-        <f aca="false">IF($E56="","",IF(OR($O56="",$M56=""),"NOT SCORED",IF($P56&gt;=$Z$11,"CRITICAL",IF($P56&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R56" s="45" t="str">
-        <f aca="false">IF($O56="","",INDEX($Y$15:$Y$19,MATCH(MAX($H56:$L56),$H56:$L56,0)))</f>
-        <v/>
-      </c>
-      <c r="S56" s="40"/>
-      <c r="T56" s="46"/>
-      <c r="U56" s="47" t="str">
-        <f aca="false">IF($E56="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E56),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V56" s="42" t="str">
-        <f aca="false">IF($E56="","",IF(ISNUMBER($U56),ROUND(6-$U56,1),""))</f>
-        <v/>
-      </c>
-      <c r="W56" s="48" t="str">
-        <f aca="false">IF($E56="","",COUNTIF('Score Log'!$C$4:$C$203,$E56))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="38"/>
-      <c r="B57" s="39"/>
-      <c r="C57" s="40"/>
-      <c r="D57" s="39"/>
-      <c r="E57" s="38"/>
-      <c r="F57" s="41"/>
-      <c r="G57" s="41"/>
-      <c r="H57" s="39"/>
-      <c r="I57" s="39"/>
-      <c r="J57" s="39"/>
-      <c r="K57" s="39"/>
-      <c r="L57" s="39"/>
-      <c r="M57" s="39"/>
-      <c r="N57" s="38"/>
-      <c r="O57" s="42" t="str">
-        <f aca="false">IF(COUNT($H57:$L57)&lt;5,"",ROUND($H57*$Z$5+$I57*$Z$6+$J57*$Z$7+$K57*$Z$8+$L57*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P57" s="43" t="str">
-        <f aca="false">IF(OR($O57="",$M57=""),"",ROUND($O57*$M57,1))</f>
-        <v/>
-      </c>
-      <c r="Q57" s="44" t="str">
-        <f aca="false">IF($E57="","",IF(OR($O57="",$M57=""),"NOT SCORED",IF($P57&gt;=$Z$11,"CRITICAL",IF($P57&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R57" s="45" t="str">
-        <f aca="false">IF($O57="","",INDEX($Y$15:$Y$19,MATCH(MAX($H57:$L57),$H57:$L57,0)))</f>
-        <v/>
-      </c>
-      <c r="S57" s="40"/>
-      <c r="T57" s="46"/>
-      <c r="U57" s="47" t="str">
-        <f aca="false">IF($E57="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E57),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V57" s="42" t="str">
-        <f aca="false">IF($E57="","",IF(ISNUMBER($U57),ROUND(6-$U57,1),""))</f>
-        <v/>
-      </c>
-      <c r="W57" s="48" t="str">
-        <f aca="false">IF($E57="","",COUNTIF('Score Log'!$C$4:$C$203,$E57))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="38"/>
-      <c r="B58" s="39"/>
-      <c r="C58" s="40"/>
-      <c r="D58" s="39"/>
-      <c r="E58" s="38"/>
-      <c r="F58" s="41"/>
-      <c r="G58" s="41"/>
-      <c r="H58" s="39"/>
-      <c r="I58" s="39"/>
-      <c r="J58" s="39"/>
-      <c r="K58" s="39"/>
-      <c r="L58" s="39"/>
-      <c r="M58" s="39"/>
-      <c r="N58" s="38"/>
-      <c r="O58" s="42" t="str">
-        <f aca="false">IF(COUNT($H58:$L58)&lt;5,"",ROUND($H58*$Z$5+$I58*$Z$6+$J58*$Z$7+$K58*$Z$8+$L58*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P58" s="43" t="str">
-        <f aca="false">IF(OR($O58="",$M58=""),"",ROUND($O58*$M58,1))</f>
-        <v/>
-      </c>
-      <c r="Q58" s="44" t="str">
-        <f aca="false">IF($E58="","",IF(OR($O58="",$M58=""),"NOT SCORED",IF($P58&gt;=$Z$11,"CRITICAL",IF($P58&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R58" s="45" t="str">
-        <f aca="false">IF($O58="","",INDEX($Y$15:$Y$19,MATCH(MAX($H58:$L58),$H58:$L58,0)))</f>
-        <v/>
-      </c>
-      <c r="S58" s="40"/>
-      <c r="T58" s="46"/>
-      <c r="U58" s="47" t="str">
-        <f aca="false">IF($E58="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E58),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V58" s="42" t="str">
-        <f aca="false">IF($E58="","",IF(ISNUMBER($U58),ROUND(6-$U58,1),""))</f>
-        <v/>
-      </c>
-      <c r="W58" s="48" t="str">
-        <f aca="false">IF($E58="","",COUNTIF('Score Log'!$C$4:$C$203,$E58))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="38"/>
-      <c r="B59" s="39"/>
-      <c r="C59" s="40"/>
-      <c r="D59" s="39"/>
-      <c r="E59" s="38"/>
-      <c r="F59" s="41"/>
-      <c r="G59" s="41"/>
-      <c r="H59" s="39"/>
-      <c r="I59" s="39"/>
-      <c r="J59" s="39"/>
-      <c r="K59" s="39"/>
-      <c r="L59" s="39"/>
-      <c r="M59" s="39"/>
-      <c r="N59" s="38"/>
-      <c r="O59" s="42" t="str">
-        <f aca="false">IF(COUNT($H59:$L59)&lt;5,"",ROUND($H59*$Z$5+$I59*$Z$6+$J59*$Z$7+$K59*$Z$8+$L59*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P59" s="43" t="str">
-        <f aca="false">IF(OR($O59="",$M59=""),"",ROUND($O59*$M59,1))</f>
-        <v/>
-      </c>
-      <c r="Q59" s="44" t="str">
-        <f aca="false">IF($E59="","",IF(OR($O59="",$M59=""),"NOT SCORED",IF($P59&gt;=$Z$11,"CRITICAL",IF($P59&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R59" s="45" t="str">
-        <f aca="false">IF($O59="","",INDEX($Y$15:$Y$19,MATCH(MAX($H59:$L59),$H59:$L59,0)))</f>
-        <v/>
-      </c>
-      <c r="S59" s="40"/>
-      <c r="T59" s="46"/>
-      <c r="U59" s="47" t="str">
-        <f aca="false">IF($E59="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E59),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V59" s="42" t="str">
-        <f aca="false">IF($E59="","",IF(ISNUMBER($U59),ROUND(6-$U59,1),""))</f>
-        <v/>
-      </c>
-      <c r="W59" s="48" t="str">
-        <f aca="false">IF($E59="","",COUNTIF('Score Log'!$C$4:$C$203,$E59))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="38"/>
-      <c r="B60" s="39"/>
-      <c r="C60" s="40"/>
-      <c r="D60" s="39"/>
-      <c r="E60" s="38"/>
-      <c r="F60" s="41"/>
-      <c r="G60" s="41"/>
-      <c r="H60" s="39"/>
-      <c r="I60" s="39"/>
-      <c r="J60" s="39"/>
-      <c r="K60" s="39"/>
-      <c r="L60" s="39"/>
-      <c r="M60" s="39"/>
-      <c r="N60" s="38"/>
-      <c r="O60" s="42" t="str">
-        <f aca="false">IF(COUNT($H60:$L60)&lt;5,"",ROUND($H60*$Z$5+$I60*$Z$6+$J60*$Z$7+$K60*$Z$8+$L60*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P60" s="43" t="str">
-        <f aca="false">IF(OR($O60="",$M60=""),"",ROUND($O60*$M60,1))</f>
-        <v/>
-      </c>
-      <c r="Q60" s="44" t="str">
-        <f aca="false">IF($E60="","",IF(OR($O60="",$M60=""),"NOT SCORED",IF($P60&gt;=$Z$11,"CRITICAL",IF($P60&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R60" s="45" t="str">
-        <f aca="false">IF($O60="","",INDEX($Y$15:$Y$19,MATCH(MAX($H60:$L60),$H60:$L60,0)))</f>
-        <v/>
-      </c>
-      <c r="S60" s="40"/>
-      <c r="T60" s="46"/>
-      <c r="U60" s="47" t="str">
-        <f aca="false">IF($E60="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E60),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V60" s="42" t="str">
-        <f aca="false">IF($E60="","",IF(ISNUMBER($U60),ROUND(6-$U60,1),""))</f>
-        <v/>
-      </c>
-      <c r="W60" s="48" t="str">
-        <f aca="false">IF($E60="","",COUNTIF('Score Log'!$C$4:$C$203,$E60))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="38"/>
-      <c r="B61" s="39"/>
-      <c r="C61" s="40"/>
-      <c r="D61" s="39"/>
-      <c r="E61" s="38"/>
-      <c r="F61" s="41"/>
-      <c r="G61" s="41"/>
-      <c r="H61" s="39"/>
-      <c r="I61" s="39"/>
-      <c r="J61" s="39"/>
-      <c r="K61" s="39"/>
-      <c r="L61" s="39"/>
-      <c r="M61" s="39"/>
-      <c r="N61" s="38"/>
-      <c r="O61" s="42" t="str">
-        <f aca="false">IF(COUNT($H61:$L61)&lt;5,"",ROUND($H61*$Z$5+$I61*$Z$6+$J61*$Z$7+$K61*$Z$8+$L61*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P61" s="43" t="str">
-        <f aca="false">IF(OR($O61="",$M61=""),"",ROUND($O61*$M61,1))</f>
-        <v/>
-      </c>
-      <c r="Q61" s="44" t="str">
-        <f aca="false">IF($E61="","",IF(OR($O61="",$M61=""),"NOT SCORED",IF($P61&gt;=$Z$11,"CRITICAL",IF($P61&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R61" s="45" t="str">
-        <f aca="false">IF($O61="","",INDEX($Y$15:$Y$19,MATCH(MAX($H61:$L61),$H61:$L61,0)))</f>
-        <v/>
-      </c>
-      <c r="S61" s="40"/>
-      <c r="T61" s="46"/>
-      <c r="U61" s="47" t="str">
-        <f aca="false">IF($E61="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E61),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V61" s="42" t="str">
-        <f aca="false">IF($E61="","",IF(ISNUMBER($U61),ROUND(6-$U61,1),""))</f>
-        <v/>
-      </c>
-      <c r="W61" s="48" t="str">
-        <f aca="false">IF($E61="","",COUNTIF('Score Log'!$C$4:$C$203,$E61))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="38"/>
-      <c r="B62" s="39"/>
-      <c r="C62" s="40"/>
-      <c r="D62" s="39"/>
-      <c r="E62" s="38"/>
-      <c r="F62" s="41"/>
-      <c r="G62" s="41"/>
-      <c r="H62" s="39"/>
-      <c r="I62" s="39"/>
-      <c r="J62" s="39"/>
-      <c r="K62" s="39"/>
-      <c r="L62" s="39"/>
-      <c r="M62" s="39"/>
-      <c r="N62" s="38"/>
-      <c r="O62" s="42" t="str">
-        <f aca="false">IF(COUNT($H62:$L62)&lt;5,"",ROUND($H62*$Z$5+$I62*$Z$6+$J62*$Z$7+$K62*$Z$8+$L62*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P62" s="43" t="str">
-        <f aca="false">IF(OR($O62="",$M62=""),"",ROUND($O62*$M62,1))</f>
-        <v/>
-      </c>
-      <c r="Q62" s="44" t="str">
-        <f aca="false">IF($E62="","",IF(OR($O62="",$M62=""),"NOT SCORED",IF($P62&gt;=$Z$11,"CRITICAL",IF($P62&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R62" s="45" t="str">
-        <f aca="false">IF($O62="","",INDEX($Y$15:$Y$19,MATCH(MAX($H62:$L62),$H62:$L62,0)))</f>
-        <v/>
-      </c>
-      <c r="S62" s="40"/>
-      <c r="T62" s="46"/>
-      <c r="U62" s="47" t="str">
-        <f aca="false">IF($E62="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E62),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V62" s="42" t="str">
-        <f aca="false">IF($E62="","",IF(ISNUMBER($U62),ROUND(6-$U62,1),""))</f>
-        <v/>
-      </c>
-      <c r="W62" s="48" t="str">
-        <f aca="false">IF($E62="","",COUNTIF('Score Log'!$C$4:$C$203,$E62))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="38"/>
-      <c r="B63" s="39"/>
-      <c r="C63" s="40"/>
-      <c r="D63" s="39"/>
-      <c r="E63" s="38"/>
-      <c r="F63" s="41"/>
-      <c r="G63" s="41"/>
-      <c r="H63" s="39"/>
-      <c r="I63" s="39"/>
-      <c r="J63" s="39"/>
-      <c r="K63" s="39"/>
-      <c r="L63" s="39"/>
-      <c r="M63" s="39"/>
-      <c r="N63" s="38"/>
-      <c r="O63" s="42" t="str">
-        <f aca="false">IF(COUNT($H63:$L63)&lt;5,"",ROUND($H63*$Z$5+$I63*$Z$6+$J63*$Z$7+$K63*$Z$8+$L63*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P63" s="43" t="str">
-        <f aca="false">IF(OR($O63="",$M63=""),"",ROUND($O63*$M63,1))</f>
-        <v/>
-      </c>
-      <c r="Q63" s="44" t="str">
-        <f aca="false">IF($E63="","",IF(OR($O63="",$M63=""),"NOT SCORED",IF($P63&gt;=$Z$11,"CRITICAL",IF($P63&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R63" s="45" t="str">
-        <f aca="false">IF($O63="","",INDEX($Y$15:$Y$19,MATCH(MAX($H63:$L63),$H63:$L63,0)))</f>
-        <v/>
-      </c>
-      <c r="S63" s="40"/>
-      <c r="T63" s="46"/>
-      <c r="U63" s="47" t="str">
-        <f aca="false">IF($E63="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E63),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V63" s="42" t="str">
-        <f aca="false">IF($E63="","",IF(ISNUMBER($U63),ROUND(6-$U63,1),""))</f>
-        <v/>
-      </c>
-      <c r="W63" s="48" t="str">
-        <f aca="false">IF($E63="","",COUNTIF('Score Log'!$C$4:$C$203,$E63))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="38"/>
-      <c r="B64" s="39"/>
-      <c r="C64" s="40"/>
-      <c r="D64" s="39"/>
-      <c r="E64" s="38"/>
-      <c r="F64" s="41"/>
-      <c r="G64" s="41"/>
-      <c r="H64" s="39"/>
-      <c r="I64" s="39"/>
-      <c r="J64" s="39"/>
-      <c r="K64" s="39"/>
-      <c r="L64" s="39"/>
-      <c r="M64" s="39"/>
-      <c r="N64" s="38"/>
-      <c r="O64" s="42" t="str">
-        <f aca="false">IF(COUNT($H64:$L64)&lt;5,"",ROUND($H64*$Z$5+$I64*$Z$6+$J64*$Z$7+$K64*$Z$8+$L64*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P64" s="43" t="str">
-        <f aca="false">IF(OR($O64="",$M64=""),"",ROUND($O64*$M64,1))</f>
-        <v/>
-      </c>
-      <c r="Q64" s="44" t="str">
-        <f aca="false">IF($E64="","",IF(OR($O64="",$M64=""),"NOT SCORED",IF($P64&gt;=$Z$11,"CRITICAL",IF($P64&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R64" s="45" t="str">
-        <f aca="false">IF($O64="","",INDEX($Y$15:$Y$19,MATCH(MAX($H64:$L64),$H64:$L64,0)))</f>
-        <v/>
-      </c>
-      <c r="S64" s="40"/>
-      <c r="T64" s="46"/>
-      <c r="U64" s="47" t="str">
-        <f aca="false">IF($E64="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E64),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V64" s="42" t="str">
-        <f aca="false">IF($E64="","",IF(ISNUMBER($U64),ROUND(6-$U64,1),""))</f>
-        <v/>
-      </c>
-      <c r="W64" s="48" t="str">
-        <f aca="false">IF($E64="","",COUNTIF('Score Log'!$C$4:$C$203,$E64))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="38"/>
-      <c r="B65" s="39"/>
-      <c r="C65" s="40"/>
-      <c r="D65" s="39"/>
-      <c r="E65" s="38"/>
-      <c r="F65" s="41"/>
-      <c r="G65" s="41"/>
-      <c r="H65" s="39"/>
-      <c r="I65" s="39"/>
-      <c r="J65" s="39"/>
-      <c r="K65" s="39"/>
-      <c r="L65" s="39"/>
-      <c r="M65" s="39"/>
-      <c r="N65" s="38"/>
-      <c r="O65" s="42" t="str">
-        <f aca="false">IF(COUNT($H65:$L65)&lt;5,"",ROUND($H65*$Z$5+$I65*$Z$6+$J65*$Z$7+$K65*$Z$8+$L65*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P65" s="43" t="str">
-        <f aca="false">IF(OR($O65="",$M65=""),"",ROUND($O65*$M65,1))</f>
-        <v/>
-      </c>
-      <c r="Q65" s="44" t="str">
-        <f aca="false">IF($E65="","",IF(OR($O65="",$M65=""),"NOT SCORED",IF($P65&gt;=$Z$11,"CRITICAL",IF($P65&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R65" s="45" t="str">
-        <f aca="false">IF($O65="","",INDEX($Y$15:$Y$19,MATCH(MAX($H65:$L65),$H65:$L65,0)))</f>
-        <v/>
-      </c>
-      <c r="S65" s="40"/>
-      <c r="T65" s="46"/>
-      <c r="U65" s="47" t="str">
-        <f aca="false">IF($E65="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E65),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V65" s="42" t="str">
-        <f aca="false">IF($E65="","",IF(ISNUMBER($U65),ROUND(6-$U65,1),""))</f>
-        <v/>
-      </c>
-      <c r="W65" s="48" t="str">
-        <f aca="false">IF($E65="","",COUNTIF('Score Log'!$C$4:$C$203,$E65))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="38"/>
-      <c r="B66" s="39"/>
-      <c r="C66" s="40"/>
-      <c r="D66" s="39"/>
-      <c r="E66" s="38"/>
-      <c r="F66" s="41"/>
-      <c r="G66" s="41"/>
-      <c r="H66" s="39"/>
-      <c r="I66" s="39"/>
-      <c r="J66" s="39"/>
-      <c r="K66" s="39"/>
-      <c r="L66" s="39"/>
-      <c r="M66" s="39"/>
-      <c r="N66" s="38"/>
-      <c r="O66" s="42" t="str">
-        <f aca="false">IF(COUNT($H66:$L66)&lt;5,"",ROUND($H66*$Z$5+$I66*$Z$6+$J66*$Z$7+$K66*$Z$8+$L66*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P66" s="43" t="str">
-        <f aca="false">IF(OR($O66="",$M66=""),"",ROUND($O66*$M66,1))</f>
-        <v/>
-      </c>
-      <c r="Q66" s="44" t="str">
-        <f aca="false">IF($E66="","",IF(OR($O66="",$M66=""),"NOT SCORED",IF($P66&gt;=$Z$11,"CRITICAL",IF($P66&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R66" s="45" t="str">
-        <f aca="false">IF($O66="","",INDEX($Y$15:$Y$19,MATCH(MAX($H66:$L66),$H66:$L66,0)))</f>
-        <v/>
-      </c>
-      <c r="S66" s="40"/>
-      <c r="T66" s="46"/>
-      <c r="U66" s="47" t="str">
-        <f aca="false">IF($E66="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E66),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V66" s="42" t="str">
-        <f aca="false">IF($E66="","",IF(ISNUMBER($U66),ROUND(6-$U66,1),""))</f>
-        <v/>
-      </c>
-      <c r="W66" s="48" t="str">
-        <f aca="false">IF($E66="","",COUNTIF('Score Log'!$C$4:$C$203,$E66))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="38"/>
-      <c r="B67" s="39"/>
-      <c r="C67" s="40"/>
-      <c r="D67" s="39"/>
-      <c r="E67" s="38"/>
-      <c r="F67" s="41"/>
-      <c r="G67" s="41"/>
-      <c r="H67" s="39"/>
-      <c r="I67" s="39"/>
-      <c r="J67" s="39"/>
-      <c r="K67" s="39"/>
-      <c r="L67" s="39"/>
-      <c r="M67" s="39"/>
-      <c r="N67" s="38"/>
-      <c r="O67" s="42" t="str">
-        <f aca="false">IF(COUNT($H67:$L67)&lt;5,"",ROUND($H67*$Z$5+$I67*$Z$6+$J67*$Z$7+$K67*$Z$8+$L67*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P67" s="43" t="str">
-        <f aca="false">IF(OR($O67="",$M67=""),"",ROUND($O67*$M67,1))</f>
-        <v/>
-      </c>
-      <c r="Q67" s="44" t="str">
-        <f aca="false">IF($E67="","",IF(OR($O67="",$M67=""),"NOT SCORED",IF($P67&gt;=$Z$11,"CRITICAL",IF($P67&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R67" s="45" t="str">
-        <f aca="false">IF($O67="","",INDEX($Y$15:$Y$19,MATCH(MAX($H67:$L67),$H67:$L67,0)))</f>
-        <v/>
-      </c>
-      <c r="S67" s="40"/>
-      <c r="T67" s="46"/>
-      <c r="U67" s="47" t="str">
-        <f aca="false">IF($E67="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E67),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V67" s="42" t="str">
-        <f aca="false">IF($E67="","",IF(ISNUMBER($U67),ROUND(6-$U67,1),""))</f>
-        <v/>
-      </c>
-      <c r="W67" s="48" t="str">
-        <f aca="false">IF($E67="","",COUNTIF('Score Log'!$C$4:$C$203,$E67))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="38"/>
-      <c r="B68" s="39"/>
-      <c r="C68" s="40"/>
-      <c r="D68" s="39"/>
-      <c r="E68" s="38"/>
-      <c r="F68" s="41"/>
-      <c r="G68" s="41"/>
-      <c r="H68" s="39"/>
-      <c r="I68" s="39"/>
-      <c r="J68" s="39"/>
-      <c r="K68" s="39"/>
-      <c r="L68" s="39"/>
-      <c r="M68" s="39"/>
-      <c r="N68" s="38"/>
-      <c r="O68" s="42" t="str">
-        <f aca="false">IF(COUNT($H68:$L68)&lt;5,"",ROUND($H68*$Z$5+$I68*$Z$6+$J68*$Z$7+$K68*$Z$8+$L68*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P68" s="43" t="str">
-        <f aca="false">IF(OR($O68="",$M68=""),"",ROUND($O68*$M68,1))</f>
-        <v/>
-      </c>
-      <c r="Q68" s="44" t="str">
-        <f aca="false">IF($E68="","",IF(OR($O68="",$M68=""),"NOT SCORED",IF($P68&gt;=$Z$11,"CRITICAL",IF($P68&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R68" s="45" t="str">
-        <f aca="false">IF($O68="","",INDEX($Y$15:$Y$19,MATCH(MAX($H68:$L68),$H68:$L68,0)))</f>
-        <v/>
-      </c>
-      <c r="S68" s="40"/>
-      <c r="T68" s="46"/>
-      <c r="U68" s="47" t="str">
-        <f aca="false">IF($E68="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E68),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V68" s="42" t="str">
-        <f aca="false">IF($E68="","",IF(ISNUMBER($U68),ROUND(6-$U68,1),""))</f>
-        <v/>
-      </c>
-      <c r="W68" s="48" t="str">
-        <f aca="false">IF($E68="","",COUNTIF('Score Log'!$C$4:$C$203,$E68))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="38"/>
-      <c r="B69" s="39"/>
-      <c r="C69" s="40"/>
-      <c r="D69" s="39"/>
-      <c r="E69" s="38"/>
-      <c r="F69" s="41"/>
-      <c r="G69" s="41"/>
-      <c r="H69" s="39"/>
-      <c r="I69" s="39"/>
-      <c r="J69" s="39"/>
-      <c r="K69" s="39"/>
-      <c r="L69" s="39"/>
-      <c r="M69" s="39"/>
-      <c r="N69" s="38"/>
-      <c r="O69" s="42" t="str">
-        <f aca="false">IF(COUNT($H69:$L69)&lt;5,"",ROUND($H69*$Z$5+$I69*$Z$6+$J69*$Z$7+$K69*$Z$8+$L69*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P69" s="43" t="str">
-        <f aca="false">IF(OR($O69="",$M69=""),"",ROUND($O69*$M69,1))</f>
-        <v/>
-      </c>
-      <c r="Q69" s="44" t="str">
-        <f aca="false">IF($E69="","",IF(OR($O69="",$M69=""),"NOT SCORED",IF($P69&gt;=$Z$11,"CRITICAL",IF($P69&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R69" s="45" t="str">
-        <f aca="false">IF($O69="","",INDEX($Y$15:$Y$19,MATCH(MAX($H69:$L69),$H69:$L69,0)))</f>
-        <v/>
-      </c>
-      <c r="S69" s="40"/>
-      <c r="T69" s="46"/>
-      <c r="U69" s="47" t="str">
-        <f aca="false">IF($E69="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E69),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V69" s="42" t="str">
-        <f aca="false">IF($E69="","",IF(ISNUMBER($U69),ROUND(6-$U69,1),""))</f>
-        <v/>
-      </c>
-      <c r="W69" s="48" t="str">
-        <f aca="false">IF($E69="","",COUNTIF('Score Log'!$C$4:$C$203,$E69))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="38"/>
-      <c r="B70" s="39"/>
-      <c r="C70" s="40"/>
-      <c r="D70" s="39"/>
-      <c r="E70" s="38"/>
-      <c r="F70" s="41"/>
-      <c r="G70" s="41"/>
-      <c r="H70" s="39"/>
-      <c r="I70" s="39"/>
-      <c r="J70" s="39"/>
-      <c r="K70" s="39"/>
-      <c r="L70" s="39"/>
-      <c r="M70" s="39"/>
-      <c r="N70" s="38"/>
-      <c r="O70" s="42" t="str">
-        <f aca="false">IF(COUNT($H70:$L70)&lt;5,"",ROUND($H70*$Z$5+$I70*$Z$6+$J70*$Z$7+$K70*$Z$8+$L70*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P70" s="43" t="str">
-        <f aca="false">IF(OR($O70="",$M70=""),"",ROUND($O70*$M70,1))</f>
-        <v/>
-      </c>
-      <c r="Q70" s="44" t="str">
-        <f aca="false">IF($E70="","",IF(OR($O70="",$M70=""),"NOT SCORED",IF($P70&gt;=$Z$11,"CRITICAL",IF($P70&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R70" s="45" t="str">
-        <f aca="false">IF($O70="","",INDEX($Y$15:$Y$19,MATCH(MAX($H70:$L70),$H70:$L70,0)))</f>
-        <v/>
-      </c>
-      <c r="S70" s="40"/>
-      <c r="T70" s="46"/>
-      <c r="U70" s="47" t="str">
-        <f aca="false">IF($E70="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E70),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V70" s="42" t="str">
-        <f aca="false">IF($E70="","",IF(ISNUMBER($U70),ROUND(6-$U70,1),""))</f>
-        <v/>
-      </c>
-      <c r="W70" s="48" t="str">
-        <f aca="false">IF($E70="","",COUNTIF('Score Log'!$C$4:$C$203,$E70))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="38"/>
-      <c r="B71" s="39"/>
-      <c r="C71" s="40"/>
-      <c r="D71" s="39"/>
-      <c r="E71" s="38"/>
-      <c r="F71" s="41"/>
-      <c r="G71" s="41"/>
-      <c r="H71" s="39"/>
-      <c r="I71" s="39"/>
-      <c r="J71" s="39"/>
-      <c r="K71" s="39"/>
-      <c r="L71" s="39"/>
-      <c r="M71" s="39"/>
-      <c r="N71" s="38"/>
-      <c r="O71" s="42" t="str">
-        <f aca="false">IF(COUNT($H71:$L71)&lt;5,"",ROUND($H71*$Z$5+$I71*$Z$6+$J71*$Z$7+$K71*$Z$8+$L71*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P71" s="43" t="str">
-        <f aca="false">IF(OR($O71="",$M71=""),"",ROUND($O71*$M71,1))</f>
-        <v/>
-      </c>
-      <c r="Q71" s="44" t="str">
-        <f aca="false">IF($E71="","",IF(OR($O71="",$M71=""),"NOT SCORED",IF($P71&gt;=$Z$11,"CRITICAL",IF($P71&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R71" s="45" t="str">
-        <f aca="false">IF($O71="","",INDEX($Y$15:$Y$19,MATCH(MAX($H71:$L71),$H71:$L71,0)))</f>
-        <v/>
-      </c>
-      <c r="S71" s="40"/>
-      <c r="T71" s="46"/>
-      <c r="U71" s="47" t="str">
-        <f aca="false">IF($E71="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E71),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V71" s="42" t="str">
-        <f aca="false">IF($E71="","",IF(ISNUMBER($U71),ROUND(6-$U71,1),""))</f>
-        <v/>
-      </c>
-      <c r="W71" s="48" t="str">
-        <f aca="false">IF($E71="","",COUNTIF('Score Log'!$C$4:$C$203,$E71))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="38"/>
-      <c r="B72" s="39"/>
-      <c r="C72" s="40"/>
-      <c r="D72" s="39"/>
-      <c r="E72" s="38"/>
-      <c r="F72" s="41"/>
-      <c r="G72" s="41"/>
-      <c r="H72" s="39"/>
-      <c r="I72" s="39"/>
-      <c r="J72" s="39"/>
-      <c r="K72" s="39"/>
-      <c r="L72" s="39"/>
-      <c r="M72" s="39"/>
-      <c r="N72" s="38"/>
-      <c r="O72" s="42" t="str">
-        <f aca="false">IF(COUNT($H72:$L72)&lt;5,"",ROUND($H72*$Z$5+$I72*$Z$6+$J72*$Z$7+$K72*$Z$8+$L72*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P72" s="43" t="str">
-        <f aca="false">IF(OR($O72="",$M72=""),"",ROUND($O72*$M72,1))</f>
-        <v/>
-      </c>
-      <c r="Q72" s="44" t="str">
-        <f aca="false">IF($E72="","",IF(OR($O72="",$M72=""),"NOT SCORED",IF($P72&gt;=$Z$11,"CRITICAL",IF($P72&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R72" s="45" t="str">
-        <f aca="false">IF($O72="","",INDEX($Y$15:$Y$19,MATCH(MAX($H72:$L72),$H72:$L72,0)))</f>
-        <v/>
-      </c>
-      <c r="S72" s="40"/>
-      <c r="T72" s="46"/>
-      <c r="U72" s="47" t="str">
-        <f aca="false">IF($E72="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E72),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V72" s="42" t="str">
-        <f aca="false">IF($E72="","",IF(ISNUMBER($U72),ROUND(6-$U72,1),""))</f>
-        <v/>
-      </c>
-      <c r="W72" s="48" t="str">
-        <f aca="false">IF($E72="","",COUNTIF('Score Log'!$C$4:$C$203,$E72))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="38"/>
-      <c r="B73" s="39"/>
-      <c r="C73" s="40"/>
-      <c r="D73" s="39"/>
-      <c r="E73" s="38"/>
-      <c r="F73" s="41"/>
-      <c r="G73" s="41"/>
-      <c r="H73" s="39"/>
-      <c r="I73" s="39"/>
-      <c r="J73" s="39"/>
-      <c r="K73" s="39"/>
-      <c r="L73" s="39"/>
-      <c r="M73" s="39"/>
-      <c r="N73" s="38"/>
-      <c r="O73" s="42" t="str">
-        <f aca="false">IF(COUNT($H73:$L73)&lt;5,"",ROUND($H73*$Z$5+$I73*$Z$6+$J73*$Z$7+$K73*$Z$8+$L73*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P73" s="43" t="str">
-        <f aca="false">IF(OR($O73="",$M73=""),"",ROUND($O73*$M73,1))</f>
-        <v/>
-      </c>
-      <c r="Q73" s="44" t="str">
-        <f aca="false">IF($E73="","",IF(OR($O73="",$M73=""),"NOT SCORED",IF($P73&gt;=$Z$11,"CRITICAL",IF($P73&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R73" s="45" t="str">
-        <f aca="false">IF($O73="","",INDEX($Y$15:$Y$19,MATCH(MAX($H73:$L73),$H73:$L73,0)))</f>
-        <v/>
-      </c>
-      <c r="S73" s="40"/>
-      <c r="T73" s="46"/>
-      <c r="U73" s="47" t="str">
-        <f aca="false">IF($E73="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E73),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V73" s="42" t="str">
-        <f aca="false">IF($E73="","",IF(ISNUMBER($U73),ROUND(6-$U73,1),""))</f>
-        <v/>
-      </c>
-      <c r="W73" s="48" t="str">
-        <f aca="false">IF($E73="","",COUNTIF('Score Log'!$C$4:$C$203,$E73))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="38"/>
-      <c r="B74" s="39"/>
-      <c r="C74" s="40"/>
-      <c r="D74" s="39"/>
-      <c r="E74" s="38"/>
-      <c r="F74" s="41"/>
-      <c r="G74" s="41"/>
-      <c r="H74" s="39"/>
-      <c r="I74" s="39"/>
-      <c r="J74" s="39"/>
-      <c r="K74" s="39"/>
-      <c r="L74" s="39"/>
-      <c r="M74" s="39"/>
-      <c r="N74" s="38"/>
-      <c r="O74" s="42" t="str">
-        <f aca="false">IF(COUNT($H74:$L74)&lt;5,"",ROUND($H74*$Z$5+$I74*$Z$6+$J74*$Z$7+$K74*$Z$8+$L74*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P74" s="43" t="str">
-        <f aca="false">IF(OR($O74="",$M74=""),"",ROUND($O74*$M74,1))</f>
-        <v/>
-      </c>
-      <c r="Q74" s="44" t="str">
-        <f aca="false">IF($E74="","",IF(OR($O74="",$M74=""),"NOT SCORED",IF($P74&gt;=$Z$11,"CRITICAL",IF($P74&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R74" s="45" t="str">
-        <f aca="false">IF($O74="","",INDEX($Y$15:$Y$19,MATCH(MAX($H74:$L74),$H74:$L74,0)))</f>
-        <v/>
-      </c>
-      <c r="S74" s="40"/>
-      <c r="T74" s="46"/>
-      <c r="U74" s="47" t="str">
-        <f aca="false">IF($E74="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E74),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V74" s="42" t="str">
-        <f aca="false">IF($E74="","",IF(ISNUMBER($U74),ROUND(6-$U74,1),""))</f>
-        <v/>
-      </c>
-      <c r="W74" s="48" t="str">
-        <f aca="false">IF($E74="","",COUNTIF('Score Log'!$C$4:$C$203,$E74))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="38"/>
-      <c r="B75" s="39"/>
-      <c r="C75" s="40"/>
-      <c r="D75" s="39"/>
-      <c r="E75" s="38"/>
-      <c r="F75" s="41"/>
-      <c r="G75" s="41"/>
-      <c r="H75" s="39"/>
-      <c r="I75" s="39"/>
-      <c r="J75" s="39"/>
-      <c r="K75" s="39"/>
-      <c r="L75" s="39"/>
-      <c r="M75" s="39"/>
-      <c r="N75" s="38"/>
-      <c r="O75" s="42" t="str">
-        <f aca="false">IF(COUNT($H75:$L75)&lt;5,"",ROUND($H75*$Z$5+$I75*$Z$6+$J75*$Z$7+$K75*$Z$8+$L75*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P75" s="43" t="str">
-        <f aca="false">IF(OR($O75="",$M75=""),"",ROUND($O75*$M75,1))</f>
-        <v/>
-      </c>
-      <c r="Q75" s="44" t="str">
-        <f aca="false">IF($E75="","",IF(OR($O75="",$M75=""),"NOT SCORED",IF($P75&gt;=$Z$11,"CRITICAL",IF($P75&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R75" s="45" t="str">
-        <f aca="false">IF($O75="","",INDEX($Y$15:$Y$19,MATCH(MAX($H75:$L75),$H75:$L75,0)))</f>
-        <v/>
-      </c>
-      <c r="S75" s="40"/>
-      <c r="T75" s="46"/>
-      <c r="U75" s="47" t="str">
-        <f aca="false">IF($E75="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E75),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V75" s="42" t="str">
-        <f aca="false">IF($E75="","",IF(ISNUMBER($U75),ROUND(6-$U75,1),""))</f>
-        <v/>
-      </c>
-      <c r="W75" s="48" t="str">
-        <f aca="false">IF($E75="","",COUNTIF('Score Log'!$C$4:$C$203,$E75))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="38"/>
-      <c r="B76" s="39"/>
-      <c r="C76" s="40"/>
-      <c r="D76" s="39"/>
-      <c r="E76" s="38"/>
-      <c r="F76" s="41"/>
-      <c r="G76" s="41"/>
-      <c r="H76" s="39"/>
-      <c r="I76" s="39"/>
-      <c r="J76" s="39"/>
-      <c r="K76" s="39"/>
-      <c r="L76" s="39"/>
-      <c r="M76" s="39"/>
-      <c r="N76" s="38"/>
-      <c r="O76" s="42" t="str">
-        <f aca="false">IF(COUNT($H76:$L76)&lt;5,"",ROUND($H76*$Z$5+$I76*$Z$6+$J76*$Z$7+$K76*$Z$8+$L76*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P76" s="43" t="str">
-        <f aca="false">IF(OR($O76="",$M76=""),"",ROUND($O76*$M76,1))</f>
-        <v/>
-      </c>
-      <c r="Q76" s="44" t="str">
-        <f aca="false">IF($E76="","",IF(OR($O76="",$M76=""),"NOT SCORED",IF($P76&gt;=$Z$11,"CRITICAL",IF($P76&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R76" s="45" t="str">
-        <f aca="false">IF($O76="","",INDEX($Y$15:$Y$19,MATCH(MAX($H76:$L76),$H76:$L76,0)))</f>
-        <v/>
-      </c>
-      <c r="S76" s="40"/>
-      <c r="T76" s="46"/>
-      <c r="U76" s="47" t="str">
-        <f aca="false">IF($E76="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E76),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V76" s="42" t="str">
-        <f aca="false">IF($E76="","",IF(ISNUMBER($U76),ROUND(6-$U76,1),""))</f>
-        <v/>
-      </c>
-      <c r="W76" s="48" t="str">
-        <f aca="false">IF($E76="","",COUNTIF('Score Log'!$C$4:$C$203,$E76))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="38"/>
-      <c r="B77" s="39"/>
-      <c r="C77" s="40"/>
-      <c r="D77" s="39"/>
-      <c r="E77" s="38"/>
-      <c r="F77" s="41"/>
-      <c r="G77" s="41"/>
-      <c r="H77" s="39"/>
-      <c r="I77" s="39"/>
-      <c r="J77" s="39"/>
-      <c r="K77" s="39"/>
-      <c r="L77" s="39"/>
-      <c r="M77" s="39"/>
-      <c r="N77" s="38"/>
-      <c r="O77" s="42" t="str">
-        <f aca="false">IF(COUNT($H77:$L77)&lt;5,"",ROUND($H77*$Z$5+$I77*$Z$6+$J77*$Z$7+$K77*$Z$8+$L77*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P77" s="43" t="str">
-        <f aca="false">IF(OR($O77="",$M77=""),"",ROUND($O77*$M77,1))</f>
-        <v/>
-      </c>
-      <c r="Q77" s="44" t="str">
-        <f aca="false">IF($E77="","",IF(OR($O77="",$M77=""),"NOT SCORED",IF($P77&gt;=$Z$11,"CRITICAL",IF($P77&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R77" s="45" t="str">
-        <f aca="false">IF($O77="","",INDEX($Y$15:$Y$19,MATCH(MAX($H77:$L77),$H77:$L77,0)))</f>
-        <v/>
-      </c>
-      <c r="S77" s="40"/>
-      <c r="T77" s="46"/>
-      <c r="U77" s="47" t="str">
-        <f aca="false">IF($E77="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E77),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V77" s="42" t="str">
-        <f aca="false">IF($E77="","",IF(ISNUMBER($U77),ROUND(6-$U77,1),""))</f>
-        <v/>
-      </c>
-      <c r="W77" s="48" t="str">
-        <f aca="false">IF($E77="","",COUNTIF('Score Log'!$C$4:$C$203,$E77))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="38"/>
-      <c r="B78" s="39"/>
-      <c r="C78" s="40"/>
-      <c r="D78" s="39"/>
-      <c r="E78" s="38"/>
-      <c r="F78" s="41"/>
-      <c r="G78" s="41"/>
-      <c r="H78" s="39"/>
-      <c r="I78" s="39"/>
-      <c r="J78" s="39"/>
-      <c r="K78" s="39"/>
-      <c r="L78" s="39"/>
-      <c r="M78" s="39"/>
-      <c r="N78" s="38"/>
-      <c r="O78" s="42" t="str">
-        <f aca="false">IF(COUNT($H78:$L78)&lt;5,"",ROUND($H78*$Z$5+$I78*$Z$6+$J78*$Z$7+$K78*$Z$8+$L78*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P78" s="43" t="str">
-        <f aca="false">IF(OR($O78="",$M78=""),"",ROUND($O78*$M78,1))</f>
-        <v/>
-      </c>
-      <c r="Q78" s="44" t="str">
-        <f aca="false">IF($E78="","",IF(OR($O78="",$M78=""),"NOT SCORED",IF($P78&gt;=$Z$11,"CRITICAL",IF($P78&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R78" s="45" t="str">
-        <f aca="false">IF($O78="","",INDEX($Y$15:$Y$19,MATCH(MAX($H78:$L78),$H78:$L78,0)))</f>
-        <v/>
-      </c>
-      <c r="S78" s="40"/>
-      <c r="T78" s="46"/>
-      <c r="U78" s="47" t="str">
-        <f aca="false">IF($E78="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E78),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V78" s="42" t="str">
-        <f aca="false">IF($E78="","",IF(ISNUMBER($U78),ROUND(6-$U78,1),""))</f>
-        <v/>
-      </c>
-      <c r="W78" s="48" t="str">
-        <f aca="false">IF($E78="","",COUNTIF('Score Log'!$C$4:$C$203,$E78))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="38"/>
-      <c r="B79" s="39"/>
-      <c r="C79" s="40"/>
-      <c r="D79" s="39"/>
-      <c r="E79" s="38"/>
-      <c r="F79" s="41"/>
-      <c r="G79" s="41"/>
-      <c r="H79" s="39"/>
-      <c r="I79" s="39"/>
-      <c r="J79" s="39"/>
-      <c r="K79" s="39"/>
-      <c r="L79" s="39"/>
-      <c r="M79" s="39"/>
-      <c r="N79" s="38"/>
-      <c r="O79" s="42" t="str">
-        <f aca="false">IF(COUNT($H79:$L79)&lt;5,"",ROUND($H79*$Z$5+$I79*$Z$6+$J79*$Z$7+$K79*$Z$8+$L79*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P79" s="43" t="str">
-        <f aca="false">IF(OR($O79="",$M79=""),"",ROUND($O79*$M79,1))</f>
-        <v/>
-      </c>
-      <c r="Q79" s="44" t="str">
-        <f aca="false">IF($E79="","",IF(OR($O79="",$M79=""),"NOT SCORED",IF($P79&gt;=$Z$11,"CRITICAL",IF($P79&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R79" s="45" t="str">
-        <f aca="false">IF($O79="","",INDEX($Y$15:$Y$19,MATCH(MAX($H79:$L79),$H79:$L79,0)))</f>
-        <v/>
-      </c>
-      <c r="S79" s="40"/>
-      <c r="T79" s="46"/>
-      <c r="U79" s="47" t="str">
-        <f aca="false">IF($E79="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E79),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V79" s="42" t="str">
-        <f aca="false">IF($E79="","",IF(ISNUMBER($U79),ROUND(6-$U79,1),""))</f>
-        <v/>
-      </c>
-      <c r="W79" s="48" t="str">
-        <f aca="false">IF($E79="","",COUNTIF('Score Log'!$C$4:$C$203,$E79))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="38"/>
-      <c r="B80" s="39"/>
-      <c r="C80" s="40"/>
-      <c r="D80" s="39"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="41"/>
-      <c r="G80" s="41"/>
-      <c r="H80" s="39"/>
-      <c r="I80" s="39"/>
-      <c r="J80" s="39"/>
-      <c r="K80" s="39"/>
-      <c r="L80" s="39"/>
-      <c r="M80" s="39"/>
-      <c r="N80" s="38"/>
-      <c r="O80" s="42" t="str">
-        <f aca="false">IF(COUNT($H80:$L80)&lt;5,"",ROUND($H80*$Z$5+$I80*$Z$6+$J80*$Z$7+$K80*$Z$8+$L80*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P80" s="43" t="str">
-        <f aca="false">IF(OR($O80="",$M80=""),"",ROUND($O80*$M80,1))</f>
-        <v/>
-      </c>
-      <c r="Q80" s="44" t="str">
-        <f aca="false">IF($E80="","",IF(OR($O80="",$M80=""),"NOT SCORED",IF($P80&gt;=$Z$11,"CRITICAL",IF($P80&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R80" s="45" t="str">
-        <f aca="false">IF($O80="","",INDEX($Y$15:$Y$19,MATCH(MAX($H80:$L80),$H80:$L80,0)))</f>
-        <v/>
-      </c>
-      <c r="S80" s="40"/>
-      <c r="T80" s="46"/>
-      <c r="U80" s="47" t="str">
-        <f aca="false">IF($E80="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E80),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V80" s="42" t="str">
-        <f aca="false">IF($E80="","",IF(ISNUMBER($U80),ROUND(6-$U80,1),""))</f>
-        <v/>
-      </c>
-      <c r="W80" s="48" t="str">
-        <f aca="false">IF($E80="","",COUNTIF('Score Log'!$C$4:$C$203,$E80))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="38"/>
-      <c r="B81" s="39"/>
-      <c r="C81" s="40"/>
-      <c r="D81" s="39"/>
-      <c r="E81" s="38"/>
-      <c r="F81" s="41"/>
-      <c r="G81" s="41"/>
-      <c r="H81" s="39"/>
-      <c r="I81" s="39"/>
-      <c r="J81" s="39"/>
-      <c r="K81" s="39"/>
-      <c r="L81" s="39"/>
-      <c r="M81" s="39"/>
-      <c r="N81" s="38"/>
-      <c r="O81" s="42" t="str">
-        <f aca="false">IF(COUNT($H81:$L81)&lt;5,"",ROUND($H81*$Z$5+$I81*$Z$6+$J81*$Z$7+$K81*$Z$8+$L81*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P81" s="43" t="str">
-        <f aca="false">IF(OR($O81="",$M81=""),"",ROUND($O81*$M81,1))</f>
-        <v/>
-      </c>
-      <c r="Q81" s="44" t="str">
-        <f aca="false">IF($E81="","",IF(OR($O81="",$M81=""),"NOT SCORED",IF($P81&gt;=$Z$11,"CRITICAL",IF($P81&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R81" s="45" t="str">
-        <f aca="false">IF($O81="","",INDEX($Y$15:$Y$19,MATCH(MAX($H81:$L81),$H81:$L81,0)))</f>
-        <v/>
-      </c>
-      <c r="S81" s="40"/>
-      <c r="T81" s="46"/>
-      <c r="U81" s="47" t="str">
-        <f aca="false">IF($E81="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E81),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V81" s="42" t="str">
-        <f aca="false">IF($E81="","",IF(ISNUMBER($U81),ROUND(6-$U81,1),""))</f>
-        <v/>
-      </c>
-      <c r="W81" s="48" t="str">
-        <f aca="false">IF($E81="","",COUNTIF('Score Log'!$C$4:$C$203,$E81))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="38"/>
-      <c r="B82" s="39"/>
-      <c r="C82" s="40"/>
-      <c r="D82" s="39"/>
-      <c r="E82" s="38"/>
-      <c r="F82" s="41"/>
-      <c r="G82" s="41"/>
-      <c r="H82" s="39"/>
-      <c r="I82" s="39"/>
-      <c r="J82" s="39"/>
-      <c r="K82" s="39"/>
-      <c r="L82" s="39"/>
-      <c r="M82" s="39"/>
-      <c r="N82" s="38"/>
-      <c r="O82" s="42" t="str">
-        <f aca="false">IF(COUNT($H82:$L82)&lt;5,"",ROUND($H82*$Z$5+$I82*$Z$6+$J82*$Z$7+$K82*$Z$8+$L82*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P82" s="43" t="str">
-        <f aca="false">IF(OR($O82="",$M82=""),"",ROUND($O82*$M82,1))</f>
-        <v/>
-      </c>
-      <c r="Q82" s="44" t="str">
-        <f aca="false">IF($E82="","",IF(OR($O82="",$M82=""),"NOT SCORED",IF($P82&gt;=$Z$11,"CRITICAL",IF($P82&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R82" s="45" t="str">
-        <f aca="false">IF($O82="","",INDEX($Y$15:$Y$19,MATCH(MAX($H82:$L82),$H82:$L82,0)))</f>
-        <v/>
-      </c>
-      <c r="S82" s="40"/>
-      <c r="T82" s="46"/>
-      <c r="U82" s="47" t="str">
-        <f aca="false">IF($E82="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E82),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V82" s="42" t="str">
-        <f aca="false">IF($E82="","",IF(ISNUMBER($U82),ROUND(6-$U82,1),""))</f>
-        <v/>
-      </c>
-      <c r="W82" s="48" t="str">
-        <f aca="false">IF($E82="","",COUNTIF('Score Log'!$C$4:$C$203,$E82))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="38"/>
-      <c r="B83" s="39"/>
-      <c r="C83" s="40"/>
-      <c r="D83" s="39"/>
-      <c r="E83" s="38"/>
-      <c r="F83" s="41"/>
-      <c r="G83" s="41"/>
-      <c r="H83" s="39"/>
-      <c r="I83" s="39"/>
-      <c r="J83" s="39"/>
-      <c r="K83" s="39"/>
-      <c r="L83" s="39"/>
-      <c r="M83" s="39"/>
-      <c r="N83" s="38"/>
-      <c r="O83" s="42" t="str">
-        <f aca="false">IF(COUNT($H83:$L83)&lt;5,"",ROUND($H83*$Z$5+$I83*$Z$6+$J83*$Z$7+$K83*$Z$8+$L83*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P83" s="43" t="str">
-        <f aca="false">IF(OR($O83="",$M83=""),"",ROUND($O83*$M83,1))</f>
-        <v/>
-      </c>
-      <c r="Q83" s="44" t="str">
-        <f aca="false">IF($E83="","",IF(OR($O83="",$M83=""),"NOT SCORED",IF($P83&gt;=$Z$11,"CRITICAL",IF($P83&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R83" s="45" t="str">
-        <f aca="false">IF($O83="","",INDEX($Y$15:$Y$19,MATCH(MAX($H83:$L83),$H83:$L83,0)))</f>
-        <v/>
-      </c>
-      <c r="S83" s="40"/>
-      <c r="T83" s="46"/>
-      <c r="U83" s="47" t="str">
-        <f aca="false">IF($E83="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E83),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V83" s="42" t="str">
-        <f aca="false">IF($E83="","",IF(ISNUMBER($U83),ROUND(6-$U83,1),""))</f>
-        <v/>
-      </c>
-      <c r="W83" s="48" t="str">
-        <f aca="false">IF($E83="","",COUNTIF('Score Log'!$C$4:$C$203,$E83))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="38"/>
-      <c r="B84" s="39"/>
-      <c r="C84" s="40"/>
-      <c r="D84" s="39"/>
-      <c r="E84" s="38"/>
-      <c r="F84" s="41"/>
-      <c r="G84" s="41"/>
-      <c r="H84" s="39"/>
-      <c r="I84" s="39"/>
-      <c r="J84" s="39"/>
-      <c r="K84" s="39"/>
-      <c r="L84" s="39"/>
-      <c r="M84" s="39"/>
-      <c r="N84" s="38"/>
-      <c r="O84" s="42" t="str">
-        <f aca="false">IF(COUNT($H84:$L84)&lt;5,"",ROUND($H84*$Z$5+$I84*$Z$6+$J84*$Z$7+$K84*$Z$8+$L84*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P84" s="43" t="str">
-        <f aca="false">IF(OR($O84="",$M84=""),"",ROUND($O84*$M84,1))</f>
-        <v/>
-      </c>
-      <c r="Q84" s="44" t="str">
-        <f aca="false">IF($E84="","",IF(OR($O84="",$M84=""),"NOT SCORED",IF($P84&gt;=$Z$11,"CRITICAL",IF($P84&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R84" s="45" t="str">
-        <f aca="false">IF($O84="","",INDEX($Y$15:$Y$19,MATCH(MAX($H84:$L84),$H84:$L84,0)))</f>
-        <v/>
-      </c>
-      <c r="S84" s="40"/>
-      <c r="T84" s="46"/>
-      <c r="U84" s="47" t="str">
-        <f aca="false">IF($E84="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E84),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V84" s="42" t="str">
-        <f aca="false">IF($E84="","",IF(ISNUMBER($U84),ROUND(6-$U84,1),""))</f>
-        <v/>
-      </c>
-      <c r="W84" s="48" t="str">
-        <f aca="false">IF($E84="","",COUNTIF('Score Log'!$C$4:$C$203,$E84))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="38"/>
-      <c r="B85" s="39"/>
-      <c r="C85" s="40"/>
-      <c r="D85" s="39"/>
-      <c r="E85" s="38"/>
-      <c r="F85" s="41"/>
-      <c r="G85" s="41"/>
-      <c r="H85" s="39"/>
-      <c r="I85" s="39"/>
-      <c r="J85" s="39"/>
-      <c r="K85" s="39"/>
-      <c r="L85" s="39"/>
-      <c r="M85" s="39"/>
-      <c r="N85" s="38"/>
-      <c r="O85" s="42" t="str">
-        <f aca="false">IF(COUNT($H85:$L85)&lt;5,"",ROUND($H85*$Z$5+$I85*$Z$6+$J85*$Z$7+$K85*$Z$8+$L85*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P85" s="43" t="str">
-        <f aca="false">IF(OR($O85="",$M85=""),"",ROUND($O85*$M85,1))</f>
-        <v/>
-      </c>
-      <c r="Q85" s="44" t="str">
-        <f aca="false">IF($E85="","",IF(OR($O85="",$M85=""),"NOT SCORED",IF($P85&gt;=$Z$11,"CRITICAL",IF($P85&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R85" s="45" t="str">
-        <f aca="false">IF($O85="","",INDEX($Y$15:$Y$19,MATCH(MAX($H85:$L85),$H85:$L85,0)))</f>
-        <v/>
-      </c>
-      <c r="S85" s="40"/>
-      <c r="T85" s="46"/>
-      <c r="U85" s="47" t="str">
-        <f aca="false">IF($E85="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E85),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V85" s="42" t="str">
-        <f aca="false">IF($E85="","",IF(ISNUMBER($U85),ROUND(6-$U85,1),""))</f>
-        <v/>
-      </c>
-      <c r="W85" s="48" t="str">
-        <f aca="false">IF($E85="","",COUNTIF('Score Log'!$C$4:$C$203,$E85))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="38"/>
-      <c r="B86" s="39"/>
-      <c r="C86" s="40"/>
-      <c r="D86" s="39"/>
-      <c r="E86" s="38"/>
-      <c r="F86" s="41"/>
-      <c r="G86" s="41"/>
-      <c r="H86" s="39"/>
-      <c r="I86" s="39"/>
-      <c r="J86" s="39"/>
-      <c r="K86" s="39"/>
-      <c r="L86" s="39"/>
-      <c r="M86" s="39"/>
-      <c r="N86" s="38"/>
-      <c r="O86" s="42" t="str">
-        <f aca="false">IF(COUNT($H86:$L86)&lt;5,"",ROUND($H86*$Z$5+$I86*$Z$6+$J86*$Z$7+$K86*$Z$8+$L86*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P86" s="43" t="str">
-        <f aca="false">IF(OR($O86="",$M86=""),"",ROUND($O86*$M86,1))</f>
-        <v/>
-      </c>
-      <c r="Q86" s="44" t="str">
-        <f aca="false">IF($E86="","",IF(OR($O86="",$M86=""),"NOT SCORED",IF($P86&gt;=$Z$11,"CRITICAL",IF($P86&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R86" s="45" t="str">
-        <f aca="false">IF($O86="","",INDEX($Y$15:$Y$19,MATCH(MAX($H86:$L86),$H86:$L86,0)))</f>
-        <v/>
-      </c>
-      <c r="S86" s="40"/>
-      <c r="T86" s="46"/>
-      <c r="U86" s="47" t="str">
-        <f aca="false">IF($E86="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E86),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V86" s="42" t="str">
-        <f aca="false">IF($E86="","",IF(ISNUMBER($U86),ROUND(6-$U86,1),""))</f>
-        <v/>
-      </c>
-      <c r="W86" s="48" t="str">
-        <f aca="false">IF($E86="","",COUNTIF('Score Log'!$C$4:$C$203,$E86))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="38"/>
-      <c r="B87" s="39"/>
-      <c r="C87" s="40"/>
-      <c r="D87" s="39"/>
-      <c r="E87" s="38"/>
-      <c r="F87" s="41"/>
-      <c r="G87" s="41"/>
-      <c r="H87" s="39"/>
-      <c r="I87" s="39"/>
-      <c r="J87" s="39"/>
-      <c r="K87" s="39"/>
-      <c r="L87" s="39"/>
-      <c r="M87" s="39"/>
-      <c r="N87" s="38"/>
-      <c r="O87" s="42" t="str">
-        <f aca="false">IF(COUNT($H87:$L87)&lt;5,"",ROUND($H87*$Z$5+$I87*$Z$6+$J87*$Z$7+$K87*$Z$8+$L87*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P87" s="43" t="str">
-        <f aca="false">IF(OR($O87="",$M87=""),"",ROUND($O87*$M87,1))</f>
-        <v/>
-      </c>
-      <c r="Q87" s="44" t="str">
-        <f aca="false">IF($E87="","",IF(OR($O87="",$M87=""),"NOT SCORED",IF($P87&gt;=$Z$11,"CRITICAL",IF($P87&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R87" s="45" t="str">
-        <f aca="false">IF($O87="","",INDEX($Y$15:$Y$19,MATCH(MAX($H87:$L87),$H87:$L87,0)))</f>
-        <v/>
-      </c>
-      <c r="S87" s="40"/>
-      <c r="T87" s="46"/>
-      <c r="U87" s="47" t="str">
-        <f aca="false">IF($E87="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E87),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V87" s="42" t="str">
-        <f aca="false">IF($E87="","",IF(ISNUMBER($U87),ROUND(6-$U87,1),""))</f>
-        <v/>
-      </c>
-      <c r="W87" s="48" t="str">
-        <f aca="false">IF($E87="","",COUNTIF('Score Log'!$C$4:$C$203,$E87))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="38"/>
-      <c r="B88" s="39"/>
-      <c r="C88" s="40"/>
-      <c r="D88" s="39"/>
-      <c r="E88" s="38"/>
-      <c r="F88" s="41"/>
-      <c r="G88" s="41"/>
-      <c r="H88" s="39"/>
-      <c r="I88" s="39"/>
-      <c r="J88" s="39"/>
-      <c r="K88" s="39"/>
-      <c r="L88" s="39"/>
-      <c r="M88" s="39"/>
-      <c r="N88" s="38"/>
-      <c r="O88" s="42" t="str">
-        <f aca="false">IF(COUNT($H88:$L88)&lt;5,"",ROUND($H88*$Z$5+$I88*$Z$6+$J88*$Z$7+$K88*$Z$8+$L88*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P88" s="43" t="str">
-        <f aca="false">IF(OR($O88="",$M88=""),"",ROUND($O88*$M88,1))</f>
-        <v/>
-      </c>
-      <c r="Q88" s="44" t="str">
-        <f aca="false">IF($E88="","",IF(OR($O88="",$M88=""),"NOT SCORED",IF($P88&gt;=$Z$11,"CRITICAL",IF($P88&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R88" s="45" t="str">
-        <f aca="false">IF($O88="","",INDEX($Y$15:$Y$19,MATCH(MAX($H88:$L88),$H88:$L88,0)))</f>
-        <v/>
-      </c>
-      <c r="S88" s="40"/>
-      <c r="T88" s="46"/>
-      <c r="U88" s="47" t="str">
-        <f aca="false">IF($E88="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E88),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V88" s="42" t="str">
-        <f aca="false">IF($E88="","",IF(ISNUMBER($U88),ROUND(6-$U88,1),""))</f>
-        <v/>
-      </c>
-      <c r="W88" s="48" t="str">
-        <f aca="false">IF($E88="","",COUNTIF('Score Log'!$C$4:$C$203,$E88))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="38"/>
-      <c r="B89" s="39"/>
-      <c r="C89" s="40"/>
-      <c r="D89" s="39"/>
-      <c r="E89" s="38"/>
-      <c r="F89" s="41"/>
-      <c r="G89" s="41"/>
-      <c r="H89" s="39"/>
-      <c r="I89" s="39"/>
-      <c r="J89" s="39"/>
-      <c r="K89" s="39"/>
-      <c r="L89" s="39"/>
-      <c r="M89" s="39"/>
-      <c r="N89" s="38"/>
-      <c r="O89" s="42" t="str">
-        <f aca="false">IF(COUNT($H89:$L89)&lt;5,"",ROUND($H89*$Z$5+$I89*$Z$6+$J89*$Z$7+$K89*$Z$8+$L89*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P89" s="43" t="str">
-        <f aca="false">IF(OR($O89="",$M89=""),"",ROUND($O89*$M89,1))</f>
-        <v/>
-      </c>
-      <c r="Q89" s="44" t="str">
-        <f aca="false">IF($E89="","",IF(OR($O89="",$M89=""),"NOT SCORED",IF($P89&gt;=$Z$11,"CRITICAL",IF($P89&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R89" s="45" t="str">
-        <f aca="false">IF($O89="","",INDEX($Y$15:$Y$19,MATCH(MAX($H89:$L89),$H89:$L89,0)))</f>
-        <v/>
-      </c>
-      <c r="S89" s="40"/>
-      <c r="T89" s="46"/>
-      <c r="U89" s="47" t="str">
-        <f aca="false">IF($E89="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E89),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V89" s="42" t="str">
-        <f aca="false">IF($E89="","",IF(ISNUMBER($U89),ROUND(6-$U89,1),""))</f>
-        <v/>
-      </c>
-      <c r="W89" s="48" t="str">
-        <f aca="false">IF($E89="","",COUNTIF('Score Log'!$C$4:$C$203,$E89))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="38"/>
-      <c r="B90" s="39"/>
-      <c r="C90" s="40"/>
-      <c r="D90" s="39"/>
-      <c r="E90" s="38"/>
-      <c r="F90" s="41"/>
-      <c r="G90" s="41"/>
-      <c r="H90" s="39"/>
-      <c r="I90" s="39"/>
-      <c r="J90" s="39"/>
-      <c r="K90" s="39"/>
-      <c r="L90" s="39"/>
-      <c r="M90" s="39"/>
-      <c r="N90" s="38"/>
-      <c r="O90" s="42" t="str">
-        <f aca="false">IF(COUNT($H90:$L90)&lt;5,"",ROUND($H90*$Z$5+$I90*$Z$6+$J90*$Z$7+$K90*$Z$8+$L90*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P90" s="43" t="str">
-        <f aca="false">IF(OR($O90="",$M90=""),"",ROUND($O90*$M90,1))</f>
-        <v/>
-      </c>
-      <c r="Q90" s="44" t="str">
-        <f aca="false">IF($E90="","",IF(OR($O90="",$M90=""),"NOT SCORED",IF($P90&gt;=$Z$11,"CRITICAL",IF($P90&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R90" s="45" t="str">
-        <f aca="false">IF($O90="","",INDEX($Y$15:$Y$19,MATCH(MAX($H90:$L90),$H90:$L90,0)))</f>
-        <v/>
-      </c>
-      <c r="S90" s="40"/>
-      <c r="T90" s="46"/>
-      <c r="U90" s="47" t="str">
-        <f aca="false">IF($E90="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E90),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V90" s="42" t="str">
-        <f aca="false">IF($E90="","",IF(ISNUMBER($U90),ROUND(6-$U90,1),""))</f>
-        <v/>
-      </c>
-      <c r="W90" s="48" t="str">
-        <f aca="false">IF($E90="","",COUNTIF('Score Log'!$C$4:$C$203,$E90))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="38"/>
-      <c r="B91" s="39"/>
-      <c r="C91" s="40"/>
-      <c r="D91" s="39"/>
-      <c r="E91" s="38"/>
-      <c r="F91" s="41"/>
-      <c r="G91" s="41"/>
-      <c r="H91" s="39"/>
-      <c r="I91" s="39"/>
-      <c r="J91" s="39"/>
-      <c r="K91" s="39"/>
-      <c r="L91" s="39"/>
-      <c r="M91" s="39"/>
-      <c r="N91" s="38"/>
-      <c r="O91" s="42" t="str">
-        <f aca="false">IF(COUNT($H91:$L91)&lt;5,"",ROUND($H91*$Z$5+$I91*$Z$6+$J91*$Z$7+$K91*$Z$8+$L91*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P91" s="43" t="str">
-        <f aca="false">IF(OR($O91="",$M91=""),"",ROUND($O91*$M91,1))</f>
-        <v/>
-      </c>
-      <c r="Q91" s="44" t="str">
-        <f aca="false">IF($E91="","",IF(OR($O91="",$M91=""),"NOT SCORED",IF($P91&gt;=$Z$11,"CRITICAL",IF($P91&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R91" s="45" t="str">
-        <f aca="false">IF($O91="","",INDEX($Y$15:$Y$19,MATCH(MAX($H91:$L91),$H91:$L91,0)))</f>
-        <v/>
-      </c>
-      <c r="S91" s="40"/>
-      <c r="T91" s="46"/>
-      <c r="U91" s="47" t="str">
-        <f aca="false">IF($E91="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E91),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V91" s="42" t="str">
-        <f aca="false">IF($E91="","",IF(ISNUMBER($U91),ROUND(6-$U91,1),""))</f>
-        <v/>
-      </c>
-      <c r="W91" s="48" t="str">
-        <f aca="false">IF($E91="","",COUNTIF('Score Log'!$C$4:$C$203,$E91))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="38"/>
-      <c r="B92" s="39"/>
-      <c r="C92" s="40"/>
-      <c r="D92" s="39"/>
-      <c r="E92" s="38"/>
-      <c r="F92" s="41"/>
-      <c r="G92" s="41"/>
-      <c r="H92" s="39"/>
-      <c r="I92" s="39"/>
-      <c r="J92" s="39"/>
-      <c r="K92" s="39"/>
-      <c r="L92" s="39"/>
-      <c r="M92" s="39"/>
-      <c r="N92" s="38"/>
-      <c r="O92" s="42" t="str">
-        <f aca="false">IF(COUNT($H92:$L92)&lt;5,"",ROUND($H92*$Z$5+$I92*$Z$6+$J92*$Z$7+$K92*$Z$8+$L92*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P92" s="43" t="str">
-        <f aca="false">IF(OR($O92="",$M92=""),"",ROUND($O92*$M92,1))</f>
-        <v/>
-      </c>
-      <c r="Q92" s="44" t="str">
-        <f aca="false">IF($E92="","",IF(OR($O92="",$M92=""),"NOT SCORED",IF($P92&gt;=$Z$11,"CRITICAL",IF($P92&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R92" s="45" t="str">
-        <f aca="false">IF($O92="","",INDEX($Y$15:$Y$19,MATCH(MAX($H92:$L92),$H92:$L92,0)))</f>
-        <v/>
-      </c>
-      <c r="S92" s="40"/>
-      <c r="T92" s="46"/>
-      <c r="U92" s="47" t="str">
-        <f aca="false">IF($E92="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E92),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V92" s="42" t="str">
-        <f aca="false">IF($E92="","",IF(ISNUMBER($U92),ROUND(6-$U92,1),""))</f>
-        <v/>
-      </c>
-      <c r="W92" s="48" t="str">
-        <f aca="false">IF($E92="","",COUNTIF('Score Log'!$C$4:$C$203,$E92))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="38"/>
-      <c r="B93" s="39"/>
-      <c r="C93" s="40"/>
-      <c r="D93" s="39"/>
-      <c r="E93" s="38"/>
-      <c r="F93" s="41"/>
-      <c r="G93" s="41"/>
-      <c r="H93" s="39"/>
-      <c r="I93" s="39"/>
-      <c r="J93" s="39"/>
-      <c r="K93" s="39"/>
-      <c r="L93" s="39"/>
-      <c r="M93" s="39"/>
-      <c r="N93" s="38"/>
-      <c r="O93" s="42" t="str">
-        <f aca="false">IF(COUNT($H93:$L93)&lt;5,"",ROUND($H93*$Z$5+$I93*$Z$6+$J93*$Z$7+$K93*$Z$8+$L93*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P93" s="43" t="str">
-        <f aca="false">IF(OR($O93="",$M93=""),"",ROUND($O93*$M93,1))</f>
-        <v/>
-      </c>
-      <c r="Q93" s="44" t="str">
-        <f aca="false">IF($E93="","",IF(OR($O93="",$M93=""),"NOT SCORED",IF($P93&gt;=$Z$11,"CRITICAL",IF($P93&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R93" s="45" t="str">
-        <f aca="false">IF($O93="","",INDEX($Y$15:$Y$19,MATCH(MAX($H93:$L93),$H93:$L93,0)))</f>
-        <v/>
-      </c>
-      <c r="S93" s="40"/>
-      <c r="T93" s="46"/>
-      <c r="U93" s="47" t="str">
-        <f aca="false">IF($E93="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E93),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V93" s="42" t="str">
-        <f aca="false">IF($E93="","",IF(ISNUMBER($U93),ROUND(6-$U93,1),""))</f>
-        <v/>
-      </c>
-      <c r="W93" s="48" t="str">
-        <f aca="false">IF($E93="","",COUNTIF('Score Log'!$C$4:$C$203,$E93))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="38"/>
-      <c r="B94" s="39"/>
-      <c r="C94" s="40"/>
-      <c r="D94" s="39"/>
-      <c r="E94" s="38"/>
-      <c r="F94" s="41"/>
-      <c r="G94" s="41"/>
-      <c r="H94" s="39"/>
-      <c r="I94" s="39"/>
-      <c r="J94" s="39"/>
-      <c r="K94" s="39"/>
-      <c r="L94" s="39"/>
-      <c r="M94" s="39"/>
-      <c r="N94" s="38"/>
-      <c r="O94" s="42" t="str">
-        <f aca="false">IF(COUNT($H94:$L94)&lt;5,"",ROUND($H94*$Z$5+$I94*$Z$6+$J94*$Z$7+$K94*$Z$8+$L94*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P94" s="43" t="str">
-        <f aca="false">IF(OR($O94="",$M94=""),"",ROUND($O94*$M94,1))</f>
-        <v/>
-      </c>
-      <c r="Q94" s="44" t="str">
-        <f aca="false">IF($E94="","",IF(OR($O94="",$M94=""),"NOT SCORED",IF($P94&gt;=$Z$11,"CRITICAL",IF($P94&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R94" s="45" t="str">
-        <f aca="false">IF($O94="","",INDEX($Y$15:$Y$19,MATCH(MAX($H94:$L94),$H94:$L94,0)))</f>
-        <v/>
-      </c>
-      <c r="S94" s="40"/>
-      <c r="T94" s="46"/>
-      <c r="U94" s="47" t="str">
-        <f aca="false">IF($E94="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E94),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V94" s="42" t="str">
-        <f aca="false">IF($E94="","",IF(ISNUMBER($U94),ROUND(6-$U94,1),""))</f>
-        <v/>
-      </c>
-      <c r="W94" s="48" t="str">
-        <f aca="false">IF($E94="","",COUNTIF('Score Log'!$C$4:$C$203,$E94))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="38"/>
-      <c r="B95" s="39"/>
-      <c r="C95" s="40"/>
-      <c r="D95" s="39"/>
-      <c r="E95" s="38"/>
-      <c r="F95" s="41"/>
-      <c r="G95" s="41"/>
-      <c r="H95" s="39"/>
-      <c r="I95" s="39"/>
-      <c r="J95" s="39"/>
-      <c r="K95" s="39"/>
-      <c r="L95" s="39"/>
-      <c r="M95" s="39"/>
-      <c r="N95" s="38"/>
-      <c r="O95" s="42" t="str">
-        <f aca="false">IF(COUNT($H95:$L95)&lt;5,"",ROUND($H95*$Z$5+$I95*$Z$6+$J95*$Z$7+$K95*$Z$8+$L95*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P95" s="43" t="str">
-        <f aca="false">IF(OR($O95="",$M95=""),"",ROUND($O95*$M95,1))</f>
-        <v/>
-      </c>
-      <c r="Q95" s="44" t="str">
-        <f aca="false">IF($E95="","",IF(OR($O95="",$M95=""),"NOT SCORED",IF($P95&gt;=$Z$11,"CRITICAL",IF($P95&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R95" s="45" t="str">
-        <f aca="false">IF($O95="","",INDEX($Y$15:$Y$19,MATCH(MAX($H95:$L95),$H95:$L95,0)))</f>
-        <v/>
-      </c>
-      <c r="S95" s="40"/>
-      <c r="T95" s="46"/>
-      <c r="U95" s="47" t="str">
-        <f aca="false">IF($E95="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E95),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V95" s="42" t="str">
-        <f aca="false">IF($E95="","",IF(ISNUMBER($U95),ROUND(6-$U95,1),""))</f>
-        <v/>
-      </c>
-      <c r="W95" s="48" t="str">
-        <f aca="false">IF($E95="","",COUNTIF('Score Log'!$C$4:$C$203,$E95))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="38"/>
-      <c r="B96" s="39"/>
-      <c r="C96" s="40"/>
-      <c r="D96" s="39"/>
-      <c r="E96" s="38"/>
-      <c r="F96" s="41"/>
-      <c r="G96" s="41"/>
-      <c r="H96" s="39"/>
-      <c r="I96" s="39"/>
-      <c r="J96" s="39"/>
-      <c r="K96" s="39"/>
-      <c r="L96" s="39"/>
-      <c r="M96" s="39"/>
-      <c r="N96" s="38"/>
-      <c r="O96" s="42" t="str">
-        <f aca="false">IF(COUNT($H96:$L96)&lt;5,"",ROUND($H96*$Z$5+$I96*$Z$6+$J96*$Z$7+$K96*$Z$8+$L96*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P96" s="43" t="str">
-        <f aca="false">IF(OR($O96="",$M96=""),"",ROUND($O96*$M96,1))</f>
-        <v/>
-      </c>
-      <c r="Q96" s="44" t="str">
-        <f aca="false">IF($E96="","",IF(OR($O96="",$M96=""),"NOT SCORED",IF($P96&gt;=$Z$11,"CRITICAL",IF($P96&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R96" s="45" t="str">
-        <f aca="false">IF($O96="","",INDEX($Y$15:$Y$19,MATCH(MAX($H96:$L96),$H96:$L96,0)))</f>
-        <v/>
-      </c>
-      <c r="S96" s="40"/>
-      <c r="T96" s="46"/>
-      <c r="U96" s="47" t="str">
-        <f aca="false">IF($E96="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E96),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V96" s="42" t="str">
-        <f aca="false">IF($E96="","",IF(ISNUMBER($U96),ROUND(6-$U96,1),""))</f>
-        <v/>
-      </c>
-      <c r="W96" s="48" t="str">
-        <f aca="false">IF($E96="","",COUNTIF('Score Log'!$C$4:$C$203,$E96))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="38"/>
-      <c r="B97" s="39"/>
-      <c r="C97" s="40"/>
-      <c r="D97" s="39"/>
-      <c r="E97" s="38"/>
-      <c r="F97" s="41"/>
-      <c r="G97" s="41"/>
-      <c r="H97" s="39"/>
-      <c r="I97" s="39"/>
-      <c r="J97" s="39"/>
-      <c r="K97" s="39"/>
-      <c r="L97" s="39"/>
-      <c r="M97" s="39"/>
-      <c r="N97" s="38"/>
-      <c r="O97" s="42" t="str">
-        <f aca="false">IF(COUNT($H97:$L97)&lt;5,"",ROUND($H97*$Z$5+$I97*$Z$6+$J97*$Z$7+$K97*$Z$8+$L97*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P97" s="43" t="str">
-        <f aca="false">IF(OR($O97="",$M97=""),"",ROUND($O97*$M97,1))</f>
-        <v/>
-      </c>
-      <c r="Q97" s="44" t="str">
-        <f aca="false">IF($E97="","",IF(OR($O97="",$M97=""),"NOT SCORED",IF($P97&gt;=$Z$11,"CRITICAL",IF($P97&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R97" s="45" t="str">
-        <f aca="false">IF($O97="","",INDEX($Y$15:$Y$19,MATCH(MAX($H97:$L97),$H97:$L97,0)))</f>
-        <v/>
-      </c>
-      <c r="S97" s="40"/>
-      <c r="T97" s="46"/>
-      <c r="U97" s="47" t="str">
-        <f aca="false">IF($E97="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E97),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V97" s="42" t="str">
-        <f aca="false">IF($E97="","",IF(ISNUMBER($U97),ROUND(6-$U97,1),""))</f>
-        <v/>
-      </c>
-      <c r="W97" s="48" t="str">
-        <f aca="false">IF($E97="","",COUNTIF('Score Log'!$C$4:$C$203,$E97))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="38"/>
-      <c r="B98" s="39"/>
-      <c r="C98" s="40"/>
-      <c r="D98" s="39"/>
-      <c r="E98" s="38"/>
-      <c r="F98" s="41"/>
-      <c r="G98" s="41"/>
-      <c r="H98" s="39"/>
-      <c r="I98" s="39"/>
-      <c r="J98" s="39"/>
-      <c r="K98" s="39"/>
-      <c r="L98" s="39"/>
-      <c r="M98" s="39"/>
-      <c r="N98" s="38"/>
-      <c r="O98" s="42" t="str">
-        <f aca="false">IF(COUNT($H98:$L98)&lt;5,"",ROUND($H98*$Z$5+$I98*$Z$6+$J98*$Z$7+$K98*$Z$8+$L98*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P98" s="43" t="str">
-        <f aca="false">IF(OR($O98="",$M98=""),"",ROUND($O98*$M98,1))</f>
-        <v/>
-      </c>
-      <c r="Q98" s="44" t="str">
-        <f aca="false">IF($E98="","",IF(OR($O98="",$M98=""),"NOT SCORED",IF($P98&gt;=$Z$11,"CRITICAL",IF($P98&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R98" s="45" t="str">
-        <f aca="false">IF($O98="","",INDEX($Y$15:$Y$19,MATCH(MAX($H98:$L98),$H98:$L98,0)))</f>
-        <v/>
-      </c>
-      <c r="S98" s="40"/>
-      <c r="T98" s="46"/>
-      <c r="U98" s="47" t="str">
-        <f aca="false">IF($E98="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E98),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V98" s="42" t="str">
-        <f aca="false">IF($E98="","",IF(ISNUMBER($U98),ROUND(6-$U98,1),""))</f>
-        <v/>
-      </c>
-      <c r="W98" s="48" t="str">
-        <f aca="false">IF($E98="","",COUNTIF('Score Log'!$C$4:$C$203,$E98))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="38"/>
-      <c r="B99" s="39"/>
-      <c r="C99" s="40"/>
-      <c r="D99" s="39"/>
-      <c r="E99" s="38"/>
-      <c r="F99" s="41"/>
-      <c r="G99" s="41"/>
-      <c r="H99" s="39"/>
-      <c r="I99" s="39"/>
-      <c r="J99" s="39"/>
-      <c r="K99" s="39"/>
-      <c r="L99" s="39"/>
-      <c r="M99" s="39"/>
-      <c r="N99" s="38"/>
-      <c r="O99" s="42" t="str">
-        <f aca="false">IF(COUNT($H99:$L99)&lt;5,"",ROUND($H99*$Z$5+$I99*$Z$6+$J99*$Z$7+$K99*$Z$8+$L99*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P99" s="43" t="str">
-        <f aca="false">IF(OR($O99="",$M99=""),"",ROUND($O99*$M99,1))</f>
-        <v/>
-      </c>
-      <c r="Q99" s="44" t="str">
-        <f aca="false">IF($E99="","",IF(OR($O99="",$M99=""),"NOT SCORED",IF($P99&gt;=$Z$11,"CRITICAL",IF($P99&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R99" s="45" t="str">
-        <f aca="false">IF($O99="","",INDEX($Y$15:$Y$19,MATCH(MAX($H99:$L99),$H99:$L99,0)))</f>
-        <v/>
-      </c>
-      <c r="S99" s="40"/>
-      <c r="T99" s="46"/>
-      <c r="U99" s="47" t="str">
-        <f aca="false">IF($E99="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E99),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V99" s="42" t="str">
-        <f aca="false">IF($E99="","",IF(ISNUMBER($U99),ROUND(6-$U99,1),""))</f>
-        <v/>
-      </c>
-      <c r="W99" s="48" t="str">
-        <f aca="false">IF($E99="","",COUNTIF('Score Log'!$C$4:$C$203,$E99))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="38"/>
-      <c r="B100" s="39"/>
-      <c r="C100" s="40"/>
-      <c r="D100" s="39"/>
-      <c r="E100" s="38"/>
-      <c r="F100" s="41"/>
-      <c r="G100" s="41"/>
-      <c r="H100" s="39"/>
-      <c r="I100" s="39"/>
-      <c r="J100" s="39"/>
-      <c r="K100" s="39"/>
-      <c r="L100" s="39"/>
-      <c r="M100" s="39"/>
-      <c r="N100" s="38"/>
-      <c r="O100" s="42" t="str">
-        <f aca="false">IF(COUNT($H100:$L100)&lt;5,"",ROUND($H100*$Z$5+$I100*$Z$6+$J100*$Z$7+$K100*$Z$8+$L100*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P100" s="43" t="str">
-        <f aca="false">IF(OR($O100="",$M100=""),"",ROUND($O100*$M100,1))</f>
-        <v/>
-      </c>
-      <c r="Q100" s="44" t="str">
-        <f aca="false">IF($E100="","",IF(OR($O100="",$M100=""),"NOT SCORED",IF($P100&gt;=$Z$11,"CRITICAL",IF($P100&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R100" s="45" t="str">
-        <f aca="false">IF($O100="","",INDEX($Y$15:$Y$19,MATCH(MAX($H100:$L100),$H100:$L100,0)))</f>
-        <v/>
-      </c>
-      <c r="S100" s="40"/>
-      <c r="T100" s="46"/>
-      <c r="U100" s="47" t="str">
-        <f aca="false">IF($E100="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E100),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V100" s="42" t="str">
-        <f aca="false">IF($E100="","",IF(ISNUMBER($U100),ROUND(6-$U100,1),""))</f>
-        <v/>
-      </c>
-      <c r="W100" s="48" t="str">
-        <f aca="false">IF($E100="","",COUNTIF('Score Log'!$C$4:$C$203,$E100))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="38"/>
-      <c r="B101" s="39"/>
-      <c r="C101" s="40"/>
-      <c r="D101" s="39"/>
-      <c r="E101" s="38"/>
-      <c r="F101" s="41"/>
-      <c r="G101" s="41"/>
-      <c r="H101" s="39"/>
-      <c r="I101" s="39"/>
-      <c r="J101" s="39"/>
-      <c r="K101" s="39"/>
-      <c r="L101" s="39"/>
-      <c r="M101" s="39"/>
-      <c r="N101" s="38"/>
-      <c r="O101" s="42" t="str">
-        <f aca="false">IF(COUNT($H101:$L101)&lt;5,"",ROUND($H101*$Z$5+$I101*$Z$6+$J101*$Z$7+$K101*$Z$8+$L101*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P101" s="43" t="str">
-        <f aca="false">IF(OR($O101="",$M101=""),"",ROUND($O101*$M101,1))</f>
-        <v/>
-      </c>
-      <c r="Q101" s="44" t="str">
-        <f aca="false">IF($E101="","",IF(OR($O101="",$M101=""),"NOT SCORED",IF($P101&gt;=$Z$11,"CRITICAL",IF($P101&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R101" s="45" t="str">
-        <f aca="false">IF($O101="","",INDEX($Y$15:$Y$19,MATCH(MAX($H101:$L101),$H101:$L101,0)))</f>
-        <v/>
-      </c>
-      <c r="S101" s="40"/>
-      <c r="T101" s="46"/>
-      <c r="U101" s="47" t="str">
-        <f aca="false">IF($E101="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E101),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V101" s="42" t="str">
-        <f aca="false">IF($E101="","",IF(ISNUMBER($U101),ROUND(6-$U101,1),""))</f>
-        <v/>
-      </c>
-      <c r="W101" s="48" t="str">
-        <f aca="false">IF($E101="","",COUNTIF('Score Log'!$C$4:$C$203,$E101))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="38"/>
-      <c r="B102" s="39"/>
-      <c r="C102" s="40"/>
-      <c r="D102" s="39"/>
-      <c r="E102" s="38"/>
-      <c r="F102" s="41"/>
-      <c r="G102" s="41"/>
-      <c r="H102" s="39"/>
-      <c r="I102" s="39"/>
-      <c r="J102" s="39"/>
-      <c r="K102" s="39"/>
-      <c r="L102" s="39"/>
-      <c r="M102" s="39"/>
-      <c r="N102" s="38"/>
-      <c r="O102" s="42" t="str">
-        <f aca="false">IF(COUNT($H102:$L102)&lt;5,"",ROUND($H102*$Z$5+$I102*$Z$6+$J102*$Z$7+$K102*$Z$8+$L102*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P102" s="43" t="str">
-        <f aca="false">IF(OR($O102="",$M102=""),"",ROUND($O102*$M102,1))</f>
-        <v/>
-      </c>
-      <c r="Q102" s="44" t="str">
-        <f aca="false">IF($E102="","",IF(OR($O102="",$M102=""),"NOT SCORED",IF($P102&gt;=$Z$11,"CRITICAL",IF($P102&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R102" s="45" t="str">
-        <f aca="false">IF($O102="","",INDEX($Y$15:$Y$19,MATCH(MAX($H102:$L102),$H102:$L102,0)))</f>
-        <v/>
-      </c>
-      <c r="S102" s="40"/>
-      <c r="T102" s="46"/>
-      <c r="U102" s="47" t="str">
-        <f aca="false">IF($E102="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E102),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V102" s="42" t="str">
-        <f aca="false">IF($E102="","",IF(ISNUMBER($U102),ROUND(6-$U102,1),""))</f>
-        <v/>
-      </c>
-      <c r="W102" s="48" t="str">
-        <f aca="false">IF($E102="","",COUNTIF('Score Log'!$C$4:$C$203,$E102))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="38"/>
-      <c r="B103" s="39"/>
-      <c r="C103" s="40"/>
-      <c r="D103" s="39"/>
-      <c r="E103" s="38"/>
-      <c r="F103" s="41"/>
-      <c r="G103" s="41"/>
-      <c r="H103" s="39"/>
-      <c r="I103" s="39"/>
-      <c r="J103" s="39"/>
-      <c r="K103" s="39"/>
-      <c r="L103" s="39"/>
-      <c r="M103" s="39"/>
-      <c r="N103" s="38"/>
-      <c r="O103" s="42" t="str">
-        <f aca="false">IF(COUNT($H103:$L103)&lt;5,"",ROUND($H103*$Z$5+$I103*$Z$6+$J103*$Z$7+$K103*$Z$8+$L103*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P103" s="43" t="str">
-        <f aca="false">IF(OR($O103="",$M103=""),"",ROUND($O103*$M103,1))</f>
-        <v/>
-      </c>
-      <c r="Q103" s="44" t="str">
-        <f aca="false">IF($E103="","",IF(OR($O103="",$M103=""),"NOT SCORED",IF($P103&gt;=$Z$11,"CRITICAL",IF($P103&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R103" s="45" t="str">
-        <f aca="false">IF($O103="","",INDEX($Y$15:$Y$19,MATCH(MAX($H103:$L103),$H103:$L103,0)))</f>
-        <v/>
-      </c>
-      <c r="S103" s="40"/>
-      <c r="T103" s="46"/>
-      <c r="U103" s="47" t="str">
-        <f aca="false">IF($E103="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E103),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V103" s="42" t="str">
-        <f aca="false">IF($E103="","",IF(ISNUMBER($U103),ROUND(6-$U103,1),""))</f>
-        <v/>
-      </c>
-      <c r="W103" s="48" t="str">
-        <f aca="false">IF($E103="","",COUNTIF('Score Log'!$C$4:$C$203,$E103))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="38"/>
-      <c r="B104" s="39"/>
-      <c r="C104" s="40"/>
-      <c r="D104" s="39"/>
-      <c r="E104" s="38"/>
-      <c r="F104" s="41"/>
-      <c r="G104" s="41"/>
-      <c r="H104" s="39"/>
-      <c r="I104" s="39"/>
-      <c r="J104" s="39"/>
-      <c r="K104" s="39"/>
-      <c r="L104" s="39"/>
-      <c r="M104" s="39"/>
-      <c r="N104" s="38"/>
-      <c r="O104" s="42" t="str">
-        <f aca="false">IF(COUNT($H104:$L104)&lt;5,"",ROUND($H104*$Z$5+$I104*$Z$6+$J104*$Z$7+$K104*$Z$8+$L104*$Z$9,1))</f>
-        <v/>
-      </c>
-      <c r="P104" s="43" t="str">
-        <f aca="false">IF(OR($O104="",$M104=""),"",ROUND($O104*$M104,1))</f>
-        <v/>
-      </c>
-      <c r="Q104" s="44" t="str">
-        <f aca="false">IF($E104="","",IF(OR($O104="",$M104=""),"NOT SCORED",IF($P104&gt;=$Z$11,"CRITICAL",IF($P104&gt;=$Z$12,"MONITOR","LOW"))))</f>
-        <v/>
-      </c>
-      <c r="R104" s="45" t="str">
-        <f aca="false">IF($O104="","",INDEX($Y$15:$Y$19,MATCH(MAX($H104:$L104),$H104:$L104,0)))</f>
-        <v/>
-      </c>
-      <c r="S104" s="40"/>
-      <c r="T104" s="46"/>
-      <c r="U104" s="47" t="str">
-        <f aca="false">IF($E104="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$E104),2),"no data"))</f>
-        <v/>
-      </c>
-      <c r="V104" s="42" t="str">
-        <f aca="false">IF($E104="","",IF(ISNUMBER($U104),ROUND(6-$U104,1),""))</f>
-        <v/>
-      </c>
-      <c r="W104" s="48" t="str">
-        <f aca="false">IF($E104="","",COUNTIF('Score Log'!$C$4:$C$203,$E104))</f>
-        <v/>
-      </c>
+      <c r="B42" s="43"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="O3:R3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="U3:W3"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A42:K42"/>
   </mergeCells>
-  <conditionalFormatting sqref="Q5:Q104">
-    <cfRule type="containsText" priority="2" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="CRITICAL" dxfId="12">
-      <formula>NOT(ISERROR(SEARCH("CRITICAL",Q5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" priority="3" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="MONITOR" dxfId="13">
-      <formula>NOT(ISERROR(SEARCH("MONITOR",Q5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" priority="4" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="LOW" dxfId="14">
-      <formula>NOT(ISERROR(SEARCH("LOW",Q5)))</formula>
+  <conditionalFormatting sqref="C5:G34">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="3"/>
+        <cfvo type="num" val="5"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P5:P104">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="I5:K34">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="1"/>
-        <cfvo type="num" val="13"/>
-        <cfvo type="num" val="25"/>
+        <cfvo type="num" val="3"/>
+        <cfvo type="num" val="5"/>
         <color rgb="FF63BE7B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:D104" type="list">
-      <formula1>"Tissue (APHIS),Tissue (Non-APHIS),Non-Tissue: Custom,Non-Tissue: COTS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Pick a supplier from the Suppliers tab (or add it there first)." errorStyle="stop" errorTitle="Unknown supplier" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E5:E104" type="list">
-      <formula1>ScorecardSuppliers</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Scores go from 1 (low risk) to 5 (high risk)." errorStyle="stop" errorTitle="Score must be 1-5" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H5:M104" type="list">
-      <formula1>"1,2,3,4,5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -16805,281 +13321,281 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="54" t="s">
-        <v>123</v>
-      </c>
-      <c r="B2" s="54" t="s">
-        <v>124</v>
-      </c>
-      <c r="C2" s="54" t="s">
-        <v>125</v>
-      </c>
-      <c r="D2" s="54" t="s">
-        <v>126</v>
-      </c>
-      <c r="E2" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="F2" s="54" t="s">
-        <v>128</v>
+      <c r="A2" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="44" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55" t="s">
-        <v>129</v>
-      </c>
-      <c r="D3" s="56" t="s">
-        <v>130</v>
-      </c>
-      <c r="E3" s="55" t="s">
-        <v>131</v>
-      </c>
-      <c r="F3" s="55"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3" s="45"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="55"/>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
+      <c r="A5" s="45"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="57"/>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
+      <c r="A6" s="47"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="57"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
+      <c r="A7" s="47"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="57"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
+      <c r="A8" s="47"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="47"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="57"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
+      <c r="A9" s="47"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="57"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="57"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
+      <c r="A11" s="47"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="57"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
+      <c r="A12" s="47"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="57"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="57"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
+      <c r="A14" s="47"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="57"/>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
+      <c r="A15" s="47"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="57"/>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
+      <c r="A16" s="47"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="57"/>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
+      <c r="A17" s="47"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="57"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="57"/>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="57"/>
-      <c r="B20" s="57"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="57"/>
-      <c r="B21" s="57"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="57"/>
-      <c r="B22" s="57"/>
-      <c r="C22" s="57"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="57"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="57"/>
-      <c r="B23" s="57"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
+      <c r="A23" s="47"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="57"/>
-      <c r="B24" s="57"/>
-      <c r="C24" s="57"/>
-      <c r="D24" s="57"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="57"/>
+      <c r="A24" s="47"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="57"/>
-      <c r="B25" s="57"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
+      <c r="A25" s="47"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="57"/>
-      <c r="B26" s="57"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="57"/>
-      <c r="B27" s="57"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="57"/>
+      <c r="A27" s="47"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="57"/>
-      <c r="B28" s="57"/>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
+      <c r="A28" s="47"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="57"/>
-      <c r="B29" s="57"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
+      <c r="A29" s="47"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="57"/>
-      <c r="B30" s="57"/>
-      <c r="C30" s="57"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="57"/>
-      <c r="B31" s="57"/>
-      <c r="C31" s="57"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="57"/>
+      <c r="A31" s="47"/>
+      <c r="B31" s="47"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="57"/>
-      <c r="B32" s="57"/>
-      <c r="C32" s="57"/>
-      <c r="D32" s="57"/>
-      <c r="E32" s="57"/>
-      <c r="F32" s="57"/>
+      <c r="A32" s="47"/>
+      <c r="B32" s="47"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -17110,112 +13626,112 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="54" t="s">
-        <v>134</v>
-      </c>
-      <c r="B4" s="54" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="54" t="s">
-        <v>136</v>
-      </c>
-      <c r="D4" s="54" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" s="54" t="s">
-        <v>138</v>
-      </c>
-      <c r="F4" s="54" t="s">
-        <v>139</v>
+      <c r="A4" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="44" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="58" t="s">
-        <v>140</v>
-      </c>
-      <c r="B5" s="59" t="s">
-        <v>141</v>
-      </c>
-      <c r="C5" s="59" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" s="59" t="s">
-        <v>143</v>
-      </c>
-      <c r="E5" s="59" t="s">
-        <v>144</v>
-      </c>
-      <c r="F5" s="59" t="s">
-        <v>145</v>
+      <c r="A5" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="49" t="s">
+        <v>111</v>
+      </c>
+      <c r="F5" s="49" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="B6" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>148</v>
-      </c>
-      <c r="D6" s="59" t="s">
-        <v>149</v>
-      </c>
-      <c r="E6" s="59" t="s">
-        <v>150</v>
-      </c>
-      <c r="F6" s="59" t="s">
-        <v>151</v>
+      <c r="A6" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="F6" s="49" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="58" t="s">
-        <v>152</v>
-      </c>
-      <c r="B7" s="59" t="s">
-        <v>153</v>
-      </c>
-      <c r="C7" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="D7" s="59" t="s">
-        <v>155</v>
-      </c>
-      <c r="E7" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="F7" s="59" t="s">
-        <v>157</v>
+      <c r="A7" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" s="49" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="58" t="s">
-        <v>158</v>
-      </c>
-      <c r="B8" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="C8" s="59" t="s">
-        <v>160</v>
-      </c>
-      <c r="D8" s="59" t="s">
-        <v>161</v>
-      </c>
-      <c r="E8" s="59" t="s">
-        <v>162</v>
-      </c>
-      <c r="F8" s="59" t="s">
-        <v>163</v>
+      <c r="A8" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="49" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8" s="49" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -17246,170 +13762,170 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="60" t="s">
-        <v>140</v>
-      </c>
-      <c r="B4" s="61" t="n">
+      <c r="A4" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="51" t="n">
         <v>0.25</v>
       </c>
-      <c r="D4" s="62" t="s">
+      <c r="D4" s="52" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="60" t="s">
-        <v>146</v>
-      </c>
-      <c r="B5" s="61" t="n">
+      <c r="A5" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="51" t="n">
         <v>0.3</v>
       </c>
-      <c r="D5" s="62" t="s">
+      <c r="D5" s="52" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="B6" s="61" t="n">
+      <c r="A6" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="51" t="n">
         <v>0.25</v>
       </c>
-      <c r="D6" s="62" t="s">
-        <v>168</v>
+      <c r="D6" s="52" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="B7" s="61" t="n">
+      <c r="A7" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" s="51" t="n">
         <v>0.2</v>
       </c>
-      <c r="D7" s="62" t="s">
-        <v>169</v>
+      <c r="D7" s="52" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="63" t="s">
-        <v>170</v>
-      </c>
-      <c r="B8" s="64" t="n">
+      <c r="A8" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" s="54" t="n">
         <f aca="false">SUM(B4:B7)</f>
         <v>1</v>
       </c>
-      <c r="D8" s="62" t="s">
-        <v>171</v>
+      <c r="D8" s="52" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D9" s="62" t="s">
-        <v>172</v>
+      <c r="D9" s="52" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="62" t="s">
-        <v>173</v>
+      <c r="D10" s="52" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D11" s="62" t="s">
-        <v>174</v>
+      <c r="D11" s="52" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D12" s="62" t="s">
-        <v>175</v>
+      <c r="D12" s="52" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D13" s="62" t="s">
-        <v>176</v>
+      <c r="D13" s="52" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D14" s="62" t="s">
-        <v>177</v>
+      <c r="D14" s="52" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="62" t="s">
-        <v>178</v>
+      <c r="D15" s="52" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="62" t="s">
-        <v>179</v>
+      <c r="D16" s="52" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="62"/>
+      <c r="D17" s="52"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="62"/>
+      <c r="D18" s="52"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="62"/>
+      <c r="D19" s="52"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="62"/>
+      <c r="D20" s="52"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D21" s="62"/>
+      <c r="D21" s="52"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D22" s="62"/>
+      <c r="D22" s="52"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D23" s="62"/>
+      <c r="D23" s="52"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D24" s="62"/>
+      <c r="D24" s="52"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D25" s="62"/>
+      <c r="D25" s="52"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D26" s="62"/>
+      <c r="D26" s="52"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D27" s="62"/>
+      <c r="D27" s="52"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D28" s="62"/>
+      <c r="D28" s="52"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D29" s="62"/>
+      <c r="D29" s="52"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D30" s="62"/>
+      <c r="D30" s="52"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D31" s="62"/>
+      <c r="D31" s="52"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D32" s="62"/>
+      <c r="D32" s="52"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D33" s="62"/>
+      <c r="D33" s="52"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B8">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>ABS(B8-1)&gt;0.005</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Part-Supplier Risk Model/Supplier_Scorecard.xlsx
+++ b/Part-Supplier Risk Model/Supplier_Scorecard.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="151">
   <si>
     <t xml:space="preserve">Supplier Scorecard — how to use</t>
   </si>
@@ -258,18 +258,24 @@
     <t xml:space="preserve">Risk Suggestions - feed for the Part-Supplier Risk Model</t>
   </si>
   <si>
-    <t xml:space="preserve">Fully automatic, one row per supplier. Translation: risk = 6 - average performance (scorecard 5 = excellent -&gt; risk 1 = low), rounded to the nearest whole score and clamped to 1-5. Type the suggested values into the PART_RISK tab of Part_Supplier_Risk_Model - they are a starting point, not an override; adjust with judgment and with what the scorecard cannot see.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPPLIER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCORECARD PERFORMANCE (auto, 5 = excellent)</t>
+    <t xml:space="preserve">One row per PART-SUPPLIER combo: label the part (as it will appear in PART_RISK), pick the Supplier and the Process/part type that makes it - the averages then use only that supplier's logged projects of that process. Leave Process blank to use all the supplier's projects. Translation: risk = 6 - average performance (scorecard 5 = excellent -&gt; risk 1 = low), rounded and clamped to 1-5. Type the suggested values into the PART_RISK tab of Part_Supplier_Risk_Model - a starting point, not an override.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. LABEL THE PART</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. PICK THE COMBO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCORECARD PERFORMANCE FOR THE COMBO (auto, 5 = excellent)</t>
   </si>
   <si>
     <t xml:space="preserve">SUGGESTED RISK ENTRIES FOR PART_RISK (1 = low risk ... 5 = high)</t>
   </si>
   <si>
+    <t xml:space="preserve">Part (number / description)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quality_Compliance (suggest)</t>
   </si>
   <si>
@@ -279,22 +285,28 @@
     <t xml:space="preserve">Supplier_Stability (suggest)</t>
   </si>
   <si>
+    <t xml:space="preserve">cA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rA</t>
+  </si>
+  <si>
     <t xml:space="preserve">HOW THE TRANSLATION WORKS</t>
   </si>
   <si>
-    <t xml:space="preserve">Quality_Compliance  &lt;-  6 - avg Quality.  What they actually delivered is direct evidence for the part's quality risk.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capacity  &lt;-  6 - avg Lead time.  Observed delivery performance is the visible side of capacity; sanity-check against On-time %.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supplier_Stability  &lt;-  6 - average(Responsiveness, Cost).  Cost has no part-level column in the risk register, but erratic pricing and poor cost transparency - like slow communication - are evidence about the supplier as a business, so both feed the Stability suggestion.</t>
+    <t xml:space="preserve">Quality_Compliance  &lt;-  6 - avg Quality of THIS combo (this supplier's projects of this process).  What they delivered on this kind of part is direct evidence for its quality risk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacity  &lt;-  6 - avg Lead time of THIS combo.  Observed delivery performance is the visible side of capacity; sanity-check against On-time %.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplier_Stability  &lt;-  6 - average(Responsiveness, Cost) across ALL the supplier's projects, regardless of process - stability is about the supplier as a business, not one part. Cost has no part-level column in the risk register, but erratic pricing and poor cost transparency - like slow communication - are stability evidence.</t>
   </si>
   <si>
     <t xml:space="preserve">No scorecard equivalent - score these by judgment in the master model:  Sourcing_Backup (do alternatives exist?),  External_Factors (location, logistics, borders),  Impact (what the part means to the model),  Qty_per_Model / volume.</t>
   </si>
   <si>
-    <t xml:space="preserve">Suggestions round to the nearest whole score and clamp to 1-5. A supplier with few projects logged (see Projects column) is thin evidence - weigh it accordingly.</t>
+    <t xml:space="preserve">Suggestions round to the nearest whole score and clamp to 1-5. Few projects behind a combo (see Projects column) = thin evidence - weigh it accordingly.</t>
   </si>
   <si>
     <t xml:space="preserve">Supplier directory</t>
@@ -478,7 +490,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="0"/>
@@ -486,8 +498,7 @@
     <numFmt numFmtId="168" formatCode="#,##0"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="0%"/>
-    <numFmt numFmtId="171" formatCode="General"/>
-    <numFmt numFmtId="172" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -672,7 +683,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -705,8 +716,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF6DC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFFFF6DC"/>
       </patternFill>
     </fill>
   </fills>
@@ -925,15 +942,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -941,7 +958,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -981,11 +998,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="24" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1142,7 +1159,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
+      <rgbColor rgb="FFFFF6DC"/>
       <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFF8696B"/>
@@ -1159,7 +1176,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFD9E2F3"/>
       <rgbColor rgb="FFF9F9F9"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -1353,11 +1370,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="29834272"/>
-        <c:axId val="67701022"/>
+        <c:axId val="68840439"/>
+        <c:axId val="82587896"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="29834272"/>
+        <c:axId val="68840439"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1389,7 +1406,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67701022"/>
+        <c:crossAx val="82587896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1397,7 +1414,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67701022"/>
+        <c:axId val="82587896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -1441,7 +1458,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29834272"/>
+        <c:crossAx val="68840439"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11721,18 +11738,22 @@
     <tabColor rgb="FFC00000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="16" min="15" style="0" width="4"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11753,1523 +11774,2290 @@
         <v>77</v>
       </c>
       <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
+      <c r="D3" s="35" t="s">
+        <v>78</v>
+      </c>
       <c r="E3" s="35"/>
       <c r="F3" s="35"/>
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
-      <c r="I3" s="35" t="s">
-        <v>78</v>
-      </c>
+      <c r="I3" s="35"/>
       <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
+      <c r="K3" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="C4" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="E4" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="F4" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="G4" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="H4" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="I4" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="36" t="s">
+      <c r="J4" s="36" t="s">
         <v>69</v>
-      </c>
-      <c r="I4" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="J4" s="36" t="s">
-        <v>80</v>
       </c>
       <c r="K4" s="36" t="s">
         <v>81</v>
       </c>
+      <c r="L4" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="M4" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="O4" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="P4" s="33" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="37" t="str">
-        <f aca="false">IF(Suppliers!A3="","",Suppliers!A3)</f>
-        <v>Fictiv</v>
-      </c>
-      <c r="B5" s="38" t="n">
-        <f aca="false">IF($A5="","",COUNTIF('Score Log'!$C$4:$C$203,$A5))</f>
-        <v>1</v>
-      </c>
-      <c r="C5" s="39" t="n">
-        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A5),1),"-"))</f>
-        <v>4</v>
-      </c>
-      <c r="D5" s="39" t="n">
-        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A5),1),"-"))</f>
-        <v>5</v>
-      </c>
-      <c r="E5" s="39" t="n">
-        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A5),1),"-"))</f>
-        <v>4</v>
-      </c>
-      <c r="F5" s="39" t="n">
-        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A5),1),"-"))</f>
-        <v>5</v>
-      </c>
-      <c r="G5" s="39" t="n">
-        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A5),1),"-"))</f>
-        <v>4.5</v>
-      </c>
-      <c r="H5" s="40" t="n">
-        <f aca="false">IF($A5="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A5,'Score Log'!$U$4:$U$203,"Yes")/$B5,"-"))</f>
-        <v>1</v>
-      </c>
-      <c r="I5" s="41" t="n">
-        <f aca="false">IF($A5="","",IF(ISNUMBER($D5),MAX(1,MIN(5,ROUND(6-$D5,0))),"-"))</f>
-        <v>1</v>
-      </c>
-      <c r="J5" s="41" t="n">
-        <f aca="false">IF($A5="","",IF(ISNUMBER($E5),MAX(1,MIN(5,ROUND(6-$E5,0))),"-"))</f>
-        <v>2</v>
-      </c>
-      <c r="K5" s="41" t="n">
-        <f aca="false">IF($A5="","",IF(AND(ISNUMBER($F5),ISNUMBER($C5)),MAX(1,MIN(5,ROUND(6-AVERAGE($F5,$C5),0))),IF(ISNUMBER($F5),MAX(1,MIN(5,ROUND(6-$F5,0))),"-")))</f>
-        <v>2</v>
+      <c r="A5" s="37"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="38" t="str">
+        <f aca="false">IF($B5="","",IF($C5="",COUNTIF('Score Log'!$C$4:$C$203,$B5),COUNTIFS('Score Log'!$C$4:$C$203,$B5,'Score Log'!$D$4:$D$203,$C5)))</f>
+        <v/>
+      </c>
+      <c r="E5" s="39" t="str">
+        <f aca="false">IF($B5="","",IFERROR(ROUND(IF($C5="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B5),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B5,'Score Log'!$D$4:$D$203,$C5)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F5" s="39" t="str">
+        <f aca="false">IF($B5="","",IFERROR(ROUND(IF($C5="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B5),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B5,'Score Log'!$D$4:$D$203,$C5)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G5" s="39" t="str">
+        <f aca="false">IF($B5="","",IFERROR(ROUND(IF($C5="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B5),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B5,'Score Log'!$D$4:$D$203,$C5)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H5" s="39" t="str">
+        <f aca="false">IF($B5="","",IFERROR(ROUND(IF($C5="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B5),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B5,'Score Log'!$D$4:$D$203,$C5)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I5" s="39" t="str">
+        <f aca="false">IF($B5="","",IFERROR(ROUND(IF($C5="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B5),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B5,'Score Log'!$D$4:$D$203,$C5)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J5" s="40" t="str">
+        <f aca="false">IF(OR($B5="",$D5=0),"",IFERROR(IF($C5="",COUNTIFS('Score Log'!$C$4:$C$203,$B5,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B5,'Score Log'!$D$4:$D$203,$C5,'Score Log'!$U$4:$U$203,"Yes"))/$D5,"-"))</f>
+        <v/>
+      </c>
+      <c r="K5" s="41" t="str">
+        <f aca="false">IF($B5="","",IF(ISNUMBER($F5),MAX(1,MIN(5,ROUND(6-$F5,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L5" s="41" t="str">
+        <f aca="false">IF($B5="","",IF(ISNUMBER($G5),MAX(1,MIN(5,ROUND(6-$G5,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M5" s="41" t="str">
+        <f aca="false">IF($B5="","",IF(AND(ISNUMBER($P5),ISNUMBER($O5)),MAX(1,MIN(5,ROUND(6-AVERAGE($P5,$O5),0))),IF(ISNUMBER($P5),MAX(1,MIN(5,ROUND(6-$P5,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O5" s="33" t="str">
+        <f aca="false">IF($B5="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B5),""))</f>
+        <v/>
+      </c>
+      <c r="P5" s="33" t="str">
+        <f aca="false">IF($B5="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B5),""))</f>
+        <v/>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="37" t="str">
-        <f aca="false">IF(Suppliers!A4="","",Suppliers!A4)</f>
-        <v>Advanced Plastiform</v>
-      </c>
-      <c r="B6" s="38" t="n">
-        <f aca="false">IF($A6="","",COUNTIF('Score Log'!$C$4:$C$203,$A6))</f>
-        <v>1</v>
-      </c>
-      <c r="C6" s="39" t="str">
-        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A6),1),"-"))</f>
-        <v>-</v>
-      </c>
-      <c r="D6" s="39" t="str">
-        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A6),1),"-"))</f>
-        <v>-</v>
+      <c r="A6" s="37"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="38" t="str">
+        <f aca="false">IF($B6="","",IF($C6="",COUNTIF('Score Log'!$C$4:$C$203,$B6),COUNTIFS('Score Log'!$C$4:$C$203,$B6,'Score Log'!$D$4:$D$203,$C6)))</f>
+        <v/>
       </c>
       <c r="E6" s="39" t="str">
-        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A6),1),"-"))</f>
-        <v>-</v>
+        <f aca="false">IF($B6="","",IFERROR(ROUND(IF($C6="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B6),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B6,'Score Log'!$D$4:$D$203,$C6)),1),"-"))</f>
+        <v/>
       </c>
       <c r="F6" s="39" t="str">
-        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A6),1),"-"))</f>
-        <v>-</v>
+        <f aca="false">IF($B6="","",IFERROR(ROUND(IF($C6="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B6),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B6,'Score Log'!$D$4:$D$203,$C6)),1),"-"))</f>
+        <v/>
       </c>
       <c r="G6" s="39" t="str">
-        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A6),1),"-"))</f>
-        <v>-</v>
-      </c>
-      <c r="H6" s="40" t="n">
-        <f aca="false">IF($A6="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A6,'Score Log'!$U$4:$U$203,"Yes")/$B6,"-"))</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="41" t="str">
-        <f aca="false">IF($A6="","",IF(ISNUMBER($D6),MAX(1,MIN(5,ROUND(6-$D6,0))),"-"))</f>
-        <v>-</v>
-      </c>
-      <c r="J6" s="41" t="str">
-        <f aca="false">IF($A6="","",IF(ISNUMBER($E6),MAX(1,MIN(5,ROUND(6-$E6,0))),"-"))</f>
-        <v>-</v>
+        <f aca="false">IF($B6="","",IFERROR(ROUND(IF($C6="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B6),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B6,'Score Log'!$D$4:$D$203,$C6)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H6" s="39" t="str">
+        <f aca="false">IF($B6="","",IFERROR(ROUND(IF($C6="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B6),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B6,'Score Log'!$D$4:$D$203,$C6)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I6" s="39" t="str">
+        <f aca="false">IF($B6="","",IFERROR(ROUND(IF($C6="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B6),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B6,'Score Log'!$D$4:$D$203,$C6)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J6" s="40" t="str">
+        <f aca="false">IF(OR($B6="",$D6=0),"",IFERROR(IF($C6="",COUNTIFS('Score Log'!$C$4:$C$203,$B6,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B6,'Score Log'!$D$4:$D$203,$C6,'Score Log'!$U$4:$U$203,"Yes"))/$D6,"-"))</f>
+        <v/>
       </c>
       <c r="K6" s="41" t="str">
-        <f aca="false">IF($A6="","",IF(AND(ISNUMBER($F6),ISNUMBER($C6)),MAX(1,MIN(5,ROUND(6-AVERAGE($F6,$C6),0))),IF(ISNUMBER($F6),MAX(1,MIN(5,ROUND(6-$F6,0))),"-")))</f>
-        <v>-</v>
+        <f aca="false">IF($B6="","",IF(ISNUMBER($F6),MAX(1,MIN(5,ROUND(6-$F6,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L6" s="41" t="str">
+        <f aca="false">IF($B6="","",IF(ISNUMBER($G6),MAX(1,MIN(5,ROUND(6-$G6,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M6" s="41" t="str">
+        <f aca="false">IF($B6="","",IF(AND(ISNUMBER($P6),ISNUMBER($O6)),MAX(1,MIN(5,ROUND(6-AVERAGE($P6,$O6),0))),IF(ISNUMBER($P6),MAX(1,MIN(5,ROUND(6-$P6,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O6" s="33" t="str">
+        <f aca="false">IF($B6="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B6),""))</f>
+        <v/>
+      </c>
+      <c r="P6" s="33" t="str">
+        <f aca="false">IF($B6="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B6),""))</f>
+        <v/>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37" t="str">
-        <f aca="false">IF(Suppliers!A5="","",Suppliers!A5)</f>
-        <v/>
-      </c>
-      <c r="B7" s="38" t="str">
-        <f aca="false">IF($A7="","",COUNTIF('Score Log'!$C$4:$C$203,$A7))</f>
-        <v/>
-      </c>
-      <c r="C7" s="39" t="str">
-        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A7),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D7" s="39" t="str">
-        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A7),1),"-"))</f>
+      <c r="A7" s="37"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="38" t="str">
+        <f aca="false">IF($B7="","",IF($C7="",COUNTIF('Score Log'!$C$4:$C$203,$B7),COUNTIFS('Score Log'!$C$4:$C$203,$B7,'Score Log'!$D$4:$D$203,$C7)))</f>
         <v/>
       </c>
       <c r="E7" s="39" t="str">
-        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A7),1),"-"))</f>
+        <f aca="false">IF($B7="","",IFERROR(ROUND(IF($C7="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B7),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B7,'Score Log'!$D$4:$D$203,$C7)),1),"-"))</f>
         <v/>
       </c>
       <c r="F7" s="39" t="str">
-        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A7),1),"-"))</f>
+        <f aca="false">IF($B7="","",IFERROR(ROUND(IF($C7="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B7),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B7,'Score Log'!$D$4:$D$203,$C7)),1),"-"))</f>
         <v/>
       </c>
       <c r="G7" s="39" t="str">
-        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A7),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H7" s="40" t="str">
-        <f aca="false">IF($A7="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A7,'Score Log'!$U$4:$U$203,"Yes")/$B7,"-"))</f>
-        <v/>
-      </c>
-      <c r="I7" s="41" t="str">
-        <f aca="false">IF($A7="","",IF(ISNUMBER($D7),MAX(1,MIN(5,ROUND(6-$D7,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J7" s="41" t="str">
-        <f aca="false">IF($A7="","",IF(ISNUMBER($E7),MAX(1,MIN(5,ROUND(6-$E7,0))),"-"))</f>
+        <f aca="false">IF($B7="","",IFERROR(ROUND(IF($C7="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B7),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B7,'Score Log'!$D$4:$D$203,$C7)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H7" s="39" t="str">
+        <f aca="false">IF($B7="","",IFERROR(ROUND(IF($C7="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B7),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B7,'Score Log'!$D$4:$D$203,$C7)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I7" s="39" t="str">
+        <f aca="false">IF($B7="","",IFERROR(ROUND(IF($C7="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B7),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B7,'Score Log'!$D$4:$D$203,$C7)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J7" s="40" t="str">
+        <f aca="false">IF(OR($B7="",$D7=0),"",IFERROR(IF($C7="",COUNTIFS('Score Log'!$C$4:$C$203,$B7,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B7,'Score Log'!$D$4:$D$203,$C7,'Score Log'!$U$4:$U$203,"Yes"))/$D7,"-"))</f>
         <v/>
       </c>
       <c r="K7" s="41" t="str">
-        <f aca="false">IF($A7="","",IF(AND(ISNUMBER($F7),ISNUMBER($C7)),MAX(1,MIN(5,ROUND(6-AVERAGE($F7,$C7),0))),IF(ISNUMBER($F7),MAX(1,MIN(5,ROUND(6-$F7,0))),"-")))</f>
+        <f aca="false">IF($B7="","",IF(ISNUMBER($F7),MAX(1,MIN(5,ROUND(6-$F7,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L7" s="41" t="str">
+        <f aca="false">IF($B7="","",IF(ISNUMBER($G7),MAX(1,MIN(5,ROUND(6-$G7,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M7" s="41" t="str">
+        <f aca="false">IF($B7="","",IF(AND(ISNUMBER($P7),ISNUMBER($O7)),MAX(1,MIN(5,ROUND(6-AVERAGE($P7,$O7),0))),IF(ISNUMBER($P7),MAX(1,MIN(5,ROUND(6-$P7,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O7" s="33" t="str">
+        <f aca="false">IF($B7="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B7),""))</f>
+        <v/>
+      </c>
+      <c r="P7" s="33" t="str">
+        <f aca="false">IF($B7="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B7),""))</f>
         <v/>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="str">
-        <f aca="false">IF(Suppliers!A6="","",Suppliers!A6)</f>
-        <v/>
-      </c>
-      <c r="B8" s="38" t="str">
-        <f aca="false">IF($A8="","",COUNTIF('Score Log'!$C$4:$C$203,$A8))</f>
-        <v/>
-      </c>
-      <c r="C8" s="39" t="str">
-        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A8),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D8" s="39" t="str">
-        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A8),1),"-"))</f>
+      <c r="A8" s="37"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="38" t="str">
+        <f aca="false">IF($B8="","",IF($C8="",COUNTIF('Score Log'!$C$4:$C$203,$B8),COUNTIFS('Score Log'!$C$4:$C$203,$B8,'Score Log'!$D$4:$D$203,$C8)))</f>
         <v/>
       </c>
       <c r="E8" s="39" t="str">
-        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A8),1),"-"))</f>
+        <f aca="false">IF($B8="","",IFERROR(ROUND(IF($C8="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B8),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B8,'Score Log'!$D$4:$D$203,$C8)),1),"-"))</f>
         <v/>
       </c>
       <c r="F8" s="39" t="str">
-        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A8),1),"-"))</f>
+        <f aca="false">IF($B8="","",IFERROR(ROUND(IF($C8="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B8),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B8,'Score Log'!$D$4:$D$203,$C8)),1),"-"))</f>
         <v/>
       </c>
       <c r="G8" s="39" t="str">
-        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A8),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H8" s="40" t="str">
-        <f aca="false">IF($A8="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A8,'Score Log'!$U$4:$U$203,"Yes")/$B8,"-"))</f>
-        <v/>
-      </c>
-      <c r="I8" s="41" t="str">
-        <f aca="false">IF($A8="","",IF(ISNUMBER($D8),MAX(1,MIN(5,ROUND(6-$D8,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J8" s="41" t="str">
-        <f aca="false">IF($A8="","",IF(ISNUMBER($E8),MAX(1,MIN(5,ROUND(6-$E8,0))),"-"))</f>
+        <f aca="false">IF($B8="","",IFERROR(ROUND(IF($C8="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B8),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B8,'Score Log'!$D$4:$D$203,$C8)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H8" s="39" t="str">
+        <f aca="false">IF($B8="","",IFERROR(ROUND(IF($C8="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B8),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B8,'Score Log'!$D$4:$D$203,$C8)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I8" s="39" t="str">
+        <f aca="false">IF($B8="","",IFERROR(ROUND(IF($C8="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B8),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B8,'Score Log'!$D$4:$D$203,$C8)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J8" s="40" t="str">
+        <f aca="false">IF(OR($B8="",$D8=0),"",IFERROR(IF($C8="",COUNTIFS('Score Log'!$C$4:$C$203,$B8,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B8,'Score Log'!$D$4:$D$203,$C8,'Score Log'!$U$4:$U$203,"Yes"))/$D8,"-"))</f>
         <v/>
       </c>
       <c r="K8" s="41" t="str">
-        <f aca="false">IF($A8="","",IF(AND(ISNUMBER($F8),ISNUMBER($C8)),MAX(1,MIN(5,ROUND(6-AVERAGE($F8,$C8),0))),IF(ISNUMBER($F8),MAX(1,MIN(5,ROUND(6-$F8,0))),"-")))</f>
+        <f aca="false">IF($B8="","",IF(ISNUMBER($F8),MAX(1,MIN(5,ROUND(6-$F8,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L8" s="41" t="str">
+        <f aca="false">IF($B8="","",IF(ISNUMBER($G8),MAX(1,MIN(5,ROUND(6-$G8,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M8" s="41" t="str">
+        <f aca="false">IF($B8="","",IF(AND(ISNUMBER($P8),ISNUMBER($O8)),MAX(1,MIN(5,ROUND(6-AVERAGE($P8,$O8),0))),IF(ISNUMBER($P8),MAX(1,MIN(5,ROUND(6-$P8,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O8" s="33" t="str">
+        <f aca="false">IF($B8="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B8),""))</f>
+        <v/>
+      </c>
+      <c r="P8" s="33" t="str">
+        <f aca="false">IF($B8="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B8),""))</f>
         <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="37" t="str">
-        <f aca="false">IF(Suppliers!A7="","",Suppliers!A7)</f>
-        <v/>
-      </c>
-      <c r="B9" s="38" t="str">
-        <f aca="false">IF($A9="","",COUNTIF('Score Log'!$C$4:$C$203,$A9))</f>
-        <v/>
-      </c>
-      <c r="C9" s="39" t="str">
-        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A9),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D9" s="39" t="str">
-        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A9),1),"-"))</f>
+      <c r="A9" s="37"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="38" t="str">
+        <f aca="false">IF($B9="","",IF($C9="",COUNTIF('Score Log'!$C$4:$C$203,$B9),COUNTIFS('Score Log'!$C$4:$C$203,$B9,'Score Log'!$D$4:$D$203,$C9)))</f>
         <v/>
       </c>
       <c r="E9" s="39" t="str">
-        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A9),1),"-"))</f>
+        <f aca="false">IF($B9="","",IFERROR(ROUND(IF($C9="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B9),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B9,'Score Log'!$D$4:$D$203,$C9)),1),"-"))</f>
         <v/>
       </c>
       <c r="F9" s="39" t="str">
-        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A9),1),"-"))</f>
+        <f aca="false">IF($B9="","",IFERROR(ROUND(IF($C9="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B9),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B9,'Score Log'!$D$4:$D$203,$C9)),1),"-"))</f>
         <v/>
       </c>
       <c r="G9" s="39" t="str">
-        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A9),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H9" s="40" t="str">
-        <f aca="false">IF($A9="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A9,'Score Log'!$U$4:$U$203,"Yes")/$B9,"-"))</f>
-        <v/>
-      </c>
-      <c r="I9" s="41" t="str">
-        <f aca="false">IF($A9="","",IF(ISNUMBER($D9),MAX(1,MIN(5,ROUND(6-$D9,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J9" s="41" t="str">
-        <f aca="false">IF($A9="","",IF(ISNUMBER($E9),MAX(1,MIN(5,ROUND(6-$E9,0))),"-"))</f>
+        <f aca="false">IF($B9="","",IFERROR(ROUND(IF($C9="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B9),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B9,'Score Log'!$D$4:$D$203,$C9)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H9" s="39" t="str">
+        <f aca="false">IF($B9="","",IFERROR(ROUND(IF($C9="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B9),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B9,'Score Log'!$D$4:$D$203,$C9)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I9" s="39" t="str">
+        <f aca="false">IF($B9="","",IFERROR(ROUND(IF($C9="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B9),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B9,'Score Log'!$D$4:$D$203,$C9)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J9" s="40" t="str">
+        <f aca="false">IF(OR($B9="",$D9=0),"",IFERROR(IF($C9="",COUNTIFS('Score Log'!$C$4:$C$203,$B9,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B9,'Score Log'!$D$4:$D$203,$C9,'Score Log'!$U$4:$U$203,"Yes"))/$D9,"-"))</f>
         <v/>
       </c>
       <c r="K9" s="41" t="str">
-        <f aca="false">IF($A9="","",IF(AND(ISNUMBER($F9),ISNUMBER($C9)),MAX(1,MIN(5,ROUND(6-AVERAGE($F9,$C9),0))),IF(ISNUMBER($F9),MAX(1,MIN(5,ROUND(6-$F9,0))),"-")))</f>
+        <f aca="false">IF($B9="","",IF(ISNUMBER($F9),MAX(1,MIN(5,ROUND(6-$F9,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L9" s="41" t="str">
+        <f aca="false">IF($B9="","",IF(ISNUMBER($G9),MAX(1,MIN(5,ROUND(6-$G9,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M9" s="41" t="str">
+        <f aca="false">IF($B9="","",IF(AND(ISNUMBER($P9),ISNUMBER($O9)),MAX(1,MIN(5,ROUND(6-AVERAGE($P9,$O9),0))),IF(ISNUMBER($P9),MAX(1,MIN(5,ROUND(6-$P9,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O9" s="33" t="str">
+        <f aca="false">IF($B9="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B9),""))</f>
+        <v/>
+      </c>
+      <c r="P9" s="33" t="str">
+        <f aca="false">IF($B9="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B9),""))</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="37" t="str">
-        <f aca="false">IF(Suppliers!A8="","",Suppliers!A8)</f>
-        <v/>
-      </c>
-      <c r="B10" s="38" t="str">
-        <f aca="false">IF($A10="","",COUNTIF('Score Log'!$C$4:$C$203,$A10))</f>
-        <v/>
-      </c>
-      <c r="C10" s="39" t="str">
-        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A10),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D10" s="39" t="str">
-        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A10),1),"-"))</f>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="38" t="str">
+        <f aca="false">IF($B10="","",IF($C10="",COUNTIF('Score Log'!$C$4:$C$203,$B10),COUNTIFS('Score Log'!$C$4:$C$203,$B10,'Score Log'!$D$4:$D$203,$C10)))</f>
         <v/>
       </c>
       <c r="E10" s="39" t="str">
-        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A10),1),"-"))</f>
+        <f aca="false">IF($B10="","",IFERROR(ROUND(IF($C10="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B10),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B10,'Score Log'!$D$4:$D$203,$C10)),1),"-"))</f>
         <v/>
       </c>
       <c r="F10" s="39" t="str">
-        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A10),1),"-"))</f>
+        <f aca="false">IF($B10="","",IFERROR(ROUND(IF($C10="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B10),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B10,'Score Log'!$D$4:$D$203,$C10)),1),"-"))</f>
         <v/>
       </c>
       <c r="G10" s="39" t="str">
-        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A10),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H10" s="40" t="str">
-        <f aca="false">IF($A10="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A10,'Score Log'!$U$4:$U$203,"Yes")/$B10,"-"))</f>
-        <v/>
-      </c>
-      <c r="I10" s="41" t="str">
-        <f aca="false">IF($A10="","",IF(ISNUMBER($D10),MAX(1,MIN(5,ROUND(6-$D10,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J10" s="41" t="str">
-        <f aca="false">IF($A10="","",IF(ISNUMBER($E10),MAX(1,MIN(5,ROUND(6-$E10,0))),"-"))</f>
+        <f aca="false">IF($B10="","",IFERROR(ROUND(IF($C10="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B10),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B10,'Score Log'!$D$4:$D$203,$C10)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H10" s="39" t="str">
+        <f aca="false">IF($B10="","",IFERROR(ROUND(IF($C10="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B10),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B10,'Score Log'!$D$4:$D$203,$C10)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I10" s="39" t="str">
+        <f aca="false">IF($B10="","",IFERROR(ROUND(IF($C10="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B10),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B10,'Score Log'!$D$4:$D$203,$C10)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J10" s="40" t="str">
+        <f aca="false">IF(OR($B10="",$D10=0),"",IFERROR(IF($C10="",COUNTIFS('Score Log'!$C$4:$C$203,$B10,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B10,'Score Log'!$D$4:$D$203,$C10,'Score Log'!$U$4:$U$203,"Yes"))/$D10,"-"))</f>
         <v/>
       </c>
       <c r="K10" s="41" t="str">
-        <f aca="false">IF($A10="","",IF(AND(ISNUMBER($F10),ISNUMBER($C10)),MAX(1,MIN(5,ROUND(6-AVERAGE($F10,$C10),0))),IF(ISNUMBER($F10),MAX(1,MIN(5,ROUND(6-$F10,0))),"-")))</f>
+        <f aca="false">IF($B10="","",IF(ISNUMBER($F10),MAX(1,MIN(5,ROUND(6-$F10,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L10" s="41" t="str">
+        <f aca="false">IF($B10="","",IF(ISNUMBER($G10),MAX(1,MIN(5,ROUND(6-$G10,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M10" s="41" t="str">
+        <f aca="false">IF($B10="","",IF(AND(ISNUMBER($P10),ISNUMBER($O10)),MAX(1,MIN(5,ROUND(6-AVERAGE($P10,$O10),0))),IF(ISNUMBER($P10),MAX(1,MIN(5,ROUND(6-$P10,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O10" s="33" t="str">
+        <f aca="false">IF($B10="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B10),""))</f>
+        <v/>
+      </c>
+      <c r="P10" s="33" t="str">
+        <f aca="false">IF($B10="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B10),""))</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37" t="str">
-        <f aca="false">IF(Suppliers!A9="","",Suppliers!A9)</f>
-        <v/>
-      </c>
-      <c r="B11" s="38" t="str">
-        <f aca="false">IF($A11="","",COUNTIF('Score Log'!$C$4:$C$203,$A11))</f>
-        <v/>
-      </c>
-      <c r="C11" s="39" t="str">
-        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A11),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D11" s="39" t="str">
-        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A11),1),"-"))</f>
+      <c r="A11" s="37"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="38" t="str">
+        <f aca="false">IF($B11="","",IF($C11="",COUNTIF('Score Log'!$C$4:$C$203,$B11),COUNTIFS('Score Log'!$C$4:$C$203,$B11,'Score Log'!$D$4:$D$203,$C11)))</f>
         <v/>
       </c>
       <c r="E11" s="39" t="str">
-        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A11),1),"-"))</f>
+        <f aca="false">IF($B11="","",IFERROR(ROUND(IF($C11="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B11),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B11,'Score Log'!$D$4:$D$203,$C11)),1),"-"))</f>
         <v/>
       </c>
       <c r="F11" s="39" t="str">
-        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A11),1),"-"))</f>
+        <f aca="false">IF($B11="","",IFERROR(ROUND(IF($C11="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B11),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B11,'Score Log'!$D$4:$D$203,$C11)),1),"-"))</f>
         <v/>
       </c>
       <c r="G11" s="39" t="str">
-        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A11),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H11" s="40" t="str">
-        <f aca="false">IF($A11="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A11,'Score Log'!$U$4:$U$203,"Yes")/$B11,"-"))</f>
-        <v/>
-      </c>
-      <c r="I11" s="41" t="str">
-        <f aca="false">IF($A11="","",IF(ISNUMBER($D11),MAX(1,MIN(5,ROUND(6-$D11,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J11" s="41" t="str">
-        <f aca="false">IF($A11="","",IF(ISNUMBER($E11),MAX(1,MIN(5,ROUND(6-$E11,0))),"-"))</f>
+        <f aca="false">IF($B11="","",IFERROR(ROUND(IF($C11="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B11),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B11,'Score Log'!$D$4:$D$203,$C11)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H11" s="39" t="str">
+        <f aca="false">IF($B11="","",IFERROR(ROUND(IF($C11="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B11),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B11,'Score Log'!$D$4:$D$203,$C11)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I11" s="39" t="str">
+        <f aca="false">IF($B11="","",IFERROR(ROUND(IF($C11="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B11),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B11,'Score Log'!$D$4:$D$203,$C11)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J11" s="40" t="str">
+        <f aca="false">IF(OR($B11="",$D11=0),"",IFERROR(IF($C11="",COUNTIFS('Score Log'!$C$4:$C$203,$B11,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B11,'Score Log'!$D$4:$D$203,$C11,'Score Log'!$U$4:$U$203,"Yes"))/$D11,"-"))</f>
         <v/>
       </c>
       <c r="K11" s="41" t="str">
-        <f aca="false">IF($A11="","",IF(AND(ISNUMBER($F11),ISNUMBER($C11)),MAX(1,MIN(5,ROUND(6-AVERAGE($F11,$C11),0))),IF(ISNUMBER($F11),MAX(1,MIN(5,ROUND(6-$F11,0))),"-")))</f>
+        <f aca="false">IF($B11="","",IF(ISNUMBER($F11),MAX(1,MIN(5,ROUND(6-$F11,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L11" s="41" t="str">
+        <f aca="false">IF($B11="","",IF(ISNUMBER($G11),MAX(1,MIN(5,ROUND(6-$G11,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M11" s="41" t="str">
+        <f aca="false">IF($B11="","",IF(AND(ISNUMBER($P11),ISNUMBER($O11)),MAX(1,MIN(5,ROUND(6-AVERAGE($P11,$O11),0))),IF(ISNUMBER($P11),MAX(1,MIN(5,ROUND(6-$P11,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O11" s="33" t="str">
+        <f aca="false">IF($B11="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B11),""))</f>
+        <v/>
+      </c>
+      <c r="P11" s="33" t="str">
+        <f aca="false">IF($B11="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B11),""))</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37" t="str">
-        <f aca="false">IF(Suppliers!A10="","",Suppliers!A10)</f>
-        <v/>
-      </c>
-      <c r="B12" s="38" t="str">
-        <f aca="false">IF($A12="","",COUNTIF('Score Log'!$C$4:$C$203,$A12))</f>
-        <v/>
-      </c>
-      <c r="C12" s="39" t="str">
-        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A12),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D12" s="39" t="str">
-        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A12),1),"-"))</f>
+      <c r="A12" s="37"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="38" t="str">
+        <f aca="false">IF($B12="","",IF($C12="",COUNTIF('Score Log'!$C$4:$C$203,$B12),COUNTIFS('Score Log'!$C$4:$C$203,$B12,'Score Log'!$D$4:$D$203,$C12)))</f>
         <v/>
       </c>
       <c r="E12" s="39" t="str">
-        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A12),1),"-"))</f>
+        <f aca="false">IF($B12="","",IFERROR(ROUND(IF($C12="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B12),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B12,'Score Log'!$D$4:$D$203,$C12)),1),"-"))</f>
         <v/>
       </c>
       <c r="F12" s="39" t="str">
-        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A12),1),"-"))</f>
+        <f aca="false">IF($B12="","",IFERROR(ROUND(IF($C12="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B12),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B12,'Score Log'!$D$4:$D$203,$C12)),1),"-"))</f>
         <v/>
       </c>
       <c r="G12" s="39" t="str">
-        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A12),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H12" s="40" t="str">
-        <f aca="false">IF($A12="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A12,'Score Log'!$U$4:$U$203,"Yes")/$B12,"-"))</f>
-        <v/>
-      </c>
-      <c r="I12" s="41" t="str">
-        <f aca="false">IF($A12="","",IF(ISNUMBER($D12),MAX(1,MIN(5,ROUND(6-$D12,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J12" s="41" t="str">
-        <f aca="false">IF($A12="","",IF(ISNUMBER($E12),MAX(1,MIN(5,ROUND(6-$E12,0))),"-"))</f>
+        <f aca="false">IF($B12="","",IFERROR(ROUND(IF($C12="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B12),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B12,'Score Log'!$D$4:$D$203,$C12)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H12" s="39" t="str">
+        <f aca="false">IF($B12="","",IFERROR(ROUND(IF($C12="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B12),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B12,'Score Log'!$D$4:$D$203,$C12)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I12" s="39" t="str">
+        <f aca="false">IF($B12="","",IFERROR(ROUND(IF($C12="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B12),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B12,'Score Log'!$D$4:$D$203,$C12)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J12" s="40" t="str">
+        <f aca="false">IF(OR($B12="",$D12=0),"",IFERROR(IF($C12="",COUNTIFS('Score Log'!$C$4:$C$203,$B12,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B12,'Score Log'!$D$4:$D$203,$C12,'Score Log'!$U$4:$U$203,"Yes"))/$D12,"-"))</f>
         <v/>
       </c>
       <c r="K12" s="41" t="str">
-        <f aca="false">IF($A12="","",IF(AND(ISNUMBER($F12),ISNUMBER($C12)),MAX(1,MIN(5,ROUND(6-AVERAGE($F12,$C12),0))),IF(ISNUMBER($F12),MAX(1,MIN(5,ROUND(6-$F12,0))),"-")))</f>
+        <f aca="false">IF($B12="","",IF(ISNUMBER($F12),MAX(1,MIN(5,ROUND(6-$F12,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L12" s="41" t="str">
+        <f aca="false">IF($B12="","",IF(ISNUMBER($G12),MAX(1,MIN(5,ROUND(6-$G12,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M12" s="41" t="str">
+        <f aca="false">IF($B12="","",IF(AND(ISNUMBER($P12),ISNUMBER($O12)),MAX(1,MIN(5,ROUND(6-AVERAGE($P12,$O12),0))),IF(ISNUMBER($P12),MAX(1,MIN(5,ROUND(6-$P12,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O12" s="33" t="str">
+        <f aca="false">IF($B12="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B12),""))</f>
+        <v/>
+      </c>
+      <c r="P12" s="33" t="str">
+        <f aca="false">IF($B12="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B12),""))</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="37" t="str">
-        <f aca="false">IF(Suppliers!A11="","",Suppliers!A11)</f>
-        <v/>
-      </c>
-      <c r="B13" s="38" t="str">
-        <f aca="false">IF($A13="","",COUNTIF('Score Log'!$C$4:$C$203,$A13))</f>
-        <v/>
-      </c>
-      <c r="C13" s="39" t="str">
-        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A13),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D13" s="39" t="str">
-        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A13),1),"-"))</f>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="38" t="str">
+        <f aca="false">IF($B13="","",IF($C13="",COUNTIF('Score Log'!$C$4:$C$203,$B13),COUNTIFS('Score Log'!$C$4:$C$203,$B13,'Score Log'!$D$4:$D$203,$C13)))</f>
         <v/>
       </c>
       <c r="E13" s="39" t="str">
-        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A13),1),"-"))</f>
+        <f aca="false">IF($B13="","",IFERROR(ROUND(IF($C13="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B13),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B13,'Score Log'!$D$4:$D$203,$C13)),1),"-"))</f>
         <v/>
       </c>
       <c r="F13" s="39" t="str">
-        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A13),1),"-"))</f>
+        <f aca="false">IF($B13="","",IFERROR(ROUND(IF($C13="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B13),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B13,'Score Log'!$D$4:$D$203,$C13)),1),"-"))</f>
         <v/>
       </c>
       <c r="G13" s="39" t="str">
-        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A13),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H13" s="40" t="str">
-        <f aca="false">IF($A13="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A13,'Score Log'!$U$4:$U$203,"Yes")/$B13,"-"))</f>
-        <v/>
-      </c>
-      <c r="I13" s="41" t="str">
-        <f aca="false">IF($A13="","",IF(ISNUMBER($D13),MAX(1,MIN(5,ROUND(6-$D13,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J13" s="41" t="str">
-        <f aca="false">IF($A13="","",IF(ISNUMBER($E13),MAX(1,MIN(5,ROUND(6-$E13,0))),"-"))</f>
+        <f aca="false">IF($B13="","",IFERROR(ROUND(IF($C13="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B13),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B13,'Score Log'!$D$4:$D$203,$C13)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H13" s="39" t="str">
+        <f aca="false">IF($B13="","",IFERROR(ROUND(IF($C13="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B13),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B13,'Score Log'!$D$4:$D$203,$C13)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I13" s="39" t="str">
+        <f aca="false">IF($B13="","",IFERROR(ROUND(IF($C13="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B13),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B13,'Score Log'!$D$4:$D$203,$C13)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J13" s="40" t="str">
+        <f aca="false">IF(OR($B13="",$D13=0),"",IFERROR(IF($C13="",COUNTIFS('Score Log'!$C$4:$C$203,$B13,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B13,'Score Log'!$D$4:$D$203,$C13,'Score Log'!$U$4:$U$203,"Yes"))/$D13,"-"))</f>
         <v/>
       </c>
       <c r="K13" s="41" t="str">
-        <f aca="false">IF($A13="","",IF(AND(ISNUMBER($F13),ISNUMBER($C13)),MAX(1,MIN(5,ROUND(6-AVERAGE($F13,$C13),0))),IF(ISNUMBER($F13),MAX(1,MIN(5,ROUND(6-$F13,0))),"-")))</f>
+        <f aca="false">IF($B13="","",IF(ISNUMBER($F13),MAX(1,MIN(5,ROUND(6-$F13,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L13" s="41" t="str">
+        <f aca="false">IF($B13="","",IF(ISNUMBER($G13),MAX(1,MIN(5,ROUND(6-$G13,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M13" s="41" t="str">
+        <f aca="false">IF($B13="","",IF(AND(ISNUMBER($P13),ISNUMBER($O13)),MAX(1,MIN(5,ROUND(6-AVERAGE($P13,$O13),0))),IF(ISNUMBER($P13),MAX(1,MIN(5,ROUND(6-$P13,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O13" s="33" t="str">
+        <f aca="false">IF($B13="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B13),""))</f>
+        <v/>
+      </c>
+      <c r="P13" s="33" t="str">
+        <f aca="false">IF($B13="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B13),""))</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="str">
-        <f aca="false">IF(Suppliers!A12="","",Suppliers!A12)</f>
-        <v/>
-      </c>
-      <c r="B14" s="38" t="str">
-        <f aca="false">IF($A14="","",COUNTIF('Score Log'!$C$4:$C$203,$A14))</f>
-        <v/>
-      </c>
-      <c r="C14" s="39" t="str">
-        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A14),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D14" s="39" t="str">
-        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A14),1),"-"))</f>
+      <c r="A14" s="37"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="38" t="str">
+        <f aca="false">IF($B14="","",IF($C14="",COUNTIF('Score Log'!$C$4:$C$203,$B14),COUNTIFS('Score Log'!$C$4:$C$203,$B14,'Score Log'!$D$4:$D$203,$C14)))</f>
         <v/>
       </c>
       <c r="E14" s="39" t="str">
-        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A14),1),"-"))</f>
+        <f aca="false">IF($B14="","",IFERROR(ROUND(IF($C14="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B14),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B14,'Score Log'!$D$4:$D$203,$C14)),1),"-"))</f>
         <v/>
       </c>
       <c r="F14" s="39" t="str">
-        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A14),1),"-"))</f>
+        <f aca="false">IF($B14="","",IFERROR(ROUND(IF($C14="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B14),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B14,'Score Log'!$D$4:$D$203,$C14)),1),"-"))</f>
         <v/>
       </c>
       <c r="G14" s="39" t="str">
-        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A14),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H14" s="40" t="str">
-        <f aca="false">IF($A14="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A14,'Score Log'!$U$4:$U$203,"Yes")/$B14,"-"))</f>
-        <v/>
-      </c>
-      <c r="I14" s="41" t="str">
-        <f aca="false">IF($A14="","",IF(ISNUMBER($D14),MAX(1,MIN(5,ROUND(6-$D14,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J14" s="41" t="str">
-        <f aca="false">IF($A14="","",IF(ISNUMBER($E14),MAX(1,MIN(5,ROUND(6-$E14,0))),"-"))</f>
+        <f aca="false">IF($B14="","",IFERROR(ROUND(IF($C14="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B14),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B14,'Score Log'!$D$4:$D$203,$C14)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H14" s="39" t="str">
+        <f aca="false">IF($B14="","",IFERROR(ROUND(IF($C14="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B14),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B14,'Score Log'!$D$4:$D$203,$C14)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I14" s="39" t="str">
+        <f aca="false">IF($B14="","",IFERROR(ROUND(IF($C14="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B14),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B14,'Score Log'!$D$4:$D$203,$C14)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J14" s="40" t="str">
+        <f aca="false">IF(OR($B14="",$D14=0),"",IFERROR(IF($C14="",COUNTIFS('Score Log'!$C$4:$C$203,$B14,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B14,'Score Log'!$D$4:$D$203,$C14,'Score Log'!$U$4:$U$203,"Yes"))/$D14,"-"))</f>
         <v/>
       </c>
       <c r="K14" s="41" t="str">
-        <f aca="false">IF($A14="","",IF(AND(ISNUMBER($F14),ISNUMBER($C14)),MAX(1,MIN(5,ROUND(6-AVERAGE($F14,$C14),0))),IF(ISNUMBER($F14),MAX(1,MIN(5,ROUND(6-$F14,0))),"-")))</f>
+        <f aca="false">IF($B14="","",IF(ISNUMBER($F14),MAX(1,MIN(5,ROUND(6-$F14,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L14" s="41" t="str">
+        <f aca="false">IF($B14="","",IF(ISNUMBER($G14),MAX(1,MIN(5,ROUND(6-$G14,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M14" s="41" t="str">
+        <f aca="false">IF($B14="","",IF(AND(ISNUMBER($P14),ISNUMBER($O14)),MAX(1,MIN(5,ROUND(6-AVERAGE($P14,$O14),0))),IF(ISNUMBER($P14),MAX(1,MIN(5,ROUND(6-$P14,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O14" s="33" t="str">
+        <f aca="false">IF($B14="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B14),""))</f>
+        <v/>
+      </c>
+      <c r="P14" s="33" t="str">
+        <f aca="false">IF($B14="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B14),""))</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="37" t="str">
-        <f aca="false">IF(Suppliers!A13="","",Suppliers!A13)</f>
-        <v/>
-      </c>
-      <c r="B15" s="38" t="str">
-        <f aca="false">IF($A15="","",COUNTIF('Score Log'!$C$4:$C$203,$A15))</f>
-        <v/>
-      </c>
-      <c r="C15" s="39" t="str">
-        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A15),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D15" s="39" t="str">
-        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A15),1),"-"))</f>
+      <c r="A15" s="37"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="38" t="str">
+        <f aca="false">IF($B15="","",IF($C15="",COUNTIF('Score Log'!$C$4:$C$203,$B15),COUNTIFS('Score Log'!$C$4:$C$203,$B15,'Score Log'!$D$4:$D$203,$C15)))</f>
         <v/>
       </c>
       <c r="E15" s="39" t="str">
-        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A15),1),"-"))</f>
+        <f aca="false">IF($B15="","",IFERROR(ROUND(IF($C15="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B15),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B15,'Score Log'!$D$4:$D$203,$C15)),1),"-"))</f>
         <v/>
       </c>
       <c r="F15" s="39" t="str">
-        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A15),1),"-"))</f>
+        <f aca="false">IF($B15="","",IFERROR(ROUND(IF($C15="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B15),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B15,'Score Log'!$D$4:$D$203,$C15)),1),"-"))</f>
         <v/>
       </c>
       <c r="G15" s="39" t="str">
-        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A15),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H15" s="40" t="str">
-        <f aca="false">IF($A15="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A15,'Score Log'!$U$4:$U$203,"Yes")/$B15,"-"))</f>
-        <v/>
-      </c>
-      <c r="I15" s="41" t="str">
-        <f aca="false">IF($A15="","",IF(ISNUMBER($D15),MAX(1,MIN(5,ROUND(6-$D15,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J15" s="41" t="str">
-        <f aca="false">IF($A15="","",IF(ISNUMBER($E15),MAX(1,MIN(5,ROUND(6-$E15,0))),"-"))</f>
+        <f aca="false">IF($B15="","",IFERROR(ROUND(IF($C15="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B15),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B15,'Score Log'!$D$4:$D$203,$C15)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H15" s="39" t="str">
+        <f aca="false">IF($B15="","",IFERROR(ROUND(IF($C15="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B15),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B15,'Score Log'!$D$4:$D$203,$C15)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I15" s="39" t="str">
+        <f aca="false">IF($B15="","",IFERROR(ROUND(IF($C15="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B15),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B15,'Score Log'!$D$4:$D$203,$C15)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J15" s="40" t="str">
+        <f aca="false">IF(OR($B15="",$D15=0),"",IFERROR(IF($C15="",COUNTIFS('Score Log'!$C$4:$C$203,$B15,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B15,'Score Log'!$D$4:$D$203,$C15,'Score Log'!$U$4:$U$203,"Yes"))/$D15,"-"))</f>
         <v/>
       </c>
       <c r="K15" s="41" t="str">
-        <f aca="false">IF($A15="","",IF(AND(ISNUMBER($F15),ISNUMBER($C15)),MAX(1,MIN(5,ROUND(6-AVERAGE($F15,$C15),0))),IF(ISNUMBER($F15),MAX(1,MIN(5,ROUND(6-$F15,0))),"-")))</f>
+        <f aca="false">IF($B15="","",IF(ISNUMBER($F15),MAX(1,MIN(5,ROUND(6-$F15,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L15" s="41" t="str">
+        <f aca="false">IF($B15="","",IF(ISNUMBER($G15),MAX(1,MIN(5,ROUND(6-$G15,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M15" s="41" t="str">
+        <f aca="false">IF($B15="","",IF(AND(ISNUMBER($P15),ISNUMBER($O15)),MAX(1,MIN(5,ROUND(6-AVERAGE($P15,$O15),0))),IF(ISNUMBER($P15),MAX(1,MIN(5,ROUND(6-$P15,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O15" s="33" t="str">
+        <f aca="false">IF($B15="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B15),""))</f>
+        <v/>
+      </c>
+      <c r="P15" s="33" t="str">
+        <f aca="false">IF($B15="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B15),""))</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="37" t="str">
-        <f aca="false">IF(Suppliers!A14="","",Suppliers!A14)</f>
-        <v/>
-      </c>
-      <c r="B16" s="38" t="str">
-        <f aca="false">IF($A16="","",COUNTIF('Score Log'!$C$4:$C$203,$A16))</f>
-        <v/>
-      </c>
-      <c r="C16" s="39" t="str">
-        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A16),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D16" s="39" t="str">
-        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A16),1),"-"))</f>
+      <c r="A16" s="37"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="38" t="str">
+        <f aca="false">IF($B16="","",IF($C16="",COUNTIF('Score Log'!$C$4:$C$203,$B16),COUNTIFS('Score Log'!$C$4:$C$203,$B16,'Score Log'!$D$4:$D$203,$C16)))</f>
         <v/>
       </c>
       <c r="E16" s="39" t="str">
-        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A16),1),"-"))</f>
+        <f aca="false">IF($B16="","",IFERROR(ROUND(IF($C16="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B16),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B16,'Score Log'!$D$4:$D$203,$C16)),1),"-"))</f>
         <v/>
       </c>
       <c r="F16" s="39" t="str">
-        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A16),1),"-"))</f>
+        <f aca="false">IF($B16="","",IFERROR(ROUND(IF($C16="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B16),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B16,'Score Log'!$D$4:$D$203,$C16)),1),"-"))</f>
         <v/>
       </c>
       <c r="G16" s="39" t="str">
-        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A16),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H16" s="40" t="str">
-        <f aca="false">IF($A16="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A16,'Score Log'!$U$4:$U$203,"Yes")/$B16,"-"))</f>
-        <v/>
-      </c>
-      <c r="I16" s="41" t="str">
-        <f aca="false">IF($A16="","",IF(ISNUMBER($D16),MAX(1,MIN(5,ROUND(6-$D16,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J16" s="41" t="str">
-        <f aca="false">IF($A16="","",IF(ISNUMBER($E16),MAX(1,MIN(5,ROUND(6-$E16,0))),"-"))</f>
+        <f aca="false">IF($B16="","",IFERROR(ROUND(IF($C16="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B16),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B16,'Score Log'!$D$4:$D$203,$C16)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H16" s="39" t="str">
+        <f aca="false">IF($B16="","",IFERROR(ROUND(IF($C16="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B16),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B16,'Score Log'!$D$4:$D$203,$C16)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I16" s="39" t="str">
+        <f aca="false">IF($B16="","",IFERROR(ROUND(IF($C16="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B16),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B16,'Score Log'!$D$4:$D$203,$C16)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J16" s="40" t="str">
+        <f aca="false">IF(OR($B16="",$D16=0),"",IFERROR(IF($C16="",COUNTIFS('Score Log'!$C$4:$C$203,$B16,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B16,'Score Log'!$D$4:$D$203,$C16,'Score Log'!$U$4:$U$203,"Yes"))/$D16,"-"))</f>
         <v/>
       </c>
       <c r="K16" s="41" t="str">
-        <f aca="false">IF($A16="","",IF(AND(ISNUMBER($F16),ISNUMBER($C16)),MAX(1,MIN(5,ROUND(6-AVERAGE($F16,$C16),0))),IF(ISNUMBER($F16),MAX(1,MIN(5,ROUND(6-$F16,0))),"-")))</f>
+        <f aca="false">IF($B16="","",IF(ISNUMBER($F16),MAX(1,MIN(5,ROUND(6-$F16,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L16" s="41" t="str">
+        <f aca="false">IF($B16="","",IF(ISNUMBER($G16),MAX(1,MIN(5,ROUND(6-$G16,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M16" s="41" t="str">
+        <f aca="false">IF($B16="","",IF(AND(ISNUMBER($P16),ISNUMBER($O16)),MAX(1,MIN(5,ROUND(6-AVERAGE($P16,$O16),0))),IF(ISNUMBER($P16),MAX(1,MIN(5,ROUND(6-$P16,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O16" s="33" t="str">
+        <f aca="false">IF($B16="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B16),""))</f>
+        <v/>
+      </c>
+      <c r="P16" s="33" t="str">
+        <f aca="false">IF($B16="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B16),""))</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="37" t="str">
-        <f aca="false">IF(Suppliers!A15="","",Suppliers!A15)</f>
-        <v/>
-      </c>
-      <c r="B17" s="38" t="str">
-        <f aca="false">IF($A17="","",COUNTIF('Score Log'!$C$4:$C$203,$A17))</f>
-        <v/>
-      </c>
-      <c r="C17" s="39" t="str">
-        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A17),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D17" s="39" t="str">
-        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A17),1),"-"))</f>
+      <c r="A17" s="37"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="38" t="str">
+        <f aca="false">IF($B17="","",IF($C17="",COUNTIF('Score Log'!$C$4:$C$203,$B17),COUNTIFS('Score Log'!$C$4:$C$203,$B17,'Score Log'!$D$4:$D$203,$C17)))</f>
         <v/>
       </c>
       <c r="E17" s="39" t="str">
-        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A17),1),"-"))</f>
+        <f aca="false">IF($B17="","",IFERROR(ROUND(IF($C17="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B17),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B17,'Score Log'!$D$4:$D$203,$C17)),1),"-"))</f>
         <v/>
       </c>
       <c r="F17" s="39" t="str">
-        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A17),1),"-"))</f>
+        <f aca="false">IF($B17="","",IFERROR(ROUND(IF($C17="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B17),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B17,'Score Log'!$D$4:$D$203,$C17)),1),"-"))</f>
         <v/>
       </c>
       <c r="G17" s="39" t="str">
-        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A17),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H17" s="40" t="str">
-        <f aca="false">IF($A17="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A17,'Score Log'!$U$4:$U$203,"Yes")/$B17,"-"))</f>
-        <v/>
-      </c>
-      <c r="I17" s="41" t="str">
-        <f aca="false">IF($A17="","",IF(ISNUMBER($D17),MAX(1,MIN(5,ROUND(6-$D17,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J17" s="41" t="str">
-        <f aca="false">IF($A17="","",IF(ISNUMBER($E17),MAX(1,MIN(5,ROUND(6-$E17,0))),"-"))</f>
+        <f aca="false">IF($B17="","",IFERROR(ROUND(IF($C17="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B17),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B17,'Score Log'!$D$4:$D$203,$C17)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H17" s="39" t="str">
+        <f aca="false">IF($B17="","",IFERROR(ROUND(IF($C17="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B17),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B17,'Score Log'!$D$4:$D$203,$C17)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I17" s="39" t="str">
+        <f aca="false">IF($B17="","",IFERROR(ROUND(IF($C17="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B17),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B17,'Score Log'!$D$4:$D$203,$C17)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J17" s="40" t="str">
+        <f aca="false">IF(OR($B17="",$D17=0),"",IFERROR(IF($C17="",COUNTIFS('Score Log'!$C$4:$C$203,$B17,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B17,'Score Log'!$D$4:$D$203,$C17,'Score Log'!$U$4:$U$203,"Yes"))/$D17,"-"))</f>
         <v/>
       </c>
       <c r="K17" s="41" t="str">
-        <f aca="false">IF($A17="","",IF(AND(ISNUMBER($F17),ISNUMBER($C17)),MAX(1,MIN(5,ROUND(6-AVERAGE($F17,$C17),0))),IF(ISNUMBER($F17),MAX(1,MIN(5,ROUND(6-$F17,0))),"-")))</f>
+        <f aca="false">IF($B17="","",IF(ISNUMBER($F17),MAX(1,MIN(5,ROUND(6-$F17,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L17" s="41" t="str">
+        <f aca="false">IF($B17="","",IF(ISNUMBER($G17),MAX(1,MIN(5,ROUND(6-$G17,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M17" s="41" t="str">
+        <f aca="false">IF($B17="","",IF(AND(ISNUMBER($P17),ISNUMBER($O17)),MAX(1,MIN(5,ROUND(6-AVERAGE($P17,$O17),0))),IF(ISNUMBER($P17),MAX(1,MIN(5,ROUND(6-$P17,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O17" s="33" t="str">
+        <f aca="false">IF($B17="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B17),""))</f>
+        <v/>
+      </c>
+      <c r="P17" s="33" t="str">
+        <f aca="false">IF($B17="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B17),""))</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="37" t="str">
-        <f aca="false">IF(Suppliers!A16="","",Suppliers!A16)</f>
-        <v/>
-      </c>
-      <c r="B18" s="38" t="str">
-        <f aca="false">IF($A18="","",COUNTIF('Score Log'!$C$4:$C$203,$A18))</f>
-        <v/>
-      </c>
-      <c r="C18" s="39" t="str">
-        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A18),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D18" s="39" t="str">
-        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A18),1),"-"))</f>
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="38" t="str">
+        <f aca="false">IF($B18="","",IF($C18="",COUNTIF('Score Log'!$C$4:$C$203,$B18),COUNTIFS('Score Log'!$C$4:$C$203,$B18,'Score Log'!$D$4:$D$203,$C18)))</f>
         <v/>
       </c>
       <c r="E18" s="39" t="str">
-        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A18),1),"-"))</f>
+        <f aca="false">IF($B18="","",IFERROR(ROUND(IF($C18="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B18),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B18,'Score Log'!$D$4:$D$203,$C18)),1),"-"))</f>
         <v/>
       </c>
       <c r="F18" s="39" t="str">
-        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A18),1),"-"))</f>
+        <f aca="false">IF($B18="","",IFERROR(ROUND(IF($C18="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B18),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B18,'Score Log'!$D$4:$D$203,$C18)),1),"-"))</f>
         <v/>
       </c>
       <c r="G18" s="39" t="str">
-        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A18),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H18" s="40" t="str">
-        <f aca="false">IF($A18="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A18,'Score Log'!$U$4:$U$203,"Yes")/$B18,"-"))</f>
-        <v/>
-      </c>
-      <c r="I18" s="41" t="str">
-        <f aca="false">IF($A18="","",IF(ISNUMBER($D18),MAX(1,MIN(5,ROUND(6-$D18,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J18" s="41" t="str">
-        <f aca="false">IF($A18="","",IF(ISNUMBER($E18),MAX(1,MIN(5,ROUND(6-$E18,0))),"-"))</f>
+        <f aca="false">IF($B18="","",IFERROR(ROUND(IF($C18="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B18),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B18,'Score Log'!$D$4:$D$203,$C18)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H18" s="39" t="str">
+        <f aca="false">IF($B18="","",IFERROR(ROUND(IF($C18="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B18),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B18,'Score Log'!$D$4:$D$203,$C18)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I18" s="39" t="str">
+        <f aca="false">IF($B18="","",IFERROR(ROUND(IF($C18="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B18),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B18,'Score Log'!$D$4:$D$203,$C18)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J18" s="40" t="str">
+        <f aca="false">IF(OR($B18="",$D18=0),"",IFERROR(IF($C18="",COUNTIFS('Score Log'!$C$4:$C$203,$B18,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B18,'Score Log'!$D$4:$D$203,$C18,'Score Log'!$U$4:$U$203,"Yes"))/$D18,"-"))</f>
         <v/>
       </c>
       <c r="K18" s="41" t="str">
-        <f aca="false">IF($A18="","",IF(AND(ISNUMBER($F18),ISNUMBER($C18)),MAX(1,MIN(5,ROUND(6-AVERAGE($F18,$C18),0))),IF(ISNUMBER($F18),MAX(1,MIN(5,ROUND(6-$F18,0))),"-")))</f>
+        <f aca="false">IF($B18="","",IF(ISNUMBER($F18),MAX(1,MIN(5,ROUND(6-$F18,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L18" s="41" t="str">
+        <f aca="false">IF($B18="","",IF(ISNUMBER($G18),MAX(1,MIN(5,ROUND(6-$G18,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M18" s="41" t="str">
+        <f aca="false">IF($B18="","",IF(AND(ISNUMBER($P18),ISNUMBER($O18)),MAX(1,MIN(5,ROUND(6-AVERAGE($P18,$O18),0))),IF(ISNUMBER($P18),MAX(1,MIN(5,ROUND(6-$P18,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O18" s="33" t="str">
+        <f aca="false">IF($B18="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B18),""))</f>
+        <v/>
+      </c>
+      <c r="P18" s="33" t="str">
+        <f aca="false">IF($B18="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B18),""))</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="37" t="str">
-        <f aca="false">IF(Suppliers!A17="","",Suppliers!A17)</f>
-        <v/>
-      </c>
-      <c r="B19" s="38" t="str">
-        <f aca="false">IF($A19="","",COUNTIF('Score Log'!$C$4:$C$203,$A19))</f>
-        <v/>
-      </c>
-      <c r="C19" s="39" t="str">
-        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A19),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D19" s="39" t="str">
-        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A19),1),"-"))</f>
+      <c r="A19" s="37"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="38" t="str">
+        <f aca="false">IF($B19="","",IF($C19="",COUNTIF('Score Log'!$C$4:$C$203,$B19),COUNTIFS('Score Log'!$C$4:$C$203,$B19,'Score Log'!$D$4:$D$203,$C19)))</f>
         <v/>
       </c>
       <c r="E19" s="39" t="str">
-        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A19),1),"-"))</f>
+        <f aca="false">IF($B19="","",IFERROR(ROUND(IF($C19="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B19),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B19,'Score Log'!$D$4:$D$203,$C19)),1),"-"))</f>
         <v/>
       </c>
       <c r="F19" s="39" t="str">
-        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A19),1),"-"))</f>
+        <f aca="false">IF($B19="","",IFERROR(ROUND(IF($C19="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B19),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B19,'Score Log'!$D$4:$D$203,$C19)),1),"-"))</f>
         <v/>
       </c>
       <c r="G19" s="39" t="str">
-        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A19),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H19" s="40" t="str">
-        <f aca="false">IF($A19="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A19,'Score Log'!$U$4:$U$203,"Yes")/$B19,"-"))</f>
-        <v/>
-      </c>
-      <c r="I19" s="41" t="str">
-        <f aca="false">IF($A19="","",IF(ISNUMBER($D19),MAX(1,MIN(5,ROUND(6-$D19,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J19" s="41" t="str">
-        <f aca="false">IF($A19="","",IF(ISNUMBER($E19),MAX(1,MIN(5,ROUND(6-$E19,0))),"-"))</f>
+        <f aca="false">IF($B19="","",IFERROR(ROUND(IF($C19="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B19),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B19,'Score Log'!$D$4:$D$203,$C19)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H19" s="39" t="str">
+        <f aca="false">IF($B19="","",IFERROR(ROUND(IF($C19="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B19),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B19,'Score Log'!$D$4:$D$203,$C19)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I19" s="39" t="str">
+        <f aca="false">IF($B19="","",IFERROR(ROUND(IF($C19="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B19),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B19,'Score Log'!$D$4:$D$203,$C19)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J19" s="40" t="str">
+        <f aca="false">IF(OR($B19="",$D19=0),"",IFERROR(IF($C19="",COUNTIFS('Score Log'!$C$4:$C$203,$B19,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B19,'Score Log'!$D$4:$D$203,$C19,'Score Log'!$U$4:$U$203,"Yes"))/$D19,"-"))</f>
         <v/>
       </c>
       <c r="K19" s="41" t="str">
-        <f aca="false">IF($A19="","",IF(AND(ISNUMBER($F19),ISNUMBER($C19)),MAX(1,MIN(5,ROUND(6-AVERAGE($F19,$C19),0))),IF(ISNUMBER($F19),MAX(1,MIN(5,ROUND(6-$F19,0))),"-")))</f>
+        <f aca="false">IF($B19="","",IF(ISNUMBER($F19),MAX(1,MIN(5,ROUND(6-$F19,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L19" s="41" t="str">
+        <f aca="false">IF($B19="","",IF(ISNUMBER($G19),MAX(1,MIN(5,ROUND(6-$G19,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M19" s="41" t="str">
+        <f aca="false">IF($B19="","",IF(AND(ISNUMBER($P19),ISNUMBER($O19)),MAX(1,MIN(5,ROUND(6-AVERAGE($P19,$O19),0))),IF(ISNUMBER($P19),MAX(1,MIN(5,ROUND(6-$P19,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O19" s="33" t="str">
+        <f aca="false">IF($B19="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B19),""))</f>
+        <v/>
+      </c>
+      <c r="P19" s="33" t="str">
+        <f aca="false">IF($B19="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B19),""))</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="37" t="str">
-        <f aca="false">IF(Suppliers!A18="","",Suppliers!A18)</f>
-        <v/>
-      </c>
-      <c r="B20" s="38" t="str">
-        <f aca="false">IF($A20="","",COUNTIF('Score Log'!$C$4:$C$203,$A20))</f>
-        <v/>
-      </c>
-      <c r="C20" s="39" t="str">
-        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A20),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D20" s="39" t="str">
-        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A20),1),"-"))</f>
+      <c r="A20" s="37"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="38" t="str">
+        <f aca="false">IF($B20="","",IF($C20="",COUNTIF('Score Log'!$C$4:$C$203,$B20),COUNTIFS('Score Log'!$C$4:$C$203,$B20,'Score Log'!$D$4:$D$203,$C20)))</f>
         <v/>
       </c>
       <c r="E20" s="39" t="str">
-        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A20),1),"-"))</f>
+        <f aca="false">IF($B20="","",IFERROR(ROUND(IF($C20="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B20),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B20,'Score Log'!$D$4:$D$203,$C20)),1),"-"))</f>
         <v/>
       </c>
       <c r="F20" s="39" t="str">
-        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A20),1),"-"))</f>
+        <f aca="false">IF($B20="","",IFERROR(ROUND(IF($C20="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B20),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B20,'Score Log'!$D$4:$D$203,$C20)),1),"-"))</f>
         <v/>
       </c>
       <c r="G20" s="39" t="str">
-        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A20),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H20" s="40" t="str">
-        <f aca="false">IF($A20="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A20,'Score Log'!$U$4:$U$203,"Yes")/$B20,"-"))</f>
-        <v/>
-      </c>
-      <c r="I20" s="41" t="str">
-        <f aca="false">IF($A20="","",IF(ISNUMBER($D20),MAX(1,MIN(5,ROUND(6-$D20,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J20" s="41" t="str">
-        <f aca="false">IF($A20="","",IF(ISNUMBER($E20),MAX(1,MIN(5,ROUND(6-$E20,0))),"-"))</f>
+        <f aca="false">IF($B20="","",IFERROR(ROUND(IF($C20="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B20),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B20,'Score Log'!$D$4:$D$203,$C20)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H20" s="39" t="str">
+        <f aca="false">IF($B20="","",IFERROR(ROUND(IF($C20="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B20),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B20,'Score Log'!$D$4:$D$203,$C20)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I20" s="39" t="str">
+        <f aca="false">IF($B20="","",IFERROR(ROUND(IF($C20="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B20),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B20,'Score Log'!$D$4:$D$203,$C20)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J20" s="40" t="str">
+        <f aca="false">IF(OR($B20="",$D20=0),"",IFERROR(IF($C20="",COUNTIFS('Score Log'!$C$4:$C$203,$B20,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B20,'Score Log'!$D$4:$D$203,$C20,'Score Log'!$U$4:$U$203,"Yes"))/$D20,"-"))</f>
         <v/>
       </c>
       <c r="K20" s="41" t="str">
-        <f aca="false">IF($A20="","",IF(AND(ISNUMBER($F20),ISNUMBER($C20)),MAX(1,MIN(5,ROUND(6-AVERAGE($F20,$C20),0))),IF(ISNUMBER($F20),MAX(1,MIN(5,ROUND(6-$F20,0))),"-")))</f>
+        <f aca="false">IF($B20="","",IF(ISNUMBER($F20),MAX(1,MIN(5,ROUND(6-$F20,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L20" s="41" t="str">
+        <f aca="false">IF($B20="","",IF(ISNUMBER($G20),MAX(1,MIN(5,ROUND(6-$G20,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M20" s="41" t="str">
+        <f aca="false">IF($B20="","",IF(AND(ISNUMBER($P20),ISNUMBER($O20)),MAX(1,MIN(5,ROUND(6-AVERAGE($P20,$O20),0))),IF(ISNUMBER($P20),MAX(1,MIN(5,ROUND(6-$P20,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O20" s="33" t="str">
+        <f aca="false">IF($B20="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B20),""))</f>
+        <v/>
+      </c>
+      <c r="P20" s="33" t="str">
+        <f aca="false">IF($B20="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B20),""))</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="37" t="str">
-        <f aca="false">IF(Suppliers!A19="","",Suppliers!A19)</f>
-        <v/>
-      </c>
-      <c r="B21" s="38" t="str">
-        <f aca="false">IF($A21="","",COUNTIF('Score Log'!$C$4:$C$203,$A21))</f>
-        <v/>
-      </c>
-      <c r="C21" s="39" t="str">
-        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A21),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D21" s="39" t="str">
-        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A21),1),"-"))</f>
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="38" t="str">
+        <f aca="false">IF($B21="","",IF($C21="",COUNTIF('Score Log'!$C$4:$C$203,$B21),COUNTIFS('Score Log'!$C$4:$C$203,$B21,'Score Log'!$D$4:$D$203,$C21)))</f>
         <v/>
       </c>
       <c r="E21" s="39" t="str">
-        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A21),1),"-"))</f>
+        <f aca="false">IF($B21="","",IFERROR(ROUND(IF($C21="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B21),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B21,'Score Log'!$D$4:$D$203,$C21)),1),"-"))</f>
         <v/>
       </c>
       <c r="F21" s="39" t="str">
-        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A21),1),"-"))</f>
+        <f aca="false">IF($B21="","",IFERROR(ROUND(IF($C21="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B21),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B21,'Score Log'!$D$4:$D$203,$C21)),1),"-"))</f>
         <v/>
       </c>
       <c r="G21" s="39" t="str">
-        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A21),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H21" s="40" t="str">
-        <f aca="false">IF($A21="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A21,'Score Log'!$U$4:$U$203,"Yes")/$B21,"-"))</f>
-        <v/>
-      </c>
-      <c r="I21" s="41" t="str">
-        <f aca="false">IF($A21="","",IF(ISNUMBER($D21),MAX(1,MIN(5,ROUND(6-$D21,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J21" s="41" t="str">
-        <f aca="false">IF($A21="","",IF(ISNUMBER($E21),MAX(1,MIN(5,ROUND(6-$E21,0))),"-"))</f>
+        <f aca="false">IF($B21="","",IFERROR(ROUND(IF($C21="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B21),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B21,'Score Log'!$D$4:$D$203,$C21)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H21" s="39" t="str">
+        <f aca="false">IF($B21="","",IFERROR(ROUND(IF($C21="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B21),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B21,'Score Log'!$D$4:$D$203,$C21)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I21" s="39" t="str">
+        <f aca="false">IF($B21="","",IFERROR(ROUND(IF($C21="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B21),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B21,'Score Log'!$D$4:$D$203,$C21)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J21" s="40" t="str">
+        <f aca="false">IF(OR($B21="",$D21=0),"",IFERROR(IF($C21="",COUNTIFS('Score Log'!$C$4:$C$203,$B21,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B21,'Score Log'!$D$4:$D$203,$C21,'Score Log'!$U$4:$U$203,"Yes"))/$D21,"-"))</f>
         <v/>
       </c>
       <c r="K21" s="41" t="str">
-        <f aca="false">IF($A21="","",IF(AND(ISNUMBER($F21),ISNUMBER($C21)),MAX(1,MIN(5,ROUND(6-AVERAGE($F21,$C21),0))),IF(ISNUMBER($F21),MAX(1,MIN(5,ROUND(6-$F21,0))),"-")))</f>
+        <f aca="false">IF($B21="","",IF(ISNUMBER($F21),MAX(1,MIN(5,ROUND(6-$F21,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L21" s="41" t="str">
+        <f aca="false">IF($B21="","",IF(ISNUMBER($G21),MAX(1,MIN(5,ROUND(6-$G21,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M21" s="41" t="str">
+        <f aca="false">IF($B21="","",IF(AND(ISNUMBER($P21),ISNUMBER($O21)),MAX(1,MIN(5,ROUND(6-AVERAGE($P21,$O21),0))),IF(ISNUMBER($P21),MAX(1,MIN(5,ROUND(6-$P21,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O21" s="33" t="str">
+        <f aca="false">IF($B21="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B21),""))</f>
+        <v/>
+      </c>
+      <c r="P21" s="33" t="str">
+        <f aca="false">IF($B21="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B21),""))</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="37" t="str">
-        <f aca="false">IF(Suppliers!A20="","",Suppliers!A20)</f>
-        <v/>
-      </c>
-      <c r="B22" s="38" t="str">
-        <f aca="false">IF($A22="","",COUNTIF('Score Log'!$C$4:$C$203,$A22))</f>
-        <v/>
-      </c>
-      <c r="C22" s="39" t="str">
-        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A22),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D22" s="39" t="str">
-        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A22),1),"-"))</f>
+      <c r="A22" s="37"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="38" t="str">
+        <f aca="false">IF($B22="","",IF($C22="",COUNTIF('Score Log'!$C$4:$C$203,$B22),COUNTIFS('Score Log'!$C$4:$C$203,$B22,'Score Log'!$D$4:$D$203,$C22)))</f>
         <v/>
       </c>
       <c r="E22" s="39" t="str">
-        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A22),1),"-"))</f>
+        <f aca="false">IF($B22="","",IFERROR(ROUND(IF($C22="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B22),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B22,'Score Log'!$D$4:$D$203,$C22)),1),"-"))</f>
         <v/>
       </c>
       <c r="F22" s="39" t="str">
-        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A22),1),"-"))</f>
+        <f aca="false">IF($B22="","",IFERROR(ROUND(IF($C22="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B22),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B22,'Score Log'!$D$4:$D$203,$C22)),1),"-"))</f>
         <v/>
       </c>
       <c r="G22" s="39" t="str">
-        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A22),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H22" s="40" t="str">
-        <f aca="false">IF($A22="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A22,'Score Log'!$U$4:$U$203,"Yes")/$B22,"-"))</f>
-        <v/>
-      </c>
-      <c r="I22" s="41" t="str">
-        <f aca="false">IF($A22="","",IF(ISNUMBER($D22),MAX(1,MIN(5,ROUND(6-$D22,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J22" s="41" t="str">
-        <f aca="false">IF($A22="","",IF(ISNUMBER($E22),MAX(1,MIN(5,ROUND(6-$E22,0))),"-"))</f>
+        <f aca="false">IF($B22="","",IFERROR(ROUND(IF($C22="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B22),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B22,'Score Log'!$D$4:$D$203,$C22)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H22" s="39" t="str">
+        <f aca="false">IF($B22="","",IFERROR(ROUND(IF($C22="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B22),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B22,'Score Log'!$D$4:$D$203,$C22)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I22" s="39" t="str">
+        <f aca="false">IF($B22="","",IFERROR(ROUND(IF($C22="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B22),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B22,'Score Log'!$D$4:$D$203,$C22)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J22" s="40" t="str">
+        <f aca="false">IF(OR($B22="",$D22=0),"",IFERROR(IF($C22="",COUNTIFS('Score Log'!$C$4:$C$203,$B22,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B22,'Score Log'!$D$4:$D$203,$C22,'Score Log'!$U$4:$U$203,"Yes"))/$D22,"-"))</f>
         <v/>
       </c>
       <c r="K22" s="41" t="str">
-        <f aca="false">IF($A22="","",IF(AND(ISNUMBER($F22),ISNUMBER($C22)),MAX(1,MIN(5,ROUND(6-AVERAGE($F22,$C22),0))),IF(ISNUMBER($F22),MAX(1,MIN(5,ROUND(6-$F22,0))),"-")))</f>
+        <f aca="false">IF($B22="","",IF(ISNUMBER($F22),MAX(1,MIN(5,ROUND(6-$F22,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L22" s="41" t="str">
+        <f aca="false">IF($B22="","",IF(ISNUMBER($G22),MAX(1,MIN(5,ROUND(6-$G22,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M22" s="41" t="str">
+        <f aca="false">IF($B22="","",IF(AND(ISNUMBER($P22),ISNUMBER($O22)),MAX(1,MIN(5,ROUND(6-AVERAGE($P22,$O22),0))),IF(ISNUMBER($P22),MAX(1,MIN(5,ROUND(6-$P22,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O22" s="33" t="str">
+        <f aca="false">IF($B22="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B22),""))</f>
+        <v/>
+      </c>
+      <c r="P22" s="33" t="str">
+        <f aca="false">IF($B22="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B22),""))</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="37" t="str">
-        <f aca="false">IF(Suppliers!A21="","",Suppliers!A21)</f>
-        <v/>
-      </c>
-      <c r="B23" s="38" t="str">
-        <f aca="false">IF($A23="","",COUNTIF('Score Log'!$C$4:$C$203,$A23))</f>
-        <v/>
-      </c>
-      <c r="C23" s="39" t="str">
-        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A23),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D23" s="39" t="str">
-        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A23),1),"-"))</f>
+      <c r="A23" s="37"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="38" t="str">
+        <f aca="false">IF($B23="","",IF($C23="",COUNTIF('Score Log'!$C$4:$C$203,$B23),COUNTIFS('Score Log'!$C$4:$C$203,$B23,'Score Log'!$D$4:$D$203,$C23)))</f>
         <v/>
       </c>
       <c r="E23" s="39" t="str">
-        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A23),1),"-"))</f>
+        <f aca="false">IF($B23="","",IFERROR(ROUND(IF($C23="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B23),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B23,'Score Log'!$D$4:$D$203,$C23)),1),"-"))</f>
         <v/>
       </c>
       <c r="F23" s="39" t="str">
-        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A23),1),"-"))</f>
+        <f aca="false">IF($B23="","",IFERROR(ROUND(IF($C23="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B23),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B23,'Score Log'!$D$4:$D$203,$C23)),1),"-"))</f>
         <v/>
       </c>
       <c r="G23" s="39" t="str">
-        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A23),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H23" s="40" t="str">
-        <f aca="false">IF($A23="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A23,'Score Log'!$U$4:$U$203,"Yes")/$B23,"-"))</f>
-        <v/>
-      </c>
-      <c r="I23" s="41" t="str">
-        <f aca="false">IF($A23="","",IF(ISNUMBER($D23),MAX(1,MIN(5,ROUND(6-$D23,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J23" s="41" t="str">
-        <f aca="false">IF($A23="","",IF(ISNUMBER($E23),MAX(1,MIN(5,ROUND(6-$E23,0))),"-"))</f>
+        <f aca="false">IF($B23="","",IFERROR(ROUND(IF($C23="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B23),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B23,'Score Log'!$D$4:$D$203,$C23)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H23" s="39" t="str">
+        <f aca="false">IF($B23="","",IFERROR(ROUND(IF($C23="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B23),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B23,'Score Log'!$D$4:$D$203,$C23)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I23" s="39" t="str">
+        <f aca="false">IF($B23="","",IFERROR(ROUND(IF($C23="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B23),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B23,'Score Log'!$D$4:$D$203,$C23)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J23" s="40" t="str">
+        <f aca="false">IF(OR($B23="",$D23=0),"",IFERROR(IF($C23="",COUNTIFS('Score Log'!$C$4:$C$203,$B23,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B23,'Score Log'!$D$4:$D$203,$C23,'Score Log'!$U$4:$U$203,"Yes"))/$D23,"-"))</f>
         <v/>
       </c>
       <c r="K23" s="41" t="str">
-        <f aca="false">IF($A23="","",IF(AND(ISNUMBER($F23),ISNUMBER($C23)),MAX(1,MIN(5,ROUND(6-AVERAGE($F23,$C23),0))),IF(ISNUMBER($F23),MAX(1,MIN(5,ROUND(6-$F23,0))),"-")))</f>
+        <f aca="false">IF($B23="","",IF(ISNUMBER($F23),MAX(1,MIN(5,ROUND(6-$F23,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L23" s="41" t="str">
+        <f aca="false">IF($B23="","",IF(ISNUMBER($G23),MAX(1,MIN(5,ROUND(6-$G23,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M23" s="41" t="str">
+        <f aca="false">IF($B23="","",IF(AND(ISNUMBER($P23),ISNUMBER($O23)),MAX(1,MIN(5,ROUND(6-AVERAGE($P23,$O23),0))),IF(ISNUMBER($P23),MAX(1,MIN(5,ROUND(6-$P23,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O23" s="33" t="str">
+        <f aca="false">IF($B23="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B23),""))</f>
+        <v/>
+      </c>
+      <c r="P23" s="33" t="str">
+        <f aca="false">IF($B23="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B23),""))</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="37" t="str">
-        <f aca="false">IF(Suppliers!A22="","",Suppliers!A22)</f>
-        <v/>
-      </c>
-      <c r="B24" s="38" t="str">
-        <f aca="false">IF($A24="","",COUNTIF('Score Log'!$C$4:$C$203,$A24))</f>
-        <v/>
-      </c>
-      <c r="C24" s="39" t="str">
-        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A24),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D24" s="39" t="str">
-        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A24),1),"-"))</f>
+      <c r="A24" s="37"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="38" t="str">
+        <f aca="false">IF($B24="","",IF($C24="",COUNTIF('Score Log'!$C$4:$C$203,$B24),COUNTIFS('Score Log'!$C$4:$C$203,$B24,'Score Log'!$D$4:$D$203,$C24)))</f>
         <v/>
       </c>
       <c r="E24" s="39" t="str">
-        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A24),1),"-"))</f>
+        <f aca="false">IF($B24="","",IFERROR(ROUND(IF($C24="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B24),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B24,'Score Log'!$D$4:$D$203,$C24)),1),"-"))</f>
         <v/>
       </c>
       <c r="F24" s="39" t="str">
-        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A24),1),"-"))</f>
+        <f aca="false">IF($B24="","",IFERROR(ROUND(IF($C24="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B24),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B24,'Score Log'!$D$4:$D$203,$C24)),1),"-"))</f>
         <v/>
       </c>
       <c r="G24" s="39" t="str">
-        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A24),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H24" s="40" t="str">
-        <f aca="false">IF($A24="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A24,'Score Log'!$U$4:$U$203,"Yes")/$B24,"-"))</f>
-        <v/>
-      </c>
-      <c r="I24" s="41" t="str">
-        <f aca="false">IF($A24="","",IF(ISNUMBER($D24),MAX(1,MIN(5,ROUND(6-$D24,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J24" s="41" t="str">
-        <f aca="false">IF($A24="","",IF(ISNUMBER($E24),MAX(1,MIN(5,ROUND(6-$E24,0))),"-"))</f>
+        <f aca="false">IF($B24="","",IFERROR(ROUND(IF($C24="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B24),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B24,'Score Log'!$D$4:$D$203,$C24)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H24" s="39" t="str">
+        <f aca="false">IF($B24="","",IFERROR(ROUND(IF($C24="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B24),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B24,'Score Log'!$D$4:$D$203,$C24)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I24" s="39" t="str">
+        <f aca="false">IF($B24="","",IFERROR(ROUND(IF($C24="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B24),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B24,'Score Log'!$D$4:$D$203,$C24)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J24" s="40" t="str">
+        <f aca="false">IF(OR($B24="",$D24=0),"",IFERROR(IF($C24="",COUNTIFS('Score Log'!$C$4:$C$203,$B24,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B24,'Score Log'!$D$4:$D$203,$C24,'Score Log'!$U$4:$U$203,"Yes"))/$D24,"-"))</f>
         <v/>
       </c>
       <c r="K24" s="41" t="str">
-        <f aca="false">IF($A24="","",IF(AND(ISNUMBER($F24),ISNUMBER($C24)),MAX(1,MIN(5,ROUND(6-AVERAGE($F24,$C24),0))),IF(ISNUMBER($F24),MAX(1,MIN(5,ROUND(6-$F24,0))),"-")))</f>
+        <f aca="false">IF($B24="","",IF(ISNUMBER($F24),MAX(1,MIN(5,ROUND(6-$F24,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L24" s="41" t="str">
+        <f aca="false">IF($B24="","",IF(ISNUMBER($G24),MAX(1,MIN(5,ROUND(6-$G24,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M24" s="41" t="str">
+        <f aca="false">IF($B24="","",IF(AND(ISNUMBER($P24),ISNUMBER($O24)),MAX(1,MIN(5,ROUND(6-AVERAGE($P24,$O24),0))),IF(ISNUMBER($P24),MAX(1,MIN(5,ROUND(6-$P24,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O24" s="33" t="str">
+        <f aca="false">IF($B24="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B24),""))</f>
+        <v/>
+      </c>
+      <c r="P24" s="33" t="str">
+        <f aca="false">IF($B24="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B24),""))</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="37" t="str">
-        <f aca="false">IF(Suppliers!A23="","",Suppliers!A23)</f>
-        <v/>
-      </c>
-      <c r="B25" s="38" t="str">
-        <f aca="false">IF($A25="","",COUNTIF('Score Log'!$C$4:$C$203,$A25))</f>
-        <v/>
-      </c>
-      <c r="C25" s="39" t="str">
-        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A25),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D25" s="39" t="str">
-        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A25),1),"-"))</f>
+      <c r="A25" s="37"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="38" t="str">
+        <f aca="false">IF($B25="","",IF($C25="",COUNTIF('Score Log'!$C$4:$C$203,$B25),COUNTIFS('Score Log'!$C$4:$C$203,$B25,'Score Log'!$D$4:$D$203,$C25)))</f>
         <v/>
       </c>
       <c r="E25" s="39" t="str">
-        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A25),1),"-"))</f>
+        <f aca="false">IF($B25="","",IFERROR(ROUND(IF($C25="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B25),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B25,'Score Log'!$D$4:$D$203,$C25)),1),"-"))</f>
         <v/>
       </c>
       <c r="F25" s="39" t="str">
-        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A25),1),"-"))</f>
+        <f aca="false">IF($B25="","",IFERROR(ROUND(IF($C25="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B25),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B25,'Score Log'!$D$4:$D$203,$C25)),1),"-"))</f>
         <v/>
       </c>
       <c r="G25" s="39" t="str">
-        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A25),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H25" s="40" t="str">
-        <f aca="false">IF($A25="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A25,'Score Log'!$U$4:$U$203,"Yes")/$B25,"-"))</f>
-        <v/>
-      </c>
-      <c r="I25" s="41" t="str">
-        <f aca="false">IF($A25="","",IF(ISNUMBER($D25),MAX(1,MIN(5,ROUND(6-$D25,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J25" s="41" t="str">
-        <f aca="false">IF($A25="","",IF(ISNUMBER($E25),MAX(1,MIN(5,ROUND(6-$E25,0))),"-"))</f>
+        <f aca="false">IF($B25="","",IFERROR(ROUND(IF($C25="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B25),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B25,'Score Log'!$D$4:$D$203,$C25)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H25" s="39" t="str">
+        <f aca="false">IF($B25="","",IFERROR(ROUND(IF($C25="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B25),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B25,'Score Log'!$D$4:$D$203,$C25)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I25" s="39" t="str">
+        <f aca="false">IF($B25="","",IFERROR(ROUND(IF($C25="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B25),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B25,'Score Log'!$D$4:$D$203,$C25)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J25" s="40" t="str">
+        <f aca="false">IF(OR($B25="",$D25=0),"",IFERROR(IF($C25="",COUNTIFS('Score Log'!$C$4:$C$203,$B25,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B25,'Score Log'!$D$4:$D$203,$C25,'Score Log'!$U$4:$U$203,"Yes"))/$D25,"-"))</f>
         <v/>
       </c>
       <c r="K25" s="41" t="str">
-        <f aca="false">IF($A25="","",IF(AND(ISNUMBER($F25),ISNUMBER($C25)),MAX(1,MIN(5,ROUND(6-AVERAGE($F25,$C25),0))),IF(ISNUMBER($F25),MAX(1,MIN(5,ROUND(6-$F25,0))),"-")))</f>
+        <f aca="false">IF($B25="","",IF(ISNUMBER($F25),MAX(1,MIN(5,ROUND(6-$F25,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L25" s="41" t="str">
+        <f aca="false">IF($B25="","",IF(ISNUMBER($G25),MAX(1,MIN(5,ROUND(6-$G25,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M25" s="41" t="str">
+        <f aca="false">IF($B25="","",IF(AND(ISNUMBER($P25),ISNUMBER($O25)),MAX(1,MIN(5,ROUND(6-AVERAGE($P25,$O25),0))),IF(ISNUMBER($P25),MAX(1,MIN(5,ROUND(6-$P25,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O25" s="33" t="str">
+        <f aca="false">IF($B25="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B25),""))</f>
+        <v/>
+      </c>
+      <c r="P25" s="33" t="str">
+        <f aca="false">IF($B25="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B25),""))</f>
         <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="37" t="str">
-        <f aca="false">IF(Suppliers!A24="","",Suppliers!A24)</f>
-        <v/>
-      </c>
-      <c r="B26" s="38" t="str">
-        <f aca="false">IF($A26="","",COUNTIF('Score Log'!$C$4:$C$203,$A26))</f>
-        <v/>
-      </c>
-      <c r="C26" s="39" t="str">
-        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A26),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D26" s="39" t="str">
-        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A26),1),"-"))</f>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="38" t="str">
+        <f aca="false">IF($B26="","",IF($C26="",COUNTIF('Score Log'!$C$4:$C$203,$B26),COUNTIFS('Score Log'!$C$4:$C$203,$B26,'Score Log'!$D$4:$D$203,$C26)))</f>
         <v/>
       </c>
       <c r="E26" s="39" t="str">
-        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A26),1),"-"))</f>
+        <f aca="false">IF($B26="","",IFERROR(ROUND(IF($C26="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B26),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B26,'Score Log'!$D$4:$D$203,$C26)),1),"-"))</f>
         <v/>
       </c>
       <c r="F26" s="39" t="str">
-        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A26),1),"-"))</f>
+        <f aca="false">IF($B26="","",IFERROR(ROUND(IF($C26="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B26),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B26,'Score Log'!$D$4:$D$203,$C26)),1),"-"))</f>
         <v/>
       </c>
       <c r="G26" s="39" t="str">
-        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A26),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H26" s="40" t="str">
-        <f aca="false">IF($A26="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A26,'Score Log'!$U$4:$U$203,"Yes")/$B26,"-"))</f>
-        <v/>
-      </c>
-      <c r="I26" s="41" t="str">
-        <f aca="false">IF($A26="","",IF(ISNUMBER($D26),MAX(1,MIN(5,ROUND(6-$D26,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J26" s="41" t="str">
-        <f aca="false">IF($A26="","",IF(ISNUMBER($E26),MAX(1,MIN(5,ROUND(6-$E26,0))),"-"))</f>
+        <f aca="false">IF($B26="","",IFERROR(ROUND(IF($C26="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B26),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B26,'Score Log'!$D$4:$D$203,$C26)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H26" s="39" t="str">
+        <f aca="false">IF($B26="","",IFERROR(ROUND(IF($C26="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B26),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B26,'Score Log'!$D$4:$D$203,$C26)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I26" s="39" t="str">
+        <f aca="false">IF($B26="","",IFERROR(ROUND(IF($C26="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B26),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B26,'Score Log'!$D$4:$D$203,$C26)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J26" s="40" t="str">
+        <f aca="false">IF(OR($B26="",$D26=0),"",IFERROR(IF($C26="",COUNTIFS('Score Log'!$C$4:$C$203,$B26,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B26,'Score Log'!$D$4:$D$203,$C26,'Score Log'!$U$4:$U$203,"Yes"))/$D26,"-"))</f>
         <v/>
       </c>
       <c r="K26" s="41" t="str">
-        <f aca="false">IF($A26="","",IF(AND(ISNUMBER($F26),ISNUMBER($C26)),MAX(1,MIN(5,ROUND(6-AVERAGE($F26,$C26),0))),IF(ISNUMBER($F26),MAX(1,MIN(5,ROUND(6-$F26,0))),"-")))</f>
+        <f aca="false">IF($B26="","",IF(ISNUMBER($F26),MAX(1,MIN(5,ROUND(6-$F26,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L26" s="41" t="str">
+        <f aca="false">IF($B26="","",IF(ISNUMBER($G26),MAX(1,MIN(5,ROUND(6-$G26,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M26" s="41" t="str">
+        <f aca="false">IF($B26="","",IF(AND(ISNUMBER($P26),ISNUMBER($O26)),MAX(1,MIN(5,ROUND(6-AVERAGE($P26,$O26),0))),IF(ISNUMBER($P26),MAX(1,MIN(5,ROUND(6-$P26,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O26" s="33" t="str">
+        <f aca="false">IF($B26="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B26),""))</f>
+        <v/>
+      </c>
+      <c r="P26" s="33" t="str">
+        <f aca="false">IF($B26="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B26),""))</f>
         <v/>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="37" t="str">
-        <f aca="false">IF(Suppliers!A25="","",Suppliers!A25)</f>
-        <v/>
-      </c>
-      <c r="B27" s="38" t="str">
-        <f aca="false">IF($A27="","",COUNTIF('Score Log'!$C$4:$C$203,$A27))</f>
-        <v/>
-      </c>
-      <c r="C27" s="39" t="str">
-        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A27),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D27" s="39" t="str">
-        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A27),1),"-"))</f>
+      <c r="A27" s="37"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="38" t="str">
+        <f aca="false">IF($B27="","",IF($C27="",COUNTIF('Score Log'!$C$4:$C$203,$B27),COUNTIFS('Score Log'!$C$4:$C$203,$B27,'Score Log'!$D$4:$D$203,$C27)))</f>
         <v/>
       </c>
       <c r="E27" s="39" t="str">
-        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A27),1),"-"))</f>
+        <f aca="false">IF($B27="","",IFERROR(ROUND(IF($C27="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B27),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B27,'Score Log'!$D$4:$D$203,$C27)),1),"-"))</f>
         <v/>
       </c>
       <c r="F27" s="39" t="str">
-        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A27),1),"-"))</f>
+        <f aca="false">IF($B27="","",IFERROR(ROUND(IF($C27="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B27),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B27,'Score Log'!$D$4:$D$203,$C27)),1),"-"))</f>
         <v/>
       </c>
       <c r="G27" s="39" t="str">
-        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A27),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H27" s="40" t="str">
-        <f aca="false">IF($A27="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A27,'Score Log'!$U$4:$U$203,"Yes")/$B27,"-"))</f>
-        <v/>
-      </c>
-      <c r="I27" s="41" t="str">
-        <f aca="false">IF($A27="","",IF(ISNUMBER($D27),MAX(1,MIN(5,ROUND(6-$D27,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J27" s="41" t="str">
-        <f aca="false">IF($A27="","",IF(ISNUMBER($E27),MAX(1,MIN(5,ROUND(6-$E27,0))),"-"))</f>
+        <f aca="false">IF($B27="","",IFERROR(ROUND(IF($C27="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B27),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B27,'Score Log'!$D$4:$D$203,$C27)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H27" s="39" t="str">
+        <f aca="false">IF($B27="","",IFERROR(ROUND(IF($C27="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B27),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B27,'Score Log'!$D$4:$D$203,$C27)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I27" s="39" t="str">
+        <f aca="false">IF($B27="","",IFERROR(ROUND(IF($C27="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B27),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B27,'Score Log'!$D$4:$D$203,$C27)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J27" s="40" t="str">
+        <f aca="false">IF(OR($B27="",$D27=0),"",IFERROR(IF($C27="",COUNTIFS('Score Log'!$C$4:$C$203,$B27,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B27,'Score Log'!$D$4:$D$203,$C27,'Score Log'!$U$4:$U$203,"Yes"))/$D27,"-"))</f>
         <v/>
       </c>
       <c r="K27" s="41" t="str">
-        <f aca="false">IF($A27="","",IF(AND(ISNUMBER($F27),ISNUMBER($C27)),MAX(1,MIN(5,ROUND(6-AVERAGE($F27,$C27),0))),IF(ISNUMBER($F27),MAX(1,MIN(5,ROUND(6-$F27,0))),"-")))</f>
+        <f aca="false">IF($B27="","",IF(ISNUMBER($F27),MAX(1,MIN(5,ROUND(6-$F27,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L27" s="41" t="str">
+        <f aca="false">IF($B27="","",IF(ISNUMBER($G27),MAX(1,MIN(5,ROUND(6-$G27,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M27" s="41" t="str">
+        <f aca="false">IF($B27="","",IF(AND(ISNUMBER($P27),ISNUMBER($O27)),MAX(1,MIN(5,ROUND(6-AVERAGE($P27,$O27),0))),IF(ISNUMBER($P27),MAX(1,MIN(5,ROUND(6-$P27,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O27" s="33" t="str">
+        <f aca="false">IF($B27="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B27),""))</f>
+        <v/>
+      </c>
+      <c r="P27" s="33" t="str">
+        <f aca="false">IF($B27="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B27),""))</f>
         <v/>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="37" t="str">
-        <f aca="false">IF(Suppliers!A26="","",Suppliers!A26)</f>
-        <v/>
-      </c>
-      <c r="B28" s="38" t="str">
-        <f aca="false">IF($A28="","",COUNTIF('Score Log'!$C$4:$C$203,$A28))</f>
-        <v/>
-      </c>
-      <c r="C28" s="39" t="str">
-        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A28),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D28" s="39" t="str">
-        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A28),1),"-"))</f>
+      <c r="A28" s="37"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="38" t="str">
+        <f aca="false">IF($B28="","",IF($C28="",COUNTIF('Score Log'!$C$4:$C$203,$B28),COUNTIFS('Score Log'!$C$4:$C$203,$B28,'Score Log'!$D$4:$D$203,$C28)))</f>
         <v/>
       </c>
       <c r="E28" s="39" t="str">
-        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A28),1),"-"))</f>
+        <f aca="false">IF($B28="","",IFERROR(ROUND(IF($C28="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B28),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B28,'Score Log'!$D$4:$D$203,$C28)),1),"-"))</f>
         <v/>
       </c>
       <c r="F28" s="39" t="str">
-        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A28),1),"-"))</f>
+        <f aca="false">IF($B28="","",IFERROR(ROUND(IF($C28="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B28),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B28,'Score Log'!$D$4:$D$203,$C28)),1),"-"))</f>
         <v/>
       </c>
       <c r="G28" s="39" t="str">
-        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A28),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H28" s="40" t="str">
-        <f aca="false">IF($A28="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A28,'Score Log'!$U$4:$U$203,"Yes")/$B28,"-"))</f>
-        <v/>
-      </c>
-      <c r="I28" s="41" t="str">
-        <f aca="false">IF($A28="","",IF(ISNUMBER($D28),MAX(1,MIN(5,ROUND(6-$D28,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J28" s="41" t="str">
-        <f aca="false">IF($A28="","",IF(ISNUMBER($E28),MAX(1,MIN(5,ROUND(6-$E28,0))),"-"))</f>
+        <f aca="false">IF($B28="","",IFERROR(ROUND(IF($C28="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B28),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B28,'Score Log'!$D$4:$D$203,$C28)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H28" s="39" t="str">
+        <f aca="false">IF($B28="","",IFERROR(ROUND(IF($C28="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B28),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B28,'Score Log'!$D$4:$D$203,$C28)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I28" s="39" t="str">
+        <f aca="false">IF($B28="","",IFERROR(ROUND(IF($C28="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B28),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B28,'Score Log'!$D$4:$D$203,$C28)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J28" s="40" t="str">
+        <f aca="false">IF(OR($B28="",$D28=0),"",IFERROR(IF($C28="",COUNTIFS('Score Log'!$C$4:$C$203,$B28,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B28,'Score Log'!$D$4:$D$203,$C28,'Score Log'!$U$4:$U$203,"Yes"))/$D28,"-"))</f>
         <v/>
       </c>
       <c r="K28" s="41" t="str">
-        <f aca="false">IF($A28="","",IF(AND(ISNUMBER($F28),ISNUMBER($C28)),MAX(1,MIN(5,ROUND(6-AVERAGE($F28,$C28),0))),IF(ISNUMBER($F28),MAX(1,MIN(5,ROUND(6-$F28,0))),"-")))</f>
+        <f aca="false">IF($B28="","",IF(ISNUMBER($F28),MAX(1,MIN(5,ROUND(6-$F28,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L28" s="41" t="str">
+        <f aca="false">IF($B28="","",IF(ISNUMBER($G28),MAX(1,MIN(5,ROUND(6-$G28,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M28" s="41" t="str">
+        <f aca="false">IF($B28="","",IF(AND(ISNUMBER($P28),ISNUMBER($O28)),MAX(1,MIN(5,ROUND(6-AVERAGE($P28,$O28),0))),IF(ISNUMBER($P28),MAX(1,MIN(5,ROUND(6-$P28,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O28" s="33" t="str">
+        <f aca="false">IF($B28="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B28),""))</f>
+        <v/>
+      </c>
+      <c r="P28" s="33" t="str">
+        <f aca="false">IF($B28="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B28),""))</f>
         <v/>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="37" t="str">
-        <f aca="false">IF(Suppliers!A27="","",Suppliers!A27)</f>
-        <v/>
-      </c>
-      <c r="B29" s="38" t="str">
-        <f aca="false">IF($A29="","",COUNTIF('Score Log'!$C$4:$C$203,$A29))</f>
-        <v/>
-      </c>
-      <c r="C29" s="39" t="str">
-        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A29),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D29" s="39" t="str">
-        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A29),1),"-"))</f>
+      <c r="A29" s="37"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="38" t="str">
+        <f aca="false">IF($B29="","",IF($C29="",COUNTIF('Score Log'!$C$4:$C$203,$B29),COUNTIFS('Score Log'!$C$4:$C$203,$B29,'Score Log'!$D$4:$D$203,$C29)))</f>
         <v/>
       </c>
       <c r="E29" s="39" t="str">
-        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A29),1),"-"))</f>
+        <f aca="false">IF($B29="","",IFERROR(ROUND(IF($C29="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B29),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B29,'Score Log'!$D$4:$D$203,$C29)),1),"-"))</f>
         <v/>
       </c>
       <c r="F29" s="39" t="str">
-        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A29),1),"-"))</f>
+        <f aca="false">IF($B29="","",IFERROR(ROUND(IF($C29="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B29),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B29,'Score Log'!$D$4:$D$203,$C29)),1),"-"))</f>
         <v/>
       </c>
       <c r="G29" s="39" t="str">
-        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A29),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H29" s="40" t="str">
-        <f aca="false">IF($A29="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A29,'Score Log'!$U$4:$U$203,"Yes")/$B29,"-"))</f>
-        <v/>
-      </c>
-      <c r="I29" s="41" t="str">
-        <f aca="false">IF($A29="","",IF(ISNUMBER($D29),MAX(1,MIN(5,ROUND(6-$D29,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J29" s="41" t="str">
-        <f aca="false">IF($A29="","",IF(ISNUMBER($E29),MAX(1,MIN(5,ROUND(6-$E29,0))),"-"))</f>
+        <f aca="false">IF($B29="","",IFERROR(ROUND(IF($C29="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B29),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B29,'Score Log'!$D$4:$D$203,$C29)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H29" s="39" t="str">
+        <f aca="false">IF($B29="","",IFERROR(ROUND(IF($C29="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B29),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B29,'Score Log'!$D$4:$D$203,$C29)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I29" s="39" t="str">
+        <f aca="false">IF($B29="","",IFERROR(ROUND(IF($C29="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B29),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B29,'Score Log'!$D$4:$D$203,$C29)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J29" s="40" t="str">
+        <f aca="false">IF(OR($B29="",$D29=0),"",IFERROR(IF($C29="",COUNTIFS('Score Log'!$C$4:$C$203,$B29,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B29,'Score Log'!$D$4:$D$203,$C29,'Score Log'!$U$4:$U$203,"Yes"))/$D29,"-"))</f>
         <v/>
       </c>
       <c r="K29" s="41" t="str">
-        <f aca="false">IF($A29="","",IF(AND(ISNUMBER($F29),ISNUMBER($C29)),MAX(1,MIN(5,ROUND(6-AVERAGE($F29,$C29),0))),IF(ISNUMBER($F29),MAX(1,MIN(5,ROUND(6-$F29,0))),"-")))</f>
+        <f aca="false">IF($B29="","",IF(ISNUMBER($F29),MAX(1,MIN(5,ROUND(6-$F29,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L29" s="41" t="str">
+        <f aca="false">IF($B29="","",IF(ISNUMBER($G29),MAX(1,MIN(5,ROUND(6-$G29,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M29" s="41" t="str">
+        <f aca="false">IF($B29="","",IF(AND(ISNUMBER($P29),ISNUMBER($O29)),MAX(1,MIN(5,ROUND(6-AVERAGE($P29,$O29),0))),IF(ISNUMBER($P29),MAX(1,MIN(5,ROUND(6-$P29,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O29" s="33" t="str">
+        <f aca="false">IF($B29="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B29),""))</f>
+        <v/>
+      </c>
+      <c r="P29" s="33" t="str">
+        <f aca="false">IF($B29="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B29),""))</f>
         <v/>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="37" t="str">
-        <f aca="false">IF(Suppliers!A28="","",Suppliers!A28)</f>
-        <v/>
-      </c>
-      <c r="B30" s="38" t="str">
-        <f aca="false">IF($A30="","",COUNTIF('Score Log'!$C$4:$C$203,$A30))</f>
-        <v/>
-      </c>
-      <c r="C30" s="39" t="str">
-        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A30),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D30" s="39" t="str">
-        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A30),1),"-"))</f>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="38" t="str">
+        <f aca="false">IF($B30="","",IF($C30="",COUNTIF('Score Log'!$C$4:$C$203,$B30),COUNTIFS('Score Log'!$C$4:$C$203,$B30,'Score Log'!$D$4:$D$203,$C30)))</f>
         <v/>
       </c>
       <c r="E30" s="39" t="str">
-        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A30),1),"-"))</f>
+        <f aca="false">IF($B30="","",IFERROR(ROUND(IF($C30="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B30),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B30,'Score Log'!$D$4:$D$203,$C30)),1),"-"))</f>
         <v/>
       </c>
       <c r="F30" s="39" t="str">
-        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A30),1),"-"))</f>
+        <f aca="false">IF($B30="","",IFERROR(ROUND(IF($C30="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B30),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B30,'Score Log'!$D$4:$D$203,$C30)),1),"-"))</f>
         <v/>
       </c>
       <c r="G30" s="39" t="str">
-        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A30),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H30" s="40" t="str">
-        <f aca="false">IF($A30="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A30,'Score Log'!$U$4:$U$203,"Yes")/$B30,"-"))</f>
-        <v/>
-      </c>
-      <c r="I30" s="41" t="str">
-        <f aca="false">IF($A30="","",IF(ISNUMBER($D30),MAX(1,MIN(5,ROUND(6-$D30,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J30" s="41" t="str">
-        <f aca="false">IF($A30="","",IF(ISNUMBER($E30),MAX(1,MIN(5,ROUND(6-$E30,0))),"-"))</f>
+        <f aca="false">IF($B30="","",IFERROR(ROUND(IF($C30="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B30),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B30,'Score Log'!$D$4:$D$203,$C30)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H30" s="39" t="str">
+        <f aca="false">IF($B30="","",IFERROR(ROUND(IF($C30="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B30),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B30,'Score Log'!$D$4:$D$203,$C30)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I30" s="39" t="str">
+        <f aca="false">IF($B30="","",IFERROR(ROUND(IF($C30="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B30),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B30,'Score Log'!$D$4:$D$203,$C30)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J30" s="40" t="str">
+        <f aca="false">IF(OR($B30="",$D30=0),"",IFERROR(IF($C30="",COUNTIFS('Score Log'!$C$4:$C$203,$B30,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B30,'Score Log'!$D$4:$D$203,$C30,'Score Log'!$U$4:$U$203,"Yes"))/$D30,"-"))</f>
         <v/>
       </c>
       <c r="K30" s="41" t="str">
-        <f aca="false">IF($A30="","",IF(AND(ISNUMBER($F30),ISNUMBER($C30)),MAX(1,MIN(5,ROUND(6-AVERAGE($F30,$C30),0))),IF(ISNUMBER($F30),MAX(1,MIN(5,ROUND(6-$F30,0))),"-")))</f>
+        <f aca="false">IF($B30="","",IF(ISNUMBER($F30),MAX(1,MIN(5,ROUND(6-$F30,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L30" s="41" t="str">
+        <f aca="false">IF($B30="","",IF(ISNUMBER($G30),MAX(1,MIN(5,ROUND(6-$G30,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M30" s="41" t="str">
+        <f aca="false">IF($B30="","",IF(AND(ISNUMBER($P30),ISNUMBER($O30)),MAX(1,MIN(5,ROUND(6-AVERAGE($P30,$O30),0))),IF(ISNUMBER($P30),MAX(1,MIN(5,ROUND(6-$P30,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O30" s="33" t="str">
+        <f aca="false">IF($B30="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B30),""))</f>
+        <v/>
+      </c>
+      <c r="P30" s="33" t="str">
+        <f aca="false">IF($B30="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B30),""))</f>
         <v/>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="37" t="str">
-        <f aca="false">IF(Suppliers!A29="","",Suppliers!A29)</f>
-        <v/>
-      </c>
-      <c r="B31" s="38" t="str">
-        <f aca="false">IF($A31="","",COUNTIF('Score Log'!$C$4:$C$203,$A31))</f>
-        <v/>
-      </c>
-      <c r="C31" s="39" t="str">
-        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A31),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D31" s="39" t="str">
-        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A31),1),"-"))</f>
+      <c r="A31" s="37"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="38" t="str">
+        <f aca="false">IF($B31="","",IF($C31="",COUNTIF('Score Log'!$C$4:$C$203,$B31),COUNTIFS('Score Log'!$C$4:$C$203,$B31,'Score Log'!$D$4:$D$203,$C31)))</f>
         <v/>
       </c>
       <c r="E31" s="39" t="str">
-        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A31),1),"-"))</f>
+        <f aca="false">IF($B31="","",IFERROR(ROUND(IF($C31="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B31),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B31,'Score Log'!$D$4:$D$203,$C31)),1),"-"))</f>
         <v/>
       </c>
       <c r="F31" s="39" t="str">
-        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A31),1),"-"))</f>
+        <f aca="false">IF($B31="","",IFERROR(ROUND(IF($C31="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B31),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B31,'Score Log'!$D$4:$D$203,$C31)),1),"-"))</f>
         <v/>
       </c>
       <c r="G31" s="39" t="str">
-        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A31),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H31" s="40" t="str">
-        <f aca="false">IF($A31="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A31,'Score Log'!$U$4:$U$203,"Yes")/$B31,"-"))</f>
-        <v/>
-      </c>
-      <c r="I31" s="41" t="str">
-        <f aca="false">IF($A31="","",IF(ISNUMBER($D31),MAX(1,MIN(5,ROUND(6-$D31,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J31" s="41" t="str">
-        <f aca="false">IF($A31="","",IF(ISNUMBER($E31),MAX(1,MIN(5,ROUND(6-$E31,0))),"-"))</f>
+        <f aca="false">IF($B31="","",IFERROR(ROUND(IF($C31="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B31),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B31,'Score Log'!$D$4:$D$203,$C31)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H31" s="39" t="str">
+        <f aca="false">IF($B31="","",IFERROR(ROUND(IF($C31="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B31),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B31,'Score Log'!$D$4:$D$203,$C31)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I31" s="39" t="str">
+        <f aca="false">IF($B31="","",IFERROR(ROUND(IF($C31="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B31),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B31,'Score Log'!$D$4:$D$203,$C31)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J31" s="40" t="str">
+        <f aca="false">IF(OR($B31="",$D31=0),"",IFERROR(IF($C31="",COUNTIFS('Score Log'!$C$4:$C$203,$B31,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B31,'Score Log'!$D$4:$D$203,$C31,'Score Log'!$U$4:$U$203,"Yes"))/$D31,"-"))</f>
         <v/>
       </c>
       <c r="K31" s="41" t="str">
-        <f aca="false">IF($A31="","",IF(AND(ISNUMBER($F31),ISNUMBER($C31)),MAX(1,MIN(5,ROUND(6-AVERAGE($F31,$C31),0))),IF(ISNUMBER($F31),MAX(1,MIN(5,ROUND(6-$F31,0))),"-")))</f>
+        <f aca="false">IF($B31="","",IF(ISNUMBER($F31),MAX(1,MIN(5,ROUND(6-$F31,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L31" s="41" t="str">
+        <f aca="false">IF($B31="","",IF(ISNUMBER($G31),MAX(1,MIN(5,ROUND(6-$G31,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M31" s="41" t="str">
+        <f aca="false">IF($B31="","",IF(AND(ISNUMBER($P31),ISNUMBER($O31)),MAX(1,MIN(5,ROUND(6-AVERAGE($P31,$O31),0))),IF(ISNUMBER($P31),MAX(1,MIN(5,ROUND(6-$P31,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O31" s="33" t="str">
+        <f aca="false">IF($B31="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B31),""))</f>
+        <v/>
+      </c>
+      <c r="P31" s="33" t="str">
+        <f aca="false">IF($B31="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B31),""))</f>
         <v/>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="37" t="str">
-        <f aca="false">IF(Suppliers!A30="","",Suppliers!A30)</f>
-        <v/>
-      </c>
-      <c r="B32" s="38" t="str">
-        <f aca="false">IF($A32="","",COUNTIF('Score Log'!$C$4:$C$203,$A32))</f>
-        <v/>
-      </c>
-      <c r="C32" s="39" t="str">
-        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A32),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D32" s="39" t="str">
-        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A32),1),"-"))</f>
+      <c r="A32" s="37"/>
+      <c r="B32" s="37"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="38" t="str">
+        <f aca="false">IF($B32="","",IF($C32="",COUNTIF('Score Log'!$C$4:$C$203,$B32),COUNTIFS('Score Log'!$C$4:$C$203,$B32,'Score Log'!$D$4:$D$203,$C32)))</f>
         <v/>
       </c>
       <c r="E32" s="39" t="str">
-        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A32),1),"-"))</f>
+        <f aca="false">IF($B32="","",IFERROR(ROUND(IF($C32="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B32),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B32,'Score Log'!$D$4:$D$203,$C32)),1),"-"))</f>
         <v/>
       </c>
       <c r="F32" s="39" t="str">
-        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A32),1),"-"))</f>
+        <f aca="false">IF($B32="","",IFERROR(ROUND(IF($C32="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B32),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B32,'Score Log'!$D$4:$D$203,$C32)),1),"-"))</f>
         <v/>
       </c>
       <c r="G32" s="39" t="str">
-        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A32),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H32" s="40" t="str">
-        <f aca="false">IF($A32="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A32,'Score Log'!$U$4:$U$203,"Yes")/$B32,"-"))</f>
-        <v/>
-      </c>
-      <c r="I32" s="41" t="str">
-        <f aca="false">IF($A32="","",IF(ISNUMBER($D32),MAX(1,MIN(5,ROUND(6-$D32,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J32" s="41" t="str">
-        <f aca="false">IF($A32="","",IF(ISNUMBER($E32),MAX(1,MIN(5,ROUND(6-$E32,0))),"-"))</f>
+        <f aca="false">IF($B32="","",IFERROR(ROUND(IF($C32="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B32),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B32,'Score Log'!$D$4:$D$203,$C32)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H32" s="39" t="str">
+        <f aca="false">IF($B32="","",IFERROR(ROUND(IF($C32="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B32),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B32,'Score Log'!$D$4:$D$203,$C32)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I32" s="39" t="str">
+        <f aca="false">IF($B32="","",IFERROR(ROUND(IF($C32="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B32),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B32,'Score Log'!$D$4:$D$203,$C32)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J32" s="40" t="str">
+        <f aca="false">IF(OR($B32="",$D32=0),"",IFERROR(IF($C32="",COUNTIFS('Score Log'!$C$4:$C$203,$B32,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B32,'Score Log'!$D$4:$D$203,$C32,'Score Log'!$U$4:$U$203,"Yes"))/$D32,"-"))</f>
         <v/>
       </c>
       <c r="K32" s="41" t="str">
-        <f aca="false">IF($A32="","",IF(AND(ISNUMBER($F32),ISNUMBER($C32)),MAX(1,MIN(5,ROUND(6-AVERAGE($F32,$C32),0))),IF(ISNUMBER($F32),MAX(1,MIN(5,ROUND(6-$F32,0))),"-")))</f>
+        <f aca="false">IF($B32="","",IF(ISNUMBER($F32),MAX(1,MIN(5,ROUND(6-$F32,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L32" s="41" t="str">
+        <f aca="false">IF($B32="","",IF(ISNUMBER($G32),MAX(1,MIN(5,ROUND(6-$G32,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M32" s="41" t="str">
+        <f aca="false">IF($B32="","",IF(AND(ISNUMBER($P32),ISNUMBER($O32)),MAX(1,MIN(5,ROUND(6-AVERAGE($P32,$O32),0))),IF(ISNUMBER($P32),MAX(1,MIN(5,ROUND(6-$P32,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O32" s="33" t="str">
+        <f aca="false">IF($B32="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B32),""))</f>
+        <v/>
+      </c>
+      <c r="P32" s="33" t="str">
+        <f aca="false">IF($B32="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B32),""))</f>
         <v/>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="37" t="str">
-        <f aca="false">IF(Suppliers!A31="","",Suppliers!A31)</f>
-        <v/>
-      </c>
-      <c r="B33" s="38" t="str">
-        <f aca="false">IF($A33="","",COUNTIF('Score Log'!$C$4:$C$203,$A33))</f>
-        <v/>
-      </c>
-      <c r="C33" s="39" t="str">
-        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A33),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D33" s="39" t="str">
-        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A33),1),"-"))</f>
+      <c r="A33" s="37"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="38" t="str">
+        <f aca="false">IF($B33="","",IF($C33="",COUNTIF('Score Log'!$C$4:$C$203,$B33),COUNTIFS('Score Log'!$C$4:$C$203,$B33,'Score Log'!$D$4:$D$203,$C33)))</f>
         <v/>
       </c>
       <c r="E33" s="39" t="str">
-        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A33),1),"-"))</f>
+        <f aca="false">IF($B33="","",IFERROR(ROUND(IF($C33="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B33),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B33,'Score Log'!$D$4:$D$203,$C33)),1),"-"))</f>
         <v/>
       </c>
       <c r="F33" s="39" t="str">
-        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A33),1),"-"))</f>
+        <f aca="false">IF($B33="","",IFERROR(ROUND(IF($C33="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B33),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B33,'Score Log'!$D$4:$D$203,$C33)),1),"-"))</f>
         <v/>
       </c>
       <c r="G33" s="39" t="str">
-        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A33),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H33" s="40" t="str">
-        <f aca="false">IF($A33="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A33,'Score Log'!$U$4:$U$203,"Yes")/$B33,"-"))</f>
-        <v/>
-      </c>
-      <c r="I33" s="41" t="str">
-        <f aca="false">IF($A33="","",IF(ISNUMBER($D33),MAX(1,MIN(5,ROUND(6-$D33,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J33" s="41" t="str">
-        <f aca="false">IF($A33="","",IF(ISNUMBER($E33),MAX(1,MIN(5,ROUND(6-$E33,0))),"-"))</f>
+        <f aca="false">IF($B33="","",IFERROR(ROUND(IF($C33="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B33),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B33,'Score Log'!$D$4:$D$203,$C33)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H33" s="39" t="str">
+        <f aca="false">IF($B33="","",IFERROR(ROUND(IF($C33="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B33),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B33,'Score Log'!$D$4:$D$203,$C33)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I33" s="39" t="str">
+        <f aca="false">IF($B33="","",IFERROR(ROUND(IF($C33="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B33),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B33,'Score Log'!$D$4:$D$203,$C33)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J33" s="40" t="str">
+        <f aca="false">IF(OR($B33="",$D33=0),"",IFERROR(IF($C33="",COUNTIFS('Score Log'!$C$4:$C$203,$B33,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B33,'Score Log'!$D$4:$D$203,$C33,'Score Log'!$U$4:$U$203,"Yes"))/$D33,"-"))</f>
         <v/>
       </c>
       <c r="K33" s="41" t="str">
-        <f aca="false">IF($A33="","",IF(AND(ISNUMBER($F33),ISNUMBER($C33)),MAX(1,MIN(5,ROUND(6-AVERAGE($F33,$C33),0))),IF(ISNUMBER($F33),MAX(1,MIN(5,ROUND(6-$F33,0))),"-")))</f>
+        <f aca="false">IF($B33="","",IF(ISNUMBER($F33),MAX(1,MIN(5,ROUND(6-$F33,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L33" s="41" t="str">
+        <f aca="false">IF($B33="","",IF(ISNUMBER($G33),MAX(1,MIN(5,ROUND(6-$G33,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M33" s="41" t="str">
+        <f aca="false">IF($B33="","",IF(AND(ISNUMBER($P33),ISNUMBER($O33)),MAX(1,MIN(5,ROUND(6-AVERAGE($P33,$O33),0))),IF(ISNUMBER($P33),MAX(1,MIN(5,ROUND(6-$P33,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O33" s="33" t="str">
+        <f aca="false">IF($B33="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B33),""))</f>
+        <v/>
+      </c>
+      <c r="P33" s="33" t="str">
+        <f aca="false">IF($B33="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B33),""))</f>
         <v/>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="37" t="str">
-        <f aca="false">IF(Suppliers!A32="","",Suppliers!A32)</f>
-        <v/>
-      </c>
-      <c r="B34" s="38" t="str">
-        <f aca="false">IF($A34="","",COUNTIF('Score Log'!$C$4:$C$203,$A34))</f>
-        <v/>
-      </c>
-      <c r="C34" s="39" t="str">
-        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A34),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="D34" s="39" t="str">
-        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A34),1),"-"))</f>
+      <c r="A34" s="37"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="38" t="str">
+        <f aca="false">IF($B34="","",IF($C34="",COUNTIF('Score Log'!$C$4:$C$203,$B34),COUNTIFS('Score Log'!$C$4:$C$203,$B34,'Score Log'!$D$4:$D$203,$C34)))</f>
         <v/>
       </c>
       <c r="E34" s="39" t="str">
-        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A34),1),"-"))</f>
+        <f aca="false">IF($B34="","",IFERROR(ROUND(IF($C34="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B34),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B34,'Score Log'!$D$4:$D$203,$C34)),1),"-"))</f>
         <v/>
       </c>
       <c r="F34" s="39" t="str">
-        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A34),1),"-"))</f>
+        <f aca="false">IF($B34="","",IFERROR(ROUND(IF($C34="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B34),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B34,'Score Log'!$D$4:$D$203,$C34)),1),"-"))</f>
         <v/>
       </c>
       <c r="G34" s="39" t="str">
-        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A34),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H34" s="40" t="str">
-        <f aca="false">IF($A34="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A34,'Score Log'!$U$4:$U$203,"Yes")/$B34,"-"))</f>
-        <v/>
-      </c>
-      <c r="I34" s="41" t="str">
-        <f aca="false">IF($A34="","",IF(ISNUMBER($D34),MAX(1,MIN(5,ROUND(6-$D34,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="J34" s="41" t="str">
-        <f aca="false">IF($A34="","",IF(ISNUMBER($E34),MAX(1,MIN(5,ROUND(6-$E34,0))),"-"))</f>
+        <f aca="false">IF($B34="","",IFERROR(ROUND(IF($C34="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B34),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B34,'Score Log'!$D$4:$D$203,$C34)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H34" s="39" t="str">
+        <f aca="false">IF($B34="","",IFERROR(ROUND(IF($C34="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B34),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B34,'Score Log'!$D$4:$D$203,$C34)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I34" s="39" t="str">
+        <f aca="false">IF($B34="","",IFERROR(ROUND(IF($C34="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B34),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B34,'Score Log'!$D$4:$D$203,$C34)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J34" s="40" t="str">
+        <f aca="false">IF(OR($B34="",$D34=0),"",IFERROR(IF($C34="",COUNTIFS('Score Log'!$C$4:$C$203,$B34,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B34,'Score Log'!$D$4:$D$203,$C34,'Score Log'!$U$4:$U$203,"Yes"))/$D34,"-"))</f>
         <v/>
       </c>
       <c r="K34" s="41" t="str">
-        <f aca="false">IF($A34="","",IF(AND(ISNUMBER($F34),ISNUMBER($C34)),MAX(1,MIN(5,ROUND(6-AVERAGE($F34,$C34),0))),IF(ISNUMBER($F34),MAX(1,MIN(5,ROUND(6-$F34,0))),"-")))</f>
+        <f aca="false">IF($B34="","",IF(ISNUMBER($F34),MAX(1,MIN(5,ROUND(6-$F34,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L34" s="41" t="str">
+        <f aca="false">IF($B34="","",IF(ISNUMBER($G34),MAX(1,MIN(5,ROUND(6-$G34,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M34" s="41" t="str">
+        <f aca="false">IF($B34="","",IF(AND(ISNUMBER($P34),ISNUMBER($O34)),MAX(1,MIN(5,ROUND(6-AVERAGE($P34,$O34),0))),IF(ISNUMBER($P34),MAX(1,MIN(5,ROUND(6-$P34,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O34" s="33" t="str">
+        <f aca="false">IF($B34="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B34),""))</f>
+        <v/>
+      </c>
+      <c r="P34" s="33" t="str">
+        <f aca="false">IF($B34="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B34),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="37"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="38" t="str">
+        <f aca="false">IF($B35="","",IF($C35="",COUNTIF('Score Log'!$C$4:$C$203,$B35),COUNTIFS('Score Log'!$C$4:$C$203,$B35,'Score Log'!$D$4:$D$203,$C35)))</f>
+        <v/>
+      </c>
+      <c r="E35" s="39" t="str">
+        <f aca="false">IF($B35="","",IFERROR(ROUND(IF($C35="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B35),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B35,'Score Log'!$D$4:$D$203,$C35)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F35" s="39" t="str">
+        <f aca="false">IF($B35="","",IFERROR(ROUND(IF($C35="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B35),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B35,'Score Log'!$D$4:$D$203,$C35)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G35" s="39" t="str">
+        <f aca="false">IF($B35="","",IFERROR(ROUND(IF($C35="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B35),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B35,'Score Log'!$D$4:$D$203,$C35)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H35" s="39" t="str">
+        <f aca="false">IF($B35="","",IFERROR(ROUND(IF($C35="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B35),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B35,'Score Log'!$D$4:$D$203,$C35)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I35" s="39" t="str">
+        <f aca="false">IF($B35="","",IFERROR(ROUND(IF($C35="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B35),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B35,'Score Log'!$D$4:$D$203,$C35)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J35" s="40" t="str">
+        <f aca="false">IF(OR($B35="",$D35=0),"",IFERROR(IF($C35="",COUNTIFS('Score Log'!$C$4:$C$203,$B35,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B35,'Score Log'!$D$4:$D$203,$C35,'Score Log'!$U$4:$U$203,"Yes"))/$D35,"-"))</f>
+        <v/>
+      </c>
+      <c r="K35" s="41" t="str">
+        <f aca="false">IF($B35="","",IF(ISNUMBER($F35),MAX(1,MIN(5,ROUND(6-$F35,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L35" s="41" t="str">
+        <f aca="false">IF($B35="","",IF(ISNUMBER($G35),MAX(1,MIN(5,ROUND(6-$G35,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M35" s="41" t="str">
+        <f aca="false">IF($B35="","",IF(AND(ISNUMBER($P35),ISNUMBER($O35)),MAX(1,MIN(5,ROUND(6-AVERAGE($P35,$O35),0))),IF(ISNUMBER($P35),MAX(1,MIN(5,ROUND(6-$P35,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O35" s="33" t="str">
+        <f aca="false">IF($B35="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B35),""))</f>
+        <v/>
+      </c>
+      <c r="P35" s="33" t="str">
+        <f aca="false">IF($B35="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B35),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="37"/>
+      <c r="B36" s="37"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="38" t="str">
+        <f aca="false">IF($B36="","",IF($C36="",COUNTIF('Score Log'!$C$4:$C$203,$B36),COUNTIFS('Score Log'!$C$4:$C$203,$B36,'Score Log'!$D$4:$D$203,$C36)))</f>
+        <v/>
+      </c>
+      <c r="E36" s="39" t="str">
+        <f aca="false">IF($B36="","",IFERROR(ROUND(IF($C36="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B36),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B36,'Score Log'!$D$4:$D$203,$C36)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F36" s="39" t="str">
+        <f aca="false">IF($B36="","",IFERROR(ROUND(IF($C36="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B36),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B36,'Score Log'!$D$4:$D$203,$C36)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G36" s="39" t="str">
+        <f aca="false">IF($B36="","",IFERROR(ROUND(IF($C36="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B36),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B36,'Score Log'!$D$4:$D$203,$C36)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H36" s="39" t="str">
+        <f aca="false">IF($B36="","",IFERROR(ROUND(IF($C36="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B36),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B36,'Score Log'!$D$4:$D$203,$C36)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I36" s="39" t="str">
+        <f aca="false">IF($B36="","",IFERROR(ROUND(IF($C36="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B36),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B36,'Score Log'!$D$4:$D$203,$C36)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J36" s="40" t="str">
+        <f aca="false">IF(OR($B36="",$D36=0),"",IFERROR(IF($C36="",COUNTIFS('Score Log'!$C$4:$C$203,$B36,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B36,'Score Log'!$D$4:$D$203,$C36,'Score Log'!$U$4:$U$203,"Yes"))/$D36,"-"))</f>
+        <v/>
+      </c>
+      <c r="K36" s="41" t="str">
+        <f aca="false">IF($B36="","",IF(ISNUMBER($F36),MAX(1,MIN(5,ROUND(6-$F36,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L36" s="41" t="str">
+        <f aca="false">IF($B36="","",IF(ISNUMBER($G36),MAX(1,MIN(5,ROUND(6-$G36,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M36" s="41" t="str">
+        <f aca="false">IF($B36="","",IF(AND(ISNUMBER($P36),ISNUMBER($O36)),MAX(1,MIN(5,ROUND(6-AVERAGE($P36,$O36),0))),IF(ISNUMBER($P36),MAX(1,MIN(5,ROUND(6-$P36,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O36" s="33" t="str">
+        <f aca="false">IF($B36="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B36),""))</f>
+        <v/>
+      </c>
+      <c r="P36" s="33" t="str">
+        <f aca="false">IF($B36="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B36),""))</f>
         <v/>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="42" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="43" t="s">
-        <v>83</v>
-      </c>
-      <c r="B38" s="43"/>
-      <c r="C38" s="43"/>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="43"/>
-      <c r="I38" s="43"/>
-      <c r="J38" s="43"/>
-      <c r="K38" s="43"/>
-    </row>
-    <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="B39" s="43"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="43"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="43"/>
-      <c r="H39" s="43"/>
-      <c r="I39" s="43"/>
-      <c r="J39" s="43"/>
-      <c r="K39" s="43"/>
-    </row>
-    <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="B40" s="43"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="43"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="43"/>
-      <c r="H40" s="43"/>
-      <c r="I40" s="43"/>
-      <c r="J40" s="43"/>
-      <c r="K40" s="43"/>
-    </row>
-    <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="43" t="s">
+      <c r="A37" s="37"/>
+      <c r="B37" s="37"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="38" t="str">
+        <f aca="false">IF($B37="","",IF($C37="",COUNTIF('Score Log'!$C$4:$C$203,$B37),COUNTIFS('Score Log'!$C$4:$C$203,$B37,'Score Log'!$D$4:$D$203,$C37)))</f>
+        <v/>
+      </c>
+      <c r="E37" s="39" t="str">
+        <f aca="false">IF($B37="","",IFERROR(ROUND(IF($C37="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B37),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B37,'Score Log'!$D$4:$D$203,$C37)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F37" s="39" t="str">
+        <f aca="false">IF($B37="","",IFERROR(ROUND(IF($C37="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B37),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B37,'Score Log'!$D$4:$D$203,$C37)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G37" s="39" t="str">
+        <f aca="false">IF($B37="","",IFERROR(ROUND(IF($C37="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B37),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B37,'Score Log'!$D$4:$D$203,$C37)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H37" s="39" t="str">
+        <f aca="false">IF($B37="","",IFERROR(ROUND(IF($C37="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B37),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B37,'Score Log'!$D$4:$D$203,$C37)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I37" s="39" t="str">
+        <f aca="false">IF($B37="","",IFERROR(ROUND(IF($C37="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B37),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B37,'Score Log'!$D$4:$D$203,$C37)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J37" s="40" t="str">
+        <f aca="false">IF(OR($B37="",$D37=0),"",IFERROR(IF($C37="",COUNTIFS('Score Log'!$C$4:$C$203,$B37,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B37,'Score Log'!$D$4:$D$203,$C37,'Score Log'!$U$4:$U$203,"Yes"))/$D37,"-"))</f>
+        <v/>
+      </c>
+      <c r="K37" s="41" t="str">
+        <f aca="false">IF($B37="","",IF(ISNUMBER($F37),MAX(1,MIN(5,ROUND(6-$F37,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L37" s="41" t="str">
+        <f aca="false">IF($B37="","",IF(ISNUMBER($G37),MAX(1,MIN(5,ROUND(6-$G37,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M37" s="41" t="str">
+        <f aca="false">IF($B37="","",IF(AND(ISNUMBER($P37),ISNUMBER($O37)),MAX(1,MIN(5,ROUND(6-AVERAGE($P37,$O37),0))),IF(ISNUMBER($P37),MAX(1,MIN(5,ROUND(6-$P37,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O37" s="33" t="str">
+        <f aca="false">IF($B37="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B37),""))</f>
+        <v/>
+      </c>
+      <c r="P37" s="33" t="str">
+        <f aca="false">IF($B37="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B37),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="37"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="38" t="str">
+        <f aca="false">IF($B38="","",IF($C38="",COUNTIF('Score Log'!$C$4:$C$203,$B38),COUNTIFS('Score Log'!$C$4:$C$203,$B38,'Score Log'!$D$4:$D$203,$C38)))</f>
+        <v/>
+      </c>
+      <c r="E38" s="39" t="str">
+        <f aca="false">IF($B38="","",IFERROR(ROUND(IF($C38="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B38),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B38,'Score Log'!$D$4:$D$203,$C38)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F38" s="39" t="str">
+        <f aca="false">IF($B38="","",IFERROR(ROUND(IF($C38="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B38),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B38,'Score Log'!$D$4:$D$203,$C38)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G38" s="39" t="str">
+        <f aca="false">IF($B38="","",IFERROR(ROUND(IF($C38="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B38),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B38,'Score Log'!$D$4:$D$203,$C38)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H38" s="39" t="str">
+        <f aca="false">IF($B38="","",IFERROR(ROUND(IF($C38="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B38),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B38,'Score Log'!$D$4:$D$203,$C38)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I38" s="39" t="str">
+        <f aca="false">IF($B38="","",IFERROR(ROUND(IF($C38="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B38),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B38,'Score Log'!$D$4:$D$203,$C38)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J38" s="40" t="str">
+        <f aca="false">IF(OR($B38="",$D38=0),"",IFERROR(IF($C38="",COUNTIFS('Score Log'!$C$4:$C$203,$B38,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B38,'Score Log'!$D$4:$D$203,$C38,'Score Log'!$U$4:$U$203,"Yes"))/$D38,"-"))</f>
+        <v/>
+      </c>
+      <c r="K38" s="41" t="str">
+        <f aca="false">IF($B38="","",IF(ISNUMBER($F38),MAX(1,MIN(5,ROUND(6-$F38,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L38" s="41" t="str">
+        <f aca="false">IF($B38="","",IF(ISNUMBER($G38),MAX(1,MIN(5,ROUND(6-$G38,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M38" s="41" t="str">
+        <f aca="false">IF($B38="","",IF(AND(ISNUMBER($P38),ISNUMBER($O38)),MAX(1,MIN(5,ROUND(6-AVERAGE($P38,$O38),0))),IF(ISNUMBER($P38),MAX(1,MIN(5,ROUND(6-$P38,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O38" s="33" t="str">
+        <f aca="false">IF($B38="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B38),""))</f>
+        <v/>
+      </c>
+      <c r="P38" s="33" t="str">
+        <f aca="false">IF($B38="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B38),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="37"/>
+      <c r="B39" s="37"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="38" t="str">
+        <f aca="false">IF($B39="","",IF($C39="",COUNTIF('Score Log'!$C$4:$C$203,$B39),COUNTIFS('Score Log'!$C$4:$C$203,$B39,'Score Log'!$D$4:$D$203,$C39)))</f>
+        <v/>
+      </c>
+      <c r="E39" s="39" t="str">
+        <f aca="false">IF($B39="","",IFERROR(ROUND(IF($C39="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B39),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B39,'Score Log'!$D$4:$D$203,$C39)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F39" s="39" t="str">
+        <f aca="false">IF($B39="","",IFERROR(ROUND(IF($C39="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B39),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B39,'Score Log'!$D$4:$D$203,$C39)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G39" s="39" t="str">
+        <f aca="false">IF($B39="","",IFERROR(ROUND(IF($C39="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B39),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B39,'Score Log'!$D$4:$D$203,$C39)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H39" s="39" t="str">
+        <f aca="false">IF($B39="","",IFERROR(ROUND(IF($C39="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B39),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B39,'Score Log'!$D$4:$D$203,$C39)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I39" s="39" t="str">
+        <f aca="false">IF($B39="","",IFERROR(ROUND(IF($C39="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B39),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B39,'Score Log'!$D$4:$D$203,$C39)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J39" s="40" t="str">
+        <f aca="false">IF(OR($B39="",$D39=0),"",IFERROR(IF($C39="",COUNTIFS('Score Log'!$C$4:$C$203,$B39,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B39,'Score Log'!$D$4:$D$203,$C39,'Score Log'!$U$4:$U$203,"Yes"))/$D39,"-"))</f>
+        <v/>
+      </c>
+      <c r="K39" s="41" t="str">
+        <f aca="false">IF($B39="","",IF(ISNUMBER($F39),MAX(1,MIN(5,ROUND(6-$F39,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L39" s="41" t="str">
+        <f aca="false">IF($B39="","",IF(ISNUMBER($G39),MAX(1,MIN(5,ROUND(6-$G39,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M39" s="41" t="str">
+        <f aca="false">IF($B39="","",IF(AND(ISNUMBER($P39),ISNUMBER($O39)),MAX(1,MIN(5,ROUND(6-AVERAGE($P39,$O39),0))),IF(ISNUMBER($P39),MAX(1,MIN(5,ROUND(6-$P39,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O39" s="33" t="str">
+        <f aca="false">IF($B39="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B39),""))</f>
+        <v/>
+      </c>
+      <c r="P39" s="33" t="str">
+        <f aca="false">IF($B39="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B39),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="37"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="38" t="str">
+        <f aca="false">IF($B40="","",IF($C40="",COUNTIF('Score Log'!$C$4:$C$203,$B40),COUNTIFS('Score Log'!$C$4:$C$203,$B40,'Score Log'!$D$4:$D$203,$C40)))</f>
+        <v/>
+      </c>
+      <c r="E40" s="39" t="str">
+        <f aca="false">IF($B40="","",IFERROR(ROUND(IF($C40="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B40),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B40,'Score Log'!$D$4:$D$203,$C40)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F40" s="39" t="str">
+        <f aca="false">IF($B40="","",IFERROR(ROUND(IF($C40="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B40),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B40,'Score Log'!$D$4:$D$203,$C40)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G40" s="39" t="str">
+        <f aca="false">IF($B40="","",IFERROR(ROUND(IF($C40="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B40),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B40,'Score Log'!$D$4:$D$203,$C40)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H40" s="39" t="str">
+        <f aca="false">IF($B40="","",IFERROR(ROUND(IF($C40="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B40),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B40,'Score Log'!$D$4:$D$203,$C40)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I40" s="39" t="str">
+        <f aca="false">IF($B40="","",IFERROR(ROUND(IF($C40="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B40),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B40,'Score Log'!$D$4:$D$203,$C40)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J40" s="40" t="str">
+        <f aca="false">IF(OR($B40="",$D40=0),"",IFERROR(IF($C40="",COUNTIFS('Score Log'!$C$4:$C$203,$B40,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B40,'Score Log'!$D$4:$D$203,$C40,'Score Log'!$U$4:$U$203,"Yes"))/$D40,"-"))</f>
+        <v/>
+      </c>
+      <c r="K40" s="41" t="str">
+        <f aca="false">IF($B40="","",IF(ISNUMBER($F40),MAX(1,MIN(5,ROUND(6-$F40,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L40" s="41" t="str">
+        <f aca="false">IF($B40="","",IF(ISNUMBER($G40),MAX(1,MIN(5,ROUND(6-$G40,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M40" s="41" t="str">
+        <f aca="false">IF($B40="","",IF(AND(ISNUMBER($P40),ISNUMBER($O40)),MAX(1,MIN(5,ROUND(6-AVERAGE($P40,$O40),0))),IF(ISNUMBER($P40),MAX(1,MIN(5,ROUND(6-$P40,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O40" s="33" t="str">
+        <f aca="false">IF($B40="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B40),""))</f>
+        <v/>
+      </c>
+      <c r="P40" s="33" t="str">
+        <f aca="false">IF($B40="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B40),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="37"/>
+      <c r="B41" s="37"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="38" t="str">
+        <f aca="false">IF($B41="","",IF($C41="",COUNTIF('Score Log'!$C$4:$C$203,$B41),COUNTIFS('Score Log'!$C$4:$C$203,$B41,'Score Log'!$D$4:$D$203,$C41)))</f>
+        <v/>
+      </c>
+      <c r="E41" s="39" t="str">
+        <f aca="false">IF($B41="","",IFERROR(ROUND(IF($C41="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B41),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B41,'Score Log'!$D$4:$D$203,$C41)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F41" s="39" t="str">
+        <f aca="false">IF($B41="","",IFERROR(ROUND(IF($C41="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B41),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B41,'Score Log'!$D$4:$D$203,$C41)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G41" s="39" t="str">
+        <f aca="false">IF($B41="","",IFERROR(ROUND(IF($C41="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B41),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B41,'Score Log'!$D$4:$D$203,$C41)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H41" s="39" t="str">
+        <f aca="false">IF($B41="","",IFERROR(ROUND(IF($C41="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B41),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B41,'Score Log'!$D$4:$D$203,$C41)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I41" s="39" t="str">
+        <f aca="false">IF($B41="","",IFERROR(ROUND(IF($C41="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B41),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B41,'Score Log'!$D$4:$D$203,$C41)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J41" s="40" t="str">
+        <f aca="false">IF(OR($B41="",$D41=0),"",IFERROR(IF($C41="",COUNTIFS('Score Log'!$C$4:$C$203,$B41,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B41,'Score Log'!$D$4:$D$203,$C41,'Score Log'!$U$4:$U$203,"Yes"))/$D41,"-"))</f>
+        <v/>
+      </c>
+      <c r="K41" s="41" t="str">
+        <f aca="false">IF($B41="","",IF(ISNUMBER($F41),MAX(1,MIN(5,ROUND(6-$F41,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L41" s="41" t="str">
+        <f aca="false">IF($B41="","",IF(ISNUMBER($G41),MAX(1,MIN(5,ROUND(6-$G41,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M41" s="41" t="str">
+        <f aca="false">IF($B41="","",IF(AND(ISNUMBER($P41),ISNUMBER($O41)),MAX(1,MIN(5,ROUND(6-AVERAGE($P41,$O41),0))),IF(ISNUMBER($P41),MAX(1,MIN(5,ROUND(6-$P41,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O41" s="33" t="str">
+        <f aca="false">IF($B41="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B41),""))</f>
+        <v/>
+      </c>
+      <c r="P41" s="33" t="str">
+        <f aca="false">IF($B41="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B41),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="37"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="38" t="str">
+        <f aca="false">IF($B42="","",IF($C42="",COUNTIF('Score Log'!$C$4:$C$203,$B42),COUNTIFS('Score Log'!$C$4:$C$203,$B42,'Score Log'!$D$4:$D$203,$C42)))</f>
+        <v/>
+      </c>
+      <c r="E42" s="39" t="str">
+        <f aca="false">IF($B42="","",IFERROR(ROUND(IF($C42="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B42),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B42,'Score Log'!$D$4:$D$203,$C42)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F42" s="39" t="str">
+        <f aca="false">IF($B42="","",IFERROR(ROUND(IF($C42="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B42),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B42,'Score Log'!$D$4:$D$203,$C42)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G42" s="39" t="str">
+        <f aca="false">IF($B42="","",IFERROR(ROUND(IF($C42="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B42),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B42,'Score Log'!$D$4:$D$203,$C42)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H42" s="39" t="str">
+        <f aca="false">IF($B42="","",IFERROR(ROUND(IF($C42="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B42),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B42,'Score Log'!$D$4:$D$203,$C42)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I42" s="39" t="str">
+        <f aca="false">IF($B42="","",IFERROR(ROUND(IF($C42="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B42),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B42,'Score Log'!$D$4:$D$203,$C42)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J42" s="40" t="str">
+        <f aca="false">IF(OR($B42="",$D42=0),"",IFERROR(IF($C42="",COUNTIFS('Score Log'!$C$4:$C$203,$B42,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B42,'Score Log'!$D$4:$D$203,$C42,'Score Log'!$U$4:$U$203,"Yes"))/$D42,"-"))</f>
+        <v/>
+      </c>
+      <c r="K42" s="41" t="str">
+        <f aca="false">IF($B42="","",IF(ISNUMBER($F42),MAX(1,MIN(5,ROUND(6-$F42,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L42" s="41" t="str">
+        <f aca="false">IF($B42="","",IF(ISNUMBER($G42),MAX(1,MIN(5,ROUND(6-$G42,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M42" s="41" t="str">
+        <f aca="false">IF($B42="","",IF(AND(ISNUMBER($P42),ISNUMBER($O42)),MAX(1,MIN(5,ROUND(6-AVERAGE($P42,$O42),0))),IF(ISNUMBER($P42),MAX(1,MIN(5,ROUND(6-$P42,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O42" s="33" t="str">
+        <f aca="false">IF($B42="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B42),""))</f>
+        <v/>
+      </c>
+      <c r="P42" s="33" t="str">
+        <f aca="false">IF($B42="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B42),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="37"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="38" t="str">
+        <f aca="false">IF($B43="","",IF($C43="",COUNTIF('Score Log'!$C$4:$C$203,$B43),COUNTIFS('Score Log'!$C$4:$C$203,$B43,'Score Log'!$D$4:$D$203,$C43)))</f>
+        <v/>
+      </c>
+      <c r="E43" s="39" t="str">
+        <f aca="false">IF($B43="","",IFERROR(ROUND(IF($C43="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B43),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B43,'Score Log'!$D$4:$D$203,$C43)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F43" s="39" t="str">
+        <f aca="false">IF($B43="","",IFERROR(ROUND(IF($C43="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B43),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B43,'Score Log'!$D$4:$D$203,$C43)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G43" s="39" t="str">
+        <f aca="false">IF($B43="","",IFERROR(ROUND(IF($C43="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B43),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B43,'Score Log'!$D$4:$D$203,$C43)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H43" s="39" t="str">
+        <f aca="false">IF($B43="","",IFERROR(ROUND(IF($C43="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B43),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B43,'Score Log'!$D$4:$D$203,$C43)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I43" s="39" t="str">
+        <f aca="false">IF($B43="","",IFERROR(ROUND(IF($C43="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B43),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B43,'Score Log'!$D$4:$D$203,$C43)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J43" s="40" t="str">
+        <f aca="false">IF(OR($B43="",$D43=0),"",IFERROR(IF($C43="",COUNTIFS('Score Log'!$C$4:$C$203,$B43,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B43,'Score Log'!$D$4:$D$203,$C43,'Score Log'!$U$4:$U$203,"Yes"))/$D43,"-"))</f>
+        <v/>
+      </c>
+      <c r="K43" s="41" t="str">
+        <f aca="false">IF($B43="","",IF(ISNUMBER($F43),MAX(1,MIN(5,ROUND(6-$F43,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L43" s="41" t="str">
+        <f aca="false">IF($B43="","",IF(ISNUMBER($G43),MAX(1,MIN(5,ROUND(6-$G43,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M43" s="41" t="str">
+        <f aca="false">IF($B43="","",IF(AND(ISNUMBER($P43),ISNUMBER($O43)),MAX(1,MIN(5,ROUND(6-AVERAGE($P43,$O43),0))),IF(ISNUMBER($P43),MAX(1,MIN(5,ROUND(6-$P43,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O43" s="33" t="str">
+        <f aca="false">IF($B43="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B43),""))</f>
+        <v/>
+      </c>
+      <c r="P43" s="33" t="str">
+        <f aca="false">IF($B43="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B43),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="37"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="38" t="str">
+        <f aca="false">IF($B44="","",IF($C44="",COUNTIF('Score Log'!$C$4:$C$203,$B44),COUNTIFS('Score Log'!$C$4:$C$203,$B44,'Score Log'!$D$4:$D$203,$C44)))</f>
+        <v/>
+      </c>
+      <c r="E44" s="39" t="str">
+        <f aca="false">IF($B44="","",IFERROR(ROUND(IF($C44="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B44),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B44,'Score Log'!$D$4:$D$203,$C44)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F44" s="39" t="str">
+        <f aca="false">IF($B44="","",IFERROR(ROUND(IF($C44="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B44),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B44,'Score Log'!$D$4:$D$203,$C44)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G44" s="39" t="str">
+        <f aca="false">IF($B44="","",IFERROR(ROUND(IF($C44="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B44),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B44,'Score Log'!$D$4:$D$203,$C44)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H44" s="39" t="str">
+        <f aca="false">IF($B44="","",IFERROR(ROUND(IF($C44="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B44),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B44,'Score Log'!$D$4:$D$203,$C44)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I44" s="39" t="str">
+        <f aca="false">IF($B44="","",IFERROR(ROUND(IF($C44="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B44),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B44,'Score Log'!$D$4:$D$203,$C44)),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J44" s="40" t="str">
+        <f aca="false">IF(OR($B44="",$D44=0),"",IFERROR(IF($C44="",COUNTIFS('Score Log'!$C$4:$C$203,$B44,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B44,'Score Log'!$D$4:$D$203,$C44,'Score Log'!$U$4:$U$203,"Yes"))/$D44,"-"))</f>
+        <v/>
+      </c>
+      <c r="K44" s="41" t="str">
+        <f aca="false">IF($B44="","",IF(ISNUMBER($F44),MAX(1,MIN(5,ROUND(6-$F44,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L44" s="41" t="str">
+        <f aca="false">IF($B44="","",IF(ISNUMBER($G44),MAX(1,MIN(5,ROUND(6-$G44,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M44" s="41" t="str">
+        <f aca="false">IF($B44="","",IF(AND(ISNUMBER($P44),ISNUMBER($O44)),MAX(1,MIN(5,ROUND(6-AVERAGE($P44,$O44),0))),IF(ISNUMBER($P44),MAX(1,MIN(5,ROUND(6-$P44,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O44" s="33" t="str">
+        <f aca="false">IF($B44="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B44),""))</f>
+        <v/>
+      </c>
+      <c r="P44" s="33" t="str">
+        <f aca="false">IF($B44="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B44),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="B41" s="43"/>
-      <c r="C41" s="43"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="43"/>
-      <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
-    </row>
-    <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="43" t="s">
+    </row>
+    <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="B42" s="43"/>
-      <c r="C42" s="43"/>
-      <c r="D42" s="43"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
-      <c r="K42" s="43"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="43"/>
+      <c r="L48" s="43"/>
+      <c r="M48" s="43"/>
+    </row>
+    <row r="49" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="B49" s="43"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="43"/>
+      <c r="F49" s="43"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="43"/>
+      <c r="L49" s="43"/>
+      <c r="M49" s="43"/>
+    </row>
+    <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="B50" s="43"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="43"/>
+      <c r="L50" s="43"/>
+      <c r="M50" s="43"/>
+    </row>
+    <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="B51" s="43"/>
+      <c r="C51" s="43"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="43"/>
+      <c r="F51" s="43"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="43"/>
+      <c r="I51" s="43"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="43"/>
+      <c r="L51" s="43"/>
+      <c r="M51" s="43"/>
+    </row>
+    <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="B52" s="43"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="43"/>
+      <c r="F52" s="43"/>
+      <c r="G52" s="43"/>
+      <c r="H52" s="43"/>
+      <c r="I52" s="43"/>
+      <c r="J52" s="43"/>
+      <c r="K52" s="43"/>
+      <c r="L52" s="43"/>
+      <c r="M52" s="43"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="A38:K38"/>
-    <mergeCell ref="A39:K39"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A42:K42"/>
+  <mergeCells count="8">
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="A49:M49"/>
+    <mergeCell ref="A50:M50"/>
+    <mergeCell ref="A51:M51"/>
+    <mergeCell ref="A52:M52"/>
   </mergeCells>
-  <conditionalFormatting sqref="C5:G34">
+  <conditionalFormatting sqref="E5:I44">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -13281,7 +14069,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:K34">
+  <conditionalFormatting sqref="K5:M44">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -13293,6 +14081,16 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Pick a supplier from the Suppliers tab (or add it there first)." errorStyle="stop" errorTitle="Unknown supplier" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B5:B44" type="list">
+      <formula1>ScorecardSuppliers</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Pick a process from the list in Settings (or add it there first)." errorStyle="stop" errorTitle="Unknown process" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C5:C44" type="list">
+      <formula1>ScorecardProcesses</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -13321,30 +14119,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="44" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D2" s="44" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F2" s="44" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13353,13 +14151,13 @@
       </c>
       <c r="B3" s="45"/>
       <c r="C3" s="45" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E3" s="45" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F3" s="45"/>
     </row>
@@ -13626,112 +14424,112 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="44" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="48" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F5" s="49" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="48" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D6" s="49" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E6" s="49" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F6" s="49" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="48" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D7" s="49" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E7" s="49" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F7" s="49" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="48" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D8" s="49" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E8" s="49" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F8" s="49" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -13762,23 +14560,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="50" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B4" s="51" t="n">
         <v>0.25</v>
@@ -13789,7 +14587,7 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="50" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B5" s="51" t="n">
         <v>0.3</v>
@@ -13800,76 +14598,76 @@
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="50" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B6" s="51" t="n">
         <v>0.25</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="50" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B7" s="51" t="n">
         <v>0.2</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="53" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B8" s="54" t="n">
         <f aca="false">SUM(B4:B7)</f>
         <v>1</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="52" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D10" s="52" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D11" s="52" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D12" s="52" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D13" s="52" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="52" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D15" s="52" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D16" s="52" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Part-Supplier Risk Model/Supplier_Scorecard.xlsx
+++ b/Part-Supplier Risk Model/Supplier_Scorecard.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Read Me" sheetId="1" state="visible" r:id="rId3"/>
@@ -17,7 +17,7 @@
     <sheet name="Settings" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Score Log'!$A$3:$V$203</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Score Log'!$A$3:$V$204</definedName>
     <definedName function="false" hidden="false" name="ScorecardProcesses" vbProcedure="false">Settings!$D$4:$D$33</definedName>
     <definedName function="false" hidden="false" name="ScorecardSuppliers" vbProcedure="false">Suppliers!$A$3:$A$32</definedName>
   </definedNames>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="155">
   <si>
     <t xml:space="preserve">Supplier Scorecard — how to use</t>
   </si>
@@ -183,7 +183,7 @@
     <t xml:space="preserve">Injection molding</t>
   </si>
   <si>
-    <t xml:space="preserve">Uterus Insert (Compression molding) and End Plate (IM)</t>
+    <t xml:space="preserve">Uterus Insert</t>
   </si>
   <si>
     <t xml:space="preserve">35% (average) under comparable quotes </t>
@@ -201,13 +201,16 @@
     <t xml:space="preserve">Good quality overall, communications, lead time and responsiveness</t>
   </si>
   <si>
-    <t xml:space="preserve">Supine Chest Base</t>
+    <t xml:space="preserve">End Plate</t>
   </si>
   <si>
     <t xml:space="preserve">Advanced Plastiform</t>
   </si>
   <si>
     <t xml:space="preserve">Thermoforming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppine chest base</t>
   </si>
   <si>
     <t xml:space="preserve">Responsive to inquiries and provided revised timelines, but Intuitive frequently had to request status updates</t>
@@ -258,13 +261,10 @@
     <t xml:space="preserve">Risk Suggestions - feed for the Part-Supplier Risk Model</t>
   </si>
   <si>
-    <t xml:space="preserve">One row per PART-SUPPLIER combo: label the part (as it will appear in PART_RISK), pick the Supplier and the Process/part type that makes it - the averages then use only that supplier's logged projects of that process. Leave Process blank to use all the supplier's projects. Translation: risk = 6 - average performance (scorecard 5 = excellent -&gt; risk 1 = low), rounded and clamped to 1-5. Type the suggested values into the PART_RISK tab of Part_Supplier_Risk_Model - a starting point, not an override.</t>
+    <t xml:space="preserve">FULLY AUTOMATIC: every distinct Part + Supplier pair in the Score Log gets exactly one line here, in order of first appearance - log projects one row per part and combos appear by themselves. Translation: risk = 6 - average performance (scorecard 5 = excellent -&gt; risk 1 = low), rounded and clamped to 1-5. Type the suggested values into the PART_RISK tab of Part_Supplier_Risk_Model - a starting point, not an override.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. LABEL THE PART</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. PICK THE COMBO</t>
+    <t xml:space="preserve">PART-SUPPLIER COMBOS (auto from Score Log)</t>
   </si>
   <si>
     <t xml:space="preserve">SCORECARD PERFORMANCE FOR THE COMBO (auto, 5 = excellent)</t>
@@ -273,7 +273,13 @@
     <t xml:space="preserve">SUGGESTED RISK ENTRIES FOR PART_RISK (1 = low risk ... 5 = high)</t>
   </si>
   <si>
-    <t xml:space="preserve">Part (number / description)</t>
+    <t xml:space="preserve">first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part (from Score Log)</t>
   </si>
   <si>
     <t xml:space="preserve">Quality_Compliance (suggest)</t>
@@ -291,16 +297,22 @@
     <t xml:space="preserve">rA</t>
   </si>
   <si>
-    <t xml:space="preserve">HOW THE TRANSLATION WORKS</t>
+    <t xml:space="preserve">lr</t>
   </si>
   <si>
-    <t xml:space="preserve">Quality_Compliance  &lt;-  6 - avg Quality of THIS combo (this supplier's projects of this process).  What they delivered on this kind of part is direct evidence for its quality risk.</t>
+    <t xml:space="preserve">HOW THIS TAB WORKS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rows appear automatically: each distinct Part + Supplier pair in the Score Log = one line (first 60 combos; log rows without a Part description are not listed). Keep part names consistent in the log - 'Uterus Insert' and 'uterus insert' would count as two parts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality_Compliance  &lt;-  6 - avg Quality of THIS combo.  What they delivered on this part is direct evidence for its quality risk.</t>
   </si>
   <si>
     <t xml:space="preserve">Capacity  &lt;-  6 - avg Lead time of THIS combo.  Observed delivery performance is the visible side of capacity; sanity-check against On-time %.</t>
   </si>
   <si>
-    <t xml:space="preserve">Supplier_Stability  &lt;-  6 - average(Responsiveness, Cost) across ALL the supplier's projects, regardless of process - stability is about the supplier as a business, not one part. Cost has no part-level column in the risk register, but erratic pricing and poor cost transparency - like slow communication - are stability evidence.</t>
+    <t xml:space="preserve">Supplier_Stability  &lt;-  6 - average(Responsiveness, Cost) across ALL the supplier's projects, regardless of part - stability is about the supplier as a business. Cost has no part-level column in the risk register, but erratic pricing and poor cost transparency - like slow communication - are stability evidence.</t>
   </si>
   <si>
     <t xml:space="preserve">No scorecard equivalent - score these by judgment in the master model:  Sourcing_Backup (do alternatives exist?),  External_Factors (location, logistics, borders),  Impact (what the part means to the model),  Qty_per_Model / volume.</t>
@@ -490,7 +502,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="0"/>
@@ -498,7 +510,8 @@
     <numFmt numFmtId="168" formatCode="#,##0"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="0%"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="General"/>
+    <numFmt numFmtId="172" formatCode="0.0"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -638,15 +651,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF1F3864"/>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -683,7 +696,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -716,14 +729,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF6DC"/>
-        <bgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF6DC"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -930,10 +937,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -942,15 +945,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -958,15 +965,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="20" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -998,11 +1005,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="24" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1159,7 +1166,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF6DC"/>
+      <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFF8696B"/>
@@ -1176,7 +1183,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFD9E2F3"/>
       <rgbColor rgb="FFF9F9F9"/>
-      <rgbColor rgb="FFFFF2CC"/>
+      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -1370,11 +1377,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="68840439"/>
-        <c:axId val="82587896"/>
+        <c:axId val="99799878"/>
+        <c:axId val="57483095"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="68840439"/>
+        <c:axId val="99799878"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1406,7 +1413,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82587896"/>
+        <c:crossAx val="57483095"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1414,7 +1421,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="82587896"/>
+        <c:axId val="57483095"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -1458,7 +1465,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68840439"/>
+        <c:crossAx val="99799878"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1501,9 +1508,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>132120</xdr:colOff>
+      <xdr:colOff>131760</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>17640</xdr:rowOff>
+      <xdr:rowOff>17280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1512,7 +1519,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="13335120" y="560880"/>
-        <a:ext cx="6768360" cy="3257280"/>
+        <a:ext cx="6768000" cy="3256920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1845,7 +1852,7 @@
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V203"/>
+  <dimension ref="A1:V204"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -2049,46 +2056,92 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L5" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N5" s="13" t="n">
+        <f aca="false">IF(COUNT(F5,H5,J5,L5)&lt;4,"",ROUND(F5*Settings!$B$4+H5*Settings!$B$5+J5*Settings!$B$6+L5*Settings!$B$7,2))</f>
+        <v>4.5</v>
+      </c>
+      <c r="O5" s="14" t="n">
+        <v>20585.77</v>
+      </c>
+      <c r="P5" s="14" t="n">
+        <v>6939</v>
+      </c>
+      <c r="Q5" s="15" t="n">
+        <f aca="false">IF(OR(O5="",P5="",O5=0),"",(P5-O5)/O5)</f>
+        <v>-0.662922494519272</v>
+      </c>
+      <c r="R5" s="10" t="n">
+        <v>46216</v>
+      </c>
+      <c r="S5" s="10" t="n">
+        <v>46216</v>
+      </c>
+      <c r="T5" s="16" t="n">
+        <f aca="false">IF(OR(R5="",S5=""),"",S5-R5)</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="17" t="str">
+        <f aca="false">IF(T5="","",IF(T5&lt;=0,"Yes","No"))</f>
+        <v>Yes</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="n">
         <v>46027</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="11" t="s">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D6" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="N5" s="13"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="10"/>
-      <c r="T5" s="16"/>
-      <c r="U5" s="17"/>
-      <c r="V5" s="11"/>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
       <c r="F6" s="12"/>
       <c r="G6" s="11"/>
       <c r="H6" s="12"/>
@@ -2096,7 +2149,9 @@
       <c r="J6" s="12"/>
       <c r="K6" s="11"/>
       <c r="L6" s="12"/>
-      <c r="M6" s="11"/>
+      <c r="M6" s="11" t="s">
+        <v>60</v>
+      </c>
       <c r="N6" s="13"/>
       <c r="O6" s="14"/>
       <c r="P6" s="14"/>
@@ -2156,40 +2211,28 @@
       <c r="V8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="20" t="str">
-        <f aca="false">IF(COUNT(F9,H9,J9,L9)&lt;4,"",ROUND(F9*Settings!$B$4+H9*Settings!$B$5+J9*Settings!$B$6+L9*Settings!$B$7,2))</f>
-        <v/>
-      </c>
-      <c r="O9" s="21"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="22" t="str">
-        <f aca="false">IF(OR(O9="",P9="",O9=0),"",(P9-O9)/O9)</f>
-        <v/>
-      </c>
-      <c r="R9" s="18"/>
-      <c r="S9" s="18"/>
-      <c r="T9" s="23" t="str">
-        <f aca="false">IF(OR(R9="",S9=""),"",S9-R9)</f>
-        <v/>
-      </c>
-      <c r="U9" s="24" t="str">
-        <f aca="false">IF(T9="","",IF(T9&lt;=0,"Yes","No"))</f>
-        <v/>
-      </c>
-      <c r="V9" s="2"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="17"/>
+      <c r="V9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18"/>
@@ -9175,15 +9218,51 @@
       </c>
       <c r="V203" s="2"/>
     </row>
+    <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="18"/>
+      <c r="B204" s="2"/>
+      <c r="C204" s="2"/>
+      <c r="D204" s="2"/>
+      <c r="E204" s="2"/>
+      <c r="F204" s="19"/>
+      <c r="G204" s="2"/>
+      <c r="H204" s="19"/>
+      <c r="I204" s="2"/>
+      <c r="J204" s="19"/>
+      <c r="K204" s="2"/>
+      <c r="L204" s="19"/>
+      <c r="M204" s="2"/>
+      <c r="N204" s="20" t="str">
+        <f aca="false">IF(COUNT(F204,H204,J204,L204)&lt;4,"",ROUND(F204*Settings!$B$4+H204*Settings!$B$5+J204*Settings!$B$6+L204*Settings!$B$7,2))</f>
+        <v/>
+      </c>
+      <c r="O204" s="21"/>
+      <c r="P204" s="21"/>
+      <c r="Q204" s="22" t="str">
+        <f aca="false">IF(OR(O204="",P204="",O204=0),"",(P204-O204)/O204)</f>
+        <v/>
+      </c>
+      <c r="R204" s="18"/>
+      <c r="S204" s="18"/>
+      <c r="T204" s="23" t="str">
+        <f aca="false">IF(OR(R204="",S204=""),"",S204-R204)</f>
+        <v/>
+      </c>
+      <c r="U204" s="24" t="str">
+        <f aca="false">IF(T204="","",IF(T204&lt;=0,"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="V204" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:V203"/>
+  <autoFilter ref="A3:V204"/>
   <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="F2:N2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:U2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F4:F203">
+  <conditionalFormatting sqref="F4:F204">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -9195,7 +9274,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H203">
+  <conditionalFormatting sqref="H4:H204">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -9207,7 +9286,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J203">
+  <conditionalFormatting sqref="J4:J204">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -9219,7 +9298,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L203">
+  <conditionalFormatting sqref="L4:L204">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -9231,7 +9310,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:N203">
+  <conditionalFormatting sqref="N4:N204">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -9243,7 +9322,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q4:Q203">
+  <conditionalFormatting sqref="Q4:Q204">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-0.2"/>
@@ -9255,7 +9334,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U4:U203">
+  <conditionalFormatting sqref="U4:U204">
     <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>"No"</formula>
     </cfRule>
@@ -9264,15 +9343,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" error="Scores go from 1 (poor) to 5 (excellent). See the Rubric tab." errorStyle="stop" errorTitle="Score must be 1–5" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F4:F203 H4:H203 J4:J203 L4:L203" type="list">
+    <dataValidation allowBlank="true" error="Scores go from 1 (poor) to 5 (excellent). See the Rubric tab." errorStyle="stop" errorTitle="Score must be 1–5" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F4:F204 H4:H204 J4:J204 L4:L204" type="list">
       <formula1>"1,2,3,4,5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Pick a supplier from the Suppliers tab (or add it there first)." errorStyle="stop" errorTitle="Unknown supplier" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C4:C203" type="list">
+    <dataValidation allowBlank="true" error="Pick a supplier from the Suppliers tab (or add it there first)." errorStyle="stop" errorTitle="Unknown supplier" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C4:C204" type="list">
       <formula1>ScorecardSuppliers</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Pick a process from the list in Settings (or add it there first)." errorStyle="stop" errorTitle="Unknown process" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D4:D203" type="list">
+    <dataValidation allowBlank="true" error="Pick a process from the list in Settings (or add it there first)." errorStyle="stop" errorTitle="Unknown process" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D4:D204" type="list">
       <formula1>ScorecardProcesses</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9309,17 +9388,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9327,31 +9406,31 @@
         <v>27</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9360,39 +9439,39 @@
         <v>Fictiv</v>
       </c>
       <c r="B5" s="27" t="n">
-        <f aca="false">IF($A5="","",COUNTIFS('Score Log'!$C$4:$C$203,$A5))</f>
+        <f aca="false">IF($A5="","",COUNTIFS('Score Log'!$C$4:$C$204,$A5))</f>
+        <v>2</v>
+      </c>
+      <c r="C5" s="28" t="n">
+        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A5),2),"–"))</f>
+        <v>4</v>
+      </c>
+      <c r="D5" s="28" t="n">
+        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A5),2),"–"))</f>
+        <v>5</v>
+      </c>
+      <c r="E5" s="28" t="n">
+        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A5),2),"–"))</f>
+        <v>4</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A5),2),"–"))</f>
+        <v>5</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A5),2),"–"))</f>
+        <v>4.5</v>
+      </c>
+      <c r="H5" s="29" t="n">
+        <f aca="false">IF($A5="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A5,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A5,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A5,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v>1</v>
       </c>
-      <c r="C5" s="28" t="n">
-        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A5),2),"–"))</f>
-        <v>4</v>
-      </c>
-      <c r="D5" s="28" t="n">
-        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A5),2),"–"))</f>
-        <v>5</v>
-      </c>
-      <c r="E5" s="28" t="n">
-        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A5),2),"–"))</f>
-        <v>4</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A5),2),"–"))</f>
-        <v>5</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <f aca="false">IF($A5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A5),2),"–"))</f>
-        <v>4.5</v>
-      </c>
-      <c r="H5" s="29" t="n">
-        <f aca="false">IF($A5="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A5,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A5,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A5,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
-        <v>1</v>
-      </c>
       <c r="I5" s="30" t="n">
-        <f aca="false">IF($A5="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A5),"–"))</f>
+        <f aca="false">IF($A5="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A5),"–"))</f>
         <v>-0.662922494519272</v>
       </c>
       <c r="J5" s="31" t="n">
-        <f aca="false">IF($A5="","",IF($B5=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A5)))</f>
+        <f aca="false">IF($A5="","",IF($B5=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A5)))</f>
         <v>46174</v>
       </c>
     </row>
@@ -9402,39 +9481,39 @@
         <v>Advanced Plastiform</v>
       </c>
       <c r="B6" s="27" t="n">
-        <f aca="false">IF($A6="","",COUNTIFS('Score Log'!$C$4:$C$203,$A6))</f>
+        <f aca="false">IF($A6="","",COUNTIFS('Score Log'!$C$4:$C$204,$A6))</f>
         <v>1</v>
       </c>
       <c r="C6" s="28" t="str">
-        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A6),2),"–"))</f>
+        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A6),2),"–"))</f>
         <v>–</v>
       </c>
       <c r="D6" s="28" t="str">
-        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A6),2),"–"))</f>
+        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A6),2),"–"))</f>
         <v>–</v>
       </c>
       <c r="E6" s="28" t="str">
-        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A6),2),"–"))</f>
+        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A6),2),"–"))</f>
         <v>–</v>
       </c>
       <c r="F6" s="28" t="str">
-        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A6),2),"–"))</f>
+        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A6),2),"–"))</f>
         <v>–</v>
       </c>
       <c r="G6" s="28" t="str">
-        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A6),2),"–"))</f>
+        <f aca="false">IF($A6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A6),2),"–"))</f>
         <v>–</v>
       </c>
       <c r="H6" s="29" t="str">
-        <f aca="false">IF($A6="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A6,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A6,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A6,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A6="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A6,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A6,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A6,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v>–</v>
       </c>
       <c r="I6" s="30" t="str">
-        <f aca="false">IF($A6="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A6),"–"))</f>
+        <f aca="false">IF($A6="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A6),"–"))</f>
         <v>–</v>
       </c>
       <c r="J6" s="31" t="n">
-        <f aca="false">IF($A6="","",IF($B6=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A6)))</f>
+        <f aca="false">IF($A6="","",IF($B6=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A6)))</f>
         <v>46027</v>
       </c>
     </row>
@@ -9444,39 +9523,39 @@
         <v/>
       </c>
       <c r="B7" s="27" t="str">
-        <f aca="false">IF($A7="","",COUNTIFS('Score Log'!$C$4:$C$203,$A7))</f>
+        <f aca="false">IF($A7="","",COUNTIFS('Score Log'!$C$4:$C$204,$A7))</f>
         <v/>
       </c>
       <c r="C7" s="28" t="str">
-        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A7),2),"–"))</f>
+        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A7),2),"–"))</f>
         <v/>
       </c>
       <c r="D7" s="28" t="str">
-        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A7),2),"–"))</f>
+        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A7),2),"–"))</f>
         <v/>
       </c>
       <c r="E7" s="28" t="str">
-        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A7),2),"–"))</f>
+        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A7),2),"–"))</f>
         <v/>
       </c>
       <c r="F7" s="28" t="str">
-        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A7),2),"–"))</f>
+        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A7),2),"–"))</f>
         <v/>
       </c>
       <c r="G7" s="28" t="str">
-        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A7),2),"–"))</f>
+        <f aca="false">IF($A7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A7),2),"–"))</f>
         <v/>
       </c>
       <c r="H7" s="29" t="str">
-        <f aca="false">IF($A7="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A7,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A7,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A7,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A7="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A7,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A7,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A7,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I7" s="30" t="str">
-        <f aca="false">IF($A7="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A7),"–"))</f>
+        <f aca="false">IF($A7="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A7),"–"))</f>
         <v/>
       </c>
       <c r="J7" s="31" t="str">
-        <f aca="false">IF($A7="","",IF($B7=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A7)))</f>
+        <f aca="false">IF($A7="","",IF($B7=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A7)))</f>
         <v/>
       </c>
     </row>
@@ -9486,39 +9565,39 @@
         <v/>
       </c>
       <c r="B8" s="27" t="str">
-        <f aca="false">IF($A8="","",COUNTIFS('Score Log'!$C$4:$C$203,$A8))</f>
+        <f aca="false">IF($A8="","",COUNTIFS('Score Log'!$C$4:$C$204,$A8))</f>
         <v/>
       </c>
       <c r="C8" s="28" t="str">
-        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A8),2),"–"))</f>
+        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A8),2),"–"))</f>
         <v/>
       </c>
       <c r="D8" s="28" t="str">
-        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A8),2),"–"))</f>
+        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A8),2),"–"))</f>
         <v/>
       </c>
       <c r="E8" s="28" t="str">
-        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A8),2),"–"))</f>
+        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A8),2),"–"))</f>
         <v/>
       </c>
       <c r="F8" s="28" t="str">
-        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A8),2),"–"))</f>
+        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A8),2),"–"))</f>
         <v/>
       </c>
       <c r="G8" s="28" t="str">
-        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A8),2),"–"))</f>
+        <f aca="false">IF($A8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A8),2),"–"))</f>
         <v/>
       </c>
       <c r="H8" s="29" t="str">
-        <f aca="false">IF($A8="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A8,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A8,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A8,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A8="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A8,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A8,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A8,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I8" s="30" t="str">
-        <f aca="false">IF($A8="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A8),"–"))</f>
+        <f aca="false">IF($A8="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A8),"–"))</f>
         <v/>
       </c>
       <c r="J8" s="31" t="str">
-        <f aca="false">IF($A8="","",IF($B8=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A8)))</f>
+        <f aca="false">IF($A8="","",IF($B8=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A8)))</f>
         <v/>
       </c>
     </row>
@@ -9528,39 +9607,39 @@
         <v/>
       </c>
       <c r="B9" s="27" t="str">
-        <f aca="false">IF($A9="","",COUNTIFS('Score Log'!$C$4:$C$203,$A9))</f>
+        <f aca="false">IF($A9="","",COUNTIFS('Score Log'!$C$4:$C$204,$A9))</f>
         <v/>
       </c>
       <c r="C9" s="28" t="str">
-        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A9),2),"–"))</f>
+        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A9),2),"–"))</f>
         <v/>
       </c>
       <c r="D9" s="28" t="str">
-        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A9),2),"–"))</f>
+        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A9),2),"–"))</f>
         <v/>
       </c>
       <c r="E9" s="28" t="str">
-        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A9),2),"–"))</f>
+        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A9),2),"–"))</f>
         <v/>
       </c>
       <c r="F9" s="28" t="str">
-        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A9),2),"–"))</f>
+        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A9),2),"–"))</f>
         <v/>
       </c>
       <c r="G9" s="28" t="str">
-        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A9),2),"–"))</f>
+        <f aca="false">IF($A9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A9),2),"–"))</f>
         <v/>
       </c>
       <c r="H9" s="29" t="str">
-        <f aca="false">IF($A9="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A9,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A9,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A9,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A9="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A9,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A9,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A9,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I9" s="30" t="str">
-        <f aca="false">IF($A9="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A9),"–"))</f>
+        <f aca="false">IF($A9="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A9),"–"))</f>
         <v/>
       </c>
       <c r="J9" s="31" t="str">
-        <f aca="false">IF($A9="","",IF($B9=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A9)))</f>
+        <f aca="false">IF($A9="","",IF($B9=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A9)))</f>
         <v/>
       </c>
     </row>
@@ -9570,39 +9649,39 @@
         <v/>
       </c>
       <c r="B10" s="27" t="str">
-        <f aca="false">IF($A10="","",COUNTIFS('Score Log'!$C$4:$C$203,$A10))</f>
+        <f aca="false">IF($A10="","",COUNTIFS('Score Log'!$C$4:$C$204,$A10))</f>
         <v/>
       </c>
       <c r="C10" s="28" t="str">
-        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A10),2),"–"))</f>
+        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A10),2),"–"))</f>
         <v/>
       </c>
       <c r="D10" s="28" t="str">
-        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A10),2),"–"))</f>
+        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A10),2),"–"))</f>
         <v/>
       </c>
       <c r="E10" s="28" t="str">
-        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A10),2),"–"))</f>
+        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A10),2),"–"))</f>
         <v/>
       </c>
       <c r="F10" s="28" t="str">
-        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A10),2),"–"))</f>
+        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A10),2),"–"))</f>
         <v/>
       </c>
       <c r="G10" s="28" t="str">
-        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A10),2),"–"))</f>
+        <f aca="false">IF($A10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A10),2),"–"))</f>
         <v/>
       </c>
       <c r="H10" s="29" t="str">
-        <f aca="false">IF($A10="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A10,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A10,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A10,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A10="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A10,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A10,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A10,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I10" s="30" t="str">
-        <f aca="false">IF($A10="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A10),"–"))</f>
+        <f aca="false">IF($A10="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A10),"–"))</f>
         <v/>
       </c>
       <c r="J10" s="31" t="str">
-        <f aca="false">IF($A10="","",IF($B10=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A10)))</f>
+        <f aca="false">IF($A10="","",IF($B10=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A10)))</f>
         <v/>
       </c>
     </row>
@@ -9612,39 +9691,39 @@
         <v/>
       </c>
       <c r="B11" s="27" t="str">
-        <f aca="false">IF($A11="","",COUNTIFS('Score Log'!$C$4:$C$203,$A11))</f>
+        <f aca="false">IF($A11="","",COUNTIFS('Score Log'!$C$4:$C$204,$A11))</f>
         <v/>
       </c>
       <c r="C11" s="28" t="str">
-        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A11),2),"–"))</f>
+        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A11),2),"–"))</f>
         <v/>
       </c>
       <c r="D11" s="28" t="str">
-        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A11),2),"–"))</f>
+        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A11),2),"–"))</f>
         <v/>
       </c>
       <c r="E11" s="28" t="str">
-        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A11),2),"–"))</f>
+        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A11),2),"–"))</f>
         <v/>
       </c>
       <c r="F11" s="28" t="str">
-        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A11),2),"–"))</f>
+        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A11),2),"–"))</f>
         <v/>
       </c>
       <c r="G11" s="28" t="str">
-        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A11),2),"–"))</f>
+        <f aca="false">IF($A11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A11),2),"–"))</f>
         <v/>
       </c>
       <c r="H11" s="29" t="str">
-        <f aca="false">IF($A11="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A11,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A11,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A11,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A11="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A11,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A11,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A11,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I11" s="30" t="str">
-        <f aca="false">IF($A11="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A11),"–"))</f>
+        <f aca="false">IF($A11="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A11),"–"))</f>
         <v/>
       </c>
       <c r="J11" s="31" t="str">
-        <f aca="false">IF($A11="","",IF($B11=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A11)))</f>
+        <f aca="false">IF($A11="","",IF($B11=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A11)))</f>
         <v/>
       </c>
     </row>
@@ -9654,39 +9733,39 @@
         <v/>
       </c>
       <c r="B12" s="27" t="str">
-        <f aca="false">IF($A12="","",COUNTIFS('Score Log'!$C$4:$C$203,$A12))</f>
+        <f aca="false">IF($A12="","",COUNTIFS('Score Log'!$C$4:$C$204,$A12))</f>
         <v/>
       </c>
       <c r="C12" s="28" t="str">
-        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A12),2),"–"))</f>
+        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A12),2),"–"))</f>
         <v/>
       </c>
       <c r="D12" s="28" t="str">
-        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A12),2),"–"))</f>
+        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A12),2),"–"))</f>
         <v/>
       </c>
       <c r="E12" s="28" t="str">
-        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A12),2),"–"))</f>
+        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A12),2),"–"))</f>
         <v/>
       </c>
       <c r="F12" s="28" t="str">
-        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A12),2),"–"))</f>
+        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A12),2),"–"))</f>
         <v/>
       </c>
       <c r="G12" s="28" t="str">
-        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A12),2),"–"))</f>
+        <f aca="false">IF($A12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A12),2),"–"))</f>
         <v/>
       </c>
       <c r="H12" s="29" t="str">
-        <f aca="false">IF($A12="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A12,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A12,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A12,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A12="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A12,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A12,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A12,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I12" s="30" t="str">
-        <f aca="false">IF($A12="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A12),"–"))</f>
+        <f aca="false">IF($A12="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A12),"–"))</f>
         <v/>
       </c>
       <c r="J12" s="31" t="str">
-        <f aca="false">IF($A12="","",IF($B12=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A12)))</f>
+        <f aca="false">IF($A12="","",IF($B12=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A12)))</f>
         <v/>
       </c>
     </row>
@@ -9696,39 +9775,39 @@
         <v/>
       </c>
       <c r="B13" s="27" t="str">
-        <f aca="false">IF($A13="","",COUNTIFS('Score Log'!$C$4:$C$203,$A13))</f>
+        <f aca="false">IF($A13="","",COUNTIFS('Score Log'!$C$4:$C$204,$A13))</f>
         <v/>
       </c>
       <c r="C13" s="28" t="str">
-        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A13),2),"–"))</f>
+        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A13),2),"–"))</f>
         <v/>
       </c>
       <c r="D13" s="28" t="str">
-        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A13),2),"–"))</f>
+        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A13),2),"–"))</f>
         <v/>
       </c>
       <c r="E13" s="28" t="str">
-        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A13),2),"–"))</f>
+        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A13),2),"–"))</f>
         <v/>
       </c>
       <c r="F13" s="28" t="str">
-        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A13),2),"–"))</f>
+        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A13),2),"–"))</f>
         <v/>
       </c>
       <c r="G13" s="28" t="str">
-        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A13),2),"–"))</f>
+        <f aca="false">IF($A13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A13),2),"–"))</f>
         <v/>
       </c>
       <c r="H13" s="29" t="str">
-        <f aca="false">IF($A13="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A13,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A13,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A13,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A13="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A13,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A13,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A13,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I13" s="30" t="str">
-        <f aca="false">IF($A13="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A13),"–"))</f>
+        <f aca="false">IF($A13="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A13),"–"))</f>
         <v/>
       </c>
       <c r="J13" s="31" t="str">
-        <f aca="false">IF($A13="","",IF($B13=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A13)))</f>
+        <f aca="false">IF($A13="","",IF($B13=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A13)))</f>
         <v/>
       </c>
     </row>
@@ -9738,39 +9817,39 @@
         <v/>
       </c>
       <c r="B14" s="27" t="str">
-        <f aca="false">IF($A14="","",COUNTIFS('Score Log'!$C$4:$C$203,$A14))</f>
+        <f aca="false">IF($A14="","",COUNTIFS('Score Log'!$C$4:$C$204,$A14))</f>
         <v/>
       </c>
       <c r="C14" s="28" t="str">
-        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A14),2),"–"))</f>
+        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A14),2),"–"))</f>
         <v/>
       </c>
       <c r="D14" s="28" t="str">
-        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A14),2),"–"))</f>
+        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A14),2),"–"))</f>
         <v/>
       </c>
       <c r="E14" s="28" t="str">
-        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A14),2),"–"))</f>
+        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A14),2),"–"))</f>
         <v/>
       </c>
       <c r="F14" s="28" t="str">
-        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A14),2),"–"))</f>
+        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A14),2),"–"))</f>
         <v/>
       </c>
       <c r="G14" s="28" t="str">
-        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A14),2),"–"))</f>
+        <f aca="false">IF($A14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A14),2),"–"))</f>
         <v/>
       </c>
       <c r="H14" s="29" t="str">
-        <f aca="false">IF($A14="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A14,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A14,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A14,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A14="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A14,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A14,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A14,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I14" s="30" t="str">
-        <f aca="false">IF($A14="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A14),"–"))</f>
+        <f aca="false">IF($A14="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A14),"–"))</f>
         <v/>
       </c>
       <c r="J14" s="31" t="str">
-        <f aca="false">IF($A14="","",IF($B14=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A14)))</f>
+        <f aca="false">IF($A14="","",IF($B14=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A14)))</f>
         <v/>
       </c>
     </row>
@@ -9780,39 +9859,39 @@
         <v/>
       </c>
       <c r="B15" s="27" t="str">
-        <f aca="false">IF($A15="","",COUNTIFS('Score Log'!$C$4:$C$203,$A15))</f>
+        <f aca="false">IF($A15="","",COUNTIFS('Score Log'!$C$4:$C$204,$A15))</f>
         <v/>
       </c>
       <c r="C15" s="28" t="str">
-        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A15),2),"–"))</f>
+        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A15),2),"–"))</f>
         <v/>
       </c>
       <c r="D15" s="28" t="str">
-        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A15),2),"–"))</f>
+        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A15),2),"–"))</f>
         <v/>
       </c>
       <c r="E15" s="28" t="str">
-        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A15),2),"–"))</f>
+        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A15),2),"–"))</f>
         <v/>
       </c>
       <c r="F15" s="28" t="str">
-        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A15),2),"–"))</f>
+        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A15),2),"–"))</f>
         <v/>
       </c>
       <c r="G15" s="28" t="str">
-        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A15),2),"–"))</f>
+        <f aca="false">IF($A15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A15),2),"–"))</f>
         <v/>
       </c>
       <c r="H15" s="29" t="str">
-        <f aca="false">IF($A15="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A15,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A15,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A15,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A15="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A15,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A15,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A15,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I15" s="30" t="str">
-        <f aca="false">IF($A15="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A15),"–"))</f>
+        <f aca="false">IF($A15="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A15),"–"))</f>
         <v/>
       </c>
       <c r="J15" s="31" t="str">
-        <f aca="false">IF($A15="","",IF($B15=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A15)))</f>
+        <f aca="false">IF($A15="","",IF($B15=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A15)))</f>
         <v/>
       </c>
     </row>
@@ -9822,39 +9901,39 @@
         <v/>
       </c>
       <c r="B16" s="27" t="str">
-        <f aca="false">IF($A16="","",COUNTIFS('Score Log'!$C$4:$C$203,$A16))</f>
+        <f aca="false">IF($A16="","",COUNTIFS('Score Log'!$C$4:$C$204,$A16))</f>
         <v/>
       </c>
       <c r="C16" s="28" t="str">
-        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A16),2),"–"))</f>
+        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A16),2),"–"))</f>
         <v/>
       </c>
       <c r="D16" s="28" t="str">
-        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A16),2),"–"))</f>
+        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A16),2),"–"))</f>
         <v/>
       </c>
       <c r="E16" s="28" t="str">
-        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A16),2),"–"))</f>
+        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A16),2),"–"))</f>
         <v/>
       </c>
       <c r="F16" s="28" t="str">
-        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A16),2),"–"))</f>
+        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A16),2),"–"))</f>
         <v/>
       </c>
       <c r="G16" s="28" t="str">
-        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A16),2),"–"))</f>
+        <f aca="false">IF($A16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A16),2),"–"))</f>
         <v/>
       </c>
       <c r="H16" s="29" t="str">
-        <f aca="false">IF($A16="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A16,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A16,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A16,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A16="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A16,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A16,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A16,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I16" s="30" t="str">
-        <f aca="false">IF($A16="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A16),"–"))</f>
+        <f aca="false">IF($A16="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A16),"–"))</f>
         <v/>
       </c>
       <c r="J16" s="31" t="str">
-        <f aca="false">IF($A16="","",IF($B16=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A16)))</f>
+        <f aca="false">IF($A16="","",IF($B16=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A16)))</f>
         <v/>
       </c>
     </row>
@@ -9864,39 +9943,39 @@
         <v/>
       </c>
       <c r="B17" s="27" t="str">
-        <f aca="false">IF($A17="","",COUNTIFS('Score Log'!$C$4:$C$203,$A17))</f>
+        <f aca="false">IF($A17="","",COUNTIFS('Score Log'!$C$4:$C$204,$A17))</f>
         <v/>
       </c>
       <c r="C17" s="28" t="str">
-        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A17),2),"–"))</f>
+        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A17),2),"–"))</f>
         <v/>
       </c>
       <c r="D17" s="28" t="str">
-        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A17),2),"–"))</f>
+        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A17),2),"–"))</f>
         <v/>
       </c>
       <c r="E17" s="28" t="str">
-        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A17),2),"–"))</f>
+        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A17),2),"–"))</f>
         <v/>
       </c>
       <c r="F17" s="28" t="str">
-        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A17),2),"–"))</f>
+        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A17),2),"–"))</f>
         <v/>
       </c>
       <c r="G17" s="28" t="str">
-        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A17),2),"–"))</f>
+        <f aca="false">IF($A17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A17),2),"–"))</f>
         <v/>
       </c>
       <c r="H17" s="29" t="str">
-        <f aca="false">IF($A17="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A17,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A17,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A17,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A17="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A17,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A17,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A17,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I17" s="30" t="str">
-        <f aca="false">IF($A17="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A17),"–"))</f>
+        <f aca="false">IF($A17="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A17),"–"))</f>
         <v/>
       </c>
       <c r="J17" s="31" t="str">
-        <f aca="false">IF($A17="","",IF($B17=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A17)))</f>
+        <f aca="false">IF($A17="","",IF($B17=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A17)))</f>
         <v/>
       </c>
     </row>
@@ -9906,39 +9985,39 @@
         <v/>
       </c>
       <c r="B18" s="27" t="str">
-        <f aca="false">IF($A18="","",COUNTIFS('Score Log'!$C$4:$C$203,$A18))</f>
+        <f aca="false">IF($A18="","",COUNTIFS('Score Log'!$C$4:$C$204,$A18))</f>
         <v/>
       </c>
       <c r="C18" s="28" t="str">
-        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A18),2),"–"))</f>
+        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A18),2),"–"))</f>
         <v/>
       </c>
       <c r="D18" s="28" t="str">
-        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A18),2),"–"))</f>
+        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A18),2),"–"))</f>
         <v/>
       </c>
       <c r="E18" s="28" t="str">
-        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A18),2),"–"))</f>
+        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A18),2),"–"))</f>
         <v/>
       </c>
       <c r="F18" s="28" t="str">
-        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A18),2),"–"))</f>
+        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A18),2),"–"))</f>
         <v/>
       </c>
       <c r="G18" s="28" t="str">
-        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A18),2),"–"))</f>
+        <f aca="false">IF($A18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A18),2),"–"))</f>
         <v/>
       </c>
       <c r="H18" s="29" t="str">
-        <f aca="false">IF($A18="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A18,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A18,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A18,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A18="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A18,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A18,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A18,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I18" s="30" t="str">
-        <f aca="false">IF($A18="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A18),"–"))</f>
+        <f aca="false">IF($A18="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A18),"–"))</f>
         <v/>
       </c>
       <c r="J18" s="31" t="str">
-        <f aca="false">IF($A18="","",IF($B18=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A18)))</f>
+        <f aca="false">IF($A18="","",IF($B18=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A18)))</f>
         <v/>
       </c>
     </row>
@@ -9948,39 +10027,39 @@
         <v/>
       </c>
       <c r="B19" s="27" t="str">
-        <f aca="false">IF($A19="","",COUNTIFS('Score Log'!$C$4:$C$203,$A19))</f>
+        <f aca="false">IF($A19="","",COUNTIFS('Score Log'!$C$4:$C$204,$A19))</f>
         <v/>
       </c>
       <c r="C19" s="28" t="str">
-        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A19),2),"–"))</f>
+        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A19),2),"–"))</f>
         <v/>
       </c>
       <c r="D19" s="28" t="str">
-        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A19),2),"–"))</f>
+        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A19),2),"–"))</f>
         <v/>
       </c>
       <c r="E19" s="28" t="str">
-        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A19),2),"–"))</f>
+        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A19),2),"–"))</f>
         <v/>
       </c>
       <c r="F19" s="28" t="str">
-        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A19),2),"–"))</f>
+        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A19),2),"–"))</f>
         <v/>
       </c>
       <c r="G19" s="28" t="str">
-        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A19),2),"–"))</f>
+        <f aca="false">IF($A19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A19),2),"–"))</f>
         <v/>
       </c>
       <c r="H19" s="29" t="str">
-        <f aca="false">IF($A19="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A19,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A19,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A19,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A19="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A19,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A19,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A19,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I19" s="30" t="str">
-        <f aca="false">IF($A19="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A19),"–"))</f>
+        <f aca="false">IF($A19="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A19),"–"))</f>
         <v/>
       </c>
       <c r="J19" s="31" t="str">
-        <f aca="false">IF($A19="","",IF($B19=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A19)))</f>
+        <f aca="false">IF($A19="","",IF($B19=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A19)))</f>
         <v/>
       </c>
     </row>
@@ -9990,39 +10069,39 @@
         <v/>
       </c>
       <c r="B20" s="27" t="str">
-        <f aca="false">IF($A20="","",COUNTIFS('Score Log'!$C$4:$C$203,$A20))</f>
+        <f aca="false">IF($A20="","",COUNTIFS('Score Log'!$C$4:$C$204,$A20))</f>
         <v/>
       </c>
       <c r="C20" s="28" t="str">
-        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A20),2),"–"))</f>
+        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A20),2),"–"))</f>
         <v/>
       </c>
       <c r="D20" s="28" t="str">
-        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A20),2),"–"))</f>
+        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A20),2),"–"))</f>
         <v/>
       </c>
       <c r="E20" s="28" t="str">
-        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A20),2),"–"))</f>
+        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A20),2),"–"))</f>
         <v/>
       </c>
       <c r="F20" s="28" t="str">
-        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A20),2),"–"))</f>
+        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A20),2),"–"))</f>
         <v/>
       </c>
       <c r="G20" s="28" t="str">
-        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A20),2),"–"))</f>
+        <f aca="false">IF($A20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A20),2),"–"))</f>
         <v/>
       </c>
       <c r="H20" s="29" t="str">
-        <f aca="false">IF($A20="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A20,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A20,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A20,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A20="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A20,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A20,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A20,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I20" s="30" t="str">
-        <f aca="false">IF($A20="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A20),"–"))</f>
+        <f aca="false">IF($A20="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A20),"–"))</f>
         <v/>
       </c>
       <c r="J20" s="31" t="str">
-        <f aca="false">IF($A20="","",IF($B20=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A20)))</f>
+        <f aca="false">IF($A20="","",IF($B20=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A20)))</f>
         <v/>
       </c>
     </row>
@@ -10032,39 +10111,39 @@
         <v/>
       </c>
       <c r="B21" s="27" t="str">
-        <f aca="false">IF($A21="","",COUNTIFS('Score Log'!$C$4:$C$203,$A21))</f>
+        <f aca="false">IF($A21="","",COUNTIFS('Score Log'!$C$4:$C$204,$A21))</f>
         <v/>
       </c>
       <c r="C21" s="28" t="str">
-        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A21),2),"–"))</f>
+        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A21),2),"–"))</f>
         <v/>
       </c>
       <c r="D21" s="28" t="str">
-        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A21),2),"–"))</f>
+        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A21),2),"–"))</f>
         <v/>
       </c>
       <c r="E21" s="28" t="str">
-        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A21),2),"–"))</f>
+        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A21),2),"–"))</f>
         <v/>
       </c>
       <c r="F21" s="28" t="str">
-        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A21),2),"–"))</f>
+        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A21),2),"–"))</f>
         <v/>
       </c>
       <c r="G21" s="28" t="str">
-        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A21),2),"–"))</f>
+        <f aca="false">IF($A21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A21),2),"–"))</f>
         <v/>
       </c>
       <c r="H21" s="29" t="str">
-        <f aca="false">IF($A21="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A21,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A21,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A21,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A21="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A21,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A21,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A21,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I21" s="30" t="str">
-        <f aca="false">IF($A21="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A21),"–"))</f>
+        <f aca="false">IF($A21="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A21),"–"))</f>
         <v/>
       </c>
       <c r="J21" s="31" t="str">
-        <f aca="false">IF($A21="","",IF($B21=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A21)))</f>
+        <f aca="false">IF($A21="","",IF($B21=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A21)))</f>
         <v/>
       </c>
     </row>
@@ -10074,39 +10153,39 @@
         <v/>
       </c>
       <c r="B22" s="27" t="str">
-        <f aca="false">IF($A22="","",COUNTIFS('Score Log'!$C$4:$C$203,$A22))</f>
+        <f aca="false">IF($A22="","",COUNTIFS('Score Log'!$C$4:$C$204,$A22))</f>
         <v/>
       </c>
       <c r="C22" s="28" t="str">
-        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A22),2),"–"))</f>
+        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A22),2),"–"))</f>
         <v/>
       </c>
       <c r="D22" s="28" t="str">
-        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A22),2),"–"))</f>
+        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A22),2),"–"))</f>
         <v/>
       </c>
       <c r="E22" s="28" t="str">
-        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A22),2),"–"))</f>
+        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A22),2),"–"))</f>
         <v/>
       </c>
       <c r="F22" s="28" t="str">
-        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A22),2),"–"))</f>
+        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A22),2),"–"))</f>
         <v/>
       </c>
       <c r="G22" s="28" t="str">
-        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A22),2),"–"))</f>
+        <f aca="false">IF($A22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A22),2),"–"))</f>
         <v/>
       </c>
       <c r="H22" s="29" t="str">
-        <f aca="false">IF($A22="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A22,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A22,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A22,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A22="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A22,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A22,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A22,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I22" s="30" t="str">
-        <f aca="false">IF($A22="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A22),"–"))</f>
+        <f aca="false">IF($A22="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A22),"–"))</f>
         <v/>
       </c>
       <c r="J22" s="31" t="str">
-        <f aca="false">IF($A22="","",IF($B22=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A22)))</f>
+        <f aca="false">IF($A22="","",IF($B22=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A22)))</f>
         <v/>
       </c>
     </row>
@@ -10116,39 +10195,39 @@
         <v/>
       </c>
       <c r="B23" s="27" t="str">
-        <f aca="false">IF($A23="","",COUNTIFS('Score Log'!$C$4:$C$203,$A23))</f>
+        <f aca="false">IF($A23="","",COUNTIFS('Score Log'!$C$4:$C$204,$A23))</f>
         <v/>
       </c>
       <c r="C23" s="28" t="str">
-        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A23),2),"–"))</f>
+        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A23),2),"–"))</f>
         <v/>
       </c>
       <c r="D23" s="28" t="str">
-        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A23),2),"–"))</f>
+        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A23),2),"–"))</f>
         <v/>
       </c>
       <c r="E23" s="28" t="str">
-        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A23),2),"–"))</f>
+        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A23),2),"–"))</f>
         <v/>
       </c>
       <c r="F23" s="28" t="str">
-        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A23),2),"–"))</f>
+        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A23),2),"–"))</f>
         <v/>
       </c>
       <c r="G23" s="28" t="str">
-        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A23),2),"–"))</f>
+        <f aca="false">IF($A23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A23),2),"–"))</f>
         <v/>
       </c>
       <c r="H23" s="29" t="str">
-        <f aca="false">IF($A23="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A23,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A23,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A23,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A23="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A23,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A23,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A23,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I23" s="30" t="str">
-        <f aca="false">IF($A23="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A23),"–"))</f>
+        <f aca="false">IF($A23="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A23),"–"))</f>
         <v/>
       </c>
       <c r="J23" s="31" t="str">
-        <f aca="false">IF($A23="","",IF($B23=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A23)))</f>
+        <f aca="false">IF($A23="","",IF($B23=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A23)))</f>
         <v/>
       </c>
     </row>
@@ -10158,39 +10237,39 @@
         <v/>
       </c>
       <c r="B24" s="27" t="str">
-        <f aca="false">IF($A24="","",COUNTIFS('Score Log'!$C$4:$C$203,$A24))</f>
+        <f aca="false">IF($A24="","",COUNTIFS('Score Log'!$C$4:$C$204,$A24))</f>
         <v/>
       </c>
       <c r="C24" s="28" t="str">
-        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A24),2),"–"))</f>
+        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A24),2),"–"))</f>
         <v/>
       </c>
       <c r="D24" s="28" t="str">
-        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A24),2),"–"))</f>
+        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A24),2),"–"))</f>
         <v/>
       </c>
       <c r="E24" s="28" t="str">
-        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A24),2),"–"))</f>
+        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A24),2),"–"))</f>
         <v/>
       </c>
       <c r="F24" s="28" t="str">
-        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A24),2),"–"))</f>
+        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A24),2),"–"))</f>
         <v/>
       </c>
       <c r="G24" s="28" t="str">
-        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A24),2),"–"))</f>
+        <f aca="false">IF($A24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A24),2),"–"))</f>
         <v/>
       </c>
       <c r="H24" s="29" t="str">
-        <f aca="false">IF($A24="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A24,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A24,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A24,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A24="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A24,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A24,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A24,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I24" s="30" t="str">
-        <f aca="false">IF($A24="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A24),"–"))</f>
+        <f aca="false">IF($A24="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A24),"–"))</f>
         <v/>
       </c>
       <c r="J24" s="31" t="str">
-        <f aca="false">IF($A24="","",IF($B24=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A24)))</f>
+        <f aca="false">IF($A24="","",IF($B24=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A24)))</f>
         <v/>
       </c>
     </row>
@@ -10200,39 +10279,39 @@
         <v/>
       </c>
       <c r="B25" s="27" t="str">
-        <f aca="false">IF($A25="","",COUNTIFS('Score Log'!$C$4:$C$203,$A25))</f>
+        <f aca="false">IF($A25="","",COUNTIFS('Score Log'!$C$4:$C$204,$A25))</f>
         <v/>
       </c>
       <c r="C25" s="28" t="str">
-        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A25),2),"–"))</f>
+        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A25),2),"–"))</f>
         <v/>
       </c>
       <c r="D25" s="28" t="str">
-        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A25),2),"–"))</f>
+        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A25),2),"–"))</f>
         <v/>
       </c>
       <c r="E25" s="28" t="str">
-        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A25),2),"–"))</f>
+        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A25),2),"–"))</f>
         <v/>
       </c>
       <c r="F25" s="28" t="str">
-        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A25),2),"–"))</f>
+        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A25),2),"–"))</f>
         <v/>
       </c>
       <c r="G25" s="28" t="str">
-        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A25),2),"–"))</f>
+        <f aca="false">IF($A25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A25),2),"–"))</f>
         <v/>
       </c>
       <c r="H25" s="29" t="str">
-        <f aca="false">IF($A25="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A25,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A25,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A25,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A25="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A25,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A25,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A25,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I25" s="30" t="str">
-        <f aca="false">IF($A25="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A25),"–"))</f>
+        <f aca="false">IF($A25="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A25),"–"))</f>
         <v/>
       </c>
       <c r="J25" s="31" t="str">
-        <f aca="false">IF($A25="","",IF($B25=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A25)))</f>
+        <f aca="false">IF($A25="","",IF($B25=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A25)))</f>
         <v/>
       </c>
     </row>
@@ -10242,39 +10321,39 @@
         <v/>
       </c>
       <c r="B26" s="27" t="str">
-        <f aca="false">IF($A26="","",COUNTIFS('Score Log'!$C$4:$C$203,$A26))</f>
+        <f aca="false">IF($A26="","",COUNTIFS('Score Log'!$C$4:$C$204,$A26))</f>
         <v/>
       </c>
       <c r="C26" s="28" t="str">
-        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A26),2),"–"))</f>
+        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A26),2),"–"))</f>
         <v/>
       </c>
       <c r="D26" s="28" t="str">
-        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A26),2),"–"))</f>
+        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A26),2),"–"))</f>
         <v/>
       </c>
       <c r="E26" s="28" t="str">
-        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A26),2),"–"))</f>
+        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A26),2),"–"))</f>
         <v/>
       </c>
       <c r="F26" s="28" t="str">
-        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A26),2),"–"))</f>
+        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A26),2),"–"))</f>
         <v/>
       </c>
       <c r="G26" s="28" t="str">
-        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A26),2),"–"))</f>
+        <f aca="false">IF($A26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A26),2),"–"))</f>
         <v/>
       </c>
       <c r="H26" s="29" t="str">
-        <f aca="false">IF($A26="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A26,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A26,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A26,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A26="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A26,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A26,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A26,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I26" s="30" t="str">
-        <f aca="false">IF($A26="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A26),"–"))</f>
+        <f aca="false">IF($A26="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A26),"–"))</f>
         <v/>
       </c>
       <c r="J26" s="31" t="str">
-        <f aca="false">IF($A26="","",IF($B26=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A26)))</f>
+        <f aca="false">IF($A26="","",IF($B26=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A26)))</f>
         <v/>
       </c>
     </row>
@@ -10284,39 +10363,39 @@
         <v/>
       </c>
       <c r="B27" s="27" t="str">
-        <f aca="false">IF($A27="","",COUNTIFS('Score Log'!$C$4:$C$203,$A27))</f>
+        <f aca="false">IF($A27="","",COUNTIFS('Score Log'!$C$4:$C$204,$A27))</f>
         <v/>
       </c>
       <c r="C27" s="28" t="str">
-        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A27),2),"–"))</f>
+        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A27),2),"–"))</f>
         <v/>
       </c>
       <c r="D27" s="28" t="str">
-        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A27),2),"–"))</f>
+        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A27),2),"–"))</f>
         <v/>
       </c>
       <c r="E27" s="28" t="str">
-        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A27),2),"–"))</f>
+        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A27),2),"–"))</f>
         <v/>
       </c>
       <c r="F27" s="28" t="str">
-        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A27),2),"–"))</f>
+        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A27),2),"–"))</f>
         <v/>
       </c>
       <c r="G27" s="28" t="str">
-        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A27),2),"–"))</f>
+        <f aca="false">IF($A27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A27),2),"–"))</f>
         <v/>
       </c>
       <c r="H27" s="29" t="str">
-        <f aca="false">IF($A27="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A27,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A27,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A27,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A27="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A27,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A27,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A27,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I27" s="30" t="str">
-        <f aca="false">IF($A27="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A27),"–"))</f>
+        <f aca="false">IF($A27="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A27),"–"))</f>
         <v/>
       </c>
       <c r="J27" s="31" t="str">
-        <f aca="false">IF($A27="","",IF($B27=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A27)))</f>
+        <f aca="false">IF($A27="","",IF($B27=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A27)))</f>
         <v/>
       </c>
     </row>
@@ -10326,39 +10405,39 @@
         <v/>
       </c>
       <c r="B28" s="27" t="str">
-        <f aca="false">IF($A28="","",COUNTIFS('Score Log'!$C$4:$C$203,$A28))</f>
+        <f aca="false">IF($A28="","",COUNTIFS('Score Log'!$C$4:$C$204,$A28))</f>
         <v/>
       </c>
       <c r="C28" s="28" t="str">
-        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A28),2),"–"))</f>
+        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A28),2),"–"))</f>
         <v/>
       </c>
       <c r="D28" s="28" t="str">
-        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A28),2),"–"))</f>
+        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A28),2),"–"))</f>
         <v/>
       </c>
       <c r="E28" s="28" t="str">
-        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A28),2),"–"))</f>
+        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A28),2),"–"))</f>
         <v/>
       </c>
       <c r="F28" s="28" t="str">
-        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A28),2),"–"))</f>
+        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A28),2),"–"))</f>
         <v/>
       </c>
       <c r="G28" s="28" t="str">
-        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A28),2),"–"))</f>
+        <f aca="false">IF($A28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A28),2),"–"))</f>
         <v/>
       </c>
       <c r="H28" s="29" t="str">
-        <f aca="false">IF($A28="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A28,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A28,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A28,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A28="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A28,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A28,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A28,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I28" s="30" t="str">
-        <f aca="false">IF($A28="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A28),"–"))</f>
+        <f aca="false">IF($A28="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A28),"–"))</f>
         <v/>
       </c>
       <c r="J28" s="31" t="str">
-        <f aca="false">IF($A28="","",IF($B28=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A28)))</f>
+        <f aca="false">IF($A28="","",IF($B28=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A28)))</f>
         <v/>
       </c>
     </row>
@@ -10368,39 +10447,39 @@
         <v/>
       </c>
       <c r="B29" s="27" t="str">
-        <f aca="false">IF($A29="","",COUNTIFS('Score Log'!$C$4:$C$203,$A29))</f>
+        <f aca="false">IF($A29="","",COUNTIFS('Score Log'!$C$4:$C$204,$A29))</f>
         <v/>
       </c>
       <c r="C29" s="28" t="str">
-        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A29),2),"–"))</f>
+        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A29),2),"–"))</f>
         <v/>
       </c>
       <c r="D29" s="28" t="str">
-        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A29),2),"–"))</f>
+        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A29),2),"–"))</f>
         <v/>
       </c>
       <c r="E29" s="28" t="str">
-        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A29),2),"–"))</f>
+        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A29),2),"–"))</f>
         <v/>
       </c>
       <c r="F29" s="28" t="str">
-        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A29),2),"–"))</f>
+        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A29),2),"–"))</f>
         <v/>
       </c>
       <c r="G29" s="28" t="str">
-        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A29),2),"–"))</f>
+        <f aca="false">IF($A29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A29),2),"–"))</f>
         <v/>
       </c>
       <c r="H29" s="29" t="str">
-        <f aca="false">IF($A29="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A29,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A29,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A29,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A29="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A29,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A29,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A29,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I29" s="30" t="str">
-        <f aca="false">IF($A29="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A29),"–"))</f>
+        <f aca="false">IF($A29="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A29),"–"))</f>
         <v/>
       </c>
       <c r="J29" s="31" t="str">
-        <f aca="false">IF($A29="","",IF($B29=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A29)))</f>
+        <f aca="false">IF($A29="","",IF($B29=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A29)))</f>
         <v/>
       </c>
     </row>
@@ -10410,39 +10489,39 @@
         <v/>
       </c>
       <c r="B30" s="27" t="str">
-        <f aca="false">IF($A30="","",COUNTIFS('Score Log'!$C$4:$C$203,$A30))</f>
+        <f aca="false">IF($A30="","",COUNTIFS('Score Log'!$C$4:$C$204,$A30))</f>
         <v/>
       </c>
       <c r="C30" s="28" t="str">
-        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A30),2),"–"))</f>
+        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A30),2),"–"))</f>
         <v/>
       </c>
       <c r="D30" s="28" t="str">
-        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A30),2),"–"))</f>
+        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A30),2),"–"))</f>
         <v/>
       </c>
       <c r="E30" s="28" t="str">
-        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A30),2),"–"))</f>
+        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A30),2),"–"))</f>
         <v/>
       </c>
       <c r="F30" s="28" t="str">
-        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A30),2),"–"))</f>
+        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A30),2),"–"))</f>
         <v/>
       </c>
       <c r="G30" s="28" t="str">
-        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A30),2),"–"))</f>
+        <f aca="false">IF($A30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A30),2),"–"))</f>
         <v/>
       </c>
       <c r="H30" s="29" t="str">
-        <f aca="false">IF($A30="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A30,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A30,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A30,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A30="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A30,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A30,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A30,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I30" s="30" t="str">
-        <f aca="false">IF($A30="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A30),"–"))</f>
+        <f aca="false">IF($A30="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A30),"–"))</f>
         <v/>
       </c>
       <c r="J30" s="31" t="str">
-        <f aca="false">IF($A30="","",IF($B30=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A30)))</f>
+        <f aca="false">IF($A30="","",IF($B30=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A30)))</f>
         <v/>
       </c>
     </row>
@@ -10452,39 +10531,39 @@
         <v/>
       </c>
       <c r="B31" s="27" t="str">
-        <f aca="false">IF($A31="","",COUNTIFS('Score Log'!$C$4:$C$203,$A31))</f>
+        <f aca="false">IF($A31="","",COUNTIFS('Score Log'!$C$4:$C$204,$A31))</f>
         <v/>
       </c>
       <c r="C31" s="28" t="str">
-        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A31),2),"–"))</f>
+        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A31),2),"–"))</f>
         <v/>
       </c>
       <c r="D31" s="28" t="str">
-        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A31),2),"–"))</f>
+        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A31),2),"–"))</f>
         <v/>
       </c>
       <c r="E31" s="28" t="str">
-        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A31),2),"–"))</f>
+        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A31),2),"–"))</f>
         <v/>
       </c>
       <c r="F31" s="28" t="str">
-        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A31),2),"–"))</f>
+        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A31),2),"–"))</f>
         <v/>
       </c>
       <c r="G31" s="28" t="str">
-        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A31),2),"–"))</f>
+        <f aca="false">IF($A31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A31),2),"–"))</f>
         <v/>
       </c>
       <c r="H31" s="29" t="str">
-        <f aca="false">IF($A31="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A31,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A31,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A31,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A31="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A31,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A31,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A31,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I31" s="30" t="str">
-        <f aca="false">IF($A31="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A31),"–"))</f>
+        <f aca="false">IF($A31="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A31),"–"))</f>
         <v/>
       </c>
       <c r="J31" s="31" t="str">
-        <f aca="false">IF($A31="","",IF($B31=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A31)))</f>
+        <f aca="false">IF($A31="","",IF($B31=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A31)))</f>
         <v/>
       </c>
     </row>
@@ -10494,39 +10573,39 @@
         <v/>
       </c>
       <c r="B32" s="27" t="str">
-        <f aca="false">IF($A32="","",COUNTIFS('Score Log'!$C$4:$C$203,$A32))</f>
+        <f aca="false">IF($A32="","",COUNTIFS('Score Log'!$C$4:$C$204,$A32))</f>
         <v/>
       </c>
       <c r="C32" s="28" t="str">
-        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A32),2),"–"))</f>
+        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A32),2),"–"))</f>
         <v/>
       </c>
       <c r="D32" s="28" t="str">
-        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A32),2),"–"))</f>
+        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A32),2),"–"))</f>
         <v/>
       </c>
       <c r="E32" s="28" t="str">
-        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A32),2),"–"))</f>
+        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A32),2),"–"))</f>
         <v/>
       </c>
       <c r="F32" s="28" t="str">
-        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A32),2),"–"))</f>
+        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A32),2),"–"))</f>
         <v/>
       </c>
       <c r="G32" s="28" t="str">
-        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A32),2),"–"))</f>
+        <f aca="false">IF($A32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A32),2),"–"))</f>
         <v/>
       </c>
       <c r="H32" s="29" t="str">
-        <f aca="false">IF($A32="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A32,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A32,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A32,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A32="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A32,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A32,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A32,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I32" s="30" t="str">
-        <f aca="false">IF($A32="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A32),"–"))</f>
+        <f aca="false">IF($A32="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A32),"–"))</f>
         <v/>
       </c>
       <c r="J32" s="31" t="str">
-        <f aca="false">IF($A32="","",IF($B32=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A32)))</f>
+        <f aca="false">IF($A32="","",IF($B32=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A32)))</f>
         <v/>
       </c>
     </row>
@@ -10536,39 +10615,39 @@
         <v/>
       </c>
       <c r="B33" s="27" t="str">
-        <f aca="false">IF($A33="","",COUNTIFS('Score Log'!$C$4:$C$203,$A33))</f>
+        <f aca="false">IF($A33="","",COUNTIFS('Score Log'!$C$4:$C$204,$A33))</f>
         <v/>
       </c>
       <c r="C33" s="28" t="str">
-        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A33),2),"–"))</f>
+        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A33),2),"–"))</f>
         <v/>
       </c>
       <c r="D33" s="28" t="str">
-        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A33),2),"–"))</f>
+        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A33),2),"–"))</f>
         <v/>
       </c>
       <c r="E33" s="28" t="str">
-        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A33),2),"–"))</f>
+        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A33),2),"–"))</f>
         <v/>
       </c>
       <c r="F33" s="28" t="str">
-        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A33),2),"–"))</f>
+        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A33),2),"–"))</f>
         <v/>
       </c>
       <c r="G33" s="28" t="str">
-        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A33),2),"–"))</f>
+        <f aca="false">IF($A33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A33),2),"–"))</f>
         <v/>
       </c>
       <c r="H33" s="29" t="str">
-        <f aca="false">IF($A33="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A33,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A33,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A33,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A33="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A33,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A33,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A33,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I33" s="30" t="str">
-        <f aca="false">IF($A33="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A33),"–"))</f>
+        <f aca="false">IF($A33="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A33),"–"))</f>
         <v/>
       </c>
       <c r="J33" s="31" t="str">
-        <f aca="false">IF($A33="","",IF($B33=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A33)))</f>
+        <f aca="false">IF($A33="","",IF($B33=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A33)))</f>
         <v/>
       </c>
     </row>
@@ -10578,50 +10657,50 @@
         <v/>
       </c>
       <c r="B34" s="27" t="str">
-        <f aca="false">IF($A34="","",COUNTIFS('Score Log'!$C$4:$C$203,$A34))</f>
+        <f aca="false">IF($A34="","",COUNTIFS('Score Log'!$C$4:$C$204,$A34))</f>
         <v/>
       </c>
       <c r="C34" s="28" t="str">
-        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$A34),2),"–"))</f>
+        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$204,'Score Log'!$C$4:$C$204,$A34),2),"–"))</f>
         <v/>
       </c>
       <c r="D34" s="28" t="str">
-        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$A34),2),"–"))</f>
+        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$204,'Score Log'!$C$4:$C$204,$A34),2),"–"))</f>
         <v/>
       </c>
       <c r="E34" s="28" t="str">
-        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$A34),2),"–"))</f>
+        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$204,'Score Log'!$C$4:$C$204,$A34),2),"–"))</f>
         <v/>
       </c>
       <c r="F34" s="28" t="str">
-        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$A34),2),"–"))</f>
+        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$204,'Score Log'!$C$4:$C$204,$A34),2),"–"))</f>
         <v/>
       </c>
       <c r="G34" s="28" t="str">
-        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$A34),2),"–"))</f>
+        <f aca="false">IF($A34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,$A34),2),"–"))</f>
         <v/>
       </c>
       <c r="H34" s="29" t="str">
-        <f aca="false">IF($A34="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$A34,'Score Log'!$U$4:$U$203,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$203,$A34,'Score Log'!$U$4:$U$203,"Yes")+COUNTIFS('Score Log'!$C$4:$C$203,$A34,'Score Log'!$U$4:$U$203,"No")),"–"))</f>
+        <f aca="false">IF($A34="","",IFERROR(COUNTIFS('Score Log'!$C$4:$C$204,$A34,'Score Log'!$U$4:$U$204,"Yes")/(COUNTIFS('Score Log'!$C$4:$C$204,$A34,'Score Log'!$U$4:$U$204,"Yes")+COUNTIFS('Score Log'!$C$4:$C$204,$A34,'Score Log'!$U$4:$U$204,"No")),"–"))</f>
         <v/>
       </c>
       <c r="I34" s="30" t="str">
-        <f aca="false">IF($A34="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$203,'Score Log'!$C$4:$C$203,$A34),"–"))</f>
+        <f aca="false">IF($A34="","",IFERROR(AVERAGEIFS('Score Log'!$Q$4:$Q$204,'Score Log'!$C$4:$C$204,$A34),"–"))</f>
         <v/>
       </c>
       <c r="J34" s="31" t="str">
-        <f aca="false">IF($A34="","",IF($B34=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$203,'Score Log'!$C$4:$C$203,$A34)))</f>
+        <f aca="false">IF($A34="","",IF($B34=0,"–",_xlfn.MAXIFS('Score Log'!$A$4:$A$204,'Score Log'!$C$4:$C$204,$A34)))</f>
         <v/>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10629,7 +10708,7 @@
         <v>28</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C41" s="9" t="str">
         <f aca="false">IF(A5="","",A5)</f>
@@ -10678,47 +10757,47 @@
         <v>Thermoforming</v>
       </c>
       <c r="B42" s="27" t="n">
-        <f aca="false">IF($A42="","",COUNTIFS('Score Log'!$D$4:$D$203,$A42))</f>
+        <f aca="false">IF($A42="","",COUNTIFS('Score Log'!$D$4:$D$204,$A42))</f>
         <v>1</v>
       </c>
       <c r="C42" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A42),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A42),2),""))</f>
         <v/>
       </c>
       <c r="D42" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A42),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A42),2),""))</f>
         <v/>
       </c>
       <c r="E42" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A42),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A42),2),""))</f>
         <v/>
       </c>
       <c r="F42" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A42),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A42),2),""))</f>
         <v/>
       </c>
       <c r="G42" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A42),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A42),2),""))</f>
         <v/>
       </c>
       <c r="H42" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A42),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A42),2),""))</f>
         <v/>
       </c>
       <c r="I42" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A42),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A42),2),""))</f>
         <v/>
       </c>
       <c r="J42" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A42),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A42),2),""))</f>
         <v/>
       </c>
       <c r="K42" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A42),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A42),2),""))</f>
         <v/>
       </c>
       <c r="L42" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A42),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A42=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A42),2),""))</f>
         <v/>
       </c>
     </row>
@@ -10728,47 +10807,47 @@
         <v>Injection molding</v>
       </c>
       <c r="B43" s="27" t="n">
-        <f aca="false">IF($A43="","",COUNTIFS('Score Log'!$D$4:$D$203,$A43))</f>
-        <v>1</v>
+        <f aca="false">IF($A43="","",COUNTIFS('Score Log'!$D$4:$D$204,$A43))</f>
+        <v>2</v>
       </c>
       <c r="C43" s="28" t="n">
-        <f aca="false">IF(OR(C$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A43),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A43),2),""))</f>
         <v>4.5</v>
       </c>
       <c r="D43" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A43),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A43),2),""))</f>
         <v/>
       </c>
       <c r="E43" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A43),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A43),2),""))</f>
         <v/>
       </c>
       <c r="F43" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A43),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A43),2),""))</f>
         <v/>
       </c>
       <c r="G43" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A43),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A43),2),""))</f>
         <v/>
       </c>
       <c r="H43" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A43),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A43),2),""))</f>
         <v/>
       </c>
       <c r="I43" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A43),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A43),2),""))</f>
         <v/>
       </c>
       <c r="J43" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A43),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A43),2),""))</f>
         <v/>
       </c>
       <c r="K43" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A43),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A43),2),""))</f>
         <v/>
       </c>
       <c r="L43" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A43),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A43=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A43),2),""))</f>
         <v/>
       </c>
     </row>
@@ -10778,47 +10857,47 @@
         <v>3D printing (FDM)</v>
       </c>
       <c r="B44" s="27" t="n">
-        <f aca="false">IF($A44="","",COUNTIFS('Score Log'!$D$4:$D$203,$A44))</f>
+        <f aca="false">IF($A44="","",COUNTIFS('Score Log'!$D$4:$D$204,$A44))</f>
         <v>0</v>
       </c>
       <c r="C44" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A44),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A44),2),""))</f>
         <v/>
       </c>
       <c r="D44" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A44),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A44),2),""))</f>
         <v/>
       </c>
       <c r="E44" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A44),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A44),2),""))</f>
         <v/>
       </c>
       <c r="F44" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A44),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A44),2),""))</f>
         <v/>
       </c>
       <c r="G44" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A44),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A44),2),""))</f>
         <v/>
       </c>
       <c r="H44" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A44),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A44),2),""))</f>
         <v/>
       </c>
       <c r="I44" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A44),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A44),2),""))</f>
         <v/>
       </c>
       <c r="J44" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A44),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A44),2),""))</f>
         <v/>
       </c>
       <c r="K44" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A44),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A44),2),""))</f>
         <v/>
       </c>
       <c r="L44" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A44),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A44=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A44),2),""))</f>
         <v/>
       </c>
     </row>
@@ -10828,47 +10907,47 @@
         <v>3D printing (SLA)</v>
       </c>
       <c r="B45" s="27" t="n">
-        <f aca="false">IF($A45="","",COUNTIFS('Score Log'!$D$4:$D$203,$A45))</f>
+        <f aca="false">IF($A45="","",COUNTIFS('Score Log'!$D$4:$D$204,$A45))</f>
         <v>0</v>
       </c>
       <c r="C45" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A45),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A45),2),""))</f>
         <v/>
       </c>
       <c r="D45" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A45),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A45),2),""))</f>
         <v/>
       </c>
       <c r="E45" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A45),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A45),2),""))</f>
         <v/>
       </c>
       <c r="F45" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A45),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A45),2),""))</f>
         <v/>
       </c>
       <c r="G45" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A45),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A45),2),""))</f>
         <v/>
       </c>
       <c r="H45" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A45),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A45),2),""))</f>
         <v/>
       </c>
       <c r="I45" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A45),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A45),2),""))</f>
         <v/>
       </c>
       <c r="J45" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A45),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A45),2),""))</f>
         <v/>
       </c>
       <c r="K45" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A45),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A45),2),""))</f>
         <v/>
       </c>
       <c r="L45" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A45),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A45=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A45),2),""))</f>
         <v/>
       </c>
     </row>
@@ -10878,47 +10957,47 @@
         <v>3D printing (SLS)</v>
       </c>
       <c r="B46" s="27" t="n">
-        <f aca="false">IF($A46="","",COUNTIFS('Score Log'!$D$4:$D$203,$A46))</f>
+        <f aca="false">IF($A46="","",COUNTIFS('Score Log'!$D$4:$D$204,$A46))</f>
         <v>0</v>
       </c>
       <c r="C46" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A46),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A46),2),""))</f>
         <v/>
       </c>
       <c r="D46" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A46),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A46),2),""))</f>
         <v/>
       </c>
       <c r="E46" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A46),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A46),2),""))</f>
         <v/>
       </c>
       <c r="F46" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A46),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A46),2),""))</f>
         <v/>
       </c>
       <c r="G46" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A46),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A46),2),""))</f>
         <v/>
       </c>
       <c r="H46" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A46),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A46),2),""))</f>
         <v/>
       </c>
       <c r="I46" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A46),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A46),2),""))</f>
         <v/>
       </c>
       <c r="J46" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A46),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A46),2),""))</f>
         <v/>
       </c>
       <c r="K46" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A46),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A46),2),""))</f>
         <v/>
       </c>
       <c r="L46" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A46),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A46=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A46),2),""))</f>
         <v/>
       </c>
     </row>
@@ -10928,47 +11007,47 @@
         <v>PVA</v>
       </c>
       <c r="B47" s="27" t="n">
-        <f aca="false">IF($A47="","",COUNTIFS('Score Log'!$D$4:$D$203,$A47))</f>
+        <f aca="false">IF($A47="","",COUNTIFS('Score Log'!$D$4:$D$204,$A47))</f>
         <v>0</v>
       </c>
       <c r="C47" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A47),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A47),2),""))</f>
         <v/>
       </c>
       <c r="D47" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A47),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A47),2),""))</f>
         <v/>
       </c>
       <c r="E47" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A47),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A47),2),""))</f>
         <v/>
       </c>
       <c r="F47" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A47),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A47),2),""))</f>
         <v/>
       </c>
       <c r="G47" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A47),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A47),2),""))</f>
         <v/>
       </c>
       <c r="H47" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A47),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A47),2),""))</f>
         <v/>
       </c>
       <c r="I47" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A47),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A47),2),""))</f>
         <v/>
       </c>
       <c r="J47" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A47),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A47),2),""))</f>
         <v/>
       </c>
       <c r="K47" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A47),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A47),2),""))</f>
         <v/>
       </c>
       <c r="L47" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A47),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A47=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A47),2),""))</f>
         <v/>
       </c>
     </row>
@@ -10978,47 +11057,47 @@
         <v>CNC machining</v>
       </c>
       <c r="B48" s="27" t="n">
-        <f aca="false">IF($A48="","",COUNTIFS('Score Log'!$D$4:$D$203,$A48))</f>
+        <f aca="false">IF($A48="","",COUNTIFS('Score Log'!$D$4:$D$204,$A48))</f>
         <v>0</v>
       </c>
       <c r="C48" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A48),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A48),2),""))</f>
         <v/>
       </c>
       <c r="D48" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A48),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A48),2),""))</f>
         <v/>
       </c>
       <c r="E48" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A48),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A48),2),""))</f>
         <v/>
       </c>
       <c r="F48" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A48),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A48),2),""))</f>
         <v/>
       </c>
       <c r="G48" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A48),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A48),2),""))</f>
         <v/>
       </c>
       <c r="H48" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A48),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A48),2),""))</f>
         <v/>
       </c>
       <c r="I48" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A48),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A48),2),""))</f>
         <v/>
       </c>
       <c r="J48" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A48),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A48),2),""))</f>
         <v/>
       </c>
       <c r="K48" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A48),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A48),2),""))</f>
         <v/>
       </c>
       <c r="L48" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A48),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A48=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A48),2),""))</f>
         <v/>
       </c>
     </row>
@@ -11028,47 +11107,47 @@
         <v>Vacuum casting</v>
       </c>
       <c r="B49" s="27" t="n">
-        <f aca="false">IF($A49="","",COUNTIFS('Score Log'!$D$4:$D$203,$A49))</f>
+        <f aca="false">IF($A49="","",COUNTIFS('Score Log'!$D$4:$D$204,$A49))</f>
         <v>0</v>
       </c>
       <c r="C49" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A49),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A49),2),""))</f>
         <v/>
       </c>
       <c r="D49" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A49),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A49),2),""))</f>
         <v/>
       </c>
       <c r="E49" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A49),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A49),2),""))</f>
         <v/>
       </c>
       <c r="F49" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A49),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A49),2),""))</f>
         <v/>
       </c>
       <c r="G49" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A49),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A49),2),""))</f>
         <v/>
       </c>
       <c r="H49" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A49),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A49),2),""))</f>
         <v/>
       </c>
       <c r="I49" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A49),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A49),2),""))</f>
         <v/>
       </c>
       <c r="J49" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A49),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A49),2),""))</f>
         <v/>
       </c>
       <c r="K49" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A49),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A49),2),""))</f>
         <v/>
       </c>
       <c r="L49" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A49),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A49=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A49),2),""))</f>
         <v/>
       </c>
     </row>
@@ -11078,47 +11157,47 @@
         <v>Sheet metal</v>
       </c>
       <c r="B50" s="27" t="n">
-        <f aca="false">IF($A50="","",COUNTIFS('Score Log'!$D$4:$D$203,$A50))</f>
+        <f aca="false">IF($A50="","",COUNTIFS('Score Log'!$D$4:$D$204,$A50))</f>
         <v>0</v>
       </c>
       <c r="C50" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A50),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A50),2),""))</f>
         <v/>
       </c>
       <c r="D50" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A50),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A50),2),""))</f>
         <v/>
       </c>
       <c r="E50" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A50),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A50),2),""))</f>
         <v/>
       </c>
       <c r="F50" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A50),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A50),2),""))</f>
         <v/>
       </c>
       <c r="G50" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A50),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A50),2),""))</f>
         <v/>
       </c>
       <c r="H50" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A50),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A50),2),""))</f>
         <v/>
       </c>
       <c r="I50" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A50),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A50),2),""))</f>
         <v/>
       </c>
       <c r="J50" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A50),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A50),2),""))</f>
         <v/>
       </c>
       <c r="K50" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A50),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A50),2),""))</f>
         <v/>
       </c>
       <c r="L50" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A50),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A50=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A50),2),""))</f>
         <v/>
       </c>
     </row>
@@ -11128,47 +11207,47 @@
         <v>Extrusion</v>
       </c>
       <c r="B51" s="27" t="n">
-        <f aca="false">IF($A51="","",COUNTIFS('Score Log'!$D$4:$D$203,$A51))</f>
+        <f aca="false">IF($A51="","",COUNTIFS('Score Log'!$D$4:$D$204,$A51))</f>
         <v>0</v>
       </c>
       <c r="C51" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A51),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A51),2),""))</f>
         <v/>
       </c>
       <c r="D51" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A51),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A51),2),""))</f>
         <v/>
       </c>
       <c r="E51" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A51),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A51),2),""))</f>
         <v/>
       </c>
       <c r="F51" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A51),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A51),2),""))</f>
         <v/>
       </c>
       <c r="G51" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A51),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A51),2),""))</f>
         <v/>
       </c>
       <c r="H51" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A51),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A51),2),""))</f>
         <v/>
       </c>
       <c r="I51" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A51),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A51),2),""))</f>
         <v/>
       </c>
       <c r="J51" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A51),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A51),2),""))</f>
         <v/>
       </c>
       <c r="K51" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A51),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A51),2),""))</f>
         <v/>
       </c>
       <c r="L51" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A51),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A51=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A51),2),""))</f>
         <v/>
       </c>
     </row>
@@ -11178,47 +11257,47 @@
         <v>Casting</v>
       </c>
       <c r="B52" s="27" t="n">
-        <f aca="false">IF($A52="","",COUNTIFS('Score Log'!$D$4:$D$203,$A52))</f>
+        <f aca="false">IF($A52="","",COUNTIFS('Score Log'!$D$4:$D$204,$A52))</f>
         <v>0</v>
       </c>
       <c r="C52" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A52),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A52),2),""))</f>
         <v/>
       </c>
       <c r="D52" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A52),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A52),2),""))</f>
         <v/>
       </c>
       <c r="E52" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A52),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A52),2),""))</f>
         <v/>
       </c>
       <c r="F52" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A52),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A52),2),""))</f>
         <v/>
       </c>
       <c r="G52" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A52),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A52),2),""))</f>
         <v/>
       </c>
       <c r="H52" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A52),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A52),2),""))</f>
         <v/>
       </c>
       <c r="I52" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A52),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A52),2),""))</f>
         <v/>
       </c>
       <c r="J52" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A52),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A52),2),""))</f>
         <v/>
       </c>
       <c r="K52" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A52),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A52),2),""))</f>
         <v/>
       </c>
       <c r="L52" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A52),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A52=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A52),2),""))</f>
         <v/>
       </c>
     </row>
@@ -11228,47 +11307,47 @@
         <v>Other</v>
       </c>
       <c r="B53" s="27" t="n">
-        <f aca="false">IF($A53="","",COUNTIFS('Score Log'!$D$4:$D$203,$A53))</f>
+        <f aca="false">IF($A53="","",COUNTIFS('Score Log'!$D$4:$D$204,$A53))</f>
         <v>0</v>
       </c>
       <c r="C53" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A53),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A53),2),""))</f>
         <v/>
       </c>
       <c r="D53" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A53),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A53),2),""))</f>
         <v/>
       </c>
       <c r="E53" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A53),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A53),2),""))</f>
         <v/>
       </c>
       <c r="F53" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A53),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A53),2),""))</f>
         <v/>
       </c>
       <c r="G53" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A53),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A53),2),""))</f>
         <v/>
       </c>
       <c r="H53" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A53),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A53),2),""))</f>
         <v/>
       </c>
       <c r="I53" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A53),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A53),2),""))</f>
         <v/>
       </c>
       <c r="J53" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A53),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A53),2),""))</f>
         <v/>
       </c>
       <c r="K53" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A53),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A53),2),""))</f>
         <v/>
       </c>
       <c r="L53" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A53),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A53=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A53),2),""))</f>
         <v/>
       </c>
     </row>
@@ -11278,47 +11357,47 @@
         <v>Compression Molding</v>
       </c>
       <c r="B54" s="27" t="n">
-        <f aca="false">IF($A54="","",COUNTIFS('Score Log'!$D$4:$D$203,$A54))</f>
+        <f aca="false">IF($A54="","",COUNTIFS('Score Log'!$D$4:$D$204,$A54))</f>
         <v>0</v>
       </c>
       <c r="C54" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A54),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A54),2),""))</f>
         <v/>
       </c>
       <c r="D54" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A54),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A54),2),""))</f>
         <v/>
       </c>
       <c r="E54" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A54),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A54),2),""))</f>
         <v/>
       </c>
       <c r="F54" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A54),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A54),2),""))</f>
         <v/>
       </c>
       <c r="G54" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A54),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A54),2),""))</f>
         <v/>
       </c>
       <c r="H54" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A54),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A54),2),""))</f>
         <v/>
       </c>
       <c r="I54" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A54),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A54),2),""))</f>
         <v/>
       </c>
       <c r="J54" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A54),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A54),2),""))</f>
         <v/>
       </c>
       <c r="K54" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A54),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A54),2),""))</f>
         <v/>
       </c>
       <c r="L54" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A54),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A54=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A54),2),""))</f>
         <v/>
       </c>
     </row>
@@ -11328,47 +11407,47 @@
         <v/>
       </c>
       <c r="B55" s="27" t="str">
-        <f aca="false">IF($A55="","",COUNTIFS('Score Log'!$D$4:$D$203,$A55))</f>
+        <f aca="false">IF($A55="","",COUNTIFS('Score Log'!$D$4:$D$204,$A55))</f>
         <v/>
       </c>
       <c r="C55" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A55),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A55),2),""))</f>
         <v/>
       </c>
       <c r="D55" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A55),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A55),2),""))</f>
         <v/>
       </c>
       <c r="E55" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A55),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A55),2),""))</f>
         <v/>
       </c>
       <c r="F55" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A55),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A55),2),""))</f>
         <v/>
       </c>
       <c r="G55" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A55),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A55),2),""))</f>
         <v/>
       </c>
       <c r="H55" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A55),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A55),2),""))</f>
         <v/>
       </c>
       <c r="I55" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A55),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A55),2),""))</f>
         <v/>
       </c>
       <c r="J55" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A55),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A55),2),""))</f>
         <v/>
       </c>
       <c r="K55" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A55),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A55),2),""))</f>
         <v/>
       </c>
       <c r="L55" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A55),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A55=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A55),2),""))</f>
         <v/>
       </c>
     </row>
@@ -11378,47 +11457,47 @@
         <v/>
       </c>
       <c r="B56" s="27" t="str">
-        <f aca="false">IF($A56="","",COUNTIFS('Score Log'!$D$4:$D$203,$A56))</f>
+        <f aca="false">IF($A56="","",COUNTIFS('Score Log'!$D$4:$D$204,$A56))</f>
         <v/>
       </c>
       <c r="C56" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A56),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A56),2),""))</f>
         <v/>
       </c>
       <c r="D56" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A56),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A56),2),""))</f>
         <v/>
       </c>
       <c r="E56" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A56),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A56),2),""))</f>
         <v/>
       </c>
       <c r="F56" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A56),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A56),2),""))</f>
         <v/>
       </c>
       <c r="G56" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A56),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A56),2),""))</f>
         <v/>
       </c>
       <c r="H56" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A56),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A56),2),""))</f>
         <v/>
       </c>
       <c r="I56" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A56),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A56),2),""))</f>
         <v/>
       </c>
       <c r="J56" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A56),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A56),2),""))</f>
         <v/>
       </c>
       <c r="K56" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A56),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A56),2),""))</f>
         <v/>
       </c>
       <c r="L56" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A56),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A56=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A56),2),""))</f>
         <v/>
       </c>
     </row>
@@ -11428,47 +11507,47 @@
         <v/>
       </c>
       <c r="B57" s="27" t="str">
-        <f aca="false">IF($A57="","",COUNTIFS('Score Log'!$D$4:$D$203,$A57))</f>
+        <f aca="false">IF($A57="","",COUNTIFS('Score Log'!$D$4:$D$204,$A57))</f>
         <v/>
       </c>
       <c r="C57" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A57),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A57),2),""))</f>
         <v/>
       </c>
       <c r="D57" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A57),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A57),2),""))</f>
         <v/>
       </c>
       <c r="E57" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A57),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A57),2),""))</f>
         <v/>
       </c>
       <c r="F57" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A57),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A57),2),""))</f>
         <v/>
       </c>
       <c r="G57" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A57),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A57),2),""))</f>
         <v/>
       </c>
       <c r="H57" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A57),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A57),2),""))</f>
         <v/>
       </c>
       <c r="I57" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A57),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A57),2),""))</f>
         <v/>
       </c>
       <c r="J57" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A57),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A57),2),""))</f>
         <v/>
       </c>
       <c r="K57" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A57),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A57),2),""))</f>
         <v/>
       </c>
       <c r="L57" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A57),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A57=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A57),2),""))</f>
         <v/>
       </c>
     </row>
@@ -11478,47 +11557,47 @@
         <v/>
       </c>
       <c r="B58" s="27" t="str">
-        <f aca="false">IF($A58="","",COUNTIFS('Score Log'!$D$4:$D$203,$A58))</f>
+        <f aca="false">IF($A58="","",COUNTIFS('Score Log'!$D$4:$D$204,$A58))</f>
         <v/>
       </c>
       <c r="C58" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A58),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A58),2),""))</f>
         <v/>
       </c>
       <c r="D58" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A58),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A58),2),""))</f>
         <v/>
       </c>
       <c r="E58" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A58),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A58),2),""))</f>
         <v/>
       </c>
       <c r="F58" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A58),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A58),2),""))</f>
         <v/>
       </c>
       <c r="G58" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A58),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A58),2),""))</f>
         <v/>
       </c>
       <c r="H58" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A58),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A58),2),""))</f>
         <v/>
       </c>
       <c r="I58" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A58),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A58),2),""))</f>
         <v/>
       </c>
       <c r="J58" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A58),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A58),2),""))</f>
         <v/>
       </c>
       <c r="K58" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A58),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A58),2),""))</f>
         <v/>
       </c>
       <c r="L58" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A58),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A58=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A58),2),""))</f>
         <v/>
       </c>
     </row>
@@ -11528,47 +11607,47 @@
         <v/>
       </c>
       <c r="B59" s="27" t="str">
-        <f aca="false">IF($A59="","",COUNTIFS('Score Log'!$D$4:$D$203,$A59))</f>
+        <f aca="false">IF($A59="","",COUNTIFS('Score Log'!$D$4:$D$204,$A59))</f>
         <v/>
       </c>
       <c r="C59" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A59),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A59),2),""))</f>
         <v/>
       </c>
       <c r="D59" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A59),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A59),2),""))</f>
         <v/>
       </c>
       <c r="E59" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A59),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A59),2),""))</f>
         <v/>
       </c>
       <c r="F59" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A59),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A59),2),""))</f>
         <v/>
       </c>
       <c r="G59" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A59),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A59),2),""))</f>
         <v/>
       </c>
       <c r="H59" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A59),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A59),2),""))</f>
         <v/>
       </c>
       <c r="I59" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A59),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A59),2),""))</f>
         <v/>
       </c>
       <c r="J59" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A59),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A59),2),""))</f>
         <v/>
       </c>
       <c r="K59" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A59),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A59),2),""))</f>
         <v/>
       </c>
       <c r="L59" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A59),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A59=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A59),2),""))</f>
         <v/>
       </c>
     </row>
@@ -11578,47 +11657,47 @@
         <v/>
       </c>
       <c r="B60" s="27" t="str">
-        <f aca="false">IF($A60="","",COUNTIFS('Score Log'!$D$4:$D$203,$A60))</f>
+        <f aca="false">IF($A60="","",COUNTIFS('Score Log'!$D$4:$D$204,$A60))</f>
         <v/>
       </c>
       <c r="C60" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A60),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A60),2),""))</f>
         <v/>
       </c>
       <c r="D60" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A60),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A60),2),""))</f>
         <v/>
       </c>
       <c r="E60" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A60),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A60),2),""))</f>
         <v/>
       </c>
       <c r="F60" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A60),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A60),2),""))</f>
         <v/>
       </c>
       <c r="G60" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A60),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A60),2),""))</f>
         <v/>
       </c>
       <c r="H60" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A60),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A60),2),""))</f>
         <v/>
       </c>
       <c r="I60" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A60),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A60),2),""))</f>
         <v/>
       </c>
       <c r="J60" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A60),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A60),2),""))</f>
         <v/>
       </c>
       <c r="K60" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A60),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A60),2),""))</f>
         <v/>
       </c>
       <c r="L60" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A60),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A60=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A60),2),""))</f>
         <v/>
       </c>
     </row>
@@ -11628,47 +11707,47 @@
         <v/>
       </c>
       <c r="B61" s="27" t="str">
-        <f aca="false">IF($A61="","",COUNTIFS('Score Log'!$D$4:$D$203,$A61))</f>
+        <f aca="false">IF($A61="","",COUNTIFS('Score Log'!$D$4:$D$204,$A61))</f>
         <v/>
       </c>
       <c r="C61" s="28" t="str">
-        <f aca="false">IF(OR(C$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,C$41,'Score Log'!$D$4:$D$203,$A61),2),""))</f>
+        <f aca="false">IF(OR(C$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,C$41,'Score Log'!$D$4:$D$204,$A61),2),""))</f>
         <v/>
       </c>
       <c r="D61" s="28" t="str">
-        <f aca="false">IF(OR(D$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,D$41,'Score Log'!$D$4:$D$203,$A61),2),""))</f>
+        <f aca="false">IF(OR(D$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,D$41,'Score Log'!$D$4:$D$204,$A61),2),""))</f>
         <v/>
       </c>
       <c r="E61" s="28" t="str">
-        <f aca="false">IF(OR(E$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,E$41,'Score Log'!$D$4:$D$203,$A61),2),""))</f>
+        <f aca="false">IF(OR(E$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,E$41,'Score Log'!$D$4:$D$204,$A61),2),""))</f>
         <v/>
       </c>
       <c r="F61" s="28" t="str">
-        <f aca="false">IF(OR(F$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,F$41,'Score Log'!$D$4:$D$203,$A61),2),""))</f>
+        <f aca="false">IF(OR(F$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,F$41,'Score Log'!$D$4:$D$204,$A61),2),""))</f>
         <v/>
       </c>
       <c r="G61" s="28" t="str">
-        <f aca="false">IF(OR(G$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,G$41,'Score Log'!$D$4:$D$203,$A61),2),""))</f>
+        <f aca="false">IF(OR(G$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,G$41,'Score Log'!$D$4:$D$204,$A61),2),""))</f>
         <v/>
       </c>
       <c r="H61" s="28" t="str">
-        <f aca="false">IF(OR(H$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,H$41,'Score Log'!$D$4:$D$203,$A61),2),""))</f>
+        <f aca="false">IF(OR(H$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,H$41,'Score Log'!$D$4:$D$204,$A61),2),""))</f>
         <v/>
       </c>
       <c r="I61" s="28" t="str">
-        <f aca="false">IF(OR(I$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,I$41,'Score Log'!$D$4:$D$203,$A61),2),""))</f>
+        <f aca="false">IF(OR(I$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,I$41,'Score Log'!$D$4:$D$204,$A61),2),""))</f>
         <v/>
       </c>
       <c r="J61" s="28" t="str">
-        <f aca="false">IF(OR(J$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,J$41,'Score Log'!$D$4:$D$203,$A61),2),""))</f>
+        <f aca="false">IF(OR(J$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,J$41,'Score Log'!$D$4:$D$204,$A61),2),""))</f>
         <v/>
       </c>
       <c r="K61" s="28" t="str">
-        <f aca="false">IF(OR(K$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,K$41,'Score Log'!$D$4:$D$203,$A61),2),""))</f>
+        <f aca="false">IF(OR(K$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,K$41,'Score Log'!$D$4:$D$204,$A61),2),""))</f>
         <v/>
       </c>
       <c r="L61" s="28" t="str">
-        <f aca="false">IF(OR(L$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,L$41,'Score Log'!$D$4:$D$203,$A61),2),""))</f>
+        <f aca="false">IF(OR(L$41="",$A61=""),"",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$204,'Score Log'!$C$4:$C$204,L$41,'Score Log'!$D$4:$D$204,$A61),2),""))</f>
         <v/>
       </c>
     </row>
@@ -11738,7 +11817,7 @@
     <tabColor rgb="FFC00000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P52"/>
+  <dimension ref="A1:AB203"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
@@ -11753,238 +11832,305 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="16" min="15" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="17" min="15" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="28" min="27" style="0" width="4"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="B3" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35" t="s">
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35" t="s">
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="AA3" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB3" s="33" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="36" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="36" t="s">
+      <c r="A4" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="36" t="s">
+      <c r="D4" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="E4" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="36" t="s">
+      <c r="G4" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="H4" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="I4" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="K4" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="L4" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="M4" s="36" t="s">
+      <c r="J4" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="K4" s="35" t="s">
         <v>83</v>
       </c>
+      <c r="L4" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="M4" s="35" t="s">
+        <v>85</v>
+      </c>
       <c r="O4" s="33" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P4" s="33" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="Q4" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA4" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C4="",'Score Log'!$E4=""),0,IF(COUNTIFS('Score Log'!$C$4:$C4,'Score Log'!$C4,'Score Log'!$E$4:$E4,'Score Log'!$E4)=1,1,0))</f>
+        <v>1</v>
+      </c>
+      <c r="AB4" s="33" t="n">
+        <f aca="false">IF($AA4=1,SUM($AA$4:$AA4),"")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="37"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="38" t="str">
-        <f aca="false">IF($B5="","",IF($C5="",COUNTIF('Score Log'!$C$4:$C$203,$B5),COUNTIFS('Score Log'!$C$4:$C$203,$B5,'Score Log'!$D$4:$D$203,$C5)))</f>
-        <v/>
-      </c>
-      <c r="E5" s="39" t="str">
-        <f aca="false">IF($B5="","",IFERROR(ROUND(IF($C5="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B5),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B5,'Score Log'!$D$4:$D$203,$C5)),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="F5" s="39" t="str">
-        <f aca="false">IF($B5="","",IFERROR(ROUND(IF($C5="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B5),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B5,'Score Log'!$D$4:$D$203,$C5)),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="G5" s="39" t="str">
-        <f aca="false">IF($B5="","",IFERROR(ROUND(IF($C5="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B5),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B5,'Score Log'!$D$4:$D$203,$C5)),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H5" s="39" t="str">
-        <f aca="false">IF($B5="","",IFERROR(ROUND(IF($C5="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B5),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B5,'Score Log'!$D$4:$D$203,$C5)),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="I5" s="39" t="str">
-        <f aca="false">IF($B5="","",IFERROR(ROUND(IF($C5="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B5),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B5,'Score Log'!$D$4:$D$203,$C5)),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="J5" s="40" t="str">
-        <f aca="false">IF(OR($B5="",$D5=0),"",IFERROR(IF($C5="",COUNTIFS('Score Log'!$C$4:$C$203,$B5,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B5,'Score Log'!$D$4:$D$203,$C5,'Score Log'!$U$4:$U$203,"Yes"))/$D5,"-"))</f>
-        <v/>
-      </c>
-      <c r="K5" s="41" t="str">
+      <c r="A5" s="36" t="str">
+        <f aca="false">IF($Q5="","",INDEX('Score Log'!$E:$E,$Q5))</f>
+        <v>Uterus Insert</v>
+      </c>
+      <c r="B5" s="36" t="str">
+        <f aca="false">IF($Q5="","",INDEX('Score Log'!$C:$C,$Q5))</f>
+        <v>Fictiv</v>
+      </c>
+      <c r="C5" s="37" t="str">
+        <f aca="false">IF($Q5="","",IF(INDEX('Score Log'!$D:$D,$Q5)="","",INDEX('Score Log'!$D:$D,$Q5)))</f>
+        <v>Injection molding</v>
+      </c>
+      <c r="D5" s="38" t="n">
+        <f aca="false">IF($B5="","",COUNTIFS('Score Log'!$C$4:$C$203,$B5,'Score Log'!$E$4:$E$203,$A5))</f>
+        <v>1</v>
+      </c>
+      <c r="E5" s="39" t="n">
+        <f aca="false">IF($B5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B5,'Score Log'!$E$4:$E$203,$A5),1),"-"))</f>
+        <v>4</v>
+      </c>
+      <c r="F5" s="39" t="n">
+        <f aca="false">IF($B5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B5,'Score Log'!$E$4:$E$203,$A5),1),"-"))</f>
+        <v>5</v>
+      </c>
+      <c r="G5" s="39" t="n">
+        <f aca="false">IF($B5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B5,'Score Log'!$E$4:$E$203,$A5),1),"-"))</f>
+        <v>4</v>
+      </c>
+      <c r="H5" s="39" t="n">
+        <f aca="false">IF($B5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B5,'Score Log'!$E$4:$E$203,$A5),1),"-"))</f>
+        <v>5</v>
+      </c>
+      <c r="I5" s="39" t="n">
+        <f aca="false">IF($B5="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B5,'Score Log'!$E$4:$E$203,$A5),1),"-"))</f>
+        <v>4.5</v>
+      </c>
+      <c r="J5" s="40" t="n">
+        <f aca="false">IF(OR($B5="",$D5=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B5,'Score Log'!$E$4:$E$203,$A5,'Score Log'!$U$4:$U$203,"Yes")/$D5,"-"))</f>
+        <v>1</v>
+      </c>
+      <c r="K5" s="41" t="n">
         <f aca="false">IF($B5="","",IF(ISNUMBER($F5),MAX(1,MIN(5,ROUND(6-$F5,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="L5" s="41" t="str">
+        <v>1</v>
+      </c>
+      <c r="L5" s="41" t="n">
         <f aca="false">IF($B5="","",IF(ISNUMBER($G5),MAX(1,MIN(5,ROUND(6-$G5,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="M5" s="41" t="str">
+        <v>2</v>
+      </c>
+      <c r="M5" s="41" t="n">
         <f aca="false">IF($B5="","",IF(AND(ISNUMBER($P5),ISNUMBER($O5)),MAX(1,MIN(5,ROUND(6-AVERAGE($P5,$O5),0))),IF(ISNUMBER($P5),MAX(1,MIN(5,ROUND(6-$P5,0))),"-")))</f>
-        <v/>
-      </c>
-      <c r="O5" s="33" t="str">
+        <v>2</v>
+      </c>
+      <c r="O5" s="33" t="n">
         <f aca="false">IF($B5="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B5),""))</f>
-        <v/>
-      </c>
-      <c r="P5" s="33" t="str">
+        <v>4</v>
+      </c>
+      <c r="P5" s="33" t="n">
         <f aca="false">IF($B5="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B5),""))</f>
-        <v/>
+        <v>5</v>
+      </c>
+      <c r="Q5" s="33" t="n">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v>4</v>
+      </c>
+      <c r="AA5" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C5="",'Score Log'!$E5=""),0,IF(COUNTIFS('Score Log'!$C$4:$C5,'Score Log'!$C5,'Score Log'!$E$4:$E5,'Score Log'!$E5)=1,1,0))</f>
+        <v>1</v>
+      </c>
+      <c r="AB5" s="33" t="n">
+        <f aca="false">IF($AA5=1,SUM($AA$4:$AA5),"")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="37"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="38" t="str">
-        <f aca="false">IF($B6="","",IF($C6="",COUNTIF('Score Log'!$C$4:$C$203,$B6),COUNTIFS('Score Log'!$C$4:$C$203,$B6,'Score Log'!$D$4:$D$203,$C6)))</f>
-        <v/>
-      </c>
-      <c r="E6" s="39" t="str">
-        <f aca="false">IF($B6="","",IFERROR(ROUND(IF($C6="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B6),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B6,'Score Log'!$D$4:$D$203,$C6)),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="F6" s="39" t="str">
-        <f aca="false">IF($B6="","",IFERROR(ROUND(IF($C6="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B6),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B6,'Score Log'!$D$4:$D$203,$C6)),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="G6" s="39" t="str">
-        <f aca="false">IF($B6="","",IFERROR(ROUND(IF($C6="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B6),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B6,'Score Log'!$D$4:$D$203,$C6)),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="H6" s="39" t="str">
-        <f aca="false">IF($B6="","",IFERROR(ROUND(IF($C6="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B6),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B6,'Score Log'!$D$4:$D$203,$C6)),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="I6" s="39" t="str">
-        <f aca="false">IF($B6="","",IFERROR(ROUND(IF($C6="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B6),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B6,'Score Log'!$D$4:$D$203,$C6)),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="J6" s="40" t="str">
-        <f aca="false">IF(OR($B6="",$D6=0),"",IFERROR(IF($C6="",COUNTIFS('Score Log'!$C$4:$C$203,$B6,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B6,'Score Log'!$D$4:$D$203,$C6,'Score Log'!$U$4:$U$203,"Yes"))/$D6,"-"))</f>
-        <v/>
-      </c>
-      <c r="K6" s="41" t="str">
+      <c r="A6" s="36" t="str">
+        <f aca="false">IF($Q6="","",INDEX('Score Log'!$E:$E,$Q6))</f>
+        <v>End Plate</v>
+      </c>
+      <c r="B6" s="36" t="str">
+        <f aca="false">IF($Q6="","",INDEX('Score Log'!$C:$C,$Q6))</f>
+        <v>Fictiv</v>
+      </c>
+      <c r="C6" s="37" t="str">
+        <f aca="false">IF($Q6="","",IF(INDEX('Score Log'!$D:$D,$Q6)="","",INDEX('Score Log'!$D:$D,$Q6)))</f>
+        <v>Injection molding</v>
+      </c>
+      <c r="D6" s="38" t="n">
+        <f aca="false">IF($B6="","",COUNTIFS('Score Log'!$C$4:$C$203,$B6,'Score Log'!$E$4:$E$203,$A6))</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="39" t="n">
+        <f aca="false">IF($B6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B6,'Score Log'!$E$4:$E$203,$A6),1),"-"))</f>
+        <v>4</v>
+      </c>
+      <c r="F6" s="39" t="n">
+        <f aca="false">IF($B6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B6,'Score Log'!$E$4:$E$203,$A6),1),"-"))</f>
+        <v>5</v>
+      </c>
+      <c r="G6" s="39" t="n">
+        <f aca="false">IF($B6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B6,'Score Log'!$E$4:$E$203,$A6),1),"-"))</f>
+        <v>4</v>
+      </c>
+      <c r="H6" s="39" t="n">
+        <f aca="false">IF($B6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B6,'Score Log'!$E$4:$E$203,$A6),1),"-"))</f>
+        <v>5</v>
+      </c>
+      <c r="I6" s="39" t="n">
+        <f aca="false">IF($B6="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B6,'Score Log'!$E$4:$E$203,$A6),1),"-"))</f>
+        <v>4.5</v>
+      </c>
+      <c r="J6" s="40" t="n">
+        <f aca="false">IF(OR($B6="",$D6=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B6,'Score Log'!$E$4:$E$203,$A6,'Score Log'!$U$4:$U$203,"Yes")/$D6,"-"))</f>
+        <v>1</v>
+      </c>
+      <c r="K6" s="41" t="n">
         <f aca="false">IF($B6="","",IF(ISNUMBER($F6),MAX(1,MIN(5,ROUND(6-$F6,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="L6" s="41" t="str">
+        <v>1</v>
+      </c>
+      <c r="L6" s="41" t="n">
         <f aca="false">IF($B6="","",IF(ISNUMBER($G6),MAX(1,MIN(5,ROUND(6-$G6,0))),"-"))</f>
-        <v/>
-      </c>
-      <c r="M6" s="41" t="str">
+        <v>2</v>
+      </c>
+      <c r="M6" s="41" t="n">
         <f aca="false">IF($B6="","",IF(AND(ISNUMBER($P6),ISNUMBER($O6)),MAX(1,MIN(5,ROUND(6-AVERAGE($P6,$O6),0))),IF(ISNUMBER($P6),MAX(1,MIN(5,ROUND(6-$P6,0))),"-")))</f>
-        <v/>
-      </c>
-      <c r="O6" s="33" t="str">
+        <v>2</v>
+      </c>
+      <c r="O6" s="33" t="n">
         <f aca="false">IF($B6="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B6),""))</f>
-        <v/>
-      </c>
-      <c r="P6" s="33" t="str">
+        <v>4</v>
+      </c>
+      <c r="P6" s="33" t="n">
         <f aca="false">IF($B6="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B6),""))</f>
-        <v/>
+        <v>5</v>
+      </c>
+      <c r="Q6" s="33" t="n">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v>5</v>
+      </c>
+      <c r="AA6" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C6="",'Score Log'!$E6=""),0,IF(COUNTIFS('Score Log'!$C$4:$C6,'Score Log'!$C6,'Score Log'!$E$4:$E6,'Score Log'!$E6)=1,1,0))</f>
+        <v>1</v>
+      </c>
+      <c r="AB6" s="33" t="n">
+        <f aca="false">IF($AA6=1,SUM($AA$4:$AA6),"")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="38" t="str">
-        <f aca="false">IF($B7="","",IF($C7="",COUNTIF('Score Log'!$C$4:$C$203,$B7),COUNTIFS('Score Log'!$C$4:$C$203,$B7,'Score Log'!$D$4:$D$203,$C7)))</f>
-        <v/>
+      <c r="A7" s="36" t="str">
+        <f aca="false">IF($Q7="","",INDEX('Score Log'!$E:$E,$Q7))</f>
+        <v>Suppine chest base</v>
+      </c>
+      <c r="B7" s="36" t="str">
+        <f aca="false">IF($Q7="","",INDEX('Score Log'!$C:$C,$Q7))</f>
+        <v>Advanced Plastiform</v>
+      </c>
+      <c r="C7" s="37" t="str">
+        <f aca="false">IF($Q7="","",IF(INDEX('Score Log'!$D:$D,$Q7)="","",INDEX('Score Log'!$D:$D,$Q7)))</f>
+        <v>Thermoforming</v>
+      </c>
+      <c r="D7" s="38" t="n">
+        <f aca="false">IF($B7="","",COUNTIFS('Score Log'!$C$4:$C$203,$B7,'Score Log'!$E$4:$E$203,$A7))</f>
+        <v>1</v>
       </c>
       <c r="E7" s="39" t="str">
-        <f aca="false">IF($B7="","",IFERROR(ROUND(IF($C7="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B7),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B7,'Score Log'!$D$4:$D$203,$C7)),1),"-"))</f>
-        <v/>
+        <f aca="false">IF($B7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B7,'Score Log'!$E$4:$E$203,$A7),1),"-"))</f>
+        <v>-</v>
       </c>
       <c r="F7" s="39" t="str">
-        <f aca="false">IF($B7="","",IFERROR(ROUND(IF($C7="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B7),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B7,'Score Log'!$D$4:$D$203,$C7)),1),"-"))</f>
-        <v/>
+        <f aca="false">IF($B7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B7,'Score Log'!$E$4:$E$203,$A7),1),"-"))</f>
+        <v>-</v>
       </c>
       <c r="G7" s="39" t="str">
-        <f aca="false">IF($B7="","",IFERROR(ROUND(IF($C7="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B7),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B7,'Score Log'!$D$4:$D$203,$C7)),1),"-"))</f>
-        <v/>
+        <f aca="false">IF($B7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B7,'Score Log'!$E$4:$E$203,$A7),1),"-"))</f>
+        <v>-</v>
       </c>
       <c r="H7" s="39" t="str">
-        <f aca="false">IF($B7="","",IFERROR(ROUND(IF($C7="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B7),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B7,'Score Log'!$D$4:$D$203,$C7)),1),"-"))</f>
-        <v/>
+        <f aca="false">IF($B7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B7,'Score Log'!$E$4:$E$203,$A7),1),"-"))</f>
+        <v>-</v>
       </c>
       <c r="I7" s="39" t="str">
-        <f aca="false">IF($B7="","",IFERROR(ROUND(IF($C7="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B7),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B7,'Score Log'!$D$4:$D$203,$C7)),1),"-"))</f>
-        <v/>
-      </c>
-      <c r="J7" s="40" t="str">
-        <f aca="false">IF(OR($B7="",$D7=0),"",IFERROR(IF($C7="",COUNTIFS('Score Log'!$C$4:$C$203,$B7,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B7,'Score Log'!$D$4:$D$203,$C7,'Score Log'!$U$4:$U$203,"Yes"))/$D7,"-"))</f>
-        <v/>
+        <f aca="false">IF($B7="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B7,'Score Log'!$E$4:$E$203,$A7),1),"-"))</f>
+        <v>-</v>
+      </c>
+      <c r="J7" s="40" t="n">
+        <f aca="false">IF(OR($B7="",$D7=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B7,'Score Log'!$E$4:$E$203,$A7,'Score Log'!$U$4:$U$203,"Yes")/$D7,"-"))</f>
+        <v>0</v>
       </c>
       <c r="K7" s="41" t="str">
         <f aca="false">IF($B7="","",IF(ISNUMBER($F7),MAX(1,MIN(5,ROUND(6-$F7,0))),"-"))</f>
-        <v/>
+        <v>-</v>
       </c>
       <c r="L7" s="41" t="str">
         <f aca="false">IF($B7="","",IF(ISNUMBER($G7),MAX(1,MIN(5,ROUND(6-$G7,0))),"-"))</f>
-        <v/>
+        <v>-</v>
       </c>
       <c r="M7" s="41" t="str">
         <f aca="false">IF($B7="","",IF(AND(ISNUMBER($P7),ISNUMBER($O7)),MAX(1,MIN(5,ROUND(6-AVERAGE($P7,$O7),0))),IF(ISNUMBER($P7),MAX(1,MIN(5,ROUND(6-$P7,0))),"-")))</f>
-        <v/>
+        <v>-</v>
       </c>
       <c r="O7" s="33" t="str">
         <f aca="false">IF($B7="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B7),""))</f>
@@ -11994,37 +12140,58 @@
         <f aca="false">IF($B7="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B7),""))</f>
         <v/>
       </c>
+      <c r="Q7" s="33" t="n">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v>6</v>
+      </c>
+      <c r="AA7" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C7="",'Score Log'!$E7=""),0,IF(COUNTIFS('Score Log'!$C$4:$C7,'Score Log'!$C7,'Score Log'!$E$4:$E7,'Score Log'!$E7)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB7" s="33" t="str">
+        <f aca="false">IF($AA7=1,SUM($AA$4:$AA7),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
+      <c r="A8" s="36" t="str">
+        <f aca="false">IF($Q8="","",INDEX('Score Log'!$E:$E,$Q8))</f>
+        <v/>
+      </c>
+      <c r="B8" s="36" t="str">
+        <f aca="false">IF($Q8="","",INDEX('Score Log'!$C:$C,$Q8))</f>
+        <v/>
+      </c>
+      <c r="C8" s="37" t="str">
+        <f aca="false">IF($Q8="","",IF(INDEX('Score Log'!$D:$D,$Q8)="","",INDEX('Score Log'!$D:$D,$Q8)))</f>
+        <v/>
+      </c>
       <c r="D8" s="38" t="str">
-        <f aca="false">IF($B8="","",IF($C8="",COUNTIF('Score Log'!$C$4:$C$203,$B8),COUNTIFS('Score Log'!$C$4:$C$203,$B8,'Score Log'!$D$4:$D$203,$C8)))</f>
+        <f aca="false">IF($B8="","",COUNTIFS('Score Log'!$C$4:$C$203,$B8,'Score Log'!$E$4:$E$203,$A8))</f>
         <v/>
       </c>
       <c r="E8" s="39" t="str">
-        <f aca="false">IF($B8="","",IFERROR(ROUND(IF($C8="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B8),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B8,'Score Log'!$D$4:$D$203,$C8)),1),"-"))</f>
+        <f aca="false">IF($B8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B8,'Score Log'!$E$4:$E$203,$A8),1),"-"))</f>
         <v/>
       </c>
       <c r="F8" s="39" t="str">
-        <f aca="false">IF($B8="","",IFERROR(ROUND(IF($C8="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B8),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B8,'Score Log'!$D$4:$D$203,$C8)),1),"-"))</f>
+        <f aca="false">IF($B8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B8,'Score Log'!$E$4:$E$203,$A8),1),"-"))</f>
         <v/>
       </c>
       <c r="G8" s="39" t="str">
-        <f aca="false">IF($B8="","",IFERROR(ROUND(IF($C8="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B8),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B8,'Score Log'!$D$4:$D$203,$C8)),1),"-"))</f>
+        <f aca="false">IF($B8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B8,'Score Log'!$E$4:$E$203,$A8),1),"-"))</f>
         <v/>
       </c>
       <c r="H8" s="39" t="str">
-        <f aca="false">IF($B8="","",IFERROR(ROUND(IF($C8="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B8),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B8,'Score Log'!$D$4:$D$203,$C8)),1),"-"))</f>
+        <f aca="false">IF($B8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B8,'Score Log'!$E$4:$E$203,$A8),1),"-"))</f>
         <v/>
       </c>
       <c r="I8" s="39" t="str">
-        <f aca="false">IF($B8="","",IFERROR(ROUND(IF($C8="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B8),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B8,'Score Log'!$D$4:$D$203,$C8)),1),"-"))</f>
+        <f aca="false">IF($B8="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B8,'Score Log'!$E$4:$E$203,$A8),1),"-"))</f>
         <v/>
       </c>
       <c r="J8" s="40" t="str">
-        <f aca="false">IF(OR($B8="",$D8=0),"",IFERROR(IF($C8="",COUNTIFS('Score Log'!$C$4:$C$203,$B8,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B8,'Score Log'!$D$4:$D$203,$C8,'Score Log'!$U$4:$U$203,"Yes"))/$D8,"-"))</f>
+        <f aca="false">IF(OR($B8="",$D8=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B8,'Score Log'!$E$4:$E$203,$A8,'Score Log'!$U$4:$U$203,"Yes")/$D8,"-"))</f>
         <v/>
       </c>
       <c r="K8" s="41" t="str">
@@ -12047,37 +12214,58 @@
         <f aca="false">IF($B8="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B8),""))</f>
         <v/>
       </c>
+      <c r="Q8" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA8" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C8="",'Score Log'!$E8=""),0,IF(COUNTIFS('Score Log'!$C$4:$C8,'Score Log'!$C8,'Score Log'!$E$4:$E8,'Score Log'!$E8)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB8" s="33" t="str">
+        <f aca="false">IF($AA8=1,SUM($AA$4:$AA8),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="37"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
+      <c r="A9" s="36" t="str">
+        <f aca="false">IF($Q9="","",INDEX('Score Log'!$E:$E,$Q9))</f>
+        <v/>
+      </c>
+      <c r="B9" s="36" t="str">
+        <f aca="false">IF($Q9="","",INDEX('Score Log'!$C:$C,$Q9))</f>
+        <v/>
+      </c>
+      <c r="C9" s="37" t="str">
+        <f aca="false">IF($Q9="","",IF(INDEX('Score Log'!$D:$D,$Q9)="","",INDEX('Score Log'!$D:$D,$Q9)))</f>
+        <v/>
+      </c>
       <c r="D9" s="38" t="str">
-        <f aca="false">IF($B9="","",IF($C9="",COUNTIF('Score Log'!$C$4:$C$203,$B9),COUNTIFS('Score Log'!$C$4:$C$203,$B9,'Score Log'!$D$4:$D$203,$C9)))</f>
+        <f aca="false">IF($B9="","",COUNTIFS('Score Log'!$C$4:$C$203,$B9,'Score Log'!$E$4:$E$203,$A9))</f>
         <v/>
       </c>
       <c r="E9" s="39" t="str">
-        <f aca="false">IF($B9="","",IFERROR(ROUND(IF($C9="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B9),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B9,'Score Log'!$D$4:$D$203,$C9)),1),"-"))</f>
+        <f aca="false">IF($B9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B9,'Score Log'!$E$4:$E$203,$A9),1),"-"))</f>
         <v/>
       </c>
       <c r="F9" s="39" t="str">
-        <f aca="false">IF($B9="","",IFERROR(ROUND(IF($C9="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B9),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B9,'Score Log'!$D$4:$D$203,$C9)),1),"-"))</f>
+        <f aca="false">IF($B9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B9,'Score Log'!$E$4:$E$203,$A9),1),"-"))</f>
         <v/>
       </c>
       <c r="G9" s="39" t="str">
-        <f aca="false">IF($B9="","",IFERROR(ROUND(IF($C9="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B9),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B9,'Score Log'!$D$4:$D$203,$C9)),1),"-"))</f>
+        <f aca="false">IF($B9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B9,'Score Log'!$E$4:$E$203,$A9),1),"-"))</f>
         <v/>
       </c>
       <c r="H9" s="39" t="str">
-        <f aca="false">IF($B9="","",IFERROR(ROUND(IF($C9="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B9),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B9,'Score Log'!$D$4:$D$203,$C9)),1),"-"))</f>
+        <f aca="false">IF($B9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B9,'Score Log'!$E$4:$E$203,$A9),1),"-"))</f>
         <v/>
       </c>
       <c r="I9" s="39" t="str">
-        <f aca="false">IF($B9="","",IFERROR(ROUND(IF($C9="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B9),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B9,'Score Log'!$D$4:$D$203,$C9)),1),"-"))</f>
+        <f aca="false">IF($B9="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B9,'Score Log'!$E$4:$E$203,$A9),1),"-"))</f>
         <v/>
       </c>
       <c r="J9" s="40" t="str">
-        <f aca="false">IF(OR($B9="",$D9=0),"",IFERROR(IF($C9="",COUNTIFS('Score Log'!$C$4:$C$203,$B9,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B9,'Score Log'!$D$4:$D$203,$C9,'Score Log'!$U$4:$U$203,"Yes"))/$D9,"-"))</f>
+        <f aca="false">IF(OR($B9="",$D9=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B9,'Score Log'!$E$4:$E$203,$A9,'Score Log'!$U$4:$U$203,"Yes")/$D9,"-"))</f>
         <v/>
       </c>
       <c r="K9" s="41" t="str">
@@ -12100,37 +12288,58 @@
         <f aca="false">IF($B9="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B9),""))</f>
         <v/>
       </c>
+      <c r="Q9" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA9" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C9="",'Score Log'!$E9=""),0,IF(COUNTIFS('Score Log'!$C$4:$C9,'Score Log'!$C9,'Score Log'!$E$4:$E9,'Score Log'!$E9)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB9" s="33" t="str">
+        <f aca="false">IF($AA9=1,SUM($AA$4:$AA9),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="37"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
+      <c r="A10" s="36" t="str">
+        <f aca="false">IF($Q10="","",INDEX('Score Log'!$E:$E,$Q10))</f>
+        <v/>
+      </c>
+      <c r="B10" s="36" t="str">
+        <f aca="false">IF($Q10="","",INDEX('Score Log'!$C:$C,$Q10))</f>
+        <v/>
+      </c>
+      <c r="C10" s="37" t="str">
+        <f aca="false">IF($Q10="","",IF(INDEX('Score Log'!$D:$D,$Q10)="","",INDEX('Score Log'!$D:$D,$Q10)))</f>
+        <v/>
+      </c>
       <c r="D10" s="38" t="str">
-        <f aca="false">IF($B10="","",IF($C10="",COUNTIF('Score Log'!$C$4:$C$203,$B10),COUNTIFS('Score Log'!$C$4:$C$203,$B10,'Score Log'!$D$4:$D$203,$C10)))</f>
+        <f aca="false">IF($B10="","",COUNTIFS('Score Log'!$C$4:$C$203,$B10,'Score Log'!$E$4:$E$203,$A10))</f>
         <v/>
       </c>
       <c r="E10" s="39" t="str">
-        <f aca="false">IF($B10="","",IFERROR(ROUND(IF($C10="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B10),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B10,'Score Log'!$D$4:$D$203,$C10)),1),"-"))</f>
+        <f aca="false">IF($B10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B10,'Score Log'!$E$4:$E$203,$A10),1),"-"))</f>
         <v/>
       </c>
       <c r="F10" s="39" t="str">
-        <f aca="false">IF($B10="","",IFERROR(ROUND(IF($C10="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B10),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B10,'Score Log'!$D$4:$D$203,$C10)),1),"-"))</f>
+        <f aca="false">IF($B10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B10,'Score Log'!$E$4:$E$203,$A10),1),"-"))</f>
         <v/>
       </c>
       <c r="G10" s="39" t="str">
-        <f aca="false">IF($B10="","",IFERROR(ROUND(IF($C10="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B10),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B10,'Score Log'!$D$4:$D$203,$C10)),1),"-"))</f>
+        <f aca="false">IF($B10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B10,'Score Log'!$E$4:$E$203,$A10),1),"-"))</f>
         <v/>
       </c>
       <c r="H10" s="39" t="str">
-        <f aca="false">IF($B10="","",IFERROR(ROUND(IF($C10="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B10),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B10,'Score Log'!$D$4:$D$203,$C10)),1),"-"))</f>
+        <f aca="false">IF($B10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B10,'Score Log'!$E$4:$E$203,$A10),1),"-"))</f>
         <v/>
       </c>
       <c r="I10" s="39" t="str">
-        <f aca="false">IF($B10="","",IFERROR(ROUND(IF($C10="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B10),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B10,'Score Log'!$D$4:$D$203,$C10)),1),"-"))</f>
+        <f aca="false">IF($B10="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B10,'Score Log'!$E$4:$E$203,$A10),1),"-"))</f>
         <v/>
       </c>
       <c r="J10" s="40" t="str">
-        <f aca="false">IF(OR($B10="",$D10=0),"",IFERROR(IF($C10="",COUNTIFS('Score Log'!$C$4:$C$203,$B10,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B10,'Score Log'!$D$4:$D$203,$C10,'Score Log'!$U$4:$U$203,"Yes"))/$D10,"-"))</f>
+        <f aca="false">IF(OR($B10="",$D10=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B10,'Score Log'!$E$4:$E$203,$A10,'Score Log'!$U$4:$U$203,"Yes")/$D10,"-"))</f>
         <v/>
       </c>
       <c r="K10" s="41" t="str">
@@ -12153,37 +12362,58 @@
         <f aca="false">IF($B10="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B10),""))</f>
         <v/>
       </c>
+      <c r="Q10" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA10" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C10="",'Score Log'!$E10=""),0,IF(COUNTIFS('Score Log'!$C$4:$C10,'Score Log'!$C10,'Score Log'!$E$4:$E10,'Score Log'!$E10)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB10" s="33" t="str">
+        <f aca="false">IF($AA10=1,SUM($AA$4:$AA10),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
+      <c r="A11" s="36" t="str">
+        <f aca="false">IF($Q11="","",INDEX('Score Log'!$E:$E,$Q11))</f>
+        <v/>
+      </c>
+      <c r="B11" s="36" t="str">
+        <f aca="false">IF($Q11="","",INDEX('Score Log'!$C:$C,$Q11))</f>
+        <v/>
+      </c>
+      <c r="C11" s="37" t="str">
+        <f aca="false">IF($Q11="","",IF(INDEX('Score Log'!$D:$D,$Q11)="","",INDEX('Score Log'!$D:$D,$Q11)))</f>
+        <v/>
+      </c>
       <c r="D11" s="38" t="str">
-        <f aca="false">IF($B11="","",IF($C11="",COUNTIF('Score Log'!$C$4:$C$203,$B11),COUNTIFS('Score Log'!$C$4:$C$203,$B11,'Score Log'!$D$4:$D$203,$C11)))</f>
+        <f aca="false">IF($B11="","",COUNTIFS('Score Log'!$C$4:$C$203,$B11,'Score Log'!$E$4:$E$203,$A11))</f>
         <v/>
       </c>
       <c r="E11" s="39" t="str">
-        <f aca="false">IF($B11="","",IFERROR(ROUND(IF($C11="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B11),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B11,'Score Log'!$D$4:$D$203,$C11)),1),"-"))</f>
+        <f aca="false">IF($B11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B11,'Score Log'!$E$4:$E$203,$A11),1),"-"))</f>
         <v/>
       </c>
       <c r="F11" s="39" t="str">
-        <f aca="false">IF($B11="","",IFERROR(ROUND(IF($C11="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B11),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B11,'Score Log'!$D$4:$D$203,$C11)),1),"-"))</f>
+        <f aca="false">IF($B11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B11,'Score Log'!$E$4:$E$203,$A11),1),"-"))</f>
         <v/>
       </c>
       <c r="G11" s="39" t="str">
-        <f aca="false">IF($B11="","",IFERROR(ROUND(IF($C11="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B11),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B11,'Score Log'!$D$4:$D$203,$C11)),1),"-"))</f>
+        <f aca="false">IF($B11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B11,'Score Log'!$E$4:$E$203,$A11),1),"-"))</f>
         <v/>
       </c>
       <c r="H11" s="39" t="str">
-        <f aca="false">IF($B11="","",IFERROR(ROUND(IF($C11="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B11),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B11,'Score Log'!$D$4:$D$203,$C11)),1),"-"))</f>
+        <f aca="false">IF($B11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B11,'Score Log'!$E$4:$E$203,$A11),1),"-"))</f>
         <v/>
       </c>
       <c r="I11" s="39" t="str">
-        <f aca="false">IF($B11="","",IFERROR(ROUND(IF($C11="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B11),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B11,'Score Log'!$D$4:$D$203,$C11)),1),"-"))</f>
+        <f aca="false">IF($B11="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B11,'Score Log'!$E$4:$E$203,$A11),1),"-"))</f>
         <v/>
       </c>
       <c r="J11" s="40" t="str">
-        <f aca="false">IF(OR($B11="",$D11=0),"",IFERROR(IF($C11="",COUNTIFS('Score Log'!$C$4:$C$203,$B11,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B11,'Score Log'!$D$4:$D$203,$C11,'Score Log'!$U$4:$U$203,"Yes"))/$D11,"-"))</f>
+        <f aca="false">IF(OR($B11="",$D11=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B11,'Score Log'!$E$4:$E$203,$A11,'Score Log'!$U$4:$U$203,"Yes")/$D11,"-"))</f>
         <v/>
       </c>
       <c r="K11" s="41" t="str">
@@ -12206,37 +12436,58 @@
         <f aca="false">IF($B11="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B11),""))</f>
         <v/>
       </c>
+      <c r="Q11" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA11" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C11="",'Score Log'!$E11=""),0,IF(COUNTIFS('Score Log'!$C$4:$C11,'Score Log'!$C11,'Score Log'!$E$4:$E11,'Score Log'!$E11)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB11" s="33" t="str">
+        <f aca="false">IF($AA11=1,SUM($AA$4:$AA11),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
+      <c r="A12" s="36" t="str">
+        <f aca="false">IF($Q12="","",INDEX('Score Log'!$E:$E,$Q12))</f>
+        <v/>
+      </c>
+      <c r="B12" s="36" t="str">
+        <f aca="false">IF($Q12="","",INDEX('Score Log'!$C:$C,$Q12))</f>
+        <v/>
+      </c>
+      <c r="C12" s="37" t="str">
+        <f aca="false">IF($Q12="","",IF(INDEX('Score Log'!$D:$D,$Q12)="","",INDEX('Score Log'!$D:$D,$Q12)))</f>
+        <v/>
+      </c>
       <c r="D12" s="38" t="str">
-        <f aca="false">IF($B12="","",IF($C12="",COUNTIF('Score Log'!$C$4:$C$203,$B12),COUNTIFS('Score Log'!$C$4:$C$203,$B12,'Score Log'!$D$4:$D$203,$C12)))</f>
+        <f aca="false">IF($B12="","",COUNTIFS('Score Log'!$C$4:$C$203,$B12,'Score Log'!$E$4:$E$203,$A12))</f>
         <v/>
       </c>
       <c r="E12" s="39" t="str">
-        <f aca="false">IF($B12="","",IFERROR(ROUND(IF($C12="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B12),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B12,'Score Log'!$D$4:$D$203,$C12)),1),"-"))</f>
+        <f aca="false">IF($B12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B12,'Score Log'!$E$4:$E$203,$A12),1),"-"))</f>
         <v/>
       </c>
       <c r="F12" s="39" t="str">
-        <f aca="false">IF($B12="","",IFERROR(ROUND(IF($C12="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B12),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B12,'Score Log'!$D$4:$D$203,$C12)),1),"-"))</f>
+        <f aca="false">IF($B12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B12,'Score Log'!$E$4:$E$203,$A12),1),"-"))</f>
         <v/>
       </c>
       <c r="G12" s="39" t="str">
-        <f aca="false">IF($B12="","",IFERROR(ROUND(IF($C12="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B12),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B12,'Score Log'!$D$4:$D$203,$C12)),1),"-"))</f>
+        <f aca="false">IF($B12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B12,'Score Log'!$E$4:$E$203,$A12),1),"-"))</f>
         <v/>
       </c>
       <c r="H12" s="39" t="str">
-        <f aca="false">IF($B12="","",IFERROR(ROUND(IF($C12="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B12),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B12,'Score Log'!$D$4:$D$203,$C12)),1),"-"))</f>
+        <f aca="false">IF($B12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B12,'Score Log'!$E$4:$E$203,$A12),1),"-"))</f>
         <v/>
       </c>
       <c r="I12" s="39" t="str">
-        <f aca="false">IF($B12="","",IFERROR(ROUND(IF($C12="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B12),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B12,'Score Log'!$D$4:$D$203,$C12)),1),"-"))</f>
+        <f aca="false">IF($B12="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B12,'Score Log'!$E$4:$E$203,$A12),1),"-"))</f>
         <v/>
       </c>
       <c r="J12" s="40" t="str">
-        <f aca="false">IF(OR($B12="",$D12=0),"",IFERROR(IF($C12="",COUNTIFS('Score Log'!$C$4:$C$203,$B12,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B12,'Score Log'!$D$4:$D$203,$C12,'Score Log'!$U$4:$U$203,"Yes"))/$D12,"-"))</f>
+        <f aca="false">IF(OR($B12="",$D12=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B12,'Score Log'!$E$4:$E$203,$A12,'Score Log'!$U$4:$U$203,"Yes")/$D12,"-"))</f>
         <v/>
       </c>
       <c r="K12" s="41" t="str">
@@ -12259,37 +12510,58 @@
         <f aca="false">IF($B12="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B12),""))</f>
         <v/>
       </c>
+      <c r="Q12" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA12" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C12="",'Score Log'!$E12=""),0,IF(COUNTIFS('Score Log'!$C$4:$C12,'Score Log'!$C12,'Score Log'!$E$4:$E12,'Score Log'!$E12)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB12" s="33" t="str">
+        <f aca="false">IF($AA12=1,SUM($AA$4:$AA12),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="37"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
+      <c r="A13" s="36" t="str">
+        <f aca="false">IF($Q13="","",INDEX('Score Log'!$E:$E,$Q13))</f>
+        <v/>
+      </c>
+      <c r="B13" s="36" t="str">
+        <f aca="false">IF($Q13="","",INDEX('Score Log'!$C:$C,$Q13))</f>
+        <v/>
+      </c>
+      <c r="C13" s="37" t="str">
+        <f aca="false">IF($Q13="","",IF(INDEX('Score Log'!$D:$D,$Q13)="","",INDEX('Score Log'!$D:$D,$Q13)))</f>
+        <v/>
+      </c>
       <c r="D13" s="38" t="str">
-        <f aca="false">IF($B13="","",IF($C13="",COUNTIF('Score Log'!$C$4:$C$203,$B13),COUNTIFS('Score Log'!$C$4:$C$203,$B13,'Score Log'!$D$4:$D$203,$C13)))</f>
+        <f aca="false">IF($B13="","",COUNTIFS('Score Log'!$C$4:$C$203,$B13,'Score Log'!$E$4:$E$203,$A13))</f>
         <v/>
       </c>
       <c r="E13" s="39" t="str">
-        <f aca="false">IF($B13="","",IFERROR(ROUND(IF($C13="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B13),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B13,'Score Log'!$D$4:$D$203,$C13)),1),"-"))</f>
+        <f aca="false">IF($B13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B13,'Score Log'!$E$4:$E$203,$A13),1),"-"))</f>
         <v/>
       </c>
       <c r="F13" s="39" t="str">
-        <f aca="false">IF($B13="","",IFERROR(ROUND(IF($C13="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B13),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B13,'Score Log'!$D$4:$D$203,$C13)),1),"-"))</f>
+        <f aca="false">IF($B13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B13,'Score Log'!$E$4:$E$203,$A13),1),"-"))</f>
         <v/>
       </c>
       <c r="G13" s="39" t="str">
-        <f aca="false">IF($B13="","",IFERROR(ROUND(IF($C13="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B13),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B13,'Score Log'!$D$4:$D$203,$C13)),1),"-"))</f>
+        <f aca="false">IF($B13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B13,'Score Log'!$E$4:$E$203,$A13),1),"-"))</f>
         <v/>
       </c>
       <c r="H13" s="39" t="str">
-        <f aca="false">IF($B13="","",IFERROR(ROUND(IF($C13="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B13),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B13,'Score Log'!$D$4:$D$203,$C13)),1),"-"))</f>
+        <f aca="false">IF($B13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B13,'Score Log'!$E$4:$E$203,$A13),1),"-"))</f>
         <v/>
       </c>
       <c r="I13" s="39" t="str">
-        <f aca="false">IF($B13="","",IFERROR(ROUND(IF($C13="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B13),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B13,'Score Log'!$D$4:$D$203,$C13)),1),"-"))</f>
+        <f aca="false">IF($B13="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B13,'Score Log'!$E$4:$E$203,$A13),1),"-"))</f>
         <v/>
       </c>
       <c r="J13" s="40" t="str">
-        <f aca="false">IF(OR($B13="",$D13=0),"",IFERROR(IF($C13="",COUNTIFS('Score Log'!$C$4:$C$203,$B13,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B13,'Score Log'!$D$4:$D$203,$C13,'Score Log'!$U$4:$U$203,"Yes"))/$D13,"-"))</f>
+        <f aca="false">IF(OR($B13="",$D13=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B13,'Score Log'!$E$4:$E$203,$A13,'Score Log'!$U$4:$U$203,"Yes")/$D13,"-"))</f>
         <v/>
       </c>
       <c r="K13" s="41" t="str">
@@ -12312,37 +12584,58 @@
         <f aca="false">IF($B13="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B13),""))</f>
         <v/>
       </c>
+      <c r="Q13" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA13" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C13="",'Score Log'!$E13=""),0,IF(COUNTIFS('Score Log'!$C$4:$C13,'Score Log'!$C13,'Score Log'!$E$4:$E13,'Score Log'!$E13)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB13" s="33" t="str">
+        <f aca="false">IF($AA13=1,SUM($AA$4:$AA13),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
+      <c r="A14" s="36" t="str">
+        <f aca="false">IF($Q14="","",INDEX('Score Log'!$E:$E,$Q14))</f>
+        <v/>
+      </c>
+      <c r="B14" s="36" t="str">
+        <f aca="false">IF($Q14="","",INDEX('Score Log'!$C:$C,$Q14))</f>
+        <v/>
+      </c>
+      <c r="C14" s="37" t="str">
+        <f aca="false">IF($Q14="","",IF(INDEX('Score Log'!$D:$D,$Q14)="","",INDEX('Score Log'!$D:$D,$Q14)))</f>
+        <v/>
+      </c>
       <c r="D14" s="38" t="str">
-        <f aca="false">IF($B14="","",IF($C14="",COUNTIF('Score Log'!$C$4:$C$203,$B14),COUNTIFS('Score Log'!$C$4:$C$203,$B14,'Score Log'!$D$4:$D$203,$C14)))</f>
+        <f aca="false">IF($B14="","",COUNTIFS('Score Log'!$C$4:$C$203,$B14,'Score Log'!$E$4:$E$203,$A14))</f>
         <v/>
       </c>
       <c r="E14" s="39" t="str">
-        <f aca="false">IF($B14="","",IFERROR(ROUND(IF($C14="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B14),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B14,'Score Log'!$D$4:$D$203,$C14)),1),"-"))</f>
+        <f aca="false">IF($B14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B14,'Score Log'!$E$4:$E$203,$A14),1),"-"))</f>
         <v/>
       </c>
       <c r="F14" s="39" t="str">
-        <f aca="false">IF($B14="","",IFERROR(ROUND(IF($C14="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B14),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B14,'Score Log'!$D$4:$D$203,$C14)),1),"-"))</f>
+        <f aca="false">IF($B14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B14,'Score Log'!$E$4:$E$203,$A14),1),"-"))</f>
         <v/>
       </c>
       <c r="G14" s="39" t="str">
-        <f aca="false">IF($B14="","",IFERROR(ROUND(IF($C14="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B14),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B14,'Score Log'!$D$4:$D$203,$C14)),1),"-"))</f>
+        <f aca="false">IF($B14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B14,'Score Log'!$E$4:$E$203,$A14),1),"-"))</f>
         <v/>
       </c>
       <c r="H14" s="39" t="str">
-        <f aca="false">IF($B14="","",IFERROR(ROUND(IF($C14="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B14),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B14,'Score Log'!$D$4:$D$203,$C14)),1),"-"))</f>
+        <f aca="false">IF($B14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B14,'Score Log'!$E$4:$E$203,$A14),1),"-"))</f>
         <v/>
       </c>
       <c r="I14" s="39" t="str">
-        <f aca="false">IF($B14="","",IFERROR(ROUND(IF($C14="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B14),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B14,'Score Log'!$D$4:$D$203,$C14)),1),"-"))</f>
+        <f aca="false">IF($B14="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B14,'Score Log'!$E$4:$E$203,$A14),1),"-"))</f>
         <v/>
       </c>
       <c r="J14" s="40" t="str">
-        <f aca="false">IF(OR($B14="",$D14=0),"",IFERROR(IF($C14="",COUNTIFS('Score Log'!$C$4:$C$203,$B14,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B14,'Score Log'!$D$4:$D$203,$C14,'Score Log'!$U$4:$U$203,"Yes"))/$D14,"-"))</f>
+        <f aca="false">IF(OR($B14="",$D14=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B14,'Score Log'!$E$4:$E$203,$A14,'Score Log'!$U$4:$U$203,"Yes")/$D14,"-"))</f>
         <v/>
       </c>
       <c r="K14" s="41" t="str">
@@ -12365,37 +12658,58 @@
         <f aca="false">IF($B14="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B14),""))</f>
         <v/>
       </c>
+      <c r="Q14" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA14" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C14="",'Score Log'!$E14=""),0,IF(COUNTIFS('Score Log'!$C$4:$C14,'Score Log'!$C14,'Score Log'!$E$4:$E14,'Score Log'!$E14)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB14" s="33" t="str">
+        <f aca="false">IF($AA14=1,SUM($AA$4:$AA14),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="37"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
+      <c r="A15" s="36" t="str">
+        <f aca="false">IF($Q15="","",INDEX('Score Log'!$E:$E,$Q15))</f>
+        <v/>
+      </c>
+      <c r="B15" s="36" t="str">
+        <f aca="false">IF($Q15="","",INDEX('Score Log'!$C:$C,$Q15))</f>
+        <v/>
+      </c>
+      <c r="C15" s="37" t="str">
+        <f aca="false">IF($Q15="","",IF(INDEX('Score Log'!$D:$D,$Q15)="","",INDEX('Score Log'!$D:$D,$Q15)))</f>
+        <v/>
+      </c>
       <c r="D15" s="38" t="str">
-        <f aca="false">IF($B15="","",IF($C15="",COUNTIF('Score Log'!$C$4:$C$203,$B15),COUNTIFS('Score Log'!$C$4:$C$203,$B15,'Score Log'!$D$4:$D$203,$C15)))</f>
+        <f aca="false">IF($B15="","",COUNTIFS('Score Log'!$C$4:$C$203,$B15,'Score Log'!$E$4:$E$203,$A15))</f>
         <v/>
       </c>
       <c r="E15" s="39" t="str">
-        <f aca="false">IF($B15="","",IFERROR(ROUND(IF($C15="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B15),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B15,'Score Log'!$D$4:$D$203,$C15)),1),"-"))</f>
+        <f aca="false">IF($B15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B15,'Score Log'!$E$4:$E$203,$A15),1),"-"))</f>
         <v/>
       </c>
       <c r="F15" s="39" t="str">
-        <f aca="false">IF($B15="","",IFERROR(ROUND(IF($C15="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B15),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B15,'Score Log'!$D$4:$D$203,$C15)),1),"-"))</f>
+        <f aca="false">IF($B15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B15,'Score Log'!$E$4:$E$203,$A15),1),"-"))</f>
         <v/>
       </c>
       <c r="G15" s="39" t="str">
-        <f aca="false">IF($B15="","",IFERROR(ROUND(IF($C15="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B15),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B15,'Score Log'!$D$4:$D$203,$C15)),1),"-"))</f>
+        <f aca="false">IF($B15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B15,'Score Log'!$E$4:$E$203,$A15),1),"-"))</f>
         <v/>
       </c>
       <c r="H15" s="39" t="str">
-        <f aca="false">IF($B15="","",IFERROR(ROUND(IF($C15="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B15),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B15,'Score Log'!$D$4:$D$203,$C15)),1),"-"))</f>
+        <f aca="false">IF($B15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B15,'Score Log'!$E$4:$E$203,$A15),1),"-"))</f>
         <v/>
       </c>
       <c r="I15" s="39" t="str">
-        <f aca="false">IF($B15="","",IFERROR(ROUND(IF($C15="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B15),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B15,'Score Log'!$D$4:$D$203,$C15)),1),"-"))</f>
+        <f aca="false">IF($B15="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B15,'Score Log'!$E$4:$E$203,$A15),1),"-"))</f>
         <v/>
       </c>
       <c r="J15" s="40" t="str">
-        <f aca="false">IF(OR($B15="",$D15=0),"",IFERROR(IF($C15="",COUNTIFS('Score Log'!$C$4:$C$203,$B15,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B15,'Score Log'!$D$4:$D$203,$C15,'Score Log'!$U$4:$U$203,"Yes"))/$D15,"-"))</f>
+        <f aca="false">IF(OR($B15="",$D15=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B15,'Score Log'!$E$4:$E$203,$A15,'Score Log'!$U$4:$U$203,"Yes")/$D15,"-"))</f>
         <v/>
       </c>
       <c r="K15" s="41" t="str">
@@ -12418,37 +12732,58 @@
         <f aca="false">IF($B15="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B15),""))</f>
         <v/>
       </c>
+      <c r="Q15" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA15" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C15="",'Score Log'!$E15=""),0,IF(COUNTIFS('Score Log'!$C$4:$C15,'Score Log'!$C15,'Score Log'!$E$4:$E15,'Score Log'!$E15)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB15" s="33" t="str">
+        <f aca="false">IF($AA15=1,SUM($AA$4:$AA15),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="37"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
+      <c r="A16" s="36" t="str">
+        <f aca="false">IF($Q16="","",INDEX('Score Log'!$E:$E,$Q16))</f>
+        <v/>
+      </c>
+      <c r="B16" s="36" t="str">
+        <f aca="false">IF($Q16="","",INDEX('Score Log'!$C:$C,$Q16))</f>
+        <v/>
+      </c>
+      <c r="C16" s="37" t="str">
+        <f aca="false">IF($Q16="","",IF(INDEX('Score Log'!$D:$D,$Q16)="","",INDEX('Score Log'!$D:$D,$Q16)))</f>
+        <v/>
+      </c>
       <c r="D16" s="38" t="str">
-        <f aca="false">IF($B16="","",IF($C16="",COUNTIF('Score Log'!$C$4:$C$203,$B16),COUNTIFS('Score Log'!$C$4:$C$203,$B16,'Score Log'!$D$4:$D$203,$C16)))</f>
+        <f aca="false">IF($B16="","",COUNTIFS('Score Log'!$C$4:$C$203,$B16,'Score Log'!$E$4:$E$203,$A16))</f>
         <v/>
       </c>
       <c r="E16" s="39" t="str">
-        <f aca="false">IF($B16="","",IFERROR(ROUND(IF($C16="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B16),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B16,'Score Log'!$D$4:$D$203,$C16)),1),"-"))</f>
+        <f aca="false">IF($B16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B16,'Score Log'!$E$4:$E$203,$A16),1),"-"))</f>
         <v/>
       </c>
       <c r="F16" s="39" t="str">
-        <f aca="false">IF($B16="","",IFERROR(ROUND(IF($C16="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B16),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B16,'Score Log'!$D$4:$D$203,$C16)),1),"-"))</f>
+        <f aca="false">IF($B16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B16,'Score Log'!$E$4:$E$203,$A16),1),"-"))</f>
         <v/>
       </c>
       <c r="G16" s="39" t="str">
-        <f aca="false">IF($B16="","",IFERROR(ROUND(IF($C16="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B16),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B16,'Score Log'!$D$4:$D$203,$C16)),1),"-"))</f>
+        <f aca="false">IF($B16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B16,'Score Log'!$E$4:$E$203,$A16),1),"-"))</f>
         <v/>
       </c>
       <c r="H16" s="39" t="str">
-        <f aca="false">IF($B16="","",IFERROR(ROUND(IF($C16="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B16),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B16,'Score Log'!$D$4:$D$203,$C16)),1),"-"))</f>
+        <f aca="false">IF($B16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B16,'Score Log'!$E$4:$E$203,$A16),1),"-"))</f>
         <v/>
       </c>
       <c r="I16" s="39" t="str">
-        <f aca="false">IF($B16="","",IFERROR(ROUND(IF($C16="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B16),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B16,'Score Log'!$D$4:$D$203,$C16)),1),"-"))</f>
+        <f aca="false">IF($B16="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B16,'Score Log'!$E$4:$E$203,$A16),1),"-"))</f>
         <v/>
       </c>
       <c r="J16" s="40" t="str">
-        <f aca="false">IF(OR($B16="",$D16=0),"",IFERROR(IF($C16="",COUNTIFS('Score Log'!$C$4:$C$203,$B16,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B16,'Score Log'!$D$4:$D$203,$C16,'Score Log'!$U$4:$U$203,"Yes"))/$D16,"-"))</f>
+        <f aca="false">IF(OR($B16="",$D16=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B16,'Score Log'!$E$4:$E$203,$A16,'Score Log'!$U$4:$U$203,"Yes")/$D16,"-"))</f>
         <v/>
       </c>
       <c r="K16" s="41" t="str">
@@ -12471,37 +12806,58 @@
         <f aca="false">IF($B16="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B16),""))</f>
         <v/>
       </c>
+      <c r="Q16" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA16" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C16="",'Score Log'!$E16=""),0,IF(COUNTIFS('Score Log'!$C$4:$C16,'Score Log'!$C16,'Score Log'!$E$4:$E16,'Score Log'!$E16)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB16" s="33" t="str">
+        <f aca="false">IF($AA16=1,SUM($AA$4:$AA16),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="37"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
+      <c r="A17" s="36" t="str">
+        <f aca="false">IF($Q17="","",INDEX('Score Log'!$E:$E,$Q17))</f>
+        <v/>
+      </c>
+      <c r="B17" s="36" t="str">
+        <f aca="false">IF($Q17="","",INDEX('Score Log'!$C:$C,$Q17))</f>
+        <v/>
+      </c>
+      <c r="C17" s="37" t="str">
+        <f aca="false">IF($Q17="","",IF(INDEX('Score Log'!$D:$D,$Q17)="","",INDEX('Score Log'!$D:$D,$Q17)))</f>
+        <v/>
+      </c>
       <c r="D17" s="38" t="str">
-        <f aca="false">IF($B17="","",IF($C17="",COUNTIF('Score Log'!$C$4:$C$203,$B17),COUNTIFS('Score Log'!$C$4:$C$203,$B17,'Score Log'!$D$4:$D$203,$C17)))</f>
+        <f aca="false">IF($B17="","",COUNTIFS('Score Log'!$C$4:$C$203,$B17,'Score Log'!$E$4:$E$203,$A17))</f>
         <v/>
       </c>
       <c r="E17" s="39" t="str">
-        <f aca="false">IF($B17="","",IFERROR(ROUND(IF($C17="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B17),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B17,'Score Log'!$D$4:$D$203,$C17)),1),"-"))</f>
+        <f aca="false">IF($B17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B17,'Score Log'!$E$4:$E$203,$A17),1),"-"))</f>
         <v/>
       </c>
       <c r="F17" s="39" t="str">
-        <f aca="false">IF($B17="","",IFERROR(ROUND(IF($C17="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B17),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B17,'Score Log'!$D$4:$D$203,$C17)),1),"-"))</f>
+        <f aca="false">IF($B17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B17,'Score Log'!$E$4:$E$203,$A17),1),"-"))</f>
         <v/>
       </c>
       <c r="G17" s="39" t="str">
-        <f aca="false">IF($B17="","",IFERROR(ROUND(IF($C17="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B17),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B17,'Score Log'!$D$4:$D$203,$C17)),1),"-"))</f>
+        <f aca="false">IF($B17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B17,'Score Log'!$E$4:$E$203,$A17),1),"-"))</f>
         <v/>
       </c>
       <c r="H17" s="39" t="str">
-        <f aca="false">IF($B17="","",IFERROR(ROUND(IF($C17="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B17),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B17,'Score Log'!$D$4:$D$203,$C17)),1),"-"))</f>
+        <f aca="false">IF($B17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B17,'Score Log'!$E$4:$E$203,$A17),1),"-"))</f>
         <v/>
       </c>
       <c r="I17" s="39" t="str">
-        <f aca="false">IF($B17="","",IFERROR(ROUND(IF($C17="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B17),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B17,'Score Log'!$D$4:$D$203,$C17)),1),"-"))</f>
+        <f aca="false">IF($B17="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B17,'Score Log'!$E$4:$E$203,$A17),1),"-"))</f>
         <v/>
       </c>
       <c r="J17" s="40" t="str">
-        <f aca="false">IF(OR($B17="",$D17=0),"",IFERROR(IF($C17="",COUNTIFS('Score Log'!$C$4:$C$203,$B17,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B17,'Score Log'!$D$4:$D$203,$C17,'Score Log'!$U$4:$U$203,"Yes"))/$D17,"-"))</f>
+        <f aca="false">IF(OR($B17="",$D17=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B17,'Score Log'!$E$4:$E$203,$A17,'Score Log'!$U$4:$U$203,"Yes")/$D17,"-"))</f>
         <v/>
       </c>
       <c r="K17" s="41" t="str">
@@ -12524,37 +12880,58 @@
         <f aca="false">IF($B17="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B17),""))</f>
         <v/>
       </c>
+      <c r="Q17" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA17" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C17="",'Score Log'!$E17=""),0,IF(COUNTIFS('Score Log'!$C$4:$C17,'Score Log'!$C17,'Score Log'!$E$4:$E17,'Score Log'!$E17)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB17" s="33" t="str">
+        <f aca="false">IF($AA17=1,SUM($AA$4:$AA17),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="37"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
+      <c r="A18" s="36" t="str">
+        <f aca="false">IF($Q18="","",INDEX('Score Log'!$E:$E,$Q18))</f>
+        <v/>
+      </c>
+      <c r="B18" s="36" t="str">
+        <f aca="false">IF($Q18="","",INDEX('Score Log'!$C:$C,$Q18))</f>
+        <v/>
+      </c>
+      <c r="C18" s="37" t="str">
+        <f aca="false">IF($Q18="","",IF(INDEX('Score Log'!$D:$D,$Q18)="","",INDEX('Score Log'!$D:$D,$Q18)))</f>
+        <v/>
+      </c>
       <c r="D18" s="38" t="str">
-        <f aca="false">IF($B18="","",IF($C18="",COUNTIF('Score Log'!$C$4:$C$203,$B18),COUNTIFS('Score Log'!$C$4:$C$203,$B18,'Score Log'!$D$4:$D$203,$C18)))</f>
+        <f aca="false">IF($B18="","",COUNTIFS('Score Log'!$C$4:$C$203,$B18,'Score Log'!$E$4:$E$203,$A18))</f>
         <v/>
       </c>
       <c r="E18" s="39" t="str">
-        <f aca="false">IF($B18="","",IFERROR(ROUND(IF($C18="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B18),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B18,'Score Log'!$D$4:$D$203,$C18)),1),"-"))</f>
+        <f aca="false">IF($B18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B18,'Score Log'!$E$4:$E$203,$A18),1),"-"))</f>
         <v/>
       </c>
       <c r="F18" s="39" t="str">
-        <f aca="false">IF($B18="","",IFERROR(ROUND(IF($C18="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B18),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B18,'Score Log'!$D$4:$D$203,$C18)),1),"-"))</f>
+        <f aca="false">IF($B18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B18,'Score Log'!$E$4:$E$203,$A18),1),"-"))</f>
         <v/>
       </c>
       <c r="G18" s="39" t="str">
-        <f aca="false">IF($B18="","",IFERROR(ROUND(IF($C18="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B18),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B18,'Score Log'!$D$4:$D$203,$C18)),1),"-"))</f>
+        <f aca="false">IF($B18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B18,'Score Log'!$E$4:$E$203,$A18),1),"-"))</f>
         <v/>
       </c>
       <c r="H18" s="39" t="str">
-        <f aca="false">IF($B18="","",IFERROR(ROUND(IF($C18="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B18),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B18,'Score Log'!$D$4:$D$203,$C18)),1),"-"))</f>
+        <f aca="false">IF($B18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B18,'Score Log'!$E$4:$E$203,$A18),1),"-"))</f>
         <v/>
       </c>
       <c r="I18" s="39" t="str">
-        <f aca="false">IF($B18="","",IFERROR(ROUND(IF($C18="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B18),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B18,'Score Log'!$D$4:$D$203,$C18)),1),"-"))</f>
+        <f aca="false">IF($B18="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B18,'Score Log'!$E$4:$E$203,$A18),1),"-"))</f>
         <v/>
       </c>
       <c r="J18" s="40" t="str">
-        <f aca="false">IF(OR($B18="",$D18=0),"",IFERROR(IF($C18="",COUNTIFS('Score Log'!$C$4:$C$203,$B18,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B18,'Score Log'!$D$4:$D$203,$C18,'Score Log'!$U$4:$U$203,"Yes"))/$D18,"-"))</f>
+        <f aca="false">IF(OR($B18="",$D18=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B18,'Score Log'!$E$4:$E$203,$A18,'Score Log'!$U$4:$U$203,"Yes")/$D18,"-"))</f>
         <v/>
       </c>
       <c r="K18" s="41" t="str">
@@ -12577,37 +12954,58 @@
         <f aca="false">IF($B18="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B18),""))</f>
         <v/>
       </c>
+      <c r="Q18" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA18" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C18="",'Score Log'!$E18=""),0,IF(COUNTIFS('Score Log'!$C$4:$C18,'Score Log'!$C18,'Score Log'!$E$4:$E18,'Score Log'!$E18)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB18" s="33" t="str">
+        <f aca="false">IF($AA18=1,SUM($AA$4:$AA18),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="37"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
+      <c r="A19" s="36" t="str">
+        <f aca="false">IF($Q19="","",INDEX('Score Log'!$E:$E,$Q19))</f>
+        <v/>
+      </c>
+      <c r="B19" s="36" t="str">
+        <f aca="false">IF($Q19="","",INDEX('Score Log'!$C:$C,$Q19))</f>
+        <v/>
+      </c>
+      <c r="C19" s="37" t="str">
+        <f aca="false">IF($Q19="","",IF(INDEX('Score Log'!$D:$D,$Q19)="","",INDEX('Score Log'!$D:$D,$Q19)))</f>
+        <v/>
+      </c>
       <c r="D19" s="38" t="str">
-        <f aca="false">IF($B19="","",IF($C19="",COUNTIF('Score Log'!$C$4:$C$203,$B19),COUNTIFS('Score Log'!$C$4:$C$203,$B19,'Score Log'!$D$4:$D$203,$C19)))</f>
+        <f aca="false">IF($B19="","",COUNTIFS('Score Log'!$C$4:$C$203,$B19,'Score Log'!$E$4:$E$203,$A19))</f>
         <v/>
       </c>
       <c r="E19" s="39" t="str">
-        <f aca="false">IF($B19="","",IFERROR(ROUND(IF($C19="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B19),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B19,'Score Log'!$D$4:$D$203,$C19)),1),"-"))</f>
+        <f aca="false">IF($B19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B19,'Score Log'!$E$4:$E$203,$A19),1),"-"))</f>
         <v/>
       </c>
       <c r="F19" s="39" t="str">
-        <f aca="false">IF($B19="","",IFERROR(ROUND(IF($C19="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B19),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B19,'Score Log'!$D$4:$D$203,$C19)),1),"-"))</f>
+        <f aca="false">IF($B19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B19,'Score Log'!$E$4:$E$203,$A19),1),"-"))</f>
         <v/>
       </c>
       <c r="G19" s="39" t="str">
-        <f aca="false">IF($B19="","",IFERROR(ROUND(IF($C19="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B19),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B19,'Score Log'!$D$4:$D$203,$C19)),1),"-"))</f>
+        <f aca="false">IF($B19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B19,'Score Log'!$E$4:$E$203,$A19),1),"-"))</f>
         <v/>
       </c>
       <c r="H19" s="39" t="str">
-        <f aca="false">IF($B19="","",IFERROR(ROUND(IF($C19="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B19),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B19,'Score Log'!$D$4:$D$203,$C19)),1),"-"))</f>
+        <f aca="false">IF($B19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B19,'Score Log'!$E$4:$E$203,$A19),1),"-"))</f>
         <v/>
       </c>
       <c r="I19" s="39" t="str">
-        <f aca="false">IF($B19="","",IFERROR(ROUND(IF($C19="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B19),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B19,'Score Log'!$D$4:$D$203,$C19)),1),"-"))</f>
+        <f aca="false">IF($B19="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B19,'Score Log'!$E$4:$E$203,$A19),1),"-"))</f>
         <v/>
       </c>
       <c r="J19" s="40" t="str">
-        <f aca="false">IF(OR($B19="",$D19=0),"",IFERROR(IF($C19="",COUNTIFS('Score Log'!$C$4:$C$203,$B19,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B19,'Score Log'!$D$4:$D$203,$C19,'Score Log'!$U$4:$U$203,"Yes"))/$D19,"-"))</f>
+        <f aca="false">IF(OR($B19="",$D19=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B19,'Score Log'!$E$4:$E$203,$A19,'Score Log'!$U$4:$U$203,"Yes")/$D19,"-"))</f>
         <v/>
       </c>
       <c r="K19" s="41" t="str">
@@ -12630,37 +13028,58 @@
         <f aca="false">IF($B19="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B19),""))</f>
         <v/>
       </c>
+      <c r="Q19" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA19" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C19="",'Score Log'!$E19=""),0,IF(COUNTIFS('Score Log'!$C$4:$C19,'Score Log'!$C19,'Score Log'!$E$4:$E19,'Score Log'!$E19)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB19" s="33" t="str">
+        <f aca="false">IF($AA19=1,SUM($AA$4:$AA19),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="37"/>
-      <c r="B20" s="37"/>
-      <c r="C20" s="37"/>
+      <c r="A20" s="36" t="str">
+        <f aca="false">IF($Q20="","",INDEX('Score Log'!$E:$E,$Q20))</f>
+        <v/>
+      </c>
+      <c r="B20" s="36" t="str">
+        <f aca="false">IF($Q20="","",INDEX('Score Log'!$C:$C,$Q20))</f>
+        <v/>
+      </c>
+      <c r="C20" s="37" t="str">
+        <f aca="false">IF($Q20="","",IF(INDEX('Score Log'!$D:$D,$Q20)="","",INDEX('Score Log'!$D:$D,$Q20)))</f>
+        <v/>
+      </c>
       <c r="D20" s="38" t="str">
-        <f aca="false">IF($B20="","",IF($C20="",COUNTIF('Score Log'!$C$4:$C$203,$B20),COUNTIFS('Score Log'!$C$4:$C$203,$B20,'Score Log'!$D$4:$D$203,$C20)))</f>
+        <f aca="false">IF($B20="","",COUNTIFS('Score Log'!$C$4:$C$203,$B20,'Score Log'!$E$4:$E$203,$A20))</f>
         <v/>
       </c>
       <c r="E20" s="39" t="str">
-        <f aca="false">IF($B20="","",IFERROR(ROUND(IF($C20="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B20),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B20,'Score Log'!$D$4:$D$203,$C20)),1),"-"))</f>
+        <f aca="false">IF($B20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B20,'Score Log'!$E$4:$E$203,$A20),1),"-"))</f>
         <v/>
       </c>
       <c r="F20" s="39" t="str">
-        <f aca="false">IF($B20="","",IFERROR(ROUND(IF($C20="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B20),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B20,'Score Log'!$D$4:$D$203,$C20)),1),"-"))</f>
+        <f aca="false">IF($B20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B20,'Score Log'!$E$4:$E$203,$A20),1),"-"))</f>
         <v/>
       </c>
       <c r="G20" s="39" t="str">
-        <f aca="false">IF($B20="","",IFERROR(ROUND(IF($C20="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B20),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B20,'Score Log'!$D$4:$D$203,$C20)),1),"-"))</f>
+        <f aca="false">IF($B20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B20,'Score Log'!$E$4:$E$203,$A20),1),"-"))</f>
         <v/>
       </c>
       <c r="H20" s="39" t="str">
-        <f aca="false">IF($B20="","",IFERROR(ROUND(IF($C20="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B20),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B20,'Score Log'!$D$4:$D$203,$C20)),1),"-"))</f>
+        <f aca="false">IF($B20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B20,'Score Log'!$E$4:$E$203,$A20),1),"-"))</f>
         <v/>
       </c>
       <c r="I20" s="39" t="str">
-        <f aca="false">IF($B20="","",IFERROR(ROUND(IF($C20="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B20),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B20,'Score Log'!$D$4:$D$203,$C20)),1),"-"))</f>
+        <f aca="false">IF($B20="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B20,'Score Log'!$E$4:$E$203,$A20),1),"-"))</f>
         <v/>
       </c>
       <c r="J20" s="40" t="str">
-        <f aca="false">IF(OR($B20="",$D20=0),"",IFERROR(IF($C20="",COUNTIFS('Score Log'!$C$4:$C$203,$B20,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B20,'Score Log'!$D$4:$D$203,$C20,'Score Log'!$U$4:$U$203,"Yes"))/$D20,"-"))</f>
+        <f aca="false">IF(OR($B20="",$D20=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B20,'Score Log'!$E$4:$E$203,$A20,'Score Log'!$U$4:$U$203,"Yes")/$D20,"-"))</f>
         <v/>
       </c>
       <c r="K20" s="41" t="str">
@@ -12683,37 +13102,58 @@
         <f aca="false">IF($B20="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B20),""))</f>
         <v/>
       </c>
+      <c r="Q20" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA20" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C20="",'Score Log'!$E20=""),0,IF(COUNTIFS('Score Log'!$C$4:$C20,'Score Log'!$C20,'Score Log'!$E$4:$E20,'Score Log'!$E20)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB20" s="33" t="str">
+        <f aca="false">IF($AA20=1,SUM($AA$4:$AA20),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="37"/>
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
+      <c r="A21" s="36" t="str">
+        <f aca="false">IF($Q21="","",INDEX('Score Log'!$E:$E,$Q21))</f>
+        <v/>
+      </c>
+      <c r="B21" s="36" t="str">
+        <f aca="false">IF($Q21="","",INDEX('Score Log'!$C:$C,$Q21))</f>
+        <v/>
+      </c>
+      <c r="C21" s="37" t="str">
+        <f aca="false">IF($Q21="","",IF(INDEX('Score Log'!$D:$D,$Q21)="","",INDEX('Score Log'!$D:$D,$Q21)))</f>
+        <v/>
+      </c>
       <c r="D21" s="38" t="str">
-        <f aca="false">IF($B21="","",IF($C21="",COUNTIF('Score Log'!$C$4:$C$203,$B21),COUNTIFS('Score Log'!$C$4:$C$203,$B21,'Score Log'!$D$4:$D$203,$C21)))</f>
+        <f aca="false">IF($B21="","",COUNTIFS('Score Log'!$C$4:$C$203,$B21,'Score Log'!$E$4:$E$203,$A21))</f>
         <v/>
       </c>
       <c r="E21" s="39" t="str">
-        <f aca="false">IF($B21="","",IFERROR(ROUND(IF($C21="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B21),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B21,'Score Log'!$D$4:$D$203,$C21)),1),"-"))</f>
+        <f aca="false">IF($B21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B21,'Score Log'!$E$4:$E$203,$A21),1),"-"))</f>
         <v/>
       </c>
       <c r="F21" s="39" t="str">
-        <f aca="false">IF($B21="","",IFERROR(ROUND(IF($C21="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B21),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B21,'Score Log'!$D$4:$D$203,$C21)),1),"-"))</f>
+        <f aca="false">IF($B21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B21,'Score Log'!$E$4:$E$203,$A21),1),"-"))</f>
         <v/>
       </c>
       <c r="G21" s="39" t="str">
-        <f aca="false">IF($B21="","",IFERROR(ROUND(IF($C21="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B21),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B21,'Score Log'!$D$4:$D$203,$C21)),1),"-"))</f>
+        <f aca="false">IF($B21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B21,'Score Log'!$E$4:$E$203,$A21),1),"-"))</f>
         <v/>
       </c>
       <c r="H21" s="39" t="str">
-        <f aca="false">IF($B21="","",IFERROR(ROUND(IF($C21="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B21),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B21,'Score Log'!$D$4:$D$203,$C21)),1),"-"))</f>
+        <f aca="false">IF($B21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B21,'Score Log'!$E$4:$E$203,$A21),1),"-"))</f>
         <v/>
       </c>
       <c r="I21" s="39" t="str">
-        <f aca="false">IF($B21="","",IFERROR(ROUND(IF($C21="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B21),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B21,'Score Log'!$D$4:$D$203,$C21)),1),"-"))</f>
+        <f aca="false">IF($B21="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B21,'Score Log'!$E$4:$E$203,$A21),1),"-"))</f>
         <v/>
       </c>
       <c r="J21" s="40" t="str">
-        <f aca="false">IF(OR($B21="",$D21=0),"",IFERROR(IF($C21="",COUNTIFS('Score Log'!$C$4:$C$203,$B21,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B21,'Score Log'!$D$4:$D$203,$C21,'Score Log'!$U$4:$U$203,"Yes"))/$D21,"-"))</f>
+        <f aca="false">IF(OR($B21="",$D21=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B21,'Score Log'!$E$4:$E$203,$A21,'Score Log'!$U$4:$U$203,"Yes")/$D21,"-"))</f>
         <v/>
       </c>
       <c r="K21" s="41" t="str">
@@ -12736,37 +13176,58 @@
         <f aca="false">IF($B21="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B21),""))</f>
         <v/>
       </c>
+      <c r="Q21" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA21" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C21="",'Score Log'!$E21=""),0,IF(COUNTIFS('Score Log'!$C$4:$C21,'Score Log'!$C21,'Score Log'!$E$4:$E21,'Score Log'!$E21)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB21" s="33" t="str">
+        <f aca="false">IF($AA21=1,SUM($AA$4:$AA21),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="37"/>
-      <c r="B22" s="37"/>
-      <c r="C22" s="37"/>
+      <c r="A22" s="36" t="str">
+        <f aca="false">IF($Q22="","",INDEX('Score Log'!$E:$E,$Q22))</f>
+        <v/>
+      </c>
+      <c r="B22" s="36" t="str">
+        <f aca="false">IF($Q22="","",INDEX('Score Log'!$C:$C,$Q22))</f>
+        <v/>
+      </c>
+      <c r="C22" s="37" t="str">
+        <f aca="false">IF($Q22="","",IF(INDEX('Score Log'!$D:$D,$Q22)="","",INDEX('Score Log'!$D:$D,$Q22)))</f>
+        <v/>
+      </c>
       <c r="D22" s="38" t="str">
-        <f aca="false">IF($B22="","",IF($C22="",COUNTIF('Score Log'!$C$4:$C$203,$B22),COUNTIFS('Score Log'!$C$4:$C$203,$B22,'Score Log'!$D$4:$D$203,$C22)))</f>
+        <f aca="false">IF($B22="","",COUNTIFS('Score Log'!$C$4:$C$203,$B22,'Score Log'!$E$4:$E$203,$A22))</f>
         <v/>
       </c>
       <c r="E22" s="39" t="str">
-        <f aca="false">IF($B22="","",IFERROR(ROUND(IF($C22="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B22),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B22,'Score Log'!$D$4:$D$203,$C22)),1),"-"))</f>
+        <f aca="false">IF($B22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B22,'Score Log'!$E$4:$E$203,$A22),1),"-"))</f>
         <v/>
       </c>
       <c r="F22" s="39" t="str">
-        <f aca="false">IF($B22="","",IFERROR(ROUND(IF($C22="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B22),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B22,'Score Log'!$D$4:$D$203,$C22)),1),"-"))</f>
+        <f aca="false">IF($B22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B22,'Score Log'!$E$4:$E$203,$A22),1),"-"))</f>
         <v/>
       </c>
       <c r="G22" s="39" t="str">
-        <f aca="false">IF($B22="","",IFERROR(ROUND(IF($C22="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B22),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B22,'Score Log'!$D$4:$D$203,$C22)),1),"-"))</f>
+        <f aca="false">IF($B22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B22,'Score Log'!$E$4:$E$203,$A22),1),"-"))</f>
         <v/>
       </c>
       <c r="H22" s="39" t="str">
-        <f aca="false">IF($B22="","",IFERROR(ROUND(IF($C22="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B22),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B22,'Score Log'!$D$4:$D$203,$C22)),1),"-"))</f>
+        <f aca="false">IF($B22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B22,'Score Log'!$E$4:$E$203,$A22),1),"-"))</f>
         <v/>
       </c>
       <c r="I22" s="39" t="str">
-        <f aca="false">IF($B22="","",IFERROR(ROUND(IF($C22="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B22),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B22,'Score Log'!$D$4:$D$203,$C22)),1),"-"))</f>
+        <f aca="false">IF($B22="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B22,'Score Log'!$E$4:$E$203,$A22),1),"-"))</f>
         <v/>
       </c>
       <c r="J22" s="40" t="str">
-        <f aca="false">IF(OR($B22="",$D22=0),"",IFERROR(IF($C22="",COUNTIFS('Score Log'!$C$4:$C$203,$B22,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B22,'Score Log'!$D$4:$D$203,$C22,'Score Log'!$U$4:$U$203,"Yes"))/$D22,"-"))</f>
+        <f aca="false">IF(OR($B22="",$D22=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B22,'Score Log'!$E$4:$E$203,$A22,'Score Log'!$U$4:$U$203,"Yes")/$D22,"-"))</f>
         <v/>
       </c>
       <c r="K22" s="41" t="str">
@@ -12789,37 +13250,58 @@
         <f aca="false">IF($B22="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B22),""))</f>
         <v/>
       </c>
+      <c r="Q22" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA22" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C22="",'Score Log'!$E22=""),0,IF(COUNTIFS('Score Log'!$C$4:$C22,'Score Log'!$C22,'Score Log'!$E$4:$E22,'Score Log'!$E22)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB22" s="33" t="str">
+        <f aca="false">IF($AA22=1,SUM($AA$4:$AA22),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="37"/>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
+      <c r="A23" s="36" t="str">
+        <f aca="false">IF($Q23="","",INDEX('Score Log'!$E:$E,$Q23))</f>
+        <v/>
+      </c>
+      <c r="B23" s="36" t="str">
+        <f aca="false">IF($Q23="","",INDEX('Score Log'!$C:$C,$Q23))</f>
+        <v/>
+      </c>
+      <c r="C23" s="37" t="str">
+        <f aca="false">IF($Q23="","",IF(INDEX('Score Log'!$D:$D,$Q23)="","",INDEX('Score Log'!$D:$D,$Q23)))</f>
+        <v/>
+      </c>
       <c r="D23" s="38" t="str">
-        <f aca="false">IF($B23="","",IF($C23="",COUNTIF('Score Log'!$C$4:$C$203,$B23),COUNTIFS('Score Log'!$C$4:$C$203,$B23,'Score Log'!$D$4:$D$203,$C23)))</f>
+        <f aca="false">IF($B23="","",COUNTIFS('Score Log'!$C$4:$C$203,$B23,'Score Log'!$E$4:$E$203,$A23))</f>
         <v/>
       </c>
       <c r="E23" s="39" t="str">
-        <f aca="false">IF($B23="","",IFERROR(ROUND(IF($C23="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B23),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B23,'Score Log'!$D$4:$D$203,$C23)),1),"-"))</f>
+        <f aca="false">IF($B23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B23,'Score Log'!$E$4:$E$203,$A23),1),"-"))</f>
         <v/>
       </c>
       <c r="F23" s="39" t="str">
-        <f aca="false">IF($B23="","",IFERROR(ROUND(IF($C23="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B23),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B23,'Score Log'!$D$4:$D$203,$C23)),1),"-"))</f>
+        <f aca="false">IF($B23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B23,'Score Log'!$E$4:$E$203,$A23),1),"-"))</f>
         <v/>
       </c>
       <c r="G23" s="39" t="str">
-        <f aca="false">IF($B23="","",IFERROR(ROUND(IF($C23="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B23),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B23,'Score Log'!$D$4:$D$203,$C23)),1),"-"))</f>
+        <f aca="false">IF($B23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B23,'Score Log'!$E$4:$E$203,$A23),1),"-"))</f>
         <v/>
       </c>
       <c r="H23" s="39" t="str">
-        <f aca="false">IF($B23="","",IFERROR(ROUND(IF($C23="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B23),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B23,'Score Log'!$D$4:$D$203,$C23)),1),"-"))</f>
+        <f aca="false">IF($B23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B23,'Score Log'!$E$4:$E$203,$A23),1),"-"))</f>
         <v/>
       </c>
       <c r="I23" s="39" t="str">
-        <f aca="false">IF($B23="","",IFERROR(ROUND(IF($C23="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B23),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B23,'Score Log'!$D$4:$D$203,$C23)),1),"-"))</f>
+        <f aca="false">IF($B23="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B23,'Score Log'!$E$4:$E$203,$A23),1),"-"))</f>
         <v/>
       </c>
       <c r="J23" s="40" t="str">
-        <f aca="false">IF(OR($B23="",$D23=0),"",IFERROR(IF($C23="",COUNTIFS('Score Log'!$C$4:$C$203,$B23,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B23,'Score Log'!$D$4:$D$203,$C23,'Score Log'!$U$4:$U$203,"Yes"))/$D23,"-"))</f>
+        <f aca="false">IF(OR($B23="",$D23=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B23,'Score Log'!$E$4:$E$203,$A23,'Score Log'!$U$4:$U$203,"Yes")/$D23,"-"))</f>
         <v/>
       </c>
       <c r="K23" s="41" t="str">
@@ -12842,37 +13324,58 @@
         <f aca="false">IF($B23="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B23),""))</f>
         <v/>
       </c>
+      <c r="Q23" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA23" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C23="",'Score Log'!$E23=""),0,IF(COUNTIFS('Score Log'!$C$4:$C23,'Score Log'!$C23,'Score Log'!$E$4:$E23,'Score Log'!$E23)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB23" s="33" t="str">
+        <f aca="false">IF($AA23=1,SUM($AA$4:$AA23),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="37"/>
-      <c r="B24" s="37"/>
-      <c r="C24" s="37"/>
+      <c r="A24" s="36" t="str">
+        <f aca="false">IF($Q24="","",INDEX('Score Log'!$E:$E,$Q24))</f>
+        <v/>
+      </c>
+      <c r="B24" s="36" t="str">
+        <f aca="false">IF($Q24="","",INDEX('Score Log'!$C:$C,$Q24))</f>
+        <v/>
+      </c>
+      <c r="C24" s="37" t="str">
+        <f aca="false">IF($Q24="","",IF(INDEX('Score Log'!$D:$D,$Q24)="","",INDEX('Score Log'!$D:$D,$Q24)))</f>
+        <v/>
+      </c>
       <c r="D24" s="38" t="str">
-        <f aca="false">IF($B24="","",IF($C24="",COUNTIF('Score Log'!$C$4:$C$203,$B24),COUNTIFS('Score Log'!$C$4:$C$203,$B24,'Score Log'!$D$4:$D$203,$C24)))</f>
+        <f aca="false">IF($B24="","",COUNTIFS('Score Log'!$C$4:$C$203,$B24,'Score Log'!$E$4:$E$203,$A24))</f>
         <v/>
       </c>
       <c r="E24" s="39" t="str">
-        <f aca="false">IF($B24="","",IFERROR(ROUND(IF($C24="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B24),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B24,'Score Log'!$D$4:$D$203,$C24)),1),"-"))</f>
+        <f aca="false">IF($B24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B24,'Score Log'!$E$4:$E$203,$A24),1),"-"))</f>
         <v/>
       </c>
       <c r="F24" s="39" t="str">
-        <f aca="false">IF($B24="","",IFERROR(ROUND(IF($C24="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B24),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B24,'Score Log'!$D$4:$D$203,$C24)),1),"-"))</f>
+        <f aca="false">IF($B24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B24,'Score Log'!$E$4:$E$203,$A24),1),"-"))</f>
         <v/>
       </c>
       <c r="G24" s="39" t="str">
-        <f aca="false">IF($B24="","",IFERROR(ROUND(IF($C24="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B24),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B24,'Score Log'!$D$4:$D$203,$C24)),1),"-"))</f>
+        <f aca="false">IF($B24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B24,'Score Log'!$E$4:$E$203,$A24),1),"-"))</f>
         <v/>
       </c>
       <c r="H24" s="39" t="str">
-        <f aca="false">IF($B24="","",IFERROR(ROUND(IF($C24="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B24),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B24,'Score Log'!$D$4:$D$203,$C24)),1),"-"))</f>
+        <f aca="false">IF($B24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B24,'Score Log'!$E$4:$E$203,$A24),1),"-"))</f>
         <v/>
       </c>
       <c r="I24" s="39" t="str">
-        <f aca="false">IF($B24="","",IFERROR(ROUND(IF($C24="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B24),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B24,'Score Log'!$D$4:$D$203,$C24)),1),"-"))</f>
+        <f aca="false">IF($B24="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B24,'Score Log'!$E$4:$E$203,$A24),1),"-"))</f>
         <v/>
       </c>
       <c r="J24" s="40" t="str">
-        <f aca="false">IF(OR($B24="",$D24=0),"",IFERROR(IF($C24="",COUNTIFS('Score Log'!$C$4:$C$203,$B24,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B24,'Score Log'!$D$4:$D$203,$C24,'Score Log'!$U$4:$U$203,"Yes"))/$D24,"-"))</f>
+        <f aca="false">IF(OR($B24="",$D24=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B24,'Score Log'!$E$4:$E$203,$A24,'Score Log'!$U$4:$U$203,"Yes")/$D24,"-"))</f>
         <v/>
       </c>
       <c r="K24" s="41" t="str">
@@ -12895,37 +13398,58 @@
         <f aca="false">IF($B24="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B24),""))</f>
         <v/>
       </c>
+      <c r="Q24" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA24" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C24="",'Score Log'!$E24=""),0,IF(COUNTIFS('Score Log'!$C$4:$C24,'Score Log'!$C24,'Score Log'!$E$4:$E24,'Score Log'!$E24)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB24" s="33" t="str">
+        <f aca="false">IF($AA24=1,SUM($AA$4:$AA24),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="37"/>
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
+      <c r="A25" s="36" t="str">
+        <f aca="false">IF($Q25="","",INDEX('Score Log'!$E:$E,$Q25))</f>
+        <v/>
+      </c>
+      <c r="B25" s="36" t="str">
+        <f aca="false">IF($Q25="","",INDEX('Score Log'!$C:$C,$Q25))</f>
+        <v/>
+      </c>
+      <c r="C25" s="37" t="str">
+        <f aca="false">IF($Q25="","",IF(INDEX('Score Log'!$D:$D,$Q25)="","",INDEX('Score Log'!$D:$D,$Q25)))</f>
+        <v/>
+      </c>
       <c r="D25" s="38" t="str">
-        <f aca="false">IF($B25="","",IF($C25="",COUNTIF('Score Log'!$C$4:$C$203,$B25),COUNTIFS('Score Log'!$C$4:$C$203,$B25,'Score Log'!$D$4:$D$203,$C25)))</f>
+        <f aca="false">IF($B25="","",COUNTIFS('Score Log'!$C$4:$C$203,$B25,'Score Log'!$E$4:$E$203,$A25))</f>
         <v/>
       </c>
       <c r="E25" s="39" t="str">
-        <f aca="false">IF($B25="","",IFERROR(ROUND(IF($C25="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B25),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B25,'Score Log'!$D$4:$D$203,$C25)),1),"-"))</f>
+        <f aca="false">IF($B25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B25,'Score Log'!$E$4:$E$203,$A25),1),"-"))</f>
         <v/>
       </c>
       <c r="F25" s="39" t="str">
-        <f aca="false">IF($B25="","",IFERROR(ROUND(IF($C25="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B25),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B25,'Score Log'!$D$4:$D$203,$C25)),1),"-"))</f>
+        <f aca="false">IF($B25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B25,'Score Log'!$E$4:$E$203,$A25),1),"-"))</f>
         <v/>
       </c>
       <c r="G25" s="39" t="str">
-        <f aca="false">IF($B25="","",IFERROR(ROUND(IF($C25="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B25),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B25,'Score Log'!$D$4:$D$203,$C25)),1),"-"))</f>
+        <f aca="false">IF($B25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B25,'Score Log'!$E$4:$E$203,$A25),1),"-"))</f>
         <v/>
       </c>
       <c r="H25" s="39" t="str">
-        <f aca="false">IF($B25="","",IFERROR(ROUND(IF($C25="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B25),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B25,'Score Log'!$D$4:$D$203,$C25)),1),"-"))</f>
+        <f aca="false">IF($B25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B25,'Score Log'!$E$4:$E$203,$A25),1),"-"))</f>
         <v/>
       </c>
       <c r="I25" s="39" t="str">
-        <f aca="false">IF($B25="","",IFERROR(ROUND(IF($C25="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B25),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B25,'Score Log'!$D$4:$D$203,$C25)),1),"-"))</f>
+        <f aca="false">IF($B25="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B25,'Score Log'!$E$4:$E$203,$A25),1),"-"))</f>
         <v/>
       </c>
       <c r="J25" s="40" t="str">
-        <f aca="false">IF(OR($B25="",$D25=0),"",IFERROR(IF($C25="",COUNTIFS('Score Log'!$C$4:$C$203,$B25,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B25,'Score Log'!$D$4:$D$203,$C25,'Score Log'!$U$4:$U$203,"Yes"))/$D25,"-"))</f>
+        <f aca="false">IF(OR($B25="",$D25=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B25,'Score Log'!$E$4:$E$203,$A25,'Score Log'!$U$4:$U$203,"Yes")/$D25,"-"))</f>
         <v/>
       </c>
       <c r="K25" s="41" t="str">
@@ -12948,37 +13472,58 @@
         <f aca="false">IF($B25="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B25),""))</f>
         <v/>
       </c>
+      <c r="Q25" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA25" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C25="",'Score Log'!$E25=""),0,IF(COUNTIFS('Score Log'!$C$4:$C25,'Score Log'!$C25,'Score Log'!$E$4:$E25,'Score Log'!$E25)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB25" s="33" t="str">
+        <f aca="false">IF($AA25=1,SUM($AA$4:$AA25),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="37"/>
-      <c r="B26" s="37"/>
-      <c r="C26" s="37"/>
+      <c r="A26" s="36" t="str">
+        <f aca="false">IF($Q26="","",INDEX('Score Log'!$E:$E,$Q26))</f>
+        <v/>
+      </c>
+      <c r="B26" s="36" t="str">
+        <f aca="false">IF($Q26="","",INDEX('Score Log'!$C:$C,$Q26))</f>
+        <v/>
+      </c>
+      <c r="C26" s="37" t="str">
+        <f aca="false">IF($Q26="","",IF(INDEX('Score Log'!$D:$D,$Q26)="","",INDEX('Score Log'!$D:$D,$Q26)))</f>
+        <v/>
+      </c>
       <c r="D26" s="38" t="str">
-        <f aca="false">IF($B26="","",IF($C26="",COUNTIF('Score Log'!$C$4:$C$203,$B26),COUNTIFS('Score Log'!$C$4:$C$203,$B26,'Score Log'!$D$4:$D$203,$C26)))</f>
+        <f aca="false">IF($B26="","",COUNTIFS('Score Log'!$C$4:$C$203,$B26,'Score Log'!$E$4:$E$203,$A26))</f>
         <v/>
       </c>
       <c r="E26" s="39" t="str">
-        <f aca="false">IF($B26="","",IFERROR(ROUND(IF($C26="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B26),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B26,'Score Log'!$D$4:$D$203,$C26)),1),"-"))</f>
+        <f aca="false">IF($B26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B26,'Score Log'!$E$4:$E$203,$A26),1),"-"))</f>
         <v/>
       </c>
       <c r="F26" s="39" t="str">
-        <f aca="false">IF($B26="","",IFERROR(ROUND(IF($C26="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B26),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B26,'Score Log'!$D$4:$D$203,$C26)),1),"-"))</f>
+        <f aca="false">IF($B26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B26,'Score Log'!$E$4:$E$203,$A26),1),"-"))</f>
         <v/>
       </c>
       <c r="G26" s="39" t="str">
-        <f aca="false">IF($B26="","",IFERROR(ROUND(IF($C26="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B26),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B26,'Score Log'!$D$4:$D$203,$C26)),1),"-"))</f>
+        <f aca="false">IF($B26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B26,'Score Log'!$E$4:$E$203,$A26),1),"-"))</f>
         <v/>
       </c>
       <c r="H26" s="39" t="str">
-        <f aca="false">IF($B26="","",IFERROR(ROUND(IF($C26="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B26),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B26,'Score Log'!$D$4:$D$203,$C26)),1),"-"))</f>
+        <f aca="false">IF($B26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B26,'Score Log'!$E$4:$E$203,$A26),1),"-"))</f>
         <v/>
       </c>
       <c r="I26" s="39" t="str">
-        <f aca="false">IF($B26="","",IFERROR(ROUND(IF($C26="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B26),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B26,'Score Log'!$D$4:$D$203,$C26)),1),"-"))</f>
+        <f aca="false">IF($B26="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B26,'Score Log'!$E$4:$E$203,$A26),1),"-"))</f>
         <v/>
       </c>
       <c r="J26" s="40" t="str">
-        <f aca="false">IF(OR($B26="",$D26=0),"",IFERROR(IF($C26="",COUNTIFS('Score Log'!$C$4:$C$203,$B26,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B26,'Score Log'!$D$4:$D$203,$C26,'Score Log'!$U$4:$U$203,"Yes"))/$D26,"-"))</f>
+        <f aca="false">IF(OR($B26="",$D26=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B26,'Score Log'!$E$4:$E$203,$A26,'Score Log'!$U$4:$U$203,"Yes")/$D26,"-"))</f>
         <v/>
       </c>
       <c r="K26" s="41" t="str">
@@ -13001,37 +13546,58 @@
         <f aca="false">IF($B26="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B26),""))</f>
         <v/>
       </c>
+      <c r="Q26" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA26" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C26="",'Score Log'!$E26=""),0,IF(COUNTIFS('Score Log'!$C$4:$C26,'Score Log'!$C26,'Score Log'!$E$4:$E26,'Score Log'!$E26)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB26" s="33" t="str">
+        <f aca="false">IF($AA26=1,SUM($AA$4:$AA26),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="37"/>
-      <c r="B27" s="37"/>
-      <c r="C27" s="37"/>
+      <c r="A27" s="36" t="str">
+        <f aca="false">IF($Q27="","",INDEX('Score Log'!$E:$E,$Q27))</f>
+        <v/>
+      </c>
+      <c r="B27" s="36" t="str">
+        <f aca="false">IF($Q27="","",INDEX('Score Log'!$C:$C,$Q27))</f>
+        <v/>
+      </c>
+      <c r="C27" s="37" t="str">
+        <f aca="false">IF($Q27="","",IF(INDEX('Score Log'!$D:$D,$Q27)="","",INDEX('Score Log'!$D:$D,$Q27)))</f>
+        <v/>
+      </c>
       <c r="D27" s="38" t="str">
-        <f aca="false">IF($B27="","",IF($C27="",COUNTIF('Score Log'!$C$4:$C$203,$B27),COUNTIFS('Score Log'!$C$4:$C$203,$B27,'Score Log'!$D$4:$D$203,$C27)))</f>
+        <f aca="false">IF($B27="","",COUNTIFS('Score Log'!$C$4:$C$203,$B27,'Score Log'!$E$4:$E$203,$A27))</f>
         <v/>
       </c>
       <c r="E27" s="39" t="str">
-        <f aca="false">IF($B27="","",IFERROR(ROUND(IF($C27="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B27),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B27,'Score Log'!$D$4:$D$203,$C27)),1),"-"))</f>
+        <f aca="false">IF($B27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B27,'Score Log'!$E$4:$E$203,$A27),1),"-"))</f>
         <v/>
       </c>
       <c r="F27" s="39" t="str">
-        <f aca="false">IF($B27="","",IFERROR(ROUND(IF($C27="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B27),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B27,'Score Log'!$D$4:$D$203,$C27)),1),"-"))</f>
+        <f aca="false">IF($B27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B27,'Score Log'!$E$4:$E$203,$A27),1),"-"))</f>
         <v/>
       </c>
       <c r="G27" s="39" t="str">
-        <f aca="false">IF($B27="","",IFERROR(ROUND(IF($C27="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B27),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B27,'Score Log'!$D$4:$D$203,$C27)),1),"-"))</f>
+        <f aca="false">IF($B27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B27,'Score Log'!$E$4:$E$203,$A27),1),"-"))</f>
         <v/>
       </c>
       <c r="H27" s="39" t="str">
-        <f aca="false">IF($B27="","",IFERROR(ROUND(IF($C27="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B27),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B27,'Score Log'!$D$4:$D$203,$C27)),1),"-"))</f>
+        <f aca="false">IF($B27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B27,'Score Log'!$E$4:$E$203,$A27),1),"-"))</f>
         <v/>
       </c>
       <c r="I27" s="39" t="str">
-        <f aca="false">IF($B27="","",IFERROR(ROUND(IF($C27="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B27),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B27,'Score Log'!$D$4:$D$203,$C27)),1),"-"))</f>
+        <f aca="false">IF($B27="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B27,'Score Log'!$E$4:$E$203,$A27),1),"-"))</f>
         <v/>
       </c>
       <c r="J27" s="40" t="str">
-        <f aca="false">IF(OR($B27="",$D27=0),"",IFERROR(IF($C27="",COUNTIFS('Score Log'!$C$4:$C$203,$B27,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B27,'Score Log'!$D$4:$D$203,$C27,'Score Log'!$U$4:$U$203,"Yes"))/$D27,"-"))</f>
+        <f aca="false">IF(OR($B27="",$D27=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B27,'Score Log'!$E$4:$E$203,$A27,'Score Log'!$U$4:$U$203,"Yes")/$D27,"-"))</f>
         <v/>
       </c>
       <c r="K27" s="41" t="str">
@@ -13054,37 +13620,58 @@
         <f aca="false">IF($B27="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B27),""))</f>
         <v/>
       </c>
+      <c r="Q27" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA27" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C27="",'Score Log'!$E27=""),0,IF(COUNTIFS('Score Log'!$C$4:$C27,'Score Log'!$C27,'Score Log'!$E$4:$E27,'Score Log'!$E27)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB27" s="33" t="str">
+        <f aca="false">IF($AA27=1,SUM($AA$4:$AA27),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="37"/>
-      <c r="B28" s="37"/>
-      <c r="C28" s="37"/>
+      <c r="A28" s="36" t="str">
+        <f aca="false">IF($Q28="","",INDEX('Score Log'!$E:$E,$Q28))</f>
+        <v/>
+      </c>
+      <c r="B28" s="36" t="str">
+        <f aca="false">IF($Q28="","",INDEX('Score Log'!$C:$C,$Q28))</f>
+        <v/>
+      </c>
+      <c r="C28" s="37" t="str">
+        <f aca="false">IF($Q28="","",IF(INDEX('Score Log'!$D:$D,$Q28)="","",INDEX('Score Log'!$D:$D,$Q28)))</f>
+        <v/>
+      </c>
       <c r="D28" s="38" t="str">
-        <f aca="false">IF($B28="","",IF($C28="",COUNTIF('Score Log'!$C$4:$C$203,$B28),COUNTIFS('Score Log'!$C$4:$C$203,$B28,'Score Log'!$D$4:$D$203,$C28)))</f>
+        <f aca="false">IF($B28="","",COUNTIFS('Score Log'!$C$4:$C$203,$B28,'Score Log'!$E$4:$E$203,$A28))</f>
         <v/>
       </c>
       <c r="E28" s="39" t="str">
-        <f aca="false">IF($B28="","",IFERROR(ROUND(IF($C28="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B28),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B28,'Score Log'!$D$4:$D$203,$C28)),1),"-"))</f>
+        <f aca="false">IF($B28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B28,'Score Log'!$E$4:$E$203,$A28),1),"-"))</f>
         <v/>
       </c>
       <c r="F28" s="39" t="str">
-        <f aca="false">IF($B28="","",IFERROR(ROUND(IF($C28="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B28),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B28,'Score Log'!$D$4:$D$203,$C28)),1),"-"))</f>
+        <f aca="false">IF($B28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B28,'Score Log'!$E$4:$E$203,$A28),1),"-"))</f>
         <v/>
       </c>
       <c r="G28" s="39" t="str">
-        <f aca="false">IF($B28="","",IFERROR(ROUND(IF($C28="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B28),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B28,'Score Log'!$D$4:$D$203,$C28)),1),"-"))</f>
+        <f aca="false">IF($B28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B28,'Score Log'!$E$4:$E$203,$A28),1),"-"))</f>
         <v/>
       </c>
       <c r="H28" s="39" t="str">
-        <f aca="false">IF($B28="","",IFERROR(ROUND(IF($C28="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B28),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B28,'Score Log'!$D$4:$D$203,$C28)),1),"-"))</f>
+        <f aca="false">IF($B28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B28,'Score Log'!$E$4:$E$203,$A28),1),"-"))</f>
         <v/>
       </c>
       <c r="I28" s="39" t="str">
-        <f aca="false">IF($B28="","",IFERROR(ROUND(IF($C28="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B28),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B28,'Score Log'!$D$4:$D$203,$C28)),1),"-"))</f>
+        <f aca="false">IF($B28="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B28,'Score Log'!$E$4:$E$203,$A28),1),"-"))</f>
         <v/>
       </c>
       <c r="J28" s="40" t="str">
-        <f aca="false">IF(OR($B28="",$D28=0),"",IFERROR(IF($C28="",COUNTIFS('Score Log'!$C$4:$C$203,$B28,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B28,'Score Log'!$D$4:$D$203,$C28,'Score Log'!$U$4:$U$203,"Yes"))/$D28,"-"))</f>
+        <f aca="false">IF(OR($B28="",$D28=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B28,'Score Log'!$E$4:$E$203,$A28,'Score Log'!$U$4:$U$203,"Yes")/$D28,"-"))</f>
         <v/>
       </c>
       <c r="K28" s="41" t="str">
@@ -13107,37 +13694,58 @@
         <f aca="false">IF($B28="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B28),""))</f>
         <v/>
       </c>
+      <c r="Q28" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA28" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C28="",'Score Log'!$E28=""),0,IF(COUNTIFS('Score Log'!$C$4:$C28,'Score Log'!$C28,'Score Log'!$E$4:$E28,'Score Log'!$E28)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB28" s="33" t="str">
+        <f aca="false">IF($AA28=1,SUM($AA$4:$AA28),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="37"/>
-      <c r="B29" s="37"/>
-      <c r="C29" s="37"/>
+      <c r="A29" s="36" t="str">
+        <f aca="false">IF($Q29="","",INDEX('Score Log'!$E:$E,$Q29))</f>
+        <v/>
+      </c>
+      <c r="B29" s="36" t="str">
+        <f aca="false">IF($Q29="","",INDEX('Score Log'!$C:$C,$Q29))</f>
+        <v/>
+      </c>
+      <c r="C29" s="37" t="str">
+        <f aca="false">IF($Q29="","",IF(INDEX('Score Log'!$D:$D,$Q29)="","",INDEX('Score Log'!$D:$D,$Q29)))</f>
+        <v/>
+      </c>
       <c r="D29" s="38" t="str">
-        <f aca="false">IF($B29="","",IF($C29="",COUNTIF('Score Log'!$C$4:$C$203,$B29),COUNTIFS('Score Log'!$C$4:$C$203,$B29,'Score Log'!$D$4:$D$203,$C29)))</f>
+        <f aca="false">IF($B29="","",COUNTIFS('Score Log'!$C$4:$C$203,$B29,'Score Log'!$E$4:$E$203,$A29))</f>
         <v/>
       </c>
       <c r="E29" s="39" t="str">
-        <f aca="false">IF($B29="","",IFERROR(ROUND(IF($C29="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B29),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B29,'Score Log'!$D$4:$D$203,$C29)),1),"-"))</f>
+        <f aca="false">IF($B29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B29,'Score Log'!$E$4:$E$203,$A29),1),"-"))</f>
         <v/>
       </c>
       <c r="F29" s="39" t="str">
-        <f aca="false">IF($B29="","",IFERROR(ROUND(IF($C29="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B29),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B29,'Score Log'!$D$4:$D$203,$C29)),1),"-"))</f>
+        <f aca="false">IF($B29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B29,'Score Log'!$E$4:$E$203,$A29),1),"-"))</f>
         <v/>
       </c>
       <c r="G29" s="39" t="str">
-        <f aca="false">IF($B29="","",IFERROR(ROUND(IF($C29="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B29),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B29,'Score Log'!$D$4:$D$203,$C29)),1),"-"))</f>
+        <f aca="false">IF($B29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B29,'Score Log'!$E$4:$E$203,$A29),1),"-"))</f>
         <v/>
       </c>
       <c r="H29" s="39" t="str">
-        <f aca="false">IF($B29="","",IFERROR(ROUND(IF($C29="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B29),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B29,'Score Log'!$D$4:$D$203,$C29)),1),"-"))</f>
+        <f aca="false">IF($B29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B29,'Score Log'!$E$4:$E$203,$A29),1),"-"))</f>
         <v/>
       </c>
       <c r="I29" s="39" t="str">
-        <f aca="false">IF($B29="","",IFERROR(ROUND(IF($C29="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B29),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B29,'Score Log'!$D$4:$D$203,$C29)),1),"-"))</f>
+        <f aca="false">IF($B29="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B29,'Score Log'!$E$4:$E$203,$A29),1),"-"))</f>
         <v/>
       </c>
       <c r="J29" s="40" t="str">
-        <f aca="false">IF(OR($B29="",$D29=0),"",IFERROR(IF($C29="",COUNTIFS('Score Log'!$C$4:$C$203,$B29,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B29,'Score Log'!$D$4:$D$203,$C29,'Score Log'!$U$4:$U$203,"Yes"))/$D29,"-"))</f>
+        <f aca="false">IF(OR($B29="",$D29=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B29,'Score Log'!$E$4:$E$203,$A29,'Score Log'!$U$4:$U$203,"Yes")/$D29,"-"))</f>
         <v/>
       </c>
       <c r="K29" s="41" t="str">
@@ -13160,37 +13768,58 @@
         <f aca="false">IF($B29="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B29),""))</f>
         <v/>
       </c>
+      <c r="Q29" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA29" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C29="",'Score Log'!$E29=""),0,IF(COUNTIFS('Score Log'!$C$4:$C29,'Score Log'!$C29,'Score Log'!$E$4:$E29,'Score Log'!$E29)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB29" s="33" t="str">
+        <f aca="false">IF($AA29=1,SUM($AA$4:$AA29),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="37"/>
-      <c r="B30" s="37"/>
-      <c r="C30" s="37"/>
+      <c r="A30" s="36" t="str">
+        <f aca="false">IF($Q30="","",INDEX('Score Log'!$E:$E,$Q30))</f>
+        <v/>
+      </c>
+      <c r="B30" s="36" t="str">
+        <f aca="false">IF($Q30="","",INDEX('Score Log'!$C:$C,$Q30))</f>
+        <v/>
+      </c>
+      <c r="C30" s="37" t="str">
+        <f aca="false">IF($Q30="","",IF(INDEX('Score Log'!$D:$D,$Q30)="","",INDEX('Score Log'!$D:$D,$Q30)))</f>
+        <v/>
+      </c>
       <c r="D30" s="38" t="str">
-        <f aca="false">IF($B30="","",IF($C30="",COUNTIF('Score Log'!$C$4:$C$203,$B30),COUNTIFS('Score Log'!$C$4:$C$203,$B30,'Score Log'!$D$4:$D$203,$C30)))</f>
+        <f aca="false">IF($B30="","",COUNTIFS('Score Log'!$C$4:$C$203,$B30,'Score Log'!$E$4:$E$203,$A30))</f>
         <v/>
       </c>
       <c r="E30" s="39" t="str">
-        <f aca="false">IF($B30="","",IFERROR(ROUND(IF($C30="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B30),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B30,'Score Log'!$D$4:$D$203,$C30)),1),"-"))</f>
+        <f aca="false">IF($B30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B30,'Score Log'!$E$4:$E$203,$A30),1),"-"))</f>
         <v/>
       </c>
       <c r="F30" s="39" t="str">
-        <f aca="false">IF($B30="","",IFERROR(ROUND(IF($C30="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B30),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B30,'Score Log'!$D$4:$D$203,$C30)),1),"-"))</f>
+        <f aca="false">IF($B30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B30,'Score Log'!$E$4:$E$203,$A30),1),"-"))</f>
         <v/>
       </c>
       <c r="G30" s="39" t="str">
-        <f aca="false">IF($B30="","",IFERROR(ROUND(IF($C30="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B30),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B30,'Score Log'!$D$4:$D$203,$C30)),1),"-"))</f>
+        <f aca="false">IF($B30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B30,'Score Log'!$E$4:$E$203,$A30),1),"-"))</f>
         <v/>
       </c>
       <c r="H30" s="39" t="str">
-        <f aca="false">IF($B30="","",IFERROR(ROUND(IF($C30="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B30),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B30,'Score Log'!$D$4:$D$203,$C30)),1),"-"))</f>
+        <f aca="false">IF($B30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B30,'Score Log'!$E$4:$E$203,$A30),1),"-"))</f>
         <v/>
       </c>
       <c r="I30" s="39" t="str">
-        <f aca="false">IF($B30="","",IFERROR(ROUND(IF($C30="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B30),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B30,'Score Log'!$D$4:$D$203,$C30)),1),"-"))</f>
+        <f aca="false">IF($B30="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B30,'Score Log'!$E$4:$E$203,$A30),1),"-"))</f>
         <v/>
       </c>
       <c r="J30" s="40" t="str">
-        <f aca="false">IF(OR($B30="",$D30=0),"",IFERROR(IF($C30="",COUNTIFS('Score Log'!$C$4:$C$203,$B30,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B30,'Score Log'!$D$4:$D$203,$C30,'Score Log'!$U$4:$U$203,"Yes"))/$D30,"-"))</f>
+        <f aca="false">IF(OR($B30="",$D30=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B30,'Score Log'!$E$4:$E$203,$A30,'Score Log'!$U$4:$U$203,"Yes")/$D30,"-"))</f>
         <v/>
       </c>
       <c r="K30" s="41" t="str">
@@ -13213,37 +13842,58 @@
         <f aca="false">IF($B30="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B30),""))</f>
         <v/>
       </c>
+      <c r="Q30" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA30" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C30="",'Score Log'!$E30=""),0,IF(COUNTIFS('Score Log'!$C$4:$C30,'Score Log'!$C30,'Score Log'!$E$4:$E30,'Score Log'!$E30)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB30" s="33" t="str">
+        <f aca="false">IF($AA30=1,SUM($AA$4:$AA30),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="37"/>
-      <c r="B31" s="37"/>
-      <c r="C31" s="37"/>
+      <c r="A31" s="36" t="str">
+        <f aca="false">IF($Q31="","",INDEX('Score Log'!$E:$E,$Q31))</f>
+        <v/>
+      </c>
+      <c r="B31" s="36" t="str">
+        <f aca="false">IF($Q31="","",INDEX('Score Log'!$C:$C,$Q31))</f>
+        <v/>
+      </c>
+      <c r="C31" s="37" t="str">
+        <f aca="false">IF($Q31="","",IF(INDEX('Score Log'!$D:$D,$Q31)="","",INDEX('Score Log'!$D:$D,$Q31)))</f>
+        <v/>
+      </c>
       <c r="D31" s="38" t="str">
-        <f aca="false">IF($B31="","",IF($C31="",COUNTIF('Score Log'!$C$4:$C$203,$B31),COUNTIFS('Score Log'!$C$4:$C$203,$B31,'Score Log'!$D$4:$D$203,$C31)))</f>
+        <f aca="false">IF($B31="","",COUNTIFS('Score Log'!$C$4:$C$203,$B31,'Score Log'!$E$4:$E$203,$A31))</f>
         <v/>
       </c>
       <c r="E31" s="39" t="str">
-        <f aca="false">IF($B31="","",IFERROR(ROUND(IF($C31="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B31),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B31,'Score Log'!$D$4:$D$203,$C31)),1),"-"))</f>
+        <f aca="false">IF($B31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B31,'Score Log'!$E$4:$E$203,$A31),1),"-"))</f>
         <v/>
       </c>
       <c r="F31" s="39" t="str">
-        <f aca="false">IF($B31="","",IFERROR(ROUND(IF($C31="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B31),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B31,'Score Log'!$D$4:$D$203,$C31)),1),"-"))</f>
+        <f aca="false">IF($B31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B31,'Score Log'!$E$4:$E$203,$A31),1),"-"))</f>
         <v/>
       </c>
       <c r="G31" s="39" t="str">
-        <f aca="false">IF($B31="","",IFERROR(ROUND(IF($C31="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B31),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B31,'Score Log'!$D$4:$D$203,$C31)),1),"-"))</f>
+        <f aca="false">IF($B31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B31,'Score Log'!$E$4:$E$203,$A31),1),"-"))</f>
         <v/>
       </c>
       <c r="H31" s="39" t="str">
-        <f aca="false">IF($B31="","",IFERROR(ROUND(IF($C31="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B31),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B31,'Score Log'!$D$4:$D$203,$C31)),1),"-"))</f>
+        <f aca="false">IF($B31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B31,'Score Log'!$E$4:$E$203,$A31),1),"-"))</f>
         <v/>
       </c>
       <c r="I31" s="39" t="str">
-        <f aca="false">IF($B31="","",IFERROR(ROUND(IF($C31="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B31),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B31,'Score Log'!$D$4:$D$203,$C31)),1),"-"))</f>
+        <f aca="false">IF($B31="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B31,'Score Log'!$E$4:$E$203,$A31),1),"-"))</f>
         <v/>
       </c>
       <c r="J31" s="40" t="str">
-        <f aca="false">IF(OR($B31="",$D31=0),"",IFERROR(IF($C31="",COUNTIFS('Score Log'!$C$4:$C$203,$B31,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B31,'Score Log'!$D$4:$D$203,$C31,'Score Log'!$U$4:$U$203,"Yes"))/$D31,"-"))</f>
+        <f aca="false">IF(OR($B31="",$D31=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B31,'Score Log'!$E$4:$E$203,$A31,'Score Log'!$U$4:$U$203,"Yes")/$D31,"-"))</f>
         <v/>
       </c>
       <c r="K31" s="41" t="str">
@@ -13266,37 +13916,58 @@
         <f aca="false">IF($B31="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B31),""))</f>
         <v/>
       </c>
+      <c r="Q31" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA31" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C31="",'Score Log'!$E31=""),0,IF(COUNTIFS('Score Log'!$C$4:$C31,'Score Log'!$C31,'Score Log'!$E$4:$E31,'Score Log'!$E31)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB31" s="33" t="str">
+        <f aca="false">IF($AA31=1,SUM($AA$4:$AA31),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="37"/>
-      <c r="B32" s="37"/>
-      <c r="C32" s="37"/>
+      <c r="A32" s="36" t="str">
+        <f aca="false">IF($Q32="","",INDEX('Score Log'!$E:$E,$Q32))</f>
+        <v/>
+      </c>
+      <c r="B32" s="36" t="str">
+        <f aca="false">IF($Q32="","",INDEX('Score Log'!$C:$C,$Q32))</f>
+        <v/>
+      </c>
+      <c r="C32" s="37" t="str">
+        <f aca="false">IF($Q32="","",IF(INDEX('Score Log'!$D:$D,$Q32)="","",INDEX('Score Log'!$D:$D,$Q32)))</f>
+        <v/>
+      </c>
       <c r="D32" s="38" t="str">
-        <f aca="false">IF($B32="","",IF($C32="",COUNTIF('Score Log'!$C$4:$C$203,$B32),COUNTIFS('Score Log'!$C$4:$C$203,$B32,'Score Log'!$D$4:$D$203,$C32)))</f>
+        <f aca="false">IF($B32="","",COUNTIFS('Score Log'!$C$4:$C$203,$B32,'Score Log'!$E$4:$E$203,$A32))</f>
         <v/>
       </c>
       <c r="E32" s="39" t="str">
-        <f aca="false">IF($B32="","",IFERROR(ROUND(IF($C32="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B32),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B32,'Score Log'!$D$4:$D$203,$C32)),1),"-"))</f>
+        <f aca="false">IF($B32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B32,'Score Log'!$E$4:$E$203,$A32),1),"-"))</f>
         <v/>
       </c>
       <c r="F32" s="39" t="str">
-        <f aca="false">IF($B32="","",IFERROR(ROUND(IF($C32="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B32),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B32,'Score Log'!$D$4:$D$203,$C32)),1),"-"))</f>
+        <f aca="false">IF($B32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B32,'Score Log'!$E$4:$E$203,$A32),1),"-"))</f>
         <v/>
       </c>
       <c r="G32" s="39" t="str">
-        <f aca="false">IF($B32="","",IFERROR(ROUND(IF($C32="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B32),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B32,'Score Log'!$D$4:$D$203,$C32)),1),"-"))</f>
+        <f aca="false">IF($B32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B32,'Score Log'!$E$4:$E$203,$A32),1),"-"))</f>
         <v/>
       </c>
       <c r="H32" s="39" t="str">
-        <f aca="false">IF($B32="","",IFERROR(ROUND(IF($C32="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B32),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B32,'Score Log'!$D$4:$D$203,$C32)),1),"-"))</f>
+        <f aca="false">IF($B32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B32,'Score Log'!$E$4:$E$203,$A32),1),"-"))</f>
         <v/>
       </c>
       <c r="I32" s="39" t="str">
-        <f aca="false">IF($B32="","",IFERROR(ROUND(IF($C32="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B32),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B32,'Score Log'!$D$4:$D$203,$C32)),1),"-"))</f>
+        <f aca="false">IF($B32="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B32,'Score Log'!$E$4:$E$203,$A32),1),"-"))</f>
         <v/>
       </c>
       <c r="J32" s="40" t="str">
-        <f aca="false">IF(OR($B32="",$D32=0),"",IFERROR(IF($C32="",COUNTIFS('Score Log'!$C$4:$C$203,$B32,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B32,'Score Log'!$D$4:$D$203,$C32,'Score Log'!$U$4:$U$203,"Yes"))/$D32,"-"))</f>
+        <f aca="false">IF(OR($B32="",$D32=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B32,'Score Log'!$E$4:$E$203,$A32,'Score Log'!$U$4:$U$203,"Yes")/$D32,"-"))</f>
         <v/>
       </c>
       <c r="K32" s="41" t="str">
@@ -13319,37 +13990,58 @@
         <f aca="false">IF($B32="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B32),""))</f>
         <v/>
       </c>
+      <c r="Q32" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA32" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C32="",'Score Log'!$E32=""),0,IF(COUNTIFS('Score Log'!$C$4:$C32,'Score Log'!$C32,'Score Log'!$E$4:$E32,'Score Log'!$E32)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB32" s="33" t="str">
+        <f aca="false">IF($AA32=1,SUM($AA$4:$AA32),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="37"/>
-      <c r="B33" s="37"/>
-      <c r="C33" s="37"/>
+      <c r="A33" s="36" t="str">
+        <f aca="false">IF($Q33="","",INDEX('Score Log'!$E:$E,$Q33))</f>
+        <v/>
+      </c>
+      <c r="B33" s="36" t="str">
+        <f aca="false">IF($Q33="","",INDEX('Score Log'!$C:$C,$Q33))</f>
+        <v/>
+      </c>
+      <c r="C33" s="37" t="str">
+        <f aca="false">IF($Q33="","",IF(INDEX('Score Log'!$D:$D,$Q33)="","",INDEX('Score Log'!$D:$D,$Q33)))</f>
+        <v/>
+      </c>
       <c r="D33" s="38" t="str">
-        <f aca="false">IF($B33="","",IF($C33="",COUNTIF('Score Log'!$C$4:$C$203,$B33),COUNTIFS('Score Log'!$C$4:$C$203,$B33,'Score Log'!$D$4:$D$203,$C33)))</f>
+        <f aca="false">IF($B33="","",COUNTIFS('Score Log'!$C$4:$C$203,$B33,'Score Log'!$E$4:$E$203,$A33))</f>
         <v/>
       </c>
       <c r="E33" s="39" t="str">
-        <f aca="false">IF($B33="","",IFERROR(ROUND(IF($C33="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B33),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B33,'Score Log'!$D$4:$D$203,$C33)),1),"-"))</f>
+        <f aca="false">IF($B33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B33,'Score Log'!$E$4:$E$203,$A33),1),"-"))</f>
         <v/>
       </c>
       <c r="F33" s="39" t="str">
-        <f aca="false">IF($B33="","",IFERROR(ROUND(IF($C33="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B33),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B33,'Score Log'!$D$4:$D$203,$C33)),1),"-"))</f>
+        <f aca="false">IF($B33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B33,'Score Log'!$E$4:$E$203,$A33),1),"-"))</f>
         <v/>
       </c>
       <c r="G33" s="39" t="str">
-        <f aca="false">IF($B33="","",IFERROR(ROUND(IF($C33="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B33),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B33,'Score Log'!$D$4:$D$203,$C33)),1),"-"))</f>
+        <f aca="false">IF($B33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B33,'Score Log'!$E$4:$E$203,$A33),1),"-"))</f>
         <v/>
       </c>
       <c r="H33" s="39" t="str">
-        <f aca="false">IF($B33="","",IFERROR(ROUND(IF($C33="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B33),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B33,'Score Log'!$D$4:$D$203,$C33)),1),"-"))</f>
+        <f aca="false">IF($B33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B33,'Score Log'!$E$4:$E$203,$A33),1),"-"))</f>
         <v/>
       </c>
       <c r="I33" s="39" t="str">
-        <f aca="false">IF($B33="","",IFERROR(ROUND(IF($C33="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B33),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B33,'Score Log'!$D$4:$D$203,$C33)),1),"-"))</f>
+        <f aca="false">IF($B33="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B33,'Score Log'!$E$4:$E$203,$A33),1),"-"))</f>
         <v/>
       </c>
       <c r="J33" s="40" t="str">
-        <f aca="false">IF(OR($B33="",$D33=0),"",IFERROR(IF($C33="",COUNTIFS('Score Log'!$C$4:$C$203,$B33,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B33,'Score Log'!$D$4:$D$203,$C33,'Score Log'!$U$4:$U$203,"Yes"))/$D33,"-"))</f>
+        <f aca="false">IF(OR($B33="",$D33=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B33,'Score Log'!$E$4:$E$203,$A33,'Score Log'!$U$4:$U$203,"Yes")/$D33,"-"))</f>
         <v/>
       </c>
       <c r="K33" s="41" t="str">
@@ -13372,37 +14064,58 @@
         <f aca="false">IF($B33="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B33),""))</f>
         <v/>
       </c>
+      <c r="Q33" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA33" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C33="",'Score Log'!$E33=""),0,IF(COUNTIFS('Score Log'!$C$4:$C33,'Score Log'!$C33,'Score Log'!$E$4:$E33,'Score Log'!$E33)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB33" s="33" t="str">
+        <f aca="false">IF($AA33=1,SUM($AA$4:$AA33),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="37"/>
-      <c r="B34" s="37"/>
-      <c r="C34" s="37"/>
+      <c r="A34" s="36" t="str">
+        <f aca="false">IF($Q34="","",INDEX('Score Log'!$E:$E,$Q34))</f>
+        <v/>
+      </c>
+      <c r="B34" s="36" t="str">
+        <f aca="false">IF($Q34="","",INDEX('Score Log'!$C:$C,$Q34))</f>
+        <v/>
+      </c>
+      <c r="C34" s="37" t="str">
+        <f aca="false">IF($Q34="","",IF(INDEX('Score Log'!$D:$D,$Q34)="","",INDEX('Score Log'!$D:$D,$Q34)))</f>
+        <v/>
+      </c>
       <c r="D34" s="38" t="str">
-        <f aca="false">IF($B34="","",IF($C34="",COUNTIF('Score Log'!$C$4:$C$203,$B34),COUNTIFS('Score Log'!$C$4:$C$203,$B34,'Score Log'!$D$4:$D$203,$C34)))</f>
+        <f aca="false">IF($B34="","",COUNTIFS('Score Log'!$C$4:$C$203,$B34,'Score Log'!$E$4:$E$203,$A34))</f>
         <v/>
       </c>
       <c r="E34" s="39" t="str">
-        <f aca="false">IF($B34="","",IFERROR(ROUND(IF($C34="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B34),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B34,'Score Log'!$D$4:$D$203,$C34)),1),"-"))</f>
+        <f aca="false">IF($B34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B34,'Score Log'!$E$4:$E$203,$A34),1),"-"))</f>
         <v/>
       </c>
       <c r="F34" s="39" t="str">
-        <f aca="false">IF($B34="","",IFERROR(ROUND(IF($C34="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B34),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B34,'Score Log'!$D$4:$D$203,$C34)),1),"-"))</f>
+        <f aca="false">IF($B34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B34,'Score Log'!$E$4:$E$203,$A34),1),"-"))</f>
         <v/>
       </c>
       <c r="G34" s="39" t="str">
-        <f aca="false">IF($B34="","",IFERROR(ROUND(IF($C34="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B34),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B34,'Score Log'!$D$4:$D$203,$C34)),1),"-"))</f>
+        <f aca="false">IF($B34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B34,'Score Log'!$E$4:$E$203,$A34),1),"-"))</f>
         <v/>
       </c>
       <c r="H34" s="39" t="str">
-        <f aca="false">IF($B34="","",IFERROR(ROUND(IF($C34="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B34),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B34,'Score Log'!$D$4:$D$203,$C34)),1),"-"))</f>
+        <f aca="false">IF($B34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B34,'Score Log'!$E$4:$E$203,$A34),1),"-"))</f>
         <v/>
       </c>
       <c r="I34" s="39" t="str">
-        <f aca="false">IF($B34="","",IFERROR(ROUND(IF($C34="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B34),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B34,'Score Log'!$D$4:$D$203,$C34)),1),"-"))</f>
+        <f aca="false">IF($B34="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B34,'Score Log'!$E$4:$E$203,$A34),1),"-"))</f>
         <v/>
       </c>
       <c r="J34" s="40" t="str">
-        <f aca="false">IF(OR($B34="",$D34=0),"",IFERROR(IF($C34="",COUNTIFS('Score Log'!$C$4:$C$203,$B34,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B34,'Score Log'!$D$4:$D$203,$C34,'Score Log'!$U$4:$U$203,"Yes"))/$D34,"-"))</f>
+        <f aca="false">IF(OR($B34="",$D34=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B34,'Score Log'!$E$4:$E$203,$A34,'Score Log'!$U$4:$U$203,"Yes")/$D34,"-"))</f>
         <v/>
       </c>
       <c r="K34" s="41" t="str">
@@ -13425,37 +14138,58 @@
         <f aca="false">IF($B34="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B34),""))</f>
         <v/>
       </c>
+      <c r="Q34" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA34" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C34="",'Score Log'!$E34=""),0,IF(COUNTIFS('Score Log'!$C$4:$C34,'Score Log'!$C34,'Score Log'!$E$4:$E34,'Score Log'!$E34)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB34" s="33" t="str">
+        <f aca="false">IF($AA34=1,SUM($AA$4:$AA34),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="37"/>
-      <c r="B35" s="37"/>
-      <c r="C35" s="37"/>
+      <c r="A35" s="36" t="str">
+        <f aca="false">IF($Q35="","",INDEX('Score Log'!$E:$E,$Q35))</f>
+        <v/>
+      </c>
+      <c r="B35" s="36" t="str">
+        <f aca="false">IF($Q35="","",INDEX('Score Log'!$C:$C,$Q35))</f>
+        <v/>
+      </c>
+      <c r="C35" s="37" t="str">
+        <f aca="false">IF($Q35="","",IF(INDEX('Score Log'!$D:$D,$Q35)="","",INDEX('Score Log'!$D:$D,$Q35)))</f>
+        <v/>
+      </c>
       <c r="D35" s="38" t="str">
-        <f aca="false">IF($B35="","",IF($C35="",COUNTIF('Score Log'!$C$4:$C$203,$B35),COUNTIFS('Score Log'!$C$4:$C$203,$B35,'Score Log'!$D$4:$D$203,$C35)))</f>
+        <f aca="false">IF($B35="","",COUNTIFS('Score Log'!$C$4:$C$203,$B35,'Score Log'!$E$4:$E$203,$A35))</f>
         <v/>
       </c>
       <c r="E35" s="39" t="str">
-        <f aca="false">IF($B35="","",IFERROR(ROUND(IF($C35="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B35),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B35,'Score Log'!$D$4:$D$203,$C35)),1),"-"))</f>
+        <f aca="false">IF($B35="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B35,'Score Log'!$E$4:$E$203,$A35),1),"-"))</f>
         <v/>
       </c>
       <c r="F35" s="39" t="str">
-        <f aca="false">IF($B35="","",IFERROR(ROUND(IF($C35="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B35),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B35,'Score Log'!$D$4:$D$203,$C35)),1),"-"))</f>
+        <f aca="false">IF($B35="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B35,'Score Log'!$E$4:$E$203,$A35),1),"-"))</f>
         <v/>
       </c>
       <c r="G35" s="39" t="str">
-        <f aca="false">IF($B35="","",IFERROR(ROUND(IF($C35="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B35),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B35,'Score Log'!$D$4:$D$203,$C35)),1),"-"))</f>
+        <f aca="false">IF($B35="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B35,'Score Log'!$E$4:$E$203,$A35),1),"-"))</f>
         <v/>
       </c>
       <c r="H35" s="39" t="str">
-        <f aca="false">IF($B35="","",IFERROR(ROUND(IF($C35="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B35),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B35,'Score Log'!$D$4:$D$203,$C35)),1),"-"))</f>
+        <f aca="false">IF($B35="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B35,'Score Log'!$E$4:$E$203,$A35),1),"-"))</f>
         <v/>
       </c>
       <c r="I35" s="39" t="str">
-        <f aca="false">IF($B35="","",IFERROR(ROUND(IF($C35="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B35),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B35,'Score Log'!$D$4:$D$203,$C35)),1),"-"))</f>
+        <f aca="false">IF($B35="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B35,'Score Log'!$E$4:$E$203,$A35),1),"-"))</f>
         <v/>
       </c>
       <c r="J35" s="40" t="str">
-        <f aca="false">IF(OR($B35="",$D35=0),"",IFERROR(IF($C35="",COUNTIFS('Score Log'!$C$4:$C$203,$B35,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B35,'Score Log'!$D$4:$D$203,$C35,'Score Log'!$U$4:$U$203,"Yes"))/$D35,"-"))</f>
+        <f aca="false">IF(OR($B35="",$D35=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B35,'Score Log'!$E$4:$E$203,$A35,'Score Log'!$U$4:$U$203,"Yes")/$D35,"-"))</f>
         <v/>
       </c>
       <c r="K35" s="41" t="str">
@@ -13478,37 +14212,58 @@
         <f aca="false">IF($B35="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B35),""))</f>
         <v/>
       </c>
+      <c r="Q35" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA35" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C35="",'Score Log'!$E35=""),0,IF(COUNTIFS('Score Log'!$C$4:$C35,'Score Log'!$C35,'Score Log'!$E$4:$E35,'Score Log'!$E35)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB35" s="33" t="str">
+        <f aca="false">IF($AA35=1,SUM($AA$4:$AA35),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="37"/>
-      <c r="B36" s="37"/>
-      <c r="C36" s="37"/>
+      <c r="A36" s="36" t="str">
+        <f aca="false">IF($Q36="","",INDEX('Score Log'!$E:$E,$Q36))</f>
+        <v/>
+      </c>
+      <c r="B36" s="36" t="str">
+        <f aca="false">IF($Q36="","",INDEX('Score Log'!$C:$C,$Q36))</f>
+        <v/>
+      </c>
+      <c r="C36" s="37" t="str">
+        <f aca="false">IF($Q36="","",IF(INDEX('Score Log'!$D:$D,$Q36)="","",INDEX('Score Log'!$D:$D,$Q36)))</f>
+        <v/>
+      </c>
       <c r="D36" s="38" t="str">
-        <f aca="false">IF($B36="","",IF($C36="",COUNTIF('Score Log'!$C$4:$C$203,$B36),COUNTIFS('Score Log'!$C$4:$C$203,$B36,'Score Log'!$D$4:$D$203,$C36)))</f>
+        <f aca="false">IF($B36="","",COUNTIFS('Score Log'!$C$4:$C$203,$B36,'Score Log'!$E$4:$E$203,$A36))</f>
         <v/>
       </c>
       <c r="E36" s="39" t="str">
-        <f aca="false">IF($B36="","",IFERROR(ROUND(IF($C36="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B36),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B36,'Score Log'!$D$4:$D$203,$C36)),1),"-"))</f>
+        <f aca="false">IF($B36="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B36,'Score Log'!$E$4:$E$203,$A36),1),"-"))</f>
         <v/>
       </c>
       <c r="F36" s="39" t="str">
-        <f aca="false">IF($B36="","",IFERROR(ROUND(IF($C36="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B36),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B36,'Score Log'!$D$4:$D$203,$C36)),1),"-"))</f>
+        <f aca="false">IF($B36="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B36,'Score Log'!$E$4:$E$203,$A36),1),"-"))</f>
         <v/>
       </c>
       <c r="G36" s="39" t="str">
-        <f aca="false">IF($B36="","",IFERROR(ROUND(IF($C36="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B36),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B36,'Score Log'!$D$4:$D$203,$C36)),1),"-"))</f>
+        <f aca="false">IF($B36="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B36,'Score Log'!$E$4:$E$203,$A36),1),"-"))</f>
         <v/>
       </c>
       <c r="H36" s="39" t="str">
-        <f aca="false">IF($B36="","",IFERROR(ROUND(IF($C36="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B36),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B36,'Score Log'!$D$4:$D$203,$C36)),1),"-"))</f>
+        <f aca="false">IF($B36="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B36,'Score Log'!$E$4:$E$203,$A36),1),"-"))</f>
         <v/>
       </c>
       <c r="I36" s="39" t="str">
-        <f aca="false">IF($B36="","",IFERROR(ROUND(IF($C36="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B36),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B36,'Score Log'!$D$4:$D$203,$C36)),1),"-"))</f>
+        <f aca="false">IF($B36="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B36,'Score Log'!$E$4:$E$203,$A36),1),"-"))</f>
         <v/>
       </c>
       <c r="J36" s="40" t="str">
-        <f aca="false">IF(OR($B36="",$D36=0),"",IFERROR(IF($C36="",COUNTIFS('Score Log'!$C$4:$C$203,$B36,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B36,'Score Log'!$D$4:$D$203,$C36,'Score Log'!$U$4:$U$203,"Yes"))/$D36,"-"))</f>
+        <f aca="false">IF(OR($B36="",$D36=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B36,'Score Log'!$E$4:$E$203,$A36,'Score Log'!$U$4:$U$203,"Yes")/$D36,"-"))</f>
         <v/>
       </c>
       <c r="K36" s="41" t="str">
@@ -13531,37 +14286,58 @@
         <f aca="false">IF($B36="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B36),""))</f>
         <v/>
       </c>
+      <c r="Q36" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA36" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C36="",'Score Log'!$E36=""),0,IF(COUNTIFS('Score Log'!$C$4:$C36,'Score Log'!$C36,'Score Log'!$E$4:$E36,'Score Log'!$E36)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB36" s="33" t="str">
+        <f aca="false">IF($AA36=1,SUM($AA$4:$AA36),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="37"/>
-      <c r="B37" s="37"/>
-      <c r="C37" s="37"/>
+      <c r="A37" s="36" t="str">
+        <f aca="false">IF($Q37="","",INDEX('Score Log'!$E:$E,$Q37))</f>
+        <v/>
+      </c>
+      <c r="B37" s="36" t="str">
+        <f aca="false">IF($Q37="","",INDEX('Score Log'!$C:$C,$Q37))</f>
+        <v/>
+      </c>
+      <c r="C37" s="37" t="str">
+        <f aca="false">IF($Q37="","",IF(INDEX('Score Log'!$D:$D,$Q37)="","",INDEX('Score Log'!$D:$D,$Q37)))</f>
+        <v/>
+      </c>
       <c r="D37" s="38" t="str">
-        <f aca="false">IF($B37="","",IF($C37="",COUNTIF('Score Log'!$C$4:$C$203,$B37),COUNTIFS('Score Log'!$C$4:$C$203,$B37,'Score Log'!$D$4:$D$203,$C37)))</f>
+        <f aca="false">IF($B37="","",COUNTIFS('Score Log'!$C$4:$C$203,$B37,'Score Log'!$E$4:$E$203,$A37))</f>
         <v/>
       </c>
       <c r="E37" s="39" t="str">
-        <f aca="false">IF($B37="","",IFERROR(ROUND(IF($C37="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B37),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B37,'Score Log'!$D$4:$D$203,$C37)),1),"-"))</f>
+        <f aca="false">IF($B37="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B37,'Score Log'!$E$4:$E$203,$A37),1),"-"))</f>
         <v/>
       </c>
       <c r="F37" s="39" t="str">
-        <f aca="false">IF($B37="","",IFERROR(ROUND(IF($C37="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B37),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B37,'Score Log'!$D$4:$D$203,$C37)),1),"-"))</f>
+        <f aca="false">IF($B37="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B37,'Score Log'!$E$4:$E$203,$A37),1),"-"))</f>
         <v/>
       </c>
       <c r="G37" s="39" t="str">
-        <f aca="false">IF($B37="","",IFERROR(ROUND(IF($C37="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B37),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B37,'Score Log'!$D$4:$D$203,$C37)),1),"-"))</f>
+        <f aca="false">IF($B37="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B37,'Score Log'!$E$4:$E$203,$A37),1),"-"))</f>
         <v/>
       </c>
       <c r="H37" s="39" t="str">
-        <f aca="false">IF($B37="","",IFERROR(ROUND(IF($C37="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B37),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B37,'Score Log'!$D$4:$D$203,$C37)),1),"-"))</f>
+        <f aca="false">IF($B37="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B37,'Score Log'!$E$4:$E$203,$A37),1),"-"))</f>
         <v/>
       </c>
       <c r="I37" s="39" t="str">
-        <f aca="false">IF($B37="","",IFERROR(ROUND(IF($C37="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B37),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B37,'Score Log'!$D$4:$D$203,$C37)),1),"-"))</f>
+        <f aca="false">IF($B37="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B37,'Score Log'!$E$4:$E$203,$A37),1),"-"))</f>
         <v/>
       </c>
       <c r="J37" s="40" t="str">
-        <f aca="false">IF(OR($B37="",$D37=0),"",IFERROR(IF($C37="",COUNTIFS('Score Log'!$C$4:$C$203,$B37,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B37,'Score Log'!$D$4:$D$203,$C37,'Score Log'!$U$4:$U$203,"Yes"))/$D37,"-"))</f>
+        <f aca="false">IF(OR($B37="",$D37=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B37,'Score Log'!$E$4:$E$203,$A37,'Score Log'!$U$4:$U$203,"Yes")/$D37,"-"))</f>
         <v/>
       </c>
       <c r="K37" s="41" t="str">
@@ -13584,37 +14360,58 @@
         <f aca="false">IF($B37="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B37),""))</f>
         <v/>
       </c>
+      <c r="Q37" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA37" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C37="",'Score Log'!$E37=""),0,IF(COUNTIFS('Score Log'!$C$4:$C37,'Score Log'!$C37,'Score Log'!$E$4:$E37,'Score Log'!$E37)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB37" s="33" t="str">
+        <f aca="false">IF($AA37=1,SUM($AA$4:$AA37),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="37"/>
-      <c r="B38" s="37"/>
-      <c r="C38" s="37"/>
+      <c r="A38" s="36" t="str">
+        <f aca="false">IF($Q38="","",INDEX('Score Log'!$E:$E,$Q38))</f>
+        <v/>
+      </c>
+      <c r="B38" s="36" t="str">
+        <f aca="false">IF($Q38="","",INDEX('Score Log'!$C:$C,$Q38))</f>
+        <v/>
+      </c>
+      <c r="C38" s="37" t="str">
+        <f aca="false">IF($Q38="","",IF(INDEX('Score Log'!$D:$D,$Q38)="","",INDEX('Score Log'!$D:$D,$Q38)))</f>
+        <v/>
+      </c>
       <c r="D38" s="38" t="str">
-        <f aca="false">IF($B38="","",IF($C38="",COUNTIF('Score Log'!$C$4:$C$203,$B38),COUNTIFS('Score Log'!$C$4:$C$203,$B38,'Score Log'!$D$4:$D$203,$C38)))</f>
+        <f aca="false">IF($B38="","",COUNTIFS('Score Log'!$C$4:$C$203,$B38,'Score Log'!$E$4:$E$203,$A38))</f>
         <v/>
       </c>
       <c r="E38" s="39" t="str">
-        <f aca="false">IF($B38="","",IFERROR(ROUND(IF($C38="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B38),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B38,'Score Log'!$D$4:$D$203,$C38)),1),"-"))</f>
+        <f aca="false">IF($B38="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B38,'Score Log'!$E$4:$E$203,$A38),1),"-"))</f>
         <v/>
       </c>
       <c r="F38" s="39" t="str">
-        <f aca="false">IF($B38="","",IFERROR(ROUND(IF($C38="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B38),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B38,'Score Log'!$D$4:$D$203,$C38)),1),"-"))</f>
+        <f aca="false">IF($B38="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B38,'Score Log'!$E$4:$E$203,$A38),1),"-"))</f>
         <v/>
       </c>
       <c r="G38" s="39" t="str">
-        <f aca="false">IF($B38="","",IFERROR(ROUND(IF($C38="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B38),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B38,'Score Log'!$D$4:$D$203,$C38)),1),"-"))</f>
+        <f aca="false">IF($B38="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B38,'Score Log'!$E$4:$E$203,$A38),1),"-"))</f>
         <v/>
       </c>
       <c r="H38" s="39" t="str">
-        <f aca="false">IF($B38="","",IFERROR(ROUND(IF($C38="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B38),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B38,'Score Log'!$D$4:$D$203,$C38)),1),"-"))</f>
+        <f aca="false">IF($B38="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B38,'Score Log'!$E$4:$E$203,$A38),1),"-"))</f>
         <v/>
       </c>
       <c r="I38" s="39" t="str">
-        <f aca="false">IF($B38="","",IFERROR(ROUND(IF($C38="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B38),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B38,'Score Log'!$D$4:$D$203,$C38)),1),"-"))</f>
+        <f aca="false">IF($B38="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B38,'Score Log'!$E$4:$E$203,$A38),1),"-"))</f>
         <v/>
       </c>
       <c r="J38" s="40" t="str">
-        <f aca="false">IF(OR($B38="",$D38=0),"",IFERROR(IF($C38="",COUNTIFS('Score Log'!$C$4:$C$203,$B38,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B38,'Score Log'!$D$4:$D$203,$C38,'Score Log'!$U$4:$U$203,"Yes"))/$D38,"-"))</f>
+        <f aca="false">IF(OR($B38="",$D38=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B38,'Score Log'!$E$4:$E$203,$A38,'Score Log'!$U$4:$U$203,"Yes")/$D38,"-"))</f>
         <v/>
       </c>
       <c r="K38" s="41" t="str">
@@ -13637,37 +14434,58 @@
         <f aca="false">IF($B38="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B38),""))</f>
         <v/>
       </c>
+      <c r="Q38" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA38" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C38="",'Score Log'!$E38=""),0,IF(COUNTIFS('Score Log'!$C$4:$C38,'Score Log'!$C38,'Score Log'!$E$4:$E38,'Score Log'!$E38)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB38" s="33" t="str">
+        <f aca="false">IF($AA38=1,SUM($AA$4:$AA38),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="37"/>
-      <c r="B39" s="37"/>
-      <c r="C39" s="37"/>
+      <c r="A39" s="36" t="str">
+        <f aca="false">IF($Q39="","",INDEX('Score Log'!$E:$E,$Q39))</f>
+        <v/>
+      </c>
+      <c r="B39" s="36" t="str">
+        <f aca="false">IF($Q39="","",INDEX('Score Log'!$C:$C,$Q39))</f>
+        <v/>
+      </c>
+      <c r="C39" s="37" t="str">
+        <f aca="false">IF($Q39="","",IF(INDEX('Score Log'!$D:$D,$Q39)="","",INDEX('Score Log'!$D:$D,$Q39)))</f>
+        <v/>
+      </c>
       <c r="D39" s="38" t="str">
-        <f aca="false">IF($B39="","",IF($C39="",COUNTIF('Score Log'!$C$4:$C$203,$B39),COUNTIFS('Score Log'!$C$4:$C$203,$B39,'Score Log'!$D$4:$D$203,$C39)))</f>
+        <f aca="false">IF($B39="","",COUNTIFS('Score Log'!$C$4:$C$203,$B39,'Score Log'!$E$4:$E$203,$A39))</f>
         <v/>
       </c>
       <c r="E39" s="39" t="str">
-        <f aca="false">IF($B39="","",IFERROR(ROUND(IF($C39="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B39),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B39,'Score Log'!$D$4:$D$203,$C39)),1),"-"))</f>
+        <f aca="false">IF($B39="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B39,'Score Log'!$E$4:$E$203,$A39),1),"-"))</f>
         <v/>
       </c>
       <c r="F39" s="39" t="str">
-        <f aca="false">IF($B39="","",IFERROR(ROUND(IF($C39="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B39),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B39,'Score Log'!$D$4:$D$203,$C39)),1),"-"))</f>
+        <f aca="false">IF($B39="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B39,'Score Log'!$E$4:$E$203,$A39),1),"-"))</f>
         <v/>
       </c>
       <c r="G39" s="39" t="str">
-        <f aca="false">IF($B39="","",IFERROR(ROUND(IF($C39="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B39),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B39,'Score Log'!$D$4:$D$203,$C39)),1),"-"))</f>
+        <f aca="false">IF($B39="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B39,'Score Log'!$E$4:$E$203,$A39),1),"-"))</f>
         <v/>
       </c>
       <c r="H39" s="39" t="str">
-        <f aca="false">IF($B39="","",IFERROR(ROUND(IF($C39="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B39),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B39,'Score Log'!$D$4:$D$203,$C39)),1),"-"))</f>
+        <f aca="false">IF($B39="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B39,'Score Log'!$E$4:$E$203,$A39),1),"-"))</f>
         <v/>
       </c>
       <c r="I39" s="39" t="str">
-        <f aca="false">IF($B39="","",IFERROR(ROUND(IF($C39="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B39),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B39,'Score Log'!$D$4:$D$203,$C39)),1),"-"))</f>
+        <f aca="false">IF($B39="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B39,'Score Log'!$E$4:$E$203,$A39),1),"-"))</f>
         <v/>
       </c>
       <c r="J39" s="40" t="str">
-        <f aca="false">IF(OR($B39="",$D39=0),"",IFERROR(IF($C39="",COUNTIFS('Score Log'!$C$4:$C$203,$B39,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B39,'Score Log'!$D$4:$D$203,$C39,'Score Log'!$U$4:$U$203,"Yes"))/$D39,"-"))</f>
+        <f aca="false">IF(OR($B39="",$D39=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B39,'Score Log'!$E$4:$E$203,$A39,'Score Log'!$U$4:$U$203,"Yes")/$D39,"-"))</f>
         <v/>
       </c>
       <c r="K39" s="41" t="str">
@@ -13690,37 +14508,58 @@
         <f aca="false">IF($B39="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B39),""))</f>
         <v/>
       </c>
+      <c r="Q39" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA39" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C39="",'Score Log'!$E39=""),0,IF(COUNTIFS('Score Log'!$C$4:$C39,'Score Log'!$C39,'Score Log'!$E$4:$E39,'Score Log'!$E39)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB39" s="33" t="str">
+        <f aca="false">IF($AA39=1,SUM($AA$4:$AA39),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="37"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
+      <c r="A40" s="36" t="str">
+        <f aca="false">IF($Q40="","",INDEX('Score Log'!$E:$E,$Q40))</f>
+        <v/>
+      </c>
+      <c r="B40" s="36" t="str">
+        <f aca="false">IF($Q40="","",INDEX('Score Log'!$C:$C,$Q40))</f>
+        <v/>
+      </c>
+      <c r="C40" s="37" t="str">
+        <f aca="false">IF($Q40="","",IF(INDEX('Score Log'!$D:$D,$Q40)="","",INDEX('Score Log'!$D:$D,$Q40)))</f>
+        <v/>
+      </c>
       <c r="D40" s="38" t="str">
-        <f aca="false">IF($B40="","",IF($C40="",COUNTIF('Score Log'!$C$4:$C$203,$B40),COUNTIFS('Score Log'!$C$4:$C$203,$B40,'Score Log'!$D$4:$D$203,$C40)))</f>
+        <f aca="false">IF($B40="","",COUNTIFS('Score Log'!$C$4:$C$203,$B40,'Score Log'!$E$4:$E$203,$A40))</f>
         <v/>
       </c>
       <c r="E40" s="39" t="str">
-        <f aca="false">IF($B40="","",IFERROR(ROUND(IF($C40="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B40),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B40,'Score Log'!$D$4:$D$203,$C40)),1),"-"))</f>
+        <f aca="false">IF($B40="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B40,'Score Log'!$E$4:$E$203,$A40),1),"-"))</f>
         <v/>
       </c>
       <c r="F40" s="39" t="str">
-        <f aca="false">IF($B40="","",IFERROR(ROUND(IF($C40="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B40),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B40,'Score Log'!$D$4:$D$203,$C40)),1),"-"))</f>
+        <f aca="false">IF($B40="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B40,'Score Log'!$E$4:$E$203,$A40),1),"-"))</f>
         <v/>
       </c>
       <c r="G40" s="39" t="str">
-        <f aca="false">IF($B40="","",IFERROR(ROUND(IF($C40="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B40),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B40,'Score Log'!$D$4:$D$203,$C40)),1),"-"))</f>
+        <f aca="false">IF($B40="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B40,'Score Log'!$E$4:$E$203,$A40),1),"-"))</f>
         <v/>
       </c>
       <c r="H40" s="39" t="str">
-        <f aca="false">IF($B40="","",IFERROR(ROUND(IF($C40="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B40),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B40,'Score Log'!$D$4:$D$203,$C40)),1),"-"))</f>
+        <f aca="false">IF($B40="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B40,'Score Log'!$E$4:$E$203,$A40),1),"-"))</f>
         <v/>
       </c>
       <c r="I40" s="39" t="str">
-        <f aca="false">IF($B40="","",IFERROR(ROUND(IF($C40="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B40),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B40,'Score Log'!$D$4:$D$203,$C40)),1),"-"))</f>
+        <f aca="false">IF($B40="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B40,'Score Log'!$E$4:$E$203,$A40),1),"-"))</f>
         <v/>
       </c>
       <c r="J40" s="40" t="str">
-        <f aca="false">IF(OR($B40="",$D40=0),"",IFERROR(IF($C40="",COUNTIFS('Score Log'!$C$4:$C$203,$B40,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B40,'Score Log'!$D$4:$D$203,$C40,'Score Log'!$U$4:$U$203,"Yes"))/$D40,"-"))</f>
+        <f aca="false">IF(OR($B40="",$D40=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B40,'Score Log'!$E$4:$E$203,$A40,'Score Log'!$U$4:$U$203,"Yes")/$D40,"-"))</f>
         <v/>
       </c>
       <c r="K40" s="41" t="str">
@@ -13743,37 +14582,58 @@
         <f aca="false">IF($B40="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B40),""))</f>
         <v/>
       </c>
+      <c r="Q40" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA40" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C40="",'Score Log'!$E40=""),0,IF(COUNTIFS('Score Log'!$C$4:$C40,'Score Log'!$C40,'Score Log'!$E$4:$E40,'Score Log'!$E40)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB40" s="33" t="str">
+        <f aca="false">IF($AA40=1,SUM($AA$4:$AA40),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="37"/>
-      <c r="B41" s="37"/>
-      <c r="C41" s="37"/>
+      <c r="A41" s="36" t="str">
+        <f aca="false">IF($Q41="","",INDEX('Score Log'!$E:$E,$Q41))</f>
+        <v/>
+      </c>
+      <c r="B41" s="36" t="str">
+        <f aca="false">IF($Q41="","",INDEX('Score Log'!$C:$C,$Q41))</f>
+        <v/>
+      </c>
+      <c r="C41" s="37" t="str">
+        <f aca="false">IF($Q41="","",IF(INDEX('Score Log'!$D:$D,$Q41)="","",INDEX('Score Log'!$D:$D,$Q41)))</f>
+        <v/>
+      </c>
       <c r="D41" s="38" t="str">
-        <f aca="false">IF($B41="","",IF($C41="",COUNTIF('Score Log'!$C$4:$C$203,$B41),COUNTIFS('Score Log'!$C$4:$C$203,$B41,'Score Log'!$D$4:$D$203,$C41)))</f>
+        <f aca="false">IF($B41="","",COUNTIFS('Score Log'!$C$4:$C$203,$B41,'Score Log'!$E$4:$E$203,$A41))</f>
         <v/>
       </c>
       <c r="E41" s="39" t="str">
-        <f aca="false">IF($B41="","",IFERROR(ROUND(IF($C41="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B41),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B41,'Score Log'!$D$4:$D$203,$C41)),1),"-"))</f>
+        <f aca="false">IF($B41="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B41,'Score Log'!$E$4:$E$203,$A41),1),"-"))</f>
         <v/>
       </c>
       <c r="F41" s="39" t="str">
-        <f aca="false">IF($B41="","",IFERROR(ROUND(IF($C41="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B41),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B41,'Score Log'!$D$4:$D$203,$C41)),1),"-"))</f>
+        <f aca="false">IF($B41="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B41,'Score Log'!$E$4:$E$203,$A41),1),"-"))</f>
         <v/>
       </c>
       <c r="G41" s="39" t="str">
-        <f aca="false">IF($B41="","",IFERROR(ROUND(IF($C41="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B41),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B41,'Score Log'!$D$4:$D$203,$C41)),1),"-"))</f>
+        <f aca="false">IF($B41="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B41,'Score Log'!$E$4:$E$203,$A41),1),"-"))</f>
         <v/>
       </c>
       <c r="H41" s="39" t="str">
-        <f aca="false">IF($B41="","",IFERROR(ROUND(IF($C41="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B41),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B41,'Score Log'!$D$4:$D$203,$C41)),1),"-"))</f>
+        <f aca="false">IF($B41="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B41,'Score Log'!$E$4:$E$203,$A41),1),"-"))</f>
         <v/>
       </c>
       <c r="I41" s="39" t="str">
-        <f aca="false">IF($B41="","",IFERROR(ROUND(IF($C41="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B41),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B41,'Score Log'!$D$4:$D$203,$C41)),1),"-"))</f>
+        <f aca="false">IF($B41="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B41,'Score Log'!$E$4:$E$203,$A41),1),"-"))</f>
         <v/>
       </c>
       <c r="J41" s="40" t="str">
-        <f aca="false">IF(OR($B41="",$D41=0),"",IFERROR(IF($C41="",COUNTIFS('Score Log'!$C$4:$C$203,$B41,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B41,'Score Log'!$D$4:$D$203,$C41,'Score Log'!$U$4:$U$203,"Yes"))/$D41,"-"))</f>
+        <f aca="false">IF(OR($B41="",$D41=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B41,'Score Log'!$E$4:$E$203,$A41,'Score Log'!$U$4:$U$203,"Yes")/$D41,"-"))</f>
         <v/>
       </c>
       <c r="K41" s="41" t="str">
@@ -13796,37 +14656,58 @@
         <f aca="false">IF($B41="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B41),""))</f>
         <v/>
       </c>
+      <c r="Q41" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA41" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C41="",'Score Log'!$E41=""),0,IF(COUNTIFS('Score Log'!$C$4:$C41,'Score Log'!$C41,'Score Log'!$E$4:$E41,'Score Log'!$E41)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB41" s="33" t="str">
+        <f aca="false">IF($AA41=1,SUM($AA$4:$AA41),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="37"/>
-      <c r="B42" s="37"/>
-      <c r="C42" s="37"/>
+      <c r="A42" s="36" t="str">
+        <f aca="false">IF($Q42="","",INDEX('Score Log'!$E:$E,$Q42))</f>
+        <v/>
+      </c>
+      <c r="B42" s="36" t="str">
+        <f aca="false">IF($Q42="","",INDEX('Score Log'!$C:$C,$Q42))</f>
+        <v/>
+      </c>
+      <c r="C42" s="37" t="str">
+        <f aca="false">IF($Q42="","",IF(INDEX('Score Log'!$D:$D,$Q42)="","",INDEX('Score Log'!$D:$D,$Q42)))</f>
+        <v/>
+      </c>
       <c r="D42" s="38" t="str">
-        <f aca="false">IF($B42="","",IF($C42="",COUNTIF('Score Log'!$C$4:$C$203,$B42),COUNTIFS('Score Log'!$C$4:$C$203,$B42,'Score Log'!$D$4:$D$203,$C42)))</f>
+        <f aca="false">IF($B42="","",COUNTIFS('Score Log'!$C$4:$C$203,$B42,'Score Log'!$E$4:$E$203,$A42))</f>
         <v/>
       </c>
       <c r="E42" s="39" t="str">
-        <f aca="false">IF($B42="","",IFERROR(ROUND(IF($C42="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B42),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B42,'Score Log'!$D$4:$D$203,$C42)),1),"-"))</f>
+        <f aca="false">IF($B42="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B42,'Score Log'!$E$4:$E$203,$A42),1),"-"))</f>
         <v/>
       </c>
       <c r="F42" s="39" t="str">
-        <f aca="false">IF($B42="","",IFERROR(ROUND(IF($C42="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B42),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B42,'Score Log'!$D$4:$D$203,$C42)),1),"-"))</f>
+        <f aca="false">IF($B42="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B42,'Score Log'!$E$4:$E$203,$A42),1),"-"))</f>
         <v/>
       </c>
       <c r="G42" s="39" t="str">
-        <f aca="false">IF($B42="","",IFERROR(ROUND(IF($C42="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B42),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B42,'Score Log'!$D$4:$D$203,$C42)),1),"-"))</f>
+        <f aca="false">IF($B42="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B42,'Score Log'!$E$4:$E$203,$A42),1),"-"))</f>
         <v/>
       </c>
       <c r="H42" s="39" t="str">
-        <f aca="false">IF($B42="","",IFERROR(ROUND(IF($C42="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B42),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B42,'Score Log'!$D$4:$D$203,$C42)),1),"-"))</f>
+        <f aca="false">IF($B42="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B42,'Score Log'!$E$4:$E$203,$A42),1),"-"))</f>
         <v/>
       </c>
       <c r="I42" s="39" t="str">
-        <f aca="false">IF($B42="","",IFERROR(ROUND(IF($C42="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B42),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B42,'Score Log'!$D$4:$D$203,$C42)),1),"-"))</f>
+        <f aca="false">IF($B42="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B42,'Score Log'!$E$4:$E$203,$A42),1),"-"))</f>
         <v/>
       </c>
       <c r="J42" s="40" t="str">
-        <f aca="false">IF(OR($B42="",$D42=0),"",IFERROR(IF($C42="",COUNTIFS('Score Log'!$C$4:$C$203,$B42,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B42,'Score Log'!$D$4:$D$203,$C42,'Score Log'!$U$4:$U$203,"Yes"))/$D42,"-"))</f>
+        <f aca="false">IF(OR($B42="",$D42=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B42,'Score Log'!$E$4:$E$203,$A42,'Score Log'!$U$4:$U$203,"Yes")/$D42,"-"))</f>
         <v/>
       </c>
       <c r="K42" s="41" t="str">
@@ -13849,37 +14730,58 @@
         <f aca="false">IF($B42="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B42),""))</f>
         <v/>
       </c>
+      <c r="Q42" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA42" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C42="",'Score Log'!$E42=""),0,IF(COUNTIFS('Score Log'!$C$4:$C42,'Score Log'!$C42,'Score Log'!$E$4:$E42,'Score Log'!$E42)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB42" s="33" t="str">
+        <f aca="false">IF($AA42=1,SUM($AA$4:$AA42),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="37"/>
-      <c r="B43" s="37"/>
-      <c r="C43" s="37"/>
+      <c r="A43" s="36" t="str">
+        <f aca="false">IF($Q43="","",INDEX('Score Log'!$E:$E,$Q43))</f>
+        <v/>
+      </c>
+      <c r="B43" s="36" t="str">
+        <f aca="false">IF($Q43="","",INDEX('Score Log'!$C:$C,$Q43))</f>
+        <v/>
+      </c>
+      <c r="C43" s="37" t="str">
+        <f aca="false">IF($Q43="","",IF(INDEX('Score Log'!$D:$D,$Q43)="","",INDEX('Score Log'!$D:$D,$Q43)))</f>
+        <v/>
+      </c>
       <c r="D43" s="38" t="str">
-        <f aca="false">IF($B43="","",IF($C43="",COUNTIF('Score Log'!$C$4:$C$203,$B43),COUNTIFS('Score Log'!$C$4:$C$203,$B43,'Score Log'!$D$4:$D$203,$C43)))</f>
+        <f aca="false">IF($B43="","",COUNTIFS('Score Log'!$C$4:$C$203,$B43,'Score Log'!$E$4:$E$203,$A43))</f>
         <v/>
       </c>
       <c r="E43" s="39" t="str">
-        <f aca="false">IF($B43="","",IFERROR(ROUND(IF($C43="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B43),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B43,'Score Log'!$D$4:$D$203,$C43)),1),"-"))</f>
+        <f aca="false">IF($B43="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B43,'Score Log'!$E$4:$E$203,$A43),1),"-"))</f>
         <v/>
       </c>
       <c r="F43" s="39" t="str">
-        <f aca="false">IF($B43="","",IFERROR(ROUND(IF($C43="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B43),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B43,'Score Log'!$D$4:$D$203,$C43)),1),"-"))</f>
+        <f aca="false">IF($B43="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B43,'Score Log'!$E$4:$E$203,$A43),1),"-"))</f>
         <v/>
       </c>
       <c r="G43" s="39" t="str">
-        <f aca="false">IF($B43="","",IFERROR(ROUND(IF($C43="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B43),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B43,'Score Log'!$D$4:$D$203,$C43)),1),"-"))</f>
+        <f aca="false">IF($B43="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B43,'Score Log'!$E$4:$E$203,$A43),1),"-"))</f>
         <v/>
       </c>
       <c r="H43" s="39" t="str">
-        <f aca="false">IF($B43="","",IFERROR(ROUND(IF($C43="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B43),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B43,'Score Log'!$D$4:$D$203,$C43)),1),"-"))</f>
+        <f aca="false">IF($B43="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B43,'Score Log'!$E$4:$E$203,$A43),1),"-"))</f>
         <v/>
       </c>
       <c r="I43" s="39" t="str">
-        <f aca="false">IF($B43="","",IFERROR(ROUND(IF($C43="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B43),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B43,'Score Log'!$D$4:$D$203,$C43)),1),"-"))</f>
+        <f aca="false">IF($B43="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B43,'Score Log'!$E$4:$E$203,$A43),1),"-"))</f>
         <v/>
       </c>
       <c r="J43" s="40" t="str">
-        <f aca="false">IF(OR($B43="",$D43=0),"",IFERROR(IF($C43="",COUNTIFS('Score Log'!$C$4:$C$203,$B43,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B43,'Score Log'!$D$4:$D$203,$C43,'Score Log'!$U$4:$U$203,"Yes"))/$D43,"-"))</f>
+        <f aca="false">IF(OR($B43="",$D43=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B43,'Score Log'!$E$4:$E$203,$A43,'Score Log'!$U$4:$U$203,"Yes")/$D43,"-"))</f>
         <v/>
       </c>
       <c r="K43" s="41" t="str">
@@ -13902,37 +14804,58 @@
         <f aca="false">IF($B43="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B43),""))</f>
         <v/>
       </c>
+      <c r="Q43" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA43" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C43="",'Score Log'!$E43=""),0,IF(COUNTIFS('Score Log'!$C$4:$C43,'Score Log'!$C43,'Score Log'!$E$4:$E43,'Score Log'!$E43)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB43" s="33" t="str">
+        <f aca="false">IF($AA43=1,SUM($AA$4:$AA43),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="37"/>
-      <c r="B44" s="37"/>
-      <c r="C44" s="37"/>
+      <c r="A44" s="36" t="str">
+        <f aca="false">IF($Q44="","",INDEX('Score Log'!$E:$E,$Q44))</f>
+        <v/>
+      </c>
+      <c r="B44" s="36" t="str">
+        <f aca="false">IF($Q44="","",INDEX('Score Log'!$C:$C,$Q44))</f>
+        <v/>
+      </c>
+      <c r="C44" s="37" t="str">
+        <f aca="false">IF($Q44="","",IF(INDEX('Score Log'!$D:$D,$Q44)="","",INDEX('Score Log'!$D:$D,$Q44)))</f>
+        <v/>
+      </c>
       <c r="D44" s="38" t="str">
-        <f aca="false">IF($B44="","",IF($C44="",COUNTIF('Score Log'!$C$4:$C$203,$B44),COUNTIFS('Score Log'!$C$4:$C$203,$B44,'Score Log'!$D$4:$D$203,$C44)))</f>
+        <f aca="false">IF($B44="","",COUNTIFS('Score Log'!$C$4:$C$203,$B44,'Score Log'!$E$4:$E$203,$A44))</f>
         <v/>
       </c>
       <c r="E44" s="39" t="str">
-        <f aca="false">IF($B44="","",IFERROR(ROUND(IF($C44="",AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B44),AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B44,'Score Log'!$D$4:$D$203,$C44)),1),"-"))</f>
+        <f aca="false">IF($B44="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B44,'Score Log'!$E$4:$E$203,$A44),1),"-"))</f>
         <v/>
       </c>
       <c r="F44" s="39" t="str">
-        <f aca="false">IF($B44="","",IFERROR(ROUND(IF($C44="",AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B44),AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B44,'Score Log'!$D$4:$D$203,$C44)),1),"-"))</f>
+        <f aca="false">IF($B44="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B44,'Score Log'!$E$4:$E$203,$A44),1),"-"))</f>
         <v/>
       </c>
       <c r="G44" s="39" t="str">
-        <f aca="false">IF($B44="","",IFERROR(ROUND(IF($C44="",AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B44),AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B44,'Score Log'!$D$4:$D$203,$C44)),1),"-"))</f>
+        <f aca="false">IF($B44="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B44,'Score Log'!$E$4:$E$203,$A44),1),"-"))</f>
         <v/>
       </c>
       <c r="H44" s="39" t="str">
-        <f aca="false">IF($B44="","",IFERROR(ROUND(IF($C44="",AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B44),AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B44,'Score Log'!$D$4:$D$203,$C44)),1),"-"))</f>
+        <f aca="false">IF($B44="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B44,'Score Log'!$E$4:$E$203,$A44),1),"-"))</f>
         <v/>
       </c>
       <c r="I44" s="39" t="str">
-        <f aca="false">IF($B44="","",IFERROR(ROUND(IF($C44="",AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B44),AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B44,'Score Log'!$D$4:$D$203,$C44)),1),"-"))</f>
+        <f aca="false">IF($B44="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B44,'Score Log'!$E$4:$E$203,$A44),1),"-"))</f>
         <v/>
       </c>
       <c r="J44" s="40" t="str">
-        <f aca="false">IF(OR($B44="",$D44=0),"",IFERROR(IF($C44="",COUNTIFS('Score Log'!$C$4:$C$203,$B44,'Score Log'!$U$4:$U$203,"Yes"),COUNTIFS('Score Log'!$C$4:$C$203,$B44,'Score Log'!$D$4:$D$203,$C44,'Score Log'!$U$4:$U$203,"Yes"))/$D44,"-"))</f>
+        <f aca="false">IF(OR($B44="",$D44=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B44,'Score Log'!$E$4:$E$203,$A44,'Score Log'!$U$4:$U$203,"Yes")/$D44,"-"))</f>
         <v/>
       </c>
       <c r="K44" s="41" t="str">
@@ -13955,109 +14878,2995 @@
         <f aca="false">IF($B44="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B44),""))</f>
         <v/>
       </c>
+      <c r="Q44" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA44" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C44="",'Score Log'!$E44=""),0,IF(COUNTIFS('Score Log'!$C$4:$C44,'Score Log'!$C44,'Score Log'!$E$4:$E44,'Score Log'!$E44)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB44" s="33" t="str">
+        <f aca="false">IF($AA44=1,SUM($AA$4:$AA44),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="36" t="str">
+        <f aca="false">IF($Q45="","",INDEX('Score Log'!$E:$E,$Q45))</f>
+        <v/>
+      </c>
+      <c r="B45" s="36" t="str">
+        <f aca="false">IF($Q45="","",INDEX('Score Log'!$C:$C,$Q45))</f>
+        <v/>
+      </c>
+      <c r="C45" s="37" t="str">
+        <f aca="false">IF($Q45="","",IF(INDEX('Score Log'!$D:$D,$Q45)="","",INDEX('Score Log'!$D:$D,$Q45)))</f>
+        <v/>
+      </c>
+      <c r="D45" s="38" t="str">
+        <f aca="false">IF($B45="","",COUNTIFS('Score Log'!$C$4:$C$203,$B45,'Score Log'!$E$4:$E$203,$A45))</f>
+        <v/>
+      </c>
+      <c r="E45" s="39" t="str">
+        <f aca="false">IF($B45="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B45,'Score Log'!$E$4:$E$203,$A45),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F45" s="39" t="str">
+        <f aca="false">IF($B45="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B45,'Score Log'!$E$4:$E$203,$A45),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G45" s="39" t="str">
+        <f aca="false">IF($B45="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B45,'Score Log'!$E$4:$E$203,$A45),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H45" s="39" t="str">
+        <f aca="false">IF($B45="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B45,'Score Log'!$E$4:$E$203,$A45),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I45" s="39" t="str">
+        <f aca="false">IF($B45="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B45,'Score Log'!$E$4:$E$203,$A45),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J45" s="40" t="str">
+        <f aca="false">IF(OR($B45="",$D45=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B45,'Score Log'!$E$4:$E$203,$A45,'Score Log'!$U$4:$U$203,"Yes")/$D45,"-"))</f>
+        <v/>
+      </c>
+      <c r="K45" s="41" t="str">
+        <f aca="false">IF($B45="","",IF(ISNUMBER($F45),MAX(1,MIN(5,ROUND(6-$F45,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L45" s="41" t="str">
+        <f aca="false">IF($B45="","",IF(ISNUMBER($G45),MAX(1,MIN(5,ROUND(6-$G45,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M45" s="41" t="str">
+        <f aca="false">IF($B45="","",IF(AND(ISNUMBER($P45),ISNUMBER($O45)),MAX(1,MIN(5,ROUND(6-AVERAGE($P45,$O45),0))),IF(ISNUMBER($P45),MAX(1,MIN(5,ROUND(6-$P45,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O45" s="33" t="str">
+        <f aca="false">IF($B45="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B45),""))</f>
+        <v/>
+      </c>
+      <c r="P45" s="33" t="str">
+        <f aca="false">IF($B45="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B45),""))</f>
+        <v/>
+      </c>
+      <c r="Q45" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA45" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C45="",'Score Log'!$E45=""),0,IF(COUNTIFS('Score Log'!$C$4:$C45,'Score Log'!$C45,'Score Log'!$E$4:$E45,'Score Log'!$E45)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB45" s="33" t="str">
+        <f aca="false">IF($AA45=1,SUM($AA$4:$AA45),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="36" t="str">
+        <f aca="false">IF($Q46="","",INDEX('Score Log'!$E:$E,$Q46))</f>
+        <v/>
+      </c>
+      <c r="B46" s="36" t="str">
+        <f aca="false">IF($Q46="","",INDEX('Score Log'!$C:$C,$Q46))</f>
+        <v/>
+      </c>
+      <c r="C46" s="37" t="str">
+        <f aca="false">IF($Q46="","",IF(INDEX('Score Log'!$D:$D,$Q46)="","",INDEX('Score Log'!$D:$D,$Q46)))</f>
+        <v/>
+      </c>
+      <c r="D46" s="38" t="str">
+        <f aca="false">IF($B46="","",COUNTIFS('Score Log'!$C$4:$C$203,$B46,'Score Log'!$E$4:$E$203,$A46))</f>
+        <v/>
+      </c>
+      <c r="E46" s="39" t="str">
+        <f aca="false">IF($B46="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B46,'Score Log'!$E$4:$E$203,$A46),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F46" s="39" t="str">
+        <f aca="false">IF($B46="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B46,'Score Log'!$E$4:$E$203,$A46),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="39" t="str">
+        <f aca="false">IF($B46="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B46,'Score Log'!$E$4:$E$203,$A46),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H46" s="39" t="str">
+        <f aca="false">IF($B46="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B46,'Score Log'!$E$4:$E$203,$A46),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I46" s="39" t="str">
+        <f aca="false">IF($B46="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B46,'Score Log'!$E$4:$E$203,$A46),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J46" s="40" t="str">
+        <f aca="false">IF(OR($B46="",$D46=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B46,'Score Log'!$E$4:$E$203,$A46,'Score Log'!$U$4:$U$203,"Yes")/$D46,"-"))</f>
+        <v/>
+      </c>
+      <c r="K46" s="41" t="str">
+        <f aca="false">IF($B46="","",IF(ISNUMBER($F46),MAX(1,MIN(5,ROUND(6-$F46,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L46" s="41" t="str">
+        <f aca="false">IF($B46="","",IF(ISNUMBER($G46),MAX(1,MIN(5,ROUND(6-$G46,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M46" s="41" t="str">
+        <f aca="false">IF($B46="","",IF(AND(ISNUMBER($P46),ISNUMBER($O46)),MAX(1,MIN(5,ROUND(6-AVERAGE($P46,$O46),0))),IF(ISNUMBER($P46),MAX(1,MIN(5,ROUND(6-$P46,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O46" s="33" t="str">
+        <f aca="false">IF($B46="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B46),""))</f>
+        <v/>
+      </c>
+      <c r="P46" s="33" t="str">
+        <f aca="false">IF($B46="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B46),""))</f>
+        <v/>
+      </c>
+      <c r="Q46" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA46" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C46="",'Score Log'!$E46=""),0,IF(COUNTIFS('Score Log'!$C$4:$C46,'Score Log'!$C46,'Score Log'!$E$4:$E46,'Score Log'!$E46)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB46" s="33" t="str">
+        <f aca="false">IF($AA46=1,SUM($AA$4:$AA46),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="42" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="B48" s="43"/>
-      <c r="C48" s="43"/>
-      <c r="D48" s="43"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="43"/>
-      <c r="G48" s="43"/>
-      <c r="H48" s="43"/>
-      <c r="I48" s="43"/>
-      <c r="J48" s="43"/>
-      <c r="K48" s="43"/>
-      <c r="L48" s="43"/>
-      <c r="M48" s="43"/>
-    </row>
-    <row r="49" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="43" t="s">
-        <v>88</v>
-      </c>
-      <c r="B49" s="43"/>
-      <c r="C49" s="43"/>
-      <c r="D49" s="43"/>
-      <c r="E49" s="43"/>
-      <c r="F49" s="43"/>
-      <c r="G49" s="43"/>
-      <c r="H49" s="43"/>
-      <c r="I49" s="43"/>
-      <c r="J49" s="43"/>
-      <c r="K49" s="43"/>
-      <c r="L49" s="43"/>
-      <c r="M49" s="43"/>
-    </row>
-    <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="43" t="s">
+      <c r="A47" s="36" t="str">
+        <f aca="false">IF($Q47="","",INDEX('Score Log'!$E:$E,$Q47))</f>
+        <v/>
+      </c>
+      <c r="B47" s="36" t="str">
+        <f aca="false">IF($Q47="","",INDEX('Score Log'!$C:$C,$Q47))</f>
+        <v/>
+      </c>
+      <c r="C47" s="37" t="str">
+        <f aca="false">IF($Q47="","",IF(INDEX('Score Log'!$D:$D,$Q47)="","",INDEX('Score Log'!$D:$D,$Q47)))</f>
+        <v/>
+      </c>
+      <c r="D47" s="38" t="str">
+        <f aca="false">IF($B47="","",COUNTIFS('Score Log'!$C$4:$C$203,$B47,'Score Log'!$E$4:$E$203,$A47))</f>
+        <v/>
+      </c>
+      <c r="E47" s="39" t="str">
+        <f aca="false">IF($B47="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B47,'Score Log'!$E$4:$E$203,$A47),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F47" s="39" t="str">
+        <f aca="false">IF($B47="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B47,'Score Log'!$E$4:$E$203,$A47),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="39" t="str">
+        <f aca="false">IF($B47="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B47,'Score Log'!$E$4:$E$203,$A47),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H47" s="39" t="str">
+        <f aca="false">IF($B47="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B47,'Score Log'!$E$4:$E$203,$A47),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I47" s="39" t="str">
+        <f aca="false">IF($B47="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B47,'Score Log'!$E$4:$E$203,$A47),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J47" s="40" t="str">
+        <f aca="false">IF(OR($B47="",$D47=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B47,'Score Log'!$E$4:$E$203,$A47,'Score Log'!$U$4:$U$203,"Yes")/$D47,"-"))</f>
+        <v/>
+      </c>
+      <c r="K47" s="41" t="str">
+        <f aca="false">IF($B47="","",IF(ISNUMBER($F47),MAX(1,MIN(5,ROUND(6-$F47,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L47" s="41" t="str">
+        <f aca="false">IF($B47="","",IF(ISNUMBER($G47),MAX(1,MIN(5,ROUND(6-$G47,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M47" s="41" t="str">
+        <f aca="false">IF($B47="","",IF(AND(ISNUMBER($P47),ISNUMBER($O47)),MAX(1,MIN(5,ROUND(6-AVERAGE($P47,$O47),0))),IF(ISNUMBER($P47),MAX(1,MIN(5,ROUND(6-$P47,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O47" s="33" t="str">
+        <f aca="false">IF($B47="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B47),""))</f>
+        <v/>
+      </c>
+      <c r="P47" s="33" t="str">
+        <f aca="false">IF($B47="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B47),""))</f>
+        <v/>
+      </c>
+      <c r="Q47" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA47" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C47="",'Score Log'!$E47=""),0,IF(COUNTIFS('Score Log'!$C$4:$C47,'Score Log'!$C47,'Score Log'!$E$4:$E47,'Score Log'!$E47)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB47" s="33" t="str">
+        <f aca="false">IF($AA47=1,SUM($AA$4:$AA47),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="36" t="str">
+        <f aca="false">IF($Q48="","",INDEX('Score Log'!$E:$E,$Q48))</f>
+        <v/>
+      </c>
+      <c r="B48" s="36" t="str">
+        <f aca="false">IF($Q48="","",INDEX('Score Log'!$C:$C,$Q48))</f>
+        <v/>
+      </c>
+      <c r="C48" s="37" t="str">
+        <f aca="false">IF($Q48="","",IF(INDEX('Score Log'!$D:$D,$Q48)="","",INDEX('Score Log'!$D:$D,$Q48)))</f>
+        <v/>
+      </c>
+      <c r="D48" s="38" t="str">
+        <f aca="false">IF($B48="","",COUNTIFS('Score Log'!$C$4:$C$203,$B48,'Score Log'!$E$4:$E$203,$A48))</f>
+        <v/>
+      </c>
+      <c r="E48" s="39" t="str">
+        <f aca="false">IF($B48="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B48,'Score Log'!$E$4:$E$203,$A48),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F48" s="39" t="str">
+        <f aca="false">IF($B48="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B48,'Score Log'!$E$4:$E$203,$A48),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="39" t="str">
+        <f aca="false">IF($B48="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B48,'Score Log'!$E$4:$E$203,$A48),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H48" s="39" t="str">
+        <f aca="false">IF($B48="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B48,'Score Log'!$E$4:$E$203,$A48),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I48" s="39" t="str">
+        <f aca="false">IF($B48="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B48,'Score Log'!$E$4:$E$203,$A48),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J48" s="40" t="str">
+        <f aca="false">IF(OR($B48="",$D48=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B48,'Score Log'!$E$4:$E$203,$A48,'Score Log'!$U$4:$U$203,"Yes")/$D48,"-"))</f>
+        <v/>
+      </c>
+      <c r="K48" s="41" t="str">
+        <f aca="false">IF($B48="","",IF(ISNUMBER($F48),MAX(1,MIN(5,ROUND(6-$F48,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L48" s="41" t="str">
+        <f aca="false">IF($B48="","",IF(ISNUMBER($G48),MAX(1,MIN(5,ROUND(6-$G48,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M48" s="41" t="str">
+        <f aca="false">IF($B48="","",IF(AND(ISNUMBER($P48),ISNUMBER($O48)),MAX(1,MIN(5,ROUND(6-AVERAGE($P48,$O48),0))),IF(ISNUMBER($P48),MAX(1,MIN(5,ROUND(6-$P48,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O48" s="33" t="str">
+        <f aca="false">IF($B48="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B48),""))</f>
+        <v/>
+      </c>
+      <c r="P48" s="33" t="str">
+        <f aca="false">IF($B48="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B48),""))</f>
+        <v/>
+      </c>
+      <c r="Q48" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA48" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C48="",'Score Log'!$E48=""),0,IF(COUNTIFS('Score Log'!$C$4:$C48,'Score Log'!$C48,'Score Log'!$E$4:$E48,'Score Log'!$E48)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB48" s="33" t="str">
+        <f aca="false">IF($AA48=1,SUM($AA$4:$AA48),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="36" t="str">
+        <f aca="false">IF($Q49="","",INDEX('Score Log'!$E:$E,$Q49))</f>
+        <v/>
+      </c>
+      <c r="B49" s="36" t="str">
+        <f aca="false">IF($Q49="","",INDEX('Score Log'!$C:$C,$Q49))</f>
+        <v/>
+      </c>
+      <c r="C49" s="37" t="str">
+        <f aca="false">IF($Q49="","",IF(INDEX('Score Log'!$D:$D,$Q49)="","",INDEX('Score Log'!$D:$D,$Q49)))</f>
+        <v/>
+      </c>
+      <c r="D49" s="38" t="str">
+        <f aca="false">IF($B49="","",COUNTIFS('Score Log'!$C$4:$C$203,$B49,'Score Log'!$E$4:$E$203,$A49))</f>
+        <v/>
+      </c>
+      <c r="E49" s="39" t="str">
+        <f aca="false">IF($B49="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B49,'Score Log'!$E$4:$E$203,$A49),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F49" s="39" t="str">
+        <f aca="false">IF($B49="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B49,'Score Log'!$E$4:$E$203,$A49),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G49" s="39" t="str">
+        <f aca="false">IF($B49="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B49,'Score Log'!$E$4:$E$203,$A49),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H49" s="39" t="str">
+        <f aca="false">IF($B49="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B49,'Score Log'!$E$4:$E$203,$A49),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I49" s="39" t="str">
+        <f aca="false">IF($B49="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B49,'Score Log'!$E$4:$E$203,$A49),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J49" s="40" t="str">
+        <f aca="false">IF(OR($B49="",$D49=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B49,'Score Log'!$E$4:$E$203,$A49,'Score Log'!$U$4:$U$203,"Yes")/$D49,"-"))</f>
+        <v/>
+      </c>
+      <c r="K49" s="41" t="str">
+        <f aca="false">IF($B49="","",IF(ISNUMBER($F49),MAX(1,MIN(5,ROUND(6-$F49,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L49" s="41" t="str">
+        <f aca="false">IF($B49="","",IF(ISNUMBER($G49),MAX(1,MIN(5,ROUND(6-$G49,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M49" s="41" t="str">
+        <f aca="false">IF($B49="","",IF(AND(ISNUMBER($P49),ISNUMBER($O49)),MAX(1,MIN(5,ROUND(6-AVERAGE($P49,$O49),0))),IF(ISNUMBER($P49),MAX(1,MIN(5,ROUND(6-$P49,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O49" s="33" t="str">
+        <f aca="false">IF($B49="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B49),""))</f>
+        <v/>
+      </c>
+      <c r="P49" s="33" t="str">
+        <f aca="false">IF($B49="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B49),""))</f>
+        <v/>
+      </c>
+      <c r="Q49" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA49" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C49="",'Score Log'!$E49=""),0,IF(COUNTIFS('Score Log'!$C$4:$C49,'Score Log'!$C49,'Score Log'!$E$4:$E49,'Score Log'!$E49)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB49" s="33" t="str">
+        <f aca="false">IF($AA49=1,SUM($AA$4:$AA49),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="36" t="str">
+        <f aca="false">IF($Q50="","",INDEX('Score Log'!$E:$E,$Q50))</f>
+        <v/>
+      </c>
+      <c r="B50" s="36" t="str">
+        <f aca="false">IF($Q50="","",INDEX('Score Log'!$C:$C,$Q50))</f>
+        <v/>
+      </c>
+      <c r="C50" s="37" t="str">
+        <f aca="false">IF($Q50="","",IF(INDEX('Score Log'!$D:$D,$Q50)="","",INDEX('Score Log'!$D:$D,$Q50)))</f>
+        <v/>
+      </c>
+      <c r="D50" s="38" t="str">
+        <f aca="false">IF($B50="","",COUNTIFS('Score Log'!$C$4:$C$203,$B50,'Score Log'!$E$4:$E$203,$A50))</f>
+        <v/>
+      </c>
+      <c r="E50" s="39" t="str">
+        <f aca="false">IF($B50="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B50,'Score Log'!$E$4:$E$203,$A50),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F50" s="39" t="str">
+        <f aca="false">IF($B50="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B50,'Score Log'!$E$4:$E$203,$A50),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G50" s="39" t="str">
+        <f aca="false">IF($B50="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B50,'Score Log'!$E$4:$E$203,$A50),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H50" s="39" t="str">
+        <f aca="false">IF($B50="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B50,'Score Log'!$E$4:$E$203,$A50),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I50" s="39" t="str">
+        <f aca="false">IF($B50="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B50,'Score Log'!$E$4:$E$203,$A50),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J50" s="40" t="str">
+        <f aca="false">IF(OR($B50="",$D50=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B50,'Score Log'!$E$4:$E$203,$A50,'Score Log'!$U$4:$U$203,"Yes")/$D50,"-"))</f>
+        <v/>
+      </c>
+      <c r="K50" s="41" t="str">
+        <f aca="false">IF($B50="","",IF(ISNUMBER($F50),MAX(1,MIN(5,ROUND(6-$F50,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L50" s="41" t="str">
+        <f aca="false">IF($B50="","",IF(ISNUMBER($G50),MAX(1,MIN(5,ROUND(6-$G50,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M50" s="41" t="str">
+        <f aca="false">IF($B50="","",IF(AND(ISNUMBER($P50),ISNUMBER($O50)),MAX(1,MIN(5,ROUND(6-AVERAGE($P50,$O50),0))),IF(ISNUMBER($P50),MAX(1,MIN(5,ROUND(6-$P50,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O50" s="33" t="str">
+        <f aca="false">IF($B50="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B50),""))</f>
+        <v/>
+      </c>
+      <c r="P50" s="33" t="str">
+        <f aca="false">IF($B50="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B50),""))</f>
+        <v/>
+      </c>
+      <c r="Q50" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA50" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C50="",'Score Log'!$E50=""),0,IF(COUNTIFS('Score Log'!$C$4:$C50,'Score Log'!$C50,'Score Log'!$E$4:$E50,'Score Log'!$E50)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB50" s="33" t="str">
+        <f aca="false">IF($AA50=1,SUM($AA$4:$AA50),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="36" t="str">
+        <f aca="false">IF($Q51="","",INDEX('Score Log'!$E:$E,$Q51))</f>
+        <v/>
+      </c>
+      <c r="B51" s="36" t="str">
+        <f aca="false">IF($Q51="","",INDEX('Score Log'!$C:$C,$Q51))</f>
+        <v/>
+      </c>
+      <c r="C51" s="37" t="str">
+        <f aca="false">IF($Q51="","",IF(INDEX('Score Log'!$D:$D,$Q51)="","",INDEX('Score Log'!$D:$D,$Q51)))</f>
+        <v/>
+      </c>
+      <c r="D51" s="38" t="str">
+        <f aca="false">IF($B51="","",COUNTIFS('Score Log'!$C$4:$C$203,$B51,'Score Log'!$E$4:$E$203,$A51))</f>
+        <v/>
+      </c>
+      <c r="E51" s="39" t="str">
+        <f aca="false">IF($B51="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B51,'Score Log'!$E$4:$E$203,$A51),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F51" s="39" t="str">
+        <f aca="false">IF($B51="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B51,'Score Log'!$E$4:$E$203,$A51),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G51" s="39" t="str">
+        <f aca="false">IF($B51="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B51,'Score Log'!$E$4:$E$203,$A51),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H51" s="39" t="str">
+        <f aca="false">IF($B51="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B51,'Score Log'!$E$4:$E$203,$A51),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I51" s="39" t="str">
+        <f aca="false">IF($B51="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B51,'Score Log'!$E$4:$E$203,$A51),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J51" s="40" t="str">
+        <f aca="false">IF(OR($B51="",$D51=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B51,'Score Log'!$E$4:$E$203,$A51,'Score Log'!$U$4:$U$203,"Yes")/$D51,"-"))</f>
+        <v/>
+      </c>
+      <c r="K51" s="41" t="str">
+        <f aca="false">IF($B51="","",IF(ISNUMBER($F51),MAX(1,MIN(5,ROUND(6-$F51,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L51" s="41" t="str">
+        <f aca="false">IF($B51="","",IF(ISNUMBER($G51),MAX(1,MIN(5,ROUND(6-$G51,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M51" s="41" t="str">
+        <f aca="false">IF($B51="","",IF(AND(ISNUMBER($P51),ISNUMBER($O51)),MAX(1,MIN(5,ROUND(6-AVERAGE($P51,$O51),0))),IF(ISNUMBER($P51),MAX(1,MIN(5,ROUND(6-$P51,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O51" s="33" t="str">
+        <f aca="false">IF($B51="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B51),""))</f>
+        <v/>
+      </c>
+      <c r="P51" s="33" t="str">
+        <f aca="false">IF($B51="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B51),""))</f>
+        <v/>
+      </c>
+      <c r="Q51" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA51" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C51="",'Score Log'!$E51=""),0,IF(COUNTIFS('Score Log'!$C$4:$C51,'Score Log'!$C51,'Score Log'!$E$4:$E51,'Score Log'!$E51)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB51" s="33" t="str">
+        <f aca="false">IF($AA51=1,SUM($AA$4:$AA51),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="36" t="str">
+        <f aca="false">IF($Q52="","",INDEX('Score Log'!$E:$E,$Q52))</f>
+        <v/>
+      </c>
+      <c r="B52" s="36" t="str">
+        <f aca="false">IF($Q52="","",INDEX('Score Log'!$C:$C,$Q52))</f>
+        <v/>
+      </c>
+      <c r="C52" s="37" t="str">
+        <f aca="false">IF($Q52="","",IF(INDEX('Score Log'!$D:$D,$Q52)="","",INDEX('Score Log'!$D:$D,$Q52)))</f>
+        <v/>
+      </c>
+      <c r="D52" s="38" t="str">
+        <f aca="false">IF($B52="","",COUNTIFS('Score Log'!$C$4:$C$203,$B52,'Score Log'!$E$4:$E$203,$A52))</f>
+        <v/>
+      </c>
+      <c r="E52" s="39" t="str">
+        <f aca="false">IF($B52="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B52,'Score Log'!$E$4:$E$203,$A52),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F52" s="39" t="str">
+        <f aca="false">IF($B52="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B52,'Score Log'!$E$4:$E$203,$A52),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G52" s="39" t="str">
+        <f aca="false">IF($B52="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B52,'Score Log'!$E$4:$E$203,$A52),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H52" s="39" t="str">
+        <f aca="false">IF($B52="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B52,'Score Log'!$E$4:$E$203,$A52),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I52" s="39" t="str">
+        <f aca="false">IF($B52="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B52,'Score Log'!$E$4:$E$203,$A52),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J52" s="40" t="str">
+        <f aca="false">IF(OR($B52="",$D52=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B52,'Score Log'!$E$4:$E$203,$A52,'Score Log'!$U$4:$U$203,"Yes")/$D52,"-"))</f>
+        <v/>
+      </c>
+      <c r="K52" s="41" t="str">
+        <f aca="false">IF($B52="","",IF(ISNUMBER($F52),MAX(1,MIN(5,ROUND(6-$F52,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L52" s="41" t="str">
+        <f aca="false">IF($B52="","",IF(ISNUMBER($G52),MAX(1,MIN(5,ROUND(6-$G52,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M52" s="41" t="str">
+        <f aca="false">IF($B52="","",IF(AND(ISNUMBER($P52),ISNUMBER($O52)),MAX(1,MIN(5,ROUND(6-AVERAGE($P52,$O52),0))),IF(ISNUMBER($P52),MAX(1,MIN(5,ROUND(6-$P52,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O52" s="33" t="str">
+        <f aca="false">IF($B52="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B52),""))</f>
+        <v/>
+      </c>
+      <c r="P52" s="33" t="str">
+        <f aca="false">IF($B52="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B52),""))</f>
+        <v/>
+      </c>
+      <c r="Q52" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA52" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C52="",'Score Log'!$E52=""),0,IF(COUNTIFS('Score Log'!$C$4:$C52,'Score Log'!$C52,'Score Log'!$E$4:$E52,'Score Log'!$E52)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB52" s="33" t="str">
+        <f aca="false">IF($AA52=1,SUM($AA$4:$AA52),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="36" t="str">
+        <f aca="false">IF($Q53="","",INDEX('Score Log'!$E:$E,$Q53))</f>
+        <v/>
+      </c>
+      <c r="B53" s="36" t="str">
+        <f aca="false">IF($Q53="","",INDEX('Score Log'!$C:$C,$Q53))</f>
+        <v/>
+      </c>
+      <c r="C53" s="37" t="str">
+        <f aca="false">IF($Q53="","",IF(INDEX('Score Log'!$D:$D,$Q53)="","",INDEX('Score Log'!$D:$D,$Q53)))</f>
+        <v/>
+      </c>
+      <c r="D53" s="38" t="str">
+        <f aca="false">IF($B53="","",COUNTIFS('Score Log'!$C$4:$C$203,$B53,'Score Log'!$E$4:$E$203,$A53))</f>
+        <v/>
+      </c>
+      <c r="E53" s="39" t="str">
+        <f aca="false">IF($B53="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B53,'Score Log'!$E$4:$E$203,$A53),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F53" s="39" t="str">
+        <f aca="false">IF($B53="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B53,'Score Log'!$E$4:$E$203,$A53),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G53" s="39" t="str">
+        <f aca="false">IF($B53="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B53,'Score Log'!$E$4:$E$203,$A53),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H53" s="39" t="str">
+        <f aca="false">IF($B53="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B53,'Score Log'!$E$4:$E$203,$A53),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I53" s="39" t="str">
+        <f aca="false">IF($B53="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B53,'Score Log'!$E$4:$E$203,$A53),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J53" s="40" t="str">
+        <f aca="false">IF(OR($B53="",$D53=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B53,'Score Log'!$E$4:$E$203,$A53,'Score Log'!$U$4:$U$203,"Yes")/$D53,"-"))</f>
+        <v/>
+      </c>
+      <c r="K53" s="41" t="str">
+        <f aca="false">IF($B53="","",IF(ISNUMBER($F53),MAX(1,MIN(5,ROUND(6-$F53,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L53" s="41" t="str">
+        <f aca="false">IF($B53="","",IF(ISNUMBER($G53),MAX(1,MIN(5,ROUND(6-$G53,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M53" s="41" t="str">
+        <f aca="false">IF($B53="","",IF(AND(ISNUMBER($P53),ISNUMBER($O53)),MAX(1,MIN(5,ROUND(6-AVERAGE($P53,$O53),0))),IF(ISNUMBER($P53),MAX(1,MIN(5,ROUND(6-$P53,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O53" s="33" t="str">
+        <f aca="false">IF($B53="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B53),""))</f>
+        <v/>
+      </c>
+      <c r="P53" s="33" t="str">
+        <f aca="false">IF($B53="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B53),""))</f>
+        <v/>
+      </c>
+      <c r="Q53" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA53" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C53="",'Score Log'!$E53=""),0,IF(COUNTIFS('Score Log'!$C$4:$C53,'Score Log'!$C53,'Score Log'!$E$4:$E53,'Score Log'!$E53)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB53" s="33" t="str">
+        <f aca="false">IF($AA53=1,SUM($AA$4:$AA53),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="36" t="str">
+        <f aca="false">IF($Q54="","",INDEX('Score Log'!$E:$E,$Q54))</f>
+        <v/>
+      </c>
+      <c r="B54" s="36" t="str">
+        <f aca="false">IF($Q54="","",INDEX('Score Log'!$C:$C,$Q54))</f>
+        <v/>
+      </c>
+      <c r="C54" s="37" t="str">
+        <f aca="false">IF($Q54="","",IF(INDEX('Score Log'!$D:$D,$Q54)="","",INDEX('Score Log'!$D:$D,$Q54)))</f>
+        <v/>
+      </c>
+      <c r="D54" s="38" t="str">
+        <f aca="false">IF($B54="","",COUNTIFS('Score Log'!$C$4:$C$203,$B54,'Score Log'!$E$4:$E$203,$A54))</f>
+        <v/>
+      </c>
+      <c r="E54" s="39" t="str">
+        <f aca="false">IF($B54="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B54,'Score Log'!$E$4:$E$203,$A54),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F54" s="39" t="str">
+        <f aca="false">IF($B54="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B54,'Score Log'!$E$4:$E$203,$A54),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G54" s="39" t="str">
+        <f aca="false">IF($B54="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B54,'Score Log'!$E$4:$E$203,$A54),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H54" s="39" t="str">
+        <f aca="false">IF($B54="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B54,'Score Log'!$E$4:$E$203,$A54),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I54" s="39" t="str">
+        <f aca="false">IF($B54="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B54,'Score Log'!$E$4:$E$203,$A54),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J54" s="40" t="str">
+        <f aca="false">IF(OR($B54="",$D54=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B54,'Score Log'!$E$4:$E$203,$A54,'Score Log'!$U$4:$U$203,"Yes")/$D54,"-"))</f>
+        <v/>
+      </c>
+      <c r="K54" s="41" t="str">
+        <f aca="false">IF($B54="","",IF(ISNUMBER($F54),MAX(1,MIN(5,ROUND(6-$F54,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L54" s="41" t="str">
+        <f aca="false">IF($B54="","",IF(ISNUMBER($G54),MAX(1,MIN(5,ROUND(6-$G54,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M54" s="41" t="str">
+        <f aca="false">IF($B54="","",IF(AND(ISNUMBER($P54),ISNUMBER($O54)),MAX(1,MIN(5,ROUND(6-AVERAGE($P54,$O54),0))),IF(ISNUMBER($P54),MAX(1,MIN(5,ROUND(6-$P54,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O54" s="33" t="str">
+        <f aca="false">IF($B54="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B54),""))</f>
+        <v/>
+      </c>
+      <c r="P54" s="33" t="str">
+        <f aca="false">IF($B54="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B54),""))</f>
+        <v/>
+      </c>
+      <c r="Q54" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA54" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C54="",'Score Log'!$E54=""),0,IF(COUNTIFS('Score Log'!$C$4:$C54,'Score Log'!$C54,'Score Log'!$E$4:$E54,'Score Log'!$E54)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB54" s="33" t="str">
+        <f aca="false">IF($AA54=1,SUM($AA$4:$AA54),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="36" t="str">
+        <f aca="false">IF($Q55="","",INDEX('Score Log'!$E:$E,$Q55))</f>
+        <v/>
+      </c>
+      <c r="B55" s="36" t="str">
+        <f aca="false">IF($Q55="","",INDEX('Score Log'!$C:$C,$Q55))</f>
+        <v/>
+      </c>
+      <c r="C55" s="37" t="str">
+        <f aca="false">IF($Q55="","",IF(INDEX('Score Log'!$D:$D,$Q55)="","",INDEX('Score Log'!$D:$D,$Q55)))</f>
+        <v/>
+      </c>
+      <c r="D55" s="38" t="str">
+        <f aca="false">IF($B55="","",COUNTIFS('Score Log'!$C$4:$C$203,$B55,'Score Log'!$E$4:$E$203,$A55))</f>
+        <v/>
+      </c>
+      <c r="E55" s="39" t="str">
+        <f aca="false">IF($B55="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B55,'Score Log'!$E$4:$E$203,$A55),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F55" s="39" t="str">
+        <f aca="false">IF($B55="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B55,'Score Log'!$E$4:$E$203,$A55),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G55" s="39" t="str">
+        <f aca="false">IF($B55="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B55,'Score Log'!$E$4:$E$203,$A55),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H55" s="39" t="str">
+        <f aca="false">IF($B55="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B55,'Score Log'!$E$4:$E$203,$A55),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I55" s="39" t="str">
+        <f aca="false">IF($B55="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B55,'Score Log'!$E$4:$E$203,$A55),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J55" s="40" t="str">
+        <f aca="false">IF(OR($B55="",$D55=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B55,'Score Log'!$E$4:$E$203,$A55,'Score Log'!$U$4:$U$203,"Yes")/$D55,"-"))</f>
+        <v/>
+      </c>
+      <c r="K55" s="41" t="str">
+        <f aca="false">IF($B55="","",IF(ISNUMBER($F55),MAX(1,MIN(5,ROUND(6-$F55,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L55" s="41" t="str">
+        <f aca="false">IF($B55="","",IF(ISNUMBER($G55),MAX(1,MIN(5,ROUND(6-$G55,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M55" s="41" t="str">
+        <f aca="false">IF($B55="","",IF(AND(ISNUMBER($P55),ISNUMBER($O55)),MAX(1,MIN(5,ROUND(6-AVERAGE($P55,$O55),0))),IF(ISNUMBER($P55),MAX(1,MIN(5,ROUND(6-$P55,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O55" s="33" t="str">
+        <f aca="false">IF($B55="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B55),""))</f>
+        <v/>
+      </c>
+      <c r="P55" s="33" t="str">
+        <f aca="false">IF($B55="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B55),""))</f>
+        <v/>
+      </c>
+      <c r="Q55" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA55" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C55="",'Score Log'!$E55=""),0,IF(COUNTIFS('Score Log'!$C$4:$C55,'Score Log'!$C55,'Score Log'!$E$4:$E55,'Score Log'!$E55)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB55" s="33" t="str">
+        <f aca="false">IF($AA55=1,SUM($AA$4:$AA55),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="36" t="str">
+        <f aca="false">IF($Q56="","",INDEX('Score Log'!$E:$E,$Q56))</f>
+        <v/>
+      </c>
+      <c r="B56" s="36" t="str">
+        <f aca="false">IF($Q56="","",INDEX('Score Log'!$C:$C,$Q56))</f>
+        <v/>
+      </c>
+      <c r="C56" s="37" t="str">
+        <f aca="false">IF($Q56="","",IF(INDEX('Score Log'!$D:$D,$Q56)="","",INDEX('Score Log'!$D:$D,$Q56)))</f>
+        <v/>
+      </c>
+      <c r="D56" s="38" t="str">
+        <f aca="false">IF($B56="","",COUNTIFS('Score Log'!$C$4:$C$203,$B56,'Score Log'!$E$4:$E$203,$A56))</f>
+        <v/>
+      </c>
+      <c r="E56" s="39" t="str">
+        <f aca="false">IF($B56="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B56,'Score Log'!$E$4:$E$203,$A56),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F56" s="39" t="str">
+        <f aca="false">IF($B56="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B56,'Score Log'!$E$4:$E$203,$A56),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G56" s="39" t="str">
+        <f aca="false">IF($B56="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B56,'Score Log'!$E$4:$E$203,$A56),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H56" s="39" t="str">
+        <f aca="false">IF($B56="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B56,'Score Log'!$E$4:$E$203,$A56),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I56" s="39" t="str">
+        <f aca="false">IF($B56="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B56,'Score Log'!$E$4:$E$203,$A56),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J56" s="40" t="str">
+        <f aca="false">IF(OR($B56="",$D56=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B56,'Score Log'!$E$4:$E$203,$A56,'Score Log'!$U$4:$U$203,"Yes")/$D56,"-"))</f>
+        <v/>
+      </c>
+      <c r="K56" s="41" t="str">
+        <f aca="false">IF($B56="","",IF(ISNUMBER($F56),MAX(1,MIN(5,ROUND(6-$F56,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L56" s="41" t="str">
+        <f aca="false">IF($B56="","",IF(ISNUMBER($G56),MAX(1,MIN(5,ROUND(6-$G56,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M56" s="41" t="str">
+        <f aca="false">IF($B56="","",IF(AND(ISNUMBER($P56),ISNUMBER($O56)),MAX(1,MIN(5,ROUND(6-AVERAGE($P56,$O56),0))),IF(ISNUMBER($P56),MAX(1,MIN(5,ROUND(6-$P56,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O56" s="33" t="str">
+        <f aca="false">IF($B56="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B56),""))</f>
+        <v/>
+      </c>
+      <c r="P56" s="33" t="str">
+        <f aca="false">IF($B56="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B56),""))</f>
+        <v/>
+      </c>
+      <c r="Q56" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA56" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C56="",'Score Log'!$E56=""),0,IF(COUNTIFS('Score Log'!$C$4:$C56,'Score Log'!$C56,'Score Log'!$E$4:$E56,'Score Log'!$E56)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB56" s="33" t="str">
+        <f aca="false">IF($AA56=1,SUM($AA$4:$AA56),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="36" t="str">
+        <f aca="false">IF($Q57="","",INDEX('Score Log'!$E:$E,$Q57))</f>
+        <v/>
+      </c>
+      <c r="B57" s="36" t="str">
+        <f aca="false">IF($Q57="","",INDEX('Score Log'!$C:$C,$Q57))</f>
+        <v/>
+      </c>
+      <c r="C57" s="37" t="str">
+        <f aca="false">IF($Q57="","",IF(INDEX('Score Log'!$D:$D,$Q57)="","",INDEX('Score Log'!$D:$D,$Q57)))</f>
+        <v/>
+      </c>
+      <c r="D57" s="38" t="str">
+        <f aca="false">IF($B57="","",COUNTIFS('Score Log'!$C$4:$C$203,$B57,'Score Log'!$E$4:$E$203,$A57))</f>
+        <v/>
+      </c>
+      <c r="E57" s="39" t="str">
+        <f aca="false">IF($B57="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B57,'Score Log'!$E$4:$E$203,$A57),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F57" s="39" t="str">
+        <f aca="false">IF($B57="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B57,'Score Log'!$E$4:$E$203,$A57),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G57" s="39" t="str">
+        <f aca="false">IF($B57="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B57,'Score Log'!$E$4:$E$203,$A57),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H57" s="39" t="str">
+        <f aca="false">IF($B57="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B57,'Score Log'!$E$4:$E$203,$A57),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I57" s="39" t="str">
+        <f aca="false">IF($B57="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B57,'Score Log'!$E$4:$E$203,$A57),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J57" s="40" t="str">
+        <f aca="false">IF(OR($B57="",$D57=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B57,'Score Log'!$E$4:$E$203,$A57,'Score Log'!$U$4:$U$203,"Yes")/$D57,"-"))</f>
+        <v/>
+      </c>
+      <c r="K57" s="41" t="str">
+        <f aca="false">IF($B57="","",IF(ISNUMBER($F57),MAX(1,MIN(5,ROUND(6-$F57,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L57" s="41" t="str">
+        <f aca="false">IF($B57="","",IF(ISNUMBER($G57),MAX(1,MIN(5,ROUND(6-$G57,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M57" s="41" t="str">
+        <f aca="false">IF($B57="","",IF(AND(ISNUMBER($P57),ISNUMBER($O57)),MAX(1,MIN(5,ROUND(6-AVERAGE($P57,$O57),0))),IF(ISNUMBER($P57),MAX(1,MIN(5,ROUND(6-$P57,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O57" s="33" t="str">
+        <f aca="false">IF($B57="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B57),""))</f>
+        <v/>
+      </c>
+      <c r="P57" s="33" t="str">
+        <f aca="false">IF($B57="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B57),""))</f>
+        <v/>
+      </c>
+      <c r="Q57" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA57" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C57="",'Score Log'!$E57=""),0,IF(COUNTIFS('Score Log'!$C$4:$C57,'Score Log'!$C57,'Score Log'!$E$4:$E57,'Score Log'!$E57)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB57" s="33" t="str">
+        <f aca="false">IF($AA57=1,SUM($AA$4:$AA57),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="36" t="str">
+        <f aca="false">IF($Q58="","",INDEX('Score Log'!$E:$E,$Q58))</f>
+        <v/>
+      </c>
+      <c r="B58" s="36" t="str">
+        <f aca="false">IF($Q58="","",INDEX('Score Log'!$C:$C,$Q58))</f>
+        <v/>
+      </c>
+      <c r="C58" s="37" t="str">
+        <f aca="false">IF($Q58="","",IF(INDEX('Score Log'!$D:$D,$Q58)="","",INDEX('Score Log'!$D:$D,$Q58)))</f>
+        <v/>
+      </c>
+      <c r="D58" s="38" t="str">
+        <f aca="false">IF($B58="","",COUNTIFS('Score Log'!$C$4:$C$203,$B58,'Score Log'!$E$4:$E$203,$A58))</f>
+        <v/>
+      </c>
+      <c r="E58" s="39" t="str">
+        <f aca="false">IF($B58="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B58,'Score Log'!$E$4:$E$203,$A58),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F58" s="39" t="str">
+        <f aca="false">IF($B58="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B58,'Score Log'!$E$4:$E$203,$A58),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G58" s="39" t="str">
+        <f aca="false">IF($B58="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B58,'Score Log'!$E$4:$E$203,$A58),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H58" s="39" t="str">
+        <f aca="false">IF($B58="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B58,'Score Log'!$E$4:$E$203,$A58),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I58" s="39" t="str">
+        <f aca="false">IF($B58="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B58,'Score Log'!$E$4:$E$203,$A58),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J58" s="40" t="str">
+        <f aca="false">IF(OR($B58="",$D58=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B58,'Score Log'!$E$4:$E$203,$A58,'Score Log'!$U$4:$U$203,"Yes")/$D58,"-"))</f>
+        <v/>
+      </c>
+      <c r="K58" s="41" t="str">
+        <f aca="false">IF($B58="","",IF(ISNUMBER($F58),MAX(1,MIN(5,ROUND(6-$F58,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L58" s="41" t="str">
+        <f aca="false">IF($B58="","",IF(ISNUMBER($G58),MAX(1,MIN(5,ROUND(6-$G58,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M58" s="41" t="str">
+        <f aca="false">IF($B58="","",IF(AND(ISNUMBER($P58),ISNUMBER($O58)),MAX(1,MIN(5,ROUND(6-AVERAGE($P58,$O58),0))),IF(ISNUMBER($P58),MAX(1,MIN(5,ROUND(6-$P58,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O58" s="33" t="str">
+        <f aca="false">IF($B58="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B58),""))</f>
+        <v/>
+      </c>
+      <c r="P58" s="33" t="str">
+        <f aca="false">IF($B58="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B58),""))</f>
+        <v/>
+      </c>
+      <c r="Q58" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA58" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C58="",'Score Log'!$E58=""),0,IF(COUNTIFS('Score Log'!$C$4:$C58,'Score Log'!$C58,'Score Log'!$E$4:$E58,'Score Log'!$E58)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB58" s="33" t="str">
+        <f aca="false">IF($AA58=1,SUM($AA$4:$AA58),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="36" t="str">
+        <f aca="false">IF($Q59="","",INDEX('Score Log'!$E:$E,$Q59))</f>
+        <v/>
+      </c>
+      <c r="B59" s="36" t="str">
+        <f aca="false">IF($Q59="","",INDEX('Score Log'!$C:$C,$Q59))</f>
+        <v/>
+      </c>
+      <c r="C59" s="37" t="str">
+        <f aca="false">IF($Q59="","",IF(INDEX('Score Log'!$D:$D,$Q59)="","",INDEX('Score Log'!$D:$D,$Q59)))</f>
+        <v/>
+      </c>
+      <c r="D59" s="38" t="str">
+        <f aca="false">IF($B59="","",COUNTIFS('Score Log'!$C$4:$C$203,$B59,'Score Log'!$E$4:$E$203,$A59))</f>
+        <v/>
+      </c>
+      <c r="E59" s="39" t="str">
+        <f aca="false">IF($B59="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B59,'Score Log'!$E$4:$E$203,$A59),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F59" s="39" t="str">
+        <f aca="false">IF($B59="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B59,'Score Log'!$E$4:$E$203,$A59),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G59" s="39" t="str">
+        <f aca="false">IF($B59="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B59,'Score Log'!$E$4:$E$203,$A59),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H59" s="39" t="str">
+        <f aca="false">IF($B59="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B59,'Score Log'!$E$4:$E$203,$A59),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I59" s="39" t="str">
+        <f aca="false">IF($B59="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B59,'Score Log'!$E$4:$E$203,$A59),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J59" s="40" t="str">
+        <f aca="false">IF(OR($B59="",$D59=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B59,'Score Log'!$E$4:$E$203,$A59,'Score Log'!$U$4:$U$203,"Yes")/$D59,"-"))</f>
+        <v/>
+      </c>
+      <c r="K59" s="41" t="str">
+        <f aca="false">IF($B59="","",IF(ISNUMBER($F59),MAX(1,MIN(5,ROUND(6-$F59,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L59" s="41" t="str">
+        <f aca="false">IF($B59="","",IF(ISNUMBER($G59),MAX(1,MIN(5,ROUND(6-$G59,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M59" s="41" t="str">
+        <f aca="false">IF($B59="","",IF(AND(ISNUMBER($P59),ISNUMBER($O59)),MAX(1,MIN(5,ROUND(6-AVERAGE($P59,$O59),0))),IF(ISNUMBER($P59),MAX(1,MIN(5,ROUND(6-$P59,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O59" s="33" t="str">
+        <f aca="false">IF($B59="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B59),""))</f>
+        <v/>
+      </c>
+      <c r="P59" s="33" t="str">
+        <f aca="false">IF($B59="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B59),""))</f>
+        <v/>
+      </c>
+      <c r="Q59" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA59" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C59="",'Score Log'!$E59=""),0,IF(COUNTIFS('Score Log'!$C$4:$C59,'Score Log'!$C59,'Score Log'!$E$4:$E59,'Score Log'!$E59)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB59" s="33" t="str">
+        <f aca="false">IF($AA59=1,SUM($AA$4:$AA59),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="36" t="str">
+        <f aca="false">IF($Q60="","",INDEX('Score Log'!$E:$E,$Q60))</f>
+        <v/>
+      </c>
+      <c r="B60" s="36" t="str">
+        <f aca="false">IF($Q60="","",INDEX('Score Log'!$C:$C,$Q60))</f>
+        <v/>
+      </c>
+      <c r="C60" s="37" t="str">
+        <f aca="false">IF($Q60="","",IF(INDEX('Score Log'!$D:$D,$Q60)="","",INDEX('Score Log'!$D:$D,$Q60)))</f>
+        <v/>
+      </c>
+      <c r="D60" s="38" t="str">
+        <f aca="false">IF($B60="","",COUNTIFS('Score Log'!$C$4:$C$203,$B60,'Score Log'!$E$4:$E$203,$A60))</f>
+        <v/>
+      </c>
+      <c r="E60" s="39" t="str">
+        <f aca="false">IF($B60="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B60,'Score Log'!$E$4:$E$203,$A60),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F60" s="39" t="str">
+        <f aca="false">IF($B60="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B60,'Score Log'!$E$4:$E$203,$A60),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G60" s="39" t="str">
+        <f aca="false">IF($B60="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B60,'Score Log'!$E$4:$E$203,$A60),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H60" s="39" t="str">
+        <f aca="false">IF($B60="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B60,'Score Log'!$E$4:$E$203,$A60),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I60" s="39" t="str">
+        <f aca="false">IF($B60="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B60,'Score Log'!$E$4:$E$203,$A60),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J60" s="40" t="str">
+        <f aca="false">IF(OR($B60="",$D60=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B60,'Score Log'!$E$4:$E$203,$A60,'Score Log'!$U$4:$U$203,"Yes")/$D60,"-"))</f>
+        <v/>
+      </c>
+      <c r="K60" s="41" t="str">
+        <f aca="false">IF($B60="","",IF(ISNUMBER($F60),MAX(1,MIN(5,ROUND(6-$F60,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L60" s="41" t="str">
+        <f aca="false">IF($B60="","",IF(ISNUMBER($G60),MAX(1,MIN(5,ROUND(6-$G60,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M60" s="41" t="str">
+        <f aca="false">IF($B60="","",IF(AND(ISNUMBER($P60),ISNUMBER($O60)),MAX(1,MIN(5,ROUND(6-AVERAGE($P60,$O60),0))),IF(ISNUMBER($P60),MAX(1,MIN(5,ROUND(6-$P60,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O60" s="33" t="str">
+        <f aca="false">IF($B60="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B60),""))</f>
+        <v/>
+      </c>
+      <c r="P60" s="33" t="str">
+        <f aca="false">IF($B60="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B60),""))</f>
+        <v/>
+      </c>
+      <c r="Q60" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA60" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C60="",'Score Log'!$E60=""),0,IF(COUNTIFS('Score Log'!$C$4:$C60,'Score Log'!$C60,'Score Log'!$E$4:$E60,'Score Log'!$E60)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB60" s="33" t="str">
+        <f aca="false">IF($AA60=1,SUM($AA$4:$AA60),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="36" t="str">
+        <f aca="false">IF($Q61="","",INDEX('Score Log'!$E:$E,$Q61))</f>
+        <v/>
+      </c>
+      <c r="B61" s="36" t="str">
+        <f aca="false">IF($Q61="","",INDEX('Score Log'!$C:$C,$Q61))</f>
+        <v/>
+      </c>
+      <c r="C61" s="37" t="str">
+        <f aca="false">IF($Q61="","",IF(INDEX('Score Log'!$D:$D,$Q61)="","",INDEX('Score Log'!$D:$D,$Q61)))</f>
+        <v/>
+      </c>
+      <c r="D61" s="38" t="str">
+        <f aca="false">IF($B61="","",COUNTIFS('Score Log'!$C$4:$C$203,$B61,'Score Log'!$E$4:$E$203,$A61))</f>
+        <v/>
+      </c>
+      <c r="E61" s="39" t="str">
+        <f aca="false">IF($B61="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B61,'Score Log'!$E$4:$E$203,$A61),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F61" s="39" t="str">
+        <f aca="false">IF($B61="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B61,'Score Log'!$E$4:$E$203,$A61),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G61" s="39" t="str">
+        <f aca="false">IF($B61="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B61,'Score Log'!$E$4:$E$203,$A61),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H61" s="39" t="str">
+        <f aca="false">IF($B61="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B61,'Score Log'!$E$4:$E$203,$A61),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I61" s="39" t="str">
+        <f aca="false">IF($B61="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B61,'Score Log'!$E$4:$E$203,$A61),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J61" s="40" t="str">
+        <f aca="false">IF(OR($B61="",$D61=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B61,'Score Log'!$E$4:$E$203,$A61,'Score Log'!$U$4:$U$203,"Yes")/$D61,"-"))</f>
+        <v/>
+      </c>
+      <c r="K61" s="41" t="str">
+        <f aca="false">IF($B61="","",IF(ISNUMBER($F61),MAX(1,MIN(5,ROUND(6-$F61,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L61" s="41" t="str">
+        <f aca="false">IF($B61="","",IF(ISNUMBER($G61),MAX(1,MIN(5,ROUND(6-$G61,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M61" s="41" t="str">
+        <f aca="false">IF($B61="","",IF(AND(ISNUMBER($P61),ISNUMBER($O61)),MAX(1,MIN(5,ROUND(6-AVERAGE($P61,$O61),0))),IF(ISNUMBER($P61),MAX(1,MIN(5,ROUND(6-$P61,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O61" s="33" t="str">
+        <f aca="false">IF($B61="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B61),""))</f>
+        <v/>
+      </c>
+      <c r="P61" s="33" t="str">
+        <f aca="false">IF($B61="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B61),""))</f>
+        <v/>
+      </c>
+      <c r="Q61" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA61" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C61="",'Score Log'!$E61=""),0,IF(COUNTIFS('Score Log'!$C$4:$C61,'Score Log'!$C61,'Score Log'!$E$4:$E61,'Score Log'!$E61)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB61" s="33" t="str">
+        <f aca="false">IF($AA61=1,SUM($AA$4:$AA61),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="36" t="str">
+        <f aca="false">IF($Q62="","",INDEX('Score Log'!$E:$E,$Q62))</f>
+        <v/>
+      </c>
+      <c r="B62" s="36" t="str">
+        <f aca="false">IF($Q62="","",INDEX('Score Log'!$C:$C,$Q62))</f>
+        <v/>
+      </c>
+      <c r="C62" s="37" t="str">
+        <f aca="false">IF($Q62="","",IF(INDEX('Score Log'!$D:$D,$Q62)="","",INDEX('Score Log'!$D:$D,$Q62)))</f>
+        <v/>
+      </c>
+      <c r="D62" s="38" t="str">
+        <f aca="false">IF($B62="","",COUNTIFS('Score Log'!$C$4:$C$203,$B62,'Score Log'!$E$4:$E$203,$A62))</f>
+        <v/>
+      </c>
+      <c r="E62" s="39" t="str">
+        <f aca="false">IF($B62="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B62,'Score Log'!$E$4:$E$203,$A62),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F62" s="39" t="str">
+        <f aca="false">IF($B62="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B62,'Score Log'!$E$4:$E$203,$A62),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G62" s="39" t="str">
+        <f aca="false">IF($B62="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B62,'Score Log'!$E$4:$E$203,$A62),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H62" s="39" t="str">
+        <f aca="false">IF($B62="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B62,'Score Log'!$E$4:$E$203,$A62),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I62" s="39" t="str">
+        <f aca="false">IF($B62="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B62,'Score Log'!$E$4:$E$203,$A62),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J62" s="40" t="str">
+        <f aca="false">IF(OR($B62="",$D62=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B62,'Score Log'!$E$4:$E$203,$A62,'Score Log'!$U$4:$U$203,"Yes")/$D62,"-"))</f>
+        <v/>
+      </c>
+      <c r="K62" s="41" t="str">
+        <f aca="false">IF($B62="","",IF(ISNUMBER($F62),MAX(1,MIN(5,ROUND(6-$F62,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L62" s="41" t="str">
+        <f aca="false">IF($B62="","",IF(ISNUMBER($G62),MAX(1,MIN(5,ROUND(6-$G62,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M62" s="41" t="str">
+        <f aca="false">IF($B62="","",IF(AND(ISNUMBER($P62),ISNUMBER($O62)),MAX(1,MIN(5,ROUND(6-AVERAGE($P62,$O62),0))),IF(ISNUMBER($P62),MAX(1,MIN(5,ROUND(6-$P62,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O62" s="33" t="str">
+        <f aca="false">IF($B62="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B62),""))</f>
+        <v/>
+      </c>
+      <c r="P62" s="33" t="str">
+        <f aca="false">IF($B62="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B62),""))</f>
+        <v/>
+      </c>
+      <c r="Q62" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA62" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C62="",'Score Log'!$E62=""),0,IF(COUNTIFS('Score Log'!$C$4:$C62,'Score Log'!$C62,'Score Log'!$E$4:$E62,'Score Log'!$E62)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB62" s="33" t="str">
+        <f aca="false">IF($AA62=1,SUM($AA$4:$AA62),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="36" t="str">
+        <f aca="false">IF($Q63="","",INDEX('Score Log'!$E:$E,$Q63))</f>
+        <v/>
+      </c>
+      <c r="B63" s="36" t="str">
+        <f aca="false">IF($Q63="","",INDEX('Score Log'!$C:$C,$Q63))</f>
+        <v/>
+      </c>
+      <c r="C63" s="37" t="str">
+        <f aca="false">IF($Q63="","",IF(INDEX('Score Log'!$D:$D,$Q63)="","",INDEX('Score Log'!$D:$D,$Q63)))</f>
+        <v/>
+      </c>
+      <c r="D63" s="38" t="str">
+        <f aca="false">IF($B63="","",COUNTIFS('Score Log'!$C$4:$C$203,$B63,'Score Log'!$E$4:$E$203,$A63))</f>
+        <v/>
+      </c>
+      <c r="E63" s="39" t="str">
+        <f aca="false">IF($B63="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B63,'Score Log'!$E$4:$E$203,$A63),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F63" s="39" t="str">
+        <f aca="false">IF($B63="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B63,'Score Log'!$E$4:$E$203,$A63),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G63" s="39" t="str">
+        <f aca="false">IF($B63="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B63,'Score Log'!$E$4:$E$203,$A63),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H63" s="39" t="str">
+        <f aca="false">IF($B63="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B63,'Score Log'!$E$4:$E$203,$A63),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I63" s="39" t="str">
+        <f aca="false">IF($B63="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B63,'Score Log'!$E$4:$E$203,$A63),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J63" s="40" t="str">
+        <f aca="false">IF(OR($B63="",$D63=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B63,'Score Log'!$E$4:$E$203,$A63,'Score Log'!$U$4:$U$203,"Yes")/$D63,"-"))</f>
+        <v/>
+      </c>
+      <c r="K63" s="41" t="str">
+        <f aca="false">IF($B63="","",IF(ISNUMBER($F63),MAX(1,MIN(5,ROUND(6-$F63,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L63" s="41" t="str">
+        <f aca="false">IF($B63="","",IF(ISNUMBER($G63),MAX(1,MIN(5,ROUND(6-$G63,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M63" s="41" t="str">
+        <f aca="false">IF($B63="","",IF(AND(ISNUMBER($P63),ISNUMBER($O63)),MAX(1,MIN(5,ROUND(6-AVERAGE($P63,$O63),0))),IF(ISNUMBER($P63),MAX(1,MIN(5,ROUND(6-$P63,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O63" s="33" t="str">
+        <f aca="false">IF($B63="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B63),""))</f>
+        <v/>
+      </c>
+      <c r="P63" s="33" t="str">
+        <f aca="false">IF($B63="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B63),""))</f>
+        <v/>
+      </c>
+      <c r="Q63" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA63" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C63="",'Score Log'!$E63=""),0,IF(COUNTIFS('Score Log'!$C$4:$C63,'Score Log'!$C63,'Score Log'!$E$4:$E63,'Score Log'!$E63)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB63" s="33" t="str">
+        <f aca="false">IF($AA63=1,SUM($AA$4:$AA63),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="36" t="str">
+        <f aca="false">IF($Q64="","",INDEX('Score Log'!$E:$E,$Q64))</f>
+        <v/>
+      </c>
+      <c r="B64" s="36" t="str">
+        <f aca="false">IF($Q64="","",INDEX('Score Log'!$C:$C,$Q64))</f>
+        <v/>
+      </c>
+      <c r="C64" s="37" t="str">
+        <f aca="false">IF($Q64="","",IF(INDEX('Score Log'!$D:$D,$Q64)="","",INDEX('Score Log'!$D:$D,$Q64)))</f>
+        <v/>
+      </c>
+      <c r="D64" s="38" t="str">
+        <f aca="false">IF($B64="","",COUNTIFS('Score Log'!$C$4:$C$203,$B64,'Score Log'!$E$4:$E$203,$A64))</f>
+        <v/>
+      </c>
+      <c r="E64" s="39" t="str">
+        <f aca="false">IF($B64="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B64,'Score Log'!$E$4:$E$203,$A64),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="F64" s="39" t="str">
+        <f aca="false">IF($B64="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$H$4:$H$203,'Score Log'!$C$4:$C$203,$B64,'Score Log'!$E$4:$E$203,$A64),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="G64" s="39" t="str">
+        <f aca="false">IF($B64="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$J$4:$J$203,'Score Log'!$C$4:$C$203,$B64,'Score Log'!$E$4:$E$203,$A64),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="H64" s="39" t="str">
+        <f aca="false">IF($B64="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B64,'Score Log'!$E$4:$E$203,$A64),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="I64" s="39" t="str">
+        <f aca="false">IF($B64="","",IFERROR(ROUND(AVERAGEIFS('Score Log'!$N$4:$N$203,'Score Log'!$C$4:$C$203,$B64,'Score Log'!$E$4:$E$203,$A64),1),"-"))</f>
+        <v/>
+      </c>
+      <c r="J64" s="40" t="str">
+        <f aca="false">IF(OR($B64="",$D64=0),"",IFERROR(COUNTIFS('Score Log'!$C$4:$C$203,$B64,'Score Log'!$E$4:$E$203,$A64,'Score Log'!$U$4:$U$203,"Yes")/$D64,"-"))</f>
+        <v/>
+      </c>
+      <c r="K64" s="41" t="str">
+        <f aca="false">IF($B64="","",IF(ISNUMBER($F64),MAX(1,MIN(5,ROUND(6-$F64,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="L64" s="41" t="str">
+        <f aca="false">IF($B64="","",IF(ISNUMBER($G64),MAX(1,MIN(5,ROUND(6-$G64,0))),"-"))</f>
+        <v/>
+      </c>
+      <c r="M64" s="41" t="str">
+        <f aca="false">IF($B64="","",IF(AND(ISNUMBER($P64),ISNUMBER($O64)),MAX(1,MIN(5,ROUND(6-AVERAGE($P64,$O64),0))),IF(ISNUMBER($P64),MAX(1,MIN(5,ROUND(6-$P64,0))),"-")))</f>
+        <v/>
+      </c>
+      <c r="O64" s="33" t="str">
+        <f aca="false">IF($B64="","",IFERROR(AVERAGEIFS('Score Log'!$F$4:$F$203,'Score Log'!$C$4:$C$203,$B64),""))</f>
+        <v/>
+      </c>
+      <c r="P64" s="33" t="str">
+        <f aca="false">IF($B64="","",IFERROR(AVERAGEIFS('Score Log'!$L$4:$L$203,'Score Log'!$C$4:$C$203,$B64),""))</f>
+        <v/>
+      </c>
+      <c r="Q64" s="33" t="str">
+        <f aca="false">IFERROR(MATCH(ROW()-4,$AB$4:$AB$203,0)+3,"")</f>
+        <v/>
+      </c>
+      <c r="AA64" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C64="",'Score Log'!$E64=""),0,IF(COUNTIFS('Score Log'!$C$4:$C64,'Score Log'!$C64,'Score Log'!$E$4:$E64,'Score Log'!$E64)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB64" s="33" t="str">
+        <f aca="false">IF($AA64=1,SUM($AA$4:$AA64),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA65" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C65="",'Score Log'!$E65=""),0,IF(COUNTIFS('Score Log'!$C$4:$C65,'Score Log'!$C65,'Score Log'!$E$4:$E65,'Score Log'!$E65)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB65" s="33" t="str">
+        <f aca="false">IF($AA65=1,SUM($AA$4:$AA65),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA66" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C66="",'Score Log'!$E66=""),0,IF(COUNTIFS('Score Log'!$C$4:$C66,'Score Log'!$C66,'Score Log'!$E$4:$E66,'Score Log'!$E66)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB66" s="33" t="str">
+        <f aca="false">IF($AA66=1,SUM($AA$4:$AA66),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="B50" s="43"/>
-      <c r="C50" s="43"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="43"/>
-      <c r="I50" s="43"/>
-      <c r="J50" s="43"/>
-      <c r="K50" s="43"/>
-      <c r="L50" s="43"/>
-      <c r="M50" s="43"/>
-    </row>
-    <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="43" t="s">
+      <c r="AA67" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C67="",'Score Log'!$E67=""),0,IF(COUNTIFS('Score Log'!$C$4:$C67,'Score Log'!$C67,'Score Log'!$E$4:$E67,'Score Log'!$E67)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB67" s="33" t="str">
+        <f aca="false">IF($AA67=1,SUM($AA$4:$AA67),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="B51" s="43"/>
-      <c r="C51" s="43"/>
-      <c r="D51" s="43"/>
-      <c r="E51" s="43"/>
-      <c r="F51" s="43"/>
-      <c r="G51" s="43"/>
-      <c r="H51" s="43"/>
-      <c r="I51" s="43"/>
-      <c r="J51" s="43"/>
-      <c r="K51" s="43"/>
-      <c r="L51" s="43"/>
-      <c r="M51" s="43"/>
-    </row>
-    <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="43" t="s">
+      <c r="B68" s="43"/>
+      <c r="C68" s="43"/>
+      <c r="D68" s="43"/>
+      <c r="E68" s="43"/>
+      <c r="F68" s="43"/>
+      <c r="G68" s="43"/>
+      <c r="H68" s="43"/>
+      <c r="I68" s="43"/>
+      <c r="J68" s="43"/>
+      <c r="K68" s="43"/>
+      <c r="L68" s="43"/>
+      <c r="M68" s="43"/>
+      <c r="AA68" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C68="",'Score Log'!$E68=""),0,IF(COUNTIFS('Score Log'!$C$4:$C68,'Score Log'!$C68,'Score Log'!$E$4:$E68,'Score Log'!$E68)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB68" s="33" t="str">
+        <f aca="false">IF($AA68=1,SUM($AA$4:$AA68),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="B52" s="43"/>
-      <c r="C52" s="43"/>
-      <c r="D52" s="43"/>
-      <c r="E52" s="43"/>
-      <c r="F52" s="43"/>
-      <c r="G52" s="43"/>
-      <c r="H52" s="43"/>
-      <c r="I52" s="43"/>
-      <c r="J52" s="43"/>
-      <c r="K52" s="43"/>
-      <c r="L52" s="43"/>
-      <c r="M52" s="43"/>
+      <c r="B69" s="43"/>
+      <c r="C69" s="43"/>
+      <c r="D69" s="43"/>
+      <c r="E69" s="43"/>
+      <c r="F69" s="43"/>
+      <c r="G69" s="43"/>
+      <c r="H69" s="43"/>
+      <c r="I69" s="43"/>
+      <c r="J69" s="43"/>
+      <c r="K69" s="43"/>
+      <c r="L69" s="43"/>
+      <c r="M69" s="43"/>
+      <c r="AA69" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C69="",'Score Log'!$E69=""),0,IF(COUNTIFS('Score Log'!$C$4:$C69,'Score Log'!$C69,'Score Log'!$E$4:$E69,'Score Log'!$E69)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB69" s="33" t="str">
+        <f aca="false">IF($AA69=1,SUM($AA$4:$AA69),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="B70" s="43"/>
+      <c r="C70" s="43"/>
+      <c r="D70" s="43"/>
+      <c r="E70" s="43"/>
+      <c r="F70" s="43"/>
+      <c r="G70" s="43"/>
+      <c r="H70" s="43"/>
+      <c r="I70" s="43"/>
+      <c r="J70" s="43"/>
+      <c r="K70" s="43"/>
+      <c r="L70" s="43"/>
+      <c r="M70" s="43"/>
+      <c r="AA70" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C70="",'Score Log'!$E70=""),0,IF(COUNTIFS('Score Log'!$C$4:$C70,'Score Log'!$C70,'Score Log'!$E$4:$E70,'Score Log'!$E70)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB70" s="33" t="str">
+        <f aca="false">IF($AA70=1,SUM($AA$4:$AA70),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="B71" s="43"/>
+      <c r="C71" s="43"/>
+      <c r="D71" s="43"/>
+      <c r="E71" s="43"/>
+      <c r="F71" s="43"/>
+      <c r="G71" s="43"/>
+      <c r="H71" s="43"/>
+      <c r="I71" s="43"/>
+      <c r="J71" s="43"/>
+      <c r="K71" s="43"/>
+      <c r="L71" s="43"/>
+      <c r="M71" s="43"/>
+      <c r="AA71" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C71="",'Score Log'!$E71=""),0,IF(COUNTIFS('Score Log'!$C$4:$C71,'Score Log'!$C71,'Score Log'!$E$4:$E71,'Score Log'!$E71)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB71" s="33" t="str">
+        <f aca="false">IF($AA71=1,SUM($AA$4:$AA71),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="B72" s="43"/>
+      <c r="C72" s="43"/>
+      <c r="D72" s="43"/>
+      <c r="E72" s="43"/>
+      <c r="F72" s="43"/>
+      <c r="G72" s="43"/>
+      <c r="H72" s="43"/>
+      <c r="I72" s="43"/>
+      <c r="J72" s="43"/>
+      <c r="K72" s="43"/>
+      <c r="L72" s="43"/>
+      <c r="M72" s="43"/>
+      <c r="AA72" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C72="",'Score Log'!$E72=""),0,IF(COUNTIFS('Score Log'!$C$4:$C72,'Score Log'!$C72,'Score Log'!$E$4:$E72,'Score Log'!$E72)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB72" s="33" t="str">
+        <f aca="false">IF($AA72=1,SUM($AA$4:$AA72),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="B73" s="43"/>
+      <c r="C73" s="43"/>
+      <c r="D73" s="43"/>
+      <c r="E73" s="43"/>
+      <c r="F73" s="43"/>
+      <c r="G73" s="43"/>
+      <c r="H73" s="43"/>
+      <c r="I73" s="43"/>
+      <c r="J73" s="43"/>
+      <c r="K73" s="43"/>
+      <c r="L73" s="43"/>
+      <c r="M73" s="43"/>
+      <c r="AA73" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C73="",'Score Log'!$E73=""),0,IF(COUNTIFS('Score Log'!$C$4:$C73,'Score Log'!$C73,'Score Log'!$E$4:$E73,'Score Log'!$E73)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB73" s="33" t="str">
+        <f aca="false">IF($AA73=1,SUM($AA$4:$AA73),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA74" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C74="",'Score Log'!$E74=""),0,IF(COUNTIFS('Score Log'!$C$4:$C74,'Score Log'!$C74,'Score Log'!$E$4:$E74,'Score Log'!$E74)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB74" s="33" t="str">
+        <f aca="false">IF($AA74=1,SUM($AA$4:$AA74),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA75" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C75="",'Score Log'!$E75=""),0,IF(COUNTIFS('Score Log'!$C$4:$C75,'Score Log'!$C75,'Score Log'!$E$4:$E75,'Score Log'!$E75)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB75" s="33" t="str">
+        <f aca="false">IF($AA75=1,SUM($AA$4:$AA75),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA76" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C76="",'Score Log'!$E76=""),0,IF(COUNTIFS('Score Log'!$C$4:$C76,'Score Log'!$C76,'Score Log'!$E$4:$E76,'Score Log'!$E76)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB76" s="33" t="str">
+        <f aca="false">IF($AA76=1,SUM($AA$4:$AA76),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA77" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C77="",'Score Log'!$E77=""),0,IF(COUNTIFS('Score Log'!$C$4:$C77,'Score Log'!$C77,'Score Log'!$E$4:$E77,'Score Log'!$E77)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB77" s="33" t="str">
+        <f aca="false">IF($AA77=1,SUM($AA$4:$AA77),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA78" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C78="",'Score Log'!$E78=""),0,IF(COUNTIFS('Score Log'!$C$4:$C78,'Score Log'!$C78,'Score Log'!$E$4:$E78,'Score Log'!$E78)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB78" s="33" t="str">
+        <f aca="false">IF($AA78=1,SUM($AA$4:$AA78),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA79" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C79="",'Score Log'!$E79=""),0,IF(COUNTIFS('Score Log'!$C$4:$C79,'Score Log'!$C79,'Score Log'!$E$4:$E79,'Score Log'!$E79)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB79" s="33" t="str">
+        <f aca="false">IF($AA79=1,SUM($AA$4:$AA79),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA80" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C80="",'Score Log'!$E80=""),0,IF(COUNTIFS('Score Log'!$C$4:$C80,'Score Log'!$C80,'Score Log'!$E$4:$E80,'Score Log'!$E80)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB80" s="33" t="str">
+        <f aca="false">IF($AA80=1,SUM($AA$4:$AA80),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA81" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C81="",'Score Log'!$E81=""),0,IF(COUNTIFS('Score Log'!$C$4:$C81,'Score Log'!$C81,'Score Log'!$E$4:$E81,'Score Log'!$E81)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB81" s="33" t="str">
+        <f aca="false">IF($AA81=1,SUM($AA$4:$AA81),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA82" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C82="",'Score Log'!$E82=""),0,IF(COUNTIFS('Score Log'!$C$4:$C82,'Score Log'!$C82,'Score Log'!$E$4:$E82,'Score Log'!$E82)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB82" s="33" t="str">
+        <f aca="false">IF($AA82=1,SUM($AA$4:$AA82),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA83" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C83="",'Score Log'!$E83=""),0,IF(COUNTIFS('Score Log'!$C$4:$C83,'Score Log'!$C83,'Score Log'!$E$4:$E83,'Score Log'!$E83)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB83" s="33" t="str">
+        <f aca="false">IF($AA83=1,SUM($AA$4:$AA83),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA84" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C84="",'Score Log'!$E84=""),0,IF(COUNTIFS('Score Log'!$C$4:$C84,'Score Log'!$C84,'Score Log'!$E$4:$E84,'Score Log'!$E84)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB84" s="33" t="str">
+        <f aca="false">IF($AA84=1,SUM($AA$4:$AA84),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA85" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C85="",'Score Log'!$E85=""),0,IF(COUNTIFS('Score Log'!$C$4:$C85,'Score Log'!$C85,'Score Log'!$E$4:$E85,'Score Log'!$E85)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB85" s="33" t="str">
+        <f aca="false">IF($AA85=1,SUM($AA$4:$AA85),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA86" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C86="",'Score Log'!$E86=""),0,IF(COUNTIFS('Score Log'!$C$4:$C86,'Score Log'!$C86,'Score Log'!$E$4:$E86,'Score Log'!$E86)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB86" s="33" t="str">
+        <f aca="false">IF($AA86=1,SUM($AA$4:$AA86),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA87" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C87="",'Score Log'!$E87=""),0,IF(COUNTIFS('Score Log'!$C$4:$C87,'Score Log'!$C87,'Score Log'!$E$4:$E87,'Score Log'!$E87)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB87" s="33" t="str">
+        <f aca="false">IF($AA87=1,SUM($AA$4:$AA87),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA88" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C88="",'Score Log'!$E88=""),0,IF(COUNTIFS('Score Log'!$C$4:$C88,'Score Log'!$C88,'Score Log'!$E$4:$E88,'Score Log'!$E88)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB88" s="33" t="str">
+        <f aca="false">IF($AA88=1,SUM($AA$4:$AA88),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA89" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C89="",'Score Log'!$E89=""),0,IF(COUNTIFS('Score Log'!$C$4:$C89,'Score Log'!$C89,'Score Log'!$E$4:$E89,'Score Log'!$E89)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB89" s="33" t="str">
+        <f aca="false">IF($AA89=1,SUM($AA$4:$AA89),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA90" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C90="",'Score Log'!$E90=""),0,IF(COUNTIFS('Score Log'!$C$4:$C90,'Score Log'!$C90,'Score Log'!$E$4:$E90,'Score Log'!$E90)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB90" s="33" t="str">
+        <f aca="false">IF($AA90=1,SUM($AA$4:$AA90),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA91" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C91="",'Score Log'!$E91=""),0,IF(COUNTIFS('Score Log'!$C$4:$C91,'Score Log'!$C91,'Score Log'!$E$4:$E91,'Score Log'!$E91)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB91" s="33" t="str">
+        <f aca="false">IF($AA91=1,SUM($AA$4:$AA91),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA92" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C92="",'Score Log'!$E92=""),0,IF(COUNTIFS('Score Log'!$C$4:$C92,'Score Log'!$C92,'Score Log'!$E$4:$E92,'Score Log'!$E92)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB92" s="33" t="str">
+        <f aca="false">IF($AA92=1,SUM($AA$4:$AA92),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA93" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C93="",'Score Log'!$E93=""),0,IF(COUNTIFS('Score Log'!$C$4:$C93,'Score Log'!$C93,'Score Log'!$E$4:$E93,'Score Log'!$E93)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB93" s="33" t="str">
+        <f aca="false">IF($AA93=1,SUM($AA$4:$AA93),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA94" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C94="",'Score Log'!$E94=""),0,IF(COUNTIFS('Score Log'!$C$4:$C94,'Score Log'!$C94,'Score Log'!$E$4:$E94,'Score Log'!$E94)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB94" s="33" t="str">
+        <f aca="false">IF($AA94=1,SUM($AA$4:$AA94),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA95" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C95="",'Score Log'!$E95=""),0,IF(COUNTIFS('Score Log'!$C$4:$C95,'Score Log'!$C95,'Score Log'!$E$4:$E95,'Score Log'!$E95)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB95" s="33" t="str">
+        <f aca="false">IF($AA95=1,SUM($AA$4:$AA95),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA96" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C96="",'Score Log'!$E96=""),0,IF(COUNTIFS('Score Log'!$C$4:$C96,'Score Log'!$C96,'Score Log'!$E$4:$E96,'Score Log'!$E96)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB96" s="33" t="str">
+        <f aca="false">IF($AA96=1,SUM($AA$4:$AA96),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA97" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C97="",'Score Log'!$E97=""),0,IF(COUNTIFS('Score Log'!$C$4:$C97,'Score Log'!$C97,'Score Log'!$E$4:$E97,'Score Log'!$E97)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB97" s="33" t="str">
+        <f aca="false">IF($AA97=1,SUM($AA$4:$AA97),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA98" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C98="",'Score Log'!$E98=""),0,IF(COUNTIFS('Score Log'!$C$4:$C98,'Score Log'!$C98,'Score Log'!$E$4:$E98,'Score Log'!$E98)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB98" s="33" t="str">
+        <f aca="false">IF($AA98=1,SUM($AA$4:$AA98),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA99" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C99="",'Score Log'!$E99=""),0,IF(COUNTIFS('Score Log'!$C$4:$C99,'Score Log'!$C99,'Score Log'!$E$4:$E99,'Score Log'!$E99)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB99" s="33" t="str">
+        <f aca="false">IF($AA99=1,SUM($AA$4:$AA99),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA100" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C100="",'Score Log'!$E100=""),0,IF(COUNTIFS('Score Log'!$C$4:$C100,'Score Log'!$C100,'Score Log'!$E$4:$E100,'Score Log'!$E100)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB100" s="33" t="str">
+        <f aca="false">IF($AA100=1,SUM($AA$4:$AA100),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA101" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C101="",'Score Log'!$E101=""),0,IF(COUNTIFS('Score Log'!$C$4:$C101,'Score Log'!$C101,'Score Log'!$E$4:$E101,'Score Log'!$E101)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB101" s="33" t="str">
+        <f aca="false">IF($AA101=1,SUM($AA$4:$AA101),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA102" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C102="",'Score Log'!$E102=""),0,IF(COUNTIFS('Score Log'!$C$4:$C102,'Score Log'!$C102,'Score Log'!$E$4:$E102,'Score Log'!$E102)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB102" s="33" t="str">
+        <f aca="false">IF($AA102=1,SUM($AA$4:$AA102),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA103" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C103="",'Score Log'!$E103=""),0,IF(COUNTIFS('Score Log'!$C$4:$C103,'Score Log'!$C103,'Score Log'!$E$4:$E103,'Score Log'!$E103)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB103" s="33" t="str">
+        <f aca="false">IF($AA103=1,SUM($AA$4:$AA103),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA104" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C104="",'Score Log'!$E104=""),0,IF(COUNTIFS('Score Log'!$C$4:$C104,'Score Log'!$C104,'Score Log'!$E$4:$E104,'Score Log'!$E104)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB104" s="33" t="str">
+        <f aca="false">IF($AA104=1,SUM($AA$4:$AA104),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA105" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C105="",'Score Log'!$E105=""),0,IF(COUNTIFS('Score Log'!$C$4:$C105,'Score Log'!$C105,'Score Log'!$E$4:$E105,'Score Log'!$E105)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB105" s="33" t="str">
+        <f aca="false">IF($AA105=1,SUM($AA$4:$AA105),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA106" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C106="",'Score Log'!$E106=""),0,IF(COUNTIFS('Score Log'!$C$4:$C106,'Score Log'!$C106,'Score Log'!$E$4:$E106,'Score Log'!$E106)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB106" s="33" t="str">
+        <f aca="false">IF($AA106=1,SUM($AA$4:$AA106),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA107" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C107="",'Score Log'!$E107=""),0,IF(COUNTIFS('Score Log'!$C$4:$C107,'Score Log'!$C107,'Score Log'!$E$4:$E107,'Score Log'!$E107)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB107" s="33" t="str">
+        <f aca="false">IF($AA107=1,SUM($AA$4:$AA107),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA108" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C108="",'Score Log'!$E108=""),0,IF(COUNTIFS('Score Log'!$C$4:$C108,'Score Log'!$C108,'Score Log'!$E$4:$E108,'Score Log'!$E108)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB108" s="33" t="str">
+        <f aca="false">IF($AA108=1,SUM($AA$4:$AA108),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA109" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C109="",'Score Log'!$E109=""),0,IF(COUNTIFS('Score Log'!$C$4:$C109,'Score Log'!$C109,'Score Log'!$E$4:$E109,'Score Log'!$E109)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB109" s="33" t="str">
+        <f aca="false">IF($AA109=1,SUM($AA$4:$AA109),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA110" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C110="",'Score Log'!$E110=""),0,IF(COUNTIFS('Score Log'!$C$4:$C110,'Score Log'!$C110,'Score Log'!$E$4:$E110,'Score Log'!$E110)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB110" s="33" t="str">
+        <f aca="false">IF($AA110=1,SUM($AA$4:$AA110),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA111" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C111="",'Score Log'!$E111=""),0,IF(COUNTIFS('Score Log'!$C$4:$C111,'Score Log'!$C111,'Score Log'!$E$4:$E111,'Score Log'!$E111)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB111" s="33" t="str">
+        <f aca="false">IF($AA111=1,SUM($AA$4:$AA111),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA112" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C112="",'Score Log'!$E112=""),0,IF(COUNTIFS('Score Log'!$C$4:$C112,'Score Log'!$C112,'Score Log'!$E$4:$E112,'Score Log'!$E112)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB112" s="33" t="str">
+        <f aca="false">IF($AA112=1,SUM($AA$4:$AA112),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA113" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C113="",'Score Log'!$E113=""),0,IF(COUNTIFS('Score Log'!$C$4:$C113,'Score Log'!$C113,'Score Log'!$E$4:$E113,'Score Log'!$E113)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB113" s="33" t="str">
+        <f aca="false">IF($AA113=1,SUM($AA$4:$AA113),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA114" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C114="",'Score Log'!$E114=""),0,IF(COUNTIFS('Score Log'!$C$4:$C114,'Score Log'!$C114,'Score Log'!$E$4:$E114,'Score Log'!$E114)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB114" s="33" t="str">
+        <f aca="false">IF($AA114=1,SUM($AA$4:$AA114),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA115" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C115="",'Score Log'!$E115=""),0,IF(COUNTIFS('Score Log'!$C$4:$C115,'Score Log'!$C115,'Score Log'!$E$4:$E115,'Score Log'!$E115)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB115" s="33" t="str">
+        <f aca="false">IF($AA115=1,SUM($AA$4:$AA115),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA116" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C116="",'Score Log'!$E116=""),0,IF(COUNTIFS('Score Log'!$C$4:$C116,'Score Log'!$C116,'Score Log'!$E$4:$E116,'Score Log'!$E116)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB116" s="33" t="str">
+        <f aca="false">IF($AA116=1,SUM($AA$4:$AA116),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA117" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C117="",'Score Log'!$E117=""),0,IF(COUNTIFS('Score Log'!$C$4:$C117,'Score Log'!$C117,'Score Log'!$E$4:$E117,'Score Log'!$E117)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB117" s="33" t="str">
+        <f aca="false">IF($AA117=1,SUM($AA$4:$AA117),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA118" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C118="",'Score Log'!$E118=""),0,IF(COUNTIFS('Score Log'!$C$4:$C118,'Score Log'!$C118,'Score Log'!$E$4:$E118,'Score Log'!$E118)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB118" s="33" t="str">
+        <f aca="false">IF($AA118=1,SUM($AA$4:$AA118),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA119" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C119="",'Score Log'!$E119=""),0,IF(COUNTIFS('Score Log'!$C$4:$C119,'Score Log'!$C119,'Score Log'!$E$4:$E119,'Score Log'!$E119)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB119" s="33" t="str">
+        <f aca="false">IF($AA119=1,SUM($AA$4:$AA119),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA120" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C120="",'Score Log'!$E120=""),0,IF(COUNTIFS('Score Log'!$C$4:$C120,'Score Log'!$C120,'Score Log'!$E$4:$E120,'Score Log'!$E120)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB120" s="33" t="str">
+        <f aca="false">IF($AA120=1,SUM($AA$4:$AA120),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA121" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C121="",'Score Log'!$E121=""),0,IF(COUNTIFS('Score Log'!$C$4:$C121,'Score Log'!$C121,'Score Log'!$E$4:$E121,'Score Log'!$E121)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB121" s="33" t="str">
+        <f aca="false">IF($AA121=1,SUM($AA$4:$AA121),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA122" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C122="",'Score Log'!$E122=""),0,IF(COUNTIFS('Score Log'!$C$4:$C122,'Score Log'!$C122,'Score Log'!$E$4:$E122,'Score Log'!$E122)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB122" s="33" t="str">
+        <f aca="false">IF($AA122=1,SUM($AA$4:$AA122),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA123" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C123="",'Score Log'!$E123=""),0,IF(COUNTIFS('Score Log'!$C$4:$C123,'Score Log'!$C123,'Score Log'!$E$4:$E123,'Score Log'!$E123)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB123" s="33" t="str">
+        <f aca="false">IF($AA123=1,SUM($AA$4:$AA123),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA124" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C124="",'Score Log'!$E124=""),0,IF(COUNTIFS('Score Log'!$C$4:$C124,'Score Log'!$C124,'Score Log'!$E$4:$E124,'Score Log'!$E124)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB124" s="33" t="str">
+        <f aca="false">IF($AA124=1,SUM($AA$4:$AA124),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA125" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C125="",'Score Log'!$E125=""),0,IF(COUNTIFS('Score Log'!$C$4:$C125,'Score Log'!$C125,'Score Log'!$E$4:$E125,'Score Log'!$E125)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB125" s="33" t="str">
+        <f aca="false">IF($AA125=1,SUM($AA$4:$AA125),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA126" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C126="",'Score Log'!$E126=""),0,IF(COUNTIFS('Score Log'!$C$4:$C126,'Score Log'!$C126,'Score Log'!$E$4:$E126,'Score Log'!$E126)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB126" s="33" t="str">
+        <f aca="false">IF($AA126=1,SUM($AA$4:$AA126),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA127" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C127="",'Score Log'!$E127=""),0,IF(COUNTIFS('Score Log'!$C$4:$C127,'Score Log'!$C127,'Score Log'!$E$4:$E127,'Score Log'!$E127)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB127" s="33" t="str">
+        <f aca="false">IF($AA127=1,SUM($AA$4:$AA127),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA128" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C128="",'Score Log'!$E128=""),0,IF(COUNTIFS('Score Log'!$C$4:$C128,'Score Log'!$C128,'Score Log'!$E$4:$E128,'Score Log'!$E128)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB128" s="33" t="str">
+        <f aca="false">IF($AA128=1,SUM($AA$4:$AA128),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA129" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C129="",'Score Log'!$E129=""),0,IF(COUNTIFS('Score Log'!$C$4:$C129,'Score Log'!$C129,'Score Log'!$E$4:$E129,'Score Log'!$E129)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB129" s="33" t="str">
+        <f aca="false">IF($AA129=1,SUM($AA$4:$AA129),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA130" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C130="",'Score Log'!$E130=""),0,IF(COUNTIFS('Score Log'!$C$4:$C130,'Score Log'!$C130,'Score Log'!$E$4:$E130,'Score Log'!$E130)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB130" s="33" t="str">
+        <f aca="false">IF($AA130=1,SUM($AA$4:$AA130),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA131" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C131="",'Score Log'!$E131=""),0,IF(COUNTIFS('Score Log'!$C$4:$C131,'Score Log'!$C131,'Score Log'!$E$4:$E131,'Score Log'!$E131)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB131" s="33" t="str">
+        <f aca="false">IF($AA131=1,SUM($AA$4:$AA131),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA132" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C132="",'Score Log'!$E132=""),0,IF(COUNTIFS('Score Log'!$C$4:$C132,'Score Log'!$C132,'Score Log'!$E$4:$E132,'Score Log'!$E132)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB132" s="33" t="str">
+        <f aca="false">IF($AA132=1,SUM($AA$4:$AA132),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA133" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C133="",'Score Log'!$E133=""),0,IF(COUNTIFS('Score Log'!$C$4:$C133,'Score Log'!$C133,'Score Log'!$E$4:$E133,'Score Log'!$E133)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB133" s="33" t="str">
+        <f aca="false">IF($AA133=1,SUM($AA$4:$AA133),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA134" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C134="",'Score Log'!$E134=""),0,IF(COUNTIFS('Score Log'!$C$4:$C134,'Score Log'!$C134,'Score Log'!$E$4:$E134,'Score Log'!$E134)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB134" s="33" t="str">
+        <f aca="false">IF($AA134=1,SUM($AA$4:$AA134),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA135" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C135="",'Score Log'!$E135=""),0,IF(COUNTIFS('Score Log'!$C$4:$C135,'Score Log'!$C135,'Score Log'!$E$4:$E135,'Score Log'!$E135)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB135" s="33" t="str">
+        <f aca="false">IF($AA135=1,SUM($AA$4:$AA135),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA136" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C136="",'Score Log'!$E136=""),0,IF(COUNTIFS('Score Log'!$C$4:$C136,'Score Log'!$C136,'Score Log'!$E$4:$E136,'Score Log'!$E136)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB136" s="33" t="str">
+        <f aca="false">IF($AA136=1,SUM($AA$4:$AA136),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA137" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C137="",'Score Log'!$E137=""),0,IF(COUNTIFS('Score Log'!$C$4:$C137,'Score Log'!$C137,'Score Log'!$E$4:$E137,'Score Log'!$E137)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB137" s="33" t="str">
+        <f aca="false">IF($AA137=1,SUM($AA$4:$AA137),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA138" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C138="",'Score Log'!$E138=""),0,IF(COUNTIFS('Score Log'!$C$4:$C138,'Score Log'!$C138,'Score Log'!$E$4:$E138,'Score Log'!$E138)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB138" s="33" t="str">
+        <f aca="false">IF($AA138=1,SUM($AA$4:$AA138),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA139" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C139="",'Score Log'!$E139=""),0,IF(COUNTIFS('Score Log'!$C$4:$C139,'Score Log'!$C139,'Score Log'!$E$4:$E139,'Score Log'!$E139)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB139" s="33" t="str">
+        <f aca="false">IF($AA139=1,SUM($AA$4:$AA139),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA140" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C140="",'Score Log'!$E140=""),0,IF(COUNTIFS('Score Log'!$C$4:$C140,'Score Log'!$C140,'Score Log'!$E$4:$E140,'Score Log'!$E140)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB140" s="33" t="str">
+        <f aca="false">IF($AA140=1,SUM($AA$4:$AA140),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA141" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C141="",'Score Log'!$E141=""),0,IF(COUNTIFS('Score Log'!$C$4:$C141,'Score Log'!$C141,'Score Log'!$E$4:$E141,'Score Log'!$E141)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB141" s="33" t="str">
+        <f aca="false">IF($AA141=1,SUM($AA$4:$AA141),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA142" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C142="",'Score Log'!$E142=""),0,IF(COUNTIFS('Score Log'!$C$4:$C142,'Score Log'!$C142,'Score Log'!$E$4:$E142,'Score Log'!$E142)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB142" s="33" t="str">
+        <f aca="false">IF($AA142=1,SUM($AA$4:$AA142),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA143" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C143="",'Score Log'!$E143=""),0,IF(COUNTIFS('Score Log'!$C$4:$C143,'Score Log'!$C143,'Score Log'!$E$4:$E143,'Score Log'!$E143)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB143" s="33" t="str">
+        <f aca="false">IF($AA143=1,SUM($AA$4:$AA143),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA144" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C144="",'Score Log'!$E144=""),0,IF(COUNTIFS('Score Log'!$C$4:$C144,'Score Log'!$C144,'Score Log'!$E$4:$E144,'Score Log'!$E144)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB144" s="33" t="str">
+        <f aca="false">IF($AA144=1,SUM($AA$4:$AA144),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA145" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C145="",'Score Log'!$E145=""),0,IF(COUNTIFS('Score Log'!$C$4:$C145,'Score Log'!$C145,'Score Log'!$E$4:$E145,'Score Log'!$E145)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB145" s="33" t="str">
+        <f aca="false">IF($AA145=1,SUM($AA$4:$AA145),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA146" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C146="",'Score Log'!$E146=""),0,IF(COUNTIFS('Score Log'!$C$4:$C146,'Score Log'!$C146,'Score Log'!$E$4:$E146,'Score Log'!$E146)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB146" s="33" t="str">
+        <f aca="false">IF($AA146=1,SUM($AA$4:$AA146),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA147" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C147="",'Score Log'!$E147=""),0,IF(COUNTIFS('Score Log'!$C$4:$C147,'Score Log'!$C147,'Score Log'!$E$4:$E147,'Score Log'!$E147)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB147" s="33" t="str">
+        <f aca="false">IF($AA147=1,SUM($AA$4:$AA147),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA148" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C148="",'Score Log'!$E148=""),0,IF(COUNTIFS('Score Log'!$C$4:$C148,'Score Log'!$C148,'Score Log'!$E$4:$E148,'Score Log'!$E148)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB148" s="33" t="str">
+        <f aca="false">IF($AA148=1,SUM($AA$4:$AA148),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA149" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C149="",'Score Log'!$E149=""),0,IF(COUNTIFS('Score Log'!$C$4:$C149,'Score Log'!$C149,'Score Log'!$E$4:$E149,'Score Log'!$E149)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB149" s="33" t="str">
+        <f aca="false">IF($AA149=1,SUM($AA$4:$AA149),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA150" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C150="",'Score Log'!$E150=""),0,IF(COUNTIFS('Score Log'!$C$4:$C150,'Score Log'!$C150,'Score Log'!$E$4:$E150,'Score Log'!$E150)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB150" s="33" t="str">
+        <f aca="false">IF($AA150=1,SUM($AA$4:$AA150),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA151" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C151="",'Score Log'!$E151=""),0,IF(COUNTIFS('Score Log'!$C$4:$C151,'Score Log'!$C151,'Score Log'!$E$4:$E151,'Score Log'!$E151)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB151" s="33" t="str">
+        <f aca="false">IF($AA151=1,SUM($AA$4:$AA151),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA152" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C152="",'Score Log'!$E152=""),0,IF(COUNTIFS('Score Log'!$C$4:$C152,'Score Log'!$C152,'Score Log'!$E$4:$E152,'Score Log'!$E152)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB152" s="33" t="str">
+        <f aca="false">IF($AA152=1,SUM($AA$4:$AA152),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA153" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C153="",'Score Log'!$E153=""),0,IF(COUNTIFS('Score Log'!$C$4:$C153,'Score Log'!$C153,'Score Log'!$E$4:$E153,'Score Log'!$E153)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB153" s="33" t="str">
+        <f aca="false">IF($AA153=1,SUM($AA$4:$AA153),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA154" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C154="",'Score Log'!$E154=""),0,IF(COUNTIFS('Score Log'!$C$4:$C154,'Score Log'!$C154,'Score Log'!$E$4:$E154,'Score Log'!$E154)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB154" s="33" t="str">
+        <f aca="false">IF($AA154=1,SUM($AA$4:$AA154),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA155" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C155="",'Score Log'!$E155=""),0,IF(COUNTIFS('Score Log'!$C$4:$C155,'Score Log'!$C155,'Score Log'!$E$4:$E155,'Score Log'!$E155)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB155" s="33" t="str">
+        <f aca="false">IF($AA155=1,SUM($AA$4:$AA155),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA156" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C156="",'Score Log'!$E156=""),0,IF(COUNTIFS('Score Log'!$C$4:$C156,'Score Log'!$C156,'Score Log'!$E$4:$E156,'Score Log'!$E156)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB156" s="33" t="str">
+        <f aca="false">IF($AA156=1,SUM($AA$4:$AA156),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA157" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C157="",'Score Log'!$E157=""),0,IF(COUNTIFS('Score Log'!$C$4:$C157,'Score Log'!$C157,'Score Log'!$E$4:$E157,'Score Log'!$E157)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB157" s="33" t="str">
+        <f aca="false">IF($AA157=1,SUM($AA$4:$AA157),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA158" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C158="",'Score Log'!$E158=""),0,IF(COUNTIFS('Score Log'!$C$4:$C158,'Score Log'!$C158,'Score Log'!$E$4:$E158,'Score Log'!$E158)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB158" s="33" t="str">
+        <f aca="false">IF($AA158=1,SUM($AA$4:$AA158),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA159" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C159="",'Score Log'!$E159=""),0,IF(COUNTIFS('Score Log'!$C$4:$C159,'Score Log'!$C159,'Score Log'!$E$4:$E159,'Score Log'!$E159)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB159" s="33" t="str">
+        <f aca="false">IF($AA159=1,SUM($AA$4:$AA159),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA160" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C160="",'Score Log'!$E160=""),0,IF(COUNTIFS('Score Log'!$C$4:$C160,'Score Log'!$C160,'Score Log'!$E$4:$E160,'Score Log'!$E160)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB160" s="33" t="str">
+        <f aca="false">IF($AA160=1,SUM($AA$4:$AA160),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA161" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C161="",'Score Log'!$E161=""),0,IF(COUNTIFS('Score Log'!$C$4:$C161,'Score Log'!$C161,'Score Log'!$E$4:$E161,'Score Log'!$E161)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB161" s="33" t="str">
+        <f aca="false">IF($AA161=1,SUM($AA$4:$AA161),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA162" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C162="",'Score Log'!$E162=""),0,IF(COUNTIFS('Score Log'!$C$4:$C162,'Score Log'!$C162,'Score Log'!$E$4:$E162,'Score Log'!$E162)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB162" s="33" t="str">
+        <f aca="false">IF($AA162=1,SUM($AA$4:$AA162),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA163" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C163="",'Score Log'!$E163=""),0,IF(COUNTIFS('Score Log'!$C$4:$C163,'Score Log'!$C163,'Score Log'!$E$4:$E163,'Score Log'!$E163)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB163" s="33" t="str">
+        <f aca="false">IF($AA163=1,SUM($AA$4:$AA163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA164" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C164="",'Score Log'!$E164=""),0,IF(COUNTIFS('Score Log'!$C$4:$C164,'Score Log'!$C164,'Score Log'!$E$4:$E164,'Score Log'!$E164)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB164" s="33" t="str">
+        <f aca="false">IF($AA164=1,SUM($AA$4:$AA164),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA165" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C165="",'Score Log'!$E165=""),0,IF(COUNTIFS('Score Log'!$C$4:$C165,'Score Log'!$C165,'Score Log'!$E$4:$E165,'Score Log'!$E165)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB165" s="33" t="str">
+        <f aca="false">IF($AA165=1,SUM($AA$4:$AA165),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA166" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C166="",'Score Log'!$E166=""),0,IF(COUNTIFS('Score Log'!$C$4:$C166,'Score Log'!$C166,'Score Log'!$E$4:$E166,'Score Log'!$E166)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB166" s="33" t="str">
+        <f aca="false">IF($AA166=1,SUM($AA$4:$AA166),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA167" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C167="",'Score Log'!$E167=""),0,IF(COUNTIFS('Score Log'!$C$4:$C167,'Score Log'!$C167,'Score Log'!$E$4:$E167,'Score Log'!$E167)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB167" s="33" t="str">
+        <f aca="false">IF($AA167=1,SUM($AA$4:$AA167),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA168" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C168="",'Score Log'!$E168=""),0,IF(COUNTIFS('Score Log'!$C$4:$C168,'Score Log'!$C168,'Score Log'!$E$4:$E168,'Score Log'!$E168)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB168" s="33" t="str">
+        <f aca="false">IF($AA168=1,SUM($AA$4:$AA168),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA169" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C169="",'Score Log'!$E169=""),0,IF(COUNTIFS('Score Log'!$C$4:$C169,'Score Log'!$C169,'Score Log'!$E$4:$E169,'Score Log'!$E169)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB169" s="33" t="str">
+        <f aca="false">IF($AA169=1,SUM($AA$4:$AA169),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA170" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C170="",'Score Log'!$E170=""),0,IF(COUNTIFS('Score Log'!$C$4:$C170,'Score Log'!$C170,'Score Log'!$E$4:$E170,'Score Log'!$E170)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB170" s="33" t="str">
+        <f aca="false">IF($AA170=1,SUM($AA$4:$AA170),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA171" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C171="",'Score Log'!$E171=""),0,IF(COUNTIFS('Score Log'!$C$4:$C171,'Score Log'!$C171,'Score Log'!$E$4:$E171,'Score Log'!$E171)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB171" s="33" t="str">
+        <f aca="false">IF($AA171=1,SUM($AA$4:$AA171),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA172" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C172="",'Score Log'!$E172=""),0,IF(COUNTIFS('Score Log'!$C$4:$C172,'Score Log'!$C172,'Score Log'!$E$4:$E172,'Score Log'!$E172)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB172" s="33" t="str">
+        <f aca="false">IF($AA172=1,SUM($AA$4:$AA172),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA173" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C173="",'Score Log'!$E173=""),0,IF(COUNTIFS('Score Log'!$C$4:$C173,'Score Log'!$C173,'Score Log'!$E$4:$E173,'Score Log'!$E173)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB173" s="33" t="str">
+        <f aca="false">IF($AA173=1,SUM($AA$4:$AA173),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA174" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C174="",'Score Log'!$E174=""),0,IF(COUNTIFS('Score Log'!$C$4:$C174,'Score Log'!$C174,'Score Log'!$E$4:$E174,'Score Log'!$E174)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB174" s="33" t="str">
+        <f aca="false">IF($AA174=1,SUM($AA$4:$AA174),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA175" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C175="",'Score Log'!$E175=""),0,IF(COUNTIFS('Score Log'!$C$4:$C175,'Score Log'!$C175,'Score Log'!$E$4:$E175,'Score Log'!$E175)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB175" s="33" t="str">
+        <f aca="false">IF($AA175=1,SUM($AA$4:$AA175),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA176" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C176="",'Score Log'!$E176=""),0,IF(COUNTIFS('Score Log'!$C$4:$C176,'Score Log'!$C176,'Score Log'!$E$4:$E176,'Score Log'!$E176)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB176" s="33" t="str">
+        <f aca="false">IF($AA176=1,SUM($AA$4:$AA176),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA177" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C177="",'Score Log'!$E177=""),0,IF(COUNTIFS('Score Log'!$C$4:$C177,'Score Log'!$C177,'Score Log'!$E$4:$E177,'Score Log'!$E177)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB177" s="33" t="str">
+        <f aca="false">IF($AA177=1,SUM($AA$4:$AA177),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA178" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C178="",'Score Log'!$E178=""),0,IF(COUNTIFS('Score Log'!$C$4:$C178,'Score Log'!$C178,'Score Log'!$E$4:$E178,'Score Log'!$E178)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB178" s="33" t="str">
+        <f aca="false">IF($AA178=1,SUM($AA$4:$AA178),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA179" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C179="",'Score Log'!$E179=""),0,IF(COUNTIFS('Score Log'!$C$4:$C179,'Score Log'!$C179,'Score Log'!$E$4:$E179,'Score Log'!$E179)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB179" s="33" t="str">
+        <f aca="false">IF($AA179=1,SUM($AA$4:$AA179),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA180" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C180="",'Score Log'!$E180=""),0,IF(COUNTIFS('Score Log'!$C$4:$C180,'Score Log'!$C180,'Score Log'!$E$4:$E180,'Score Log'!$E180)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB180" s="33" t="str">
+        <f aca="false">IF($AA180=1,SUM($AA$4:$AA180),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA181" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C181="",'Score Log'!$E181=""),0,IF(COUNTIFS('Score Log'!$C$4:$C181,'Score Log'!$C181,'Score Log'!$E$4:$E181,'Score Log'!$E181)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB181" s="33" t="str">
+        <f aca="false">IF($AA181=1,SUM($AA$4:$AA181),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA182" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C182="",'Score Log'!$E182=""),0,IF(COUNTIFS('Score Log'!$C$4:$C182,'Score Log'!$C182,'Score Log'!$E$4:$E182,'Score Log'!$E182)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB182" s="33" t="str">
+        <f aca="false">IF($AA182=1,SUM($AA$4:$AA182),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA183" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C183="",'Score Log'!$E183=""),0,IF(COUNTIFS('Score Log'!$C$4:$C183,'Score Log'!$C183,'Score Log'!$E$4:$E183,'Score Log'!$E183)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB183" s="33" t="str">
+        <f aca="false">IF($AA183=1,SUM($AA$4:$AA183),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA184" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C184="",'Score Log'!$E184=""),0,IF(COUNTIFS('Score Log'!$C$4:$C184,'Score Log'!$C184,'Score Log'!$E$4:$E184,'Score Log'!$E184)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB184" s="33" t="str">
+        <f aca="false">IF($AA184=1,SUM($AA$4:$AA184),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA185" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C185="",'Score Log'!$E185=""),0,IF(COUNTIFS('Score Log'!$C$4:$C185,'Score Log'!$C185,'Score Log'!$E$4:$E185,'Score Log'!$E185)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB185" s="33" t="str">
+        <f aca="false">IF($AA185=1,SUM($AA$4:$AA185),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA186" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C186="",'Score Log'!$E186=""),0,IF(COUNTIFS('Score Log'!$C$4:$C186,'Score Log'!$C186,'Score Log'!$E$4:$E186,'Score Log'!$E186)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB186" s="33" t="str">
+        <f aca="false">IF($AA186=1,SUM($AA$4:$AA186),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA187" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C187="",'Score Log'!$E187=""),0,IF(COUNTIFS('Score Log'!$C$4:$C187,'Score Log'!$C187,'Score Log'!$E$4:$E187,'Score Log'!$E187)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB187" s="33" t="str">
+        <f aca="false">IF($AA187=1,SUM($AA$4:$AA187),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA188" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C188="",'Score Log'!$E188=""),0,IF(COUNTIFS('Score Log'!$C$4:$C188,'Score Log'!$C188,'Score Log'!$E$4:$E188,'Score Log'!$E188)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB188" s="33" t="str">
+        <f aca="false">IF($AA188=1,SUM($AA$4:$AA188),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA189" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C189="",'Score Log'!$E189=""),0,IF(COUNTIFS('Score Log'!$C$4:$C189,'Score Log'!$C189,'Score Log'!$E$4:$E189,'Score Log'!$E189)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB189" s="33" t="str">
+        <f aca="false">IF($AA189=1,SUM($AA$4:$AA189),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA190" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C190="",'Score Log'!$E190=""),0,IF(COUNTIFS('Score Log'!$C$4:$C190,'Score Log'!$C190,'Score Log'!$E$4:$E190,'Score Log'!$E190)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB190" s="33" t="str">
+        <f aca="false">IF($AA190=1,SUM($AA$4:$AA190),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA191" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C191="",'Score Log'!$E191=""),0,IF(COUNTIFS('Score Log'!$C$4:$C191,'Score Log'!$C191,'Score Log'!$E$4:$E191,'Score Log'!$E191)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB191" s="33" t="str">
+        <f aca="false">IF($AA191=1,SUM($AA$4:$AA191),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA192" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C192="",'Score Log'!$E192=""),0,IF(COUNTIFS('Score Log'!$C$4:$C192,'Score Log'!$C192,'Score Log'!$E$4:$E192,'Score Log'!$E192)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB192" s="33" t="str">
+        <f aca="false">IF($AA192=1,SUM($AA$4:$AA192),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA193" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C193="",'Score Log'!$E193=""),0,IF(COUNTIFS('Score Log'!$C$4:$C193,'Score Log'!$C193,'Score Log'!$E$4:$E193,'Score Log'!$E193)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB193" s="33" t="str">
+        <f aca="false">IF($AA193=1,SUM($AA$4:$AA193),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA194" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C194="",'Score Log'!$E194=""),0,IF(COUNTIFS('Score Log'!$C$4:$C194,'Score Log'!$C194,'Score Log'!$E$4:$E194,'Score Log'!$E194)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB194" s="33" t="str">
+        <f aca="false">IF($AA194=1,SUM($AA$4:$AA194),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA195" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C195="",'Score Log'!$E195=""),0,IF(COUNTIFS('Score Log'!$C$4:$C195,'Score Log'!$C195,'Score Log'!$E$4:$E195,'Score Log'!$E195)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB195" s="33" t="str">
+        <f aca="false">IF($AA195=1,SUM($AA$4:$AA195),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA196" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C196="",'Score Log'!$E196=""),0,IF(COUNTIFS('Score Log'!$C$4:$C196,'Score Log'!$C196,'Score Log'!$E$4:$E196,'Score Log'!$E196)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB196" s="33" t="str">
+        <f aca="false">IF($AA196=1,SUM($AA$4:$AA196),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA197" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C197="",'Score Log'!$E197=""),0,IF(COUNTIFS('Score Log'!$C$4:$C197,'Score Log'!$C197,'Score Log'!$E$4:$E197,'Score Log'!$E197)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB197" s="33" t="str">
+        <f aca="false">IF($AA197=1,SUM($AA$4:$AA197),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA198" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C198="",'Score Log'!$E198=""),0,IF(COUNTIFS('Score Log'!$C$4:$C198,'Score Log'!$C198,'Score Log'!$E$4:$E198,'Score Log'!$E198)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB198" s="33" t="str">
+        <f aca="false">IF($AA198=1,SUM($AA$4:$AA198),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA199" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C199="",'Score Log'!$E199=""),0,IF(COUNTIFS('Score Log'!$C$4:$C199,'Score Log'!$C199,'Score Log'!$E$4:$E199,'Score Log'!$E199)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB199" s="33" t="str">
+        <f aca="false">IF($AA199=1,SUM($AA$4:$AA199),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA200" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C200="",'Score Log'!$E200=""),0,IF(COUNTIFS('Score Log'!$C$4:$C200,'Score Log'!$C200,'Score Log'!$E$4:$E200,'Score Log'!$E200)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB200" s="33" t="str">
+        <f aca="false">IF($AA200=1,SUM($AA$4:$AA200),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA201" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C201="",'Score Log'!$E201=""),0,IF(COUNTIFS('Score Log'!$C$4:$C201,'Score Log'!$C201,'Score Log'!$E$4:$E201,'Score Log'!$E201)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB201" s="33" t="str">
+        <f aca="false">IF($AA201=1,SUM($AA$4:$AA201),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA202" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C202="",'Score Log'!$E202=""),0,IF(COUNTIFS('Score Log'!$C$4:$C202,'Score Log'!$C202,'Score Log'!$E$4:$E202,'Score Log'!$E202)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB202" s="33" t="str">
+        <f aca="false">IF($AA202=1,SUM($AA$4:$AA202),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA203" s="33" t="n">
+        <f aca="false">IF(OR('Score Log'!$C203="",'Score Log'!$E203=""),0,IF(COUNTIFS('Score Log'!$C$4:$C203,'Score Log'!$C203,'Score Log'!$E$4:$E203,'Score Log'!$E203)=1,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="AB203" s="33" t="str">
+        <f aca="false">IF($AA203=1,SUM($AA$4:$AA203),"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B3:C3"/>
+  <mergeCells count="9">
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="D3:J3"/>
     <mergeCell ref="K3:M3"/>
-    <mergeCell ref="A48:M48"/>
-    <mergeCell ref="A49:M49"/>
-    <mergeCell ref="A50:M50"/>
-    <mergeCell ref="A51:M51"/>
-    <mergeCell ref="A52:M52"/>
+    <mergeCell ref="A68:M68"/>
+    <mergeCell ref="A69:M69"/>
+    <mergeCell ref="A70:M70"/>
+    <mergeCell ref="A71:M71"/>
+    <mergeCell ref="A72:M72"/>
+    <mergeCell ref="A73:M73"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:I44">
+  <conditionalFormatting sqref="E5:I64">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -14069,7 +17878,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:M44">
+  <conditionalFormatting sqref="K5:M64">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -14081,16 +17890,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation allowBlank="true" error="Pick a supplier from the Suppliers tab (or add it there first)." errorStyle="stop" errorTitle="Unknown supplier" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B5:B44" type="list">
-      <formula1>ScorecardSuppliers</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Pick a process from the list in Settings (or add it there first)." errorStyle="stop" errorTitle="Unknown process" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C5:C44" type="list">
-      <formula1>ScorecardProcesses</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -14119,30 +17918,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="44" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D2" s="44" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F2" s="44" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14151,13 +17950,13 @@
       </c>
       <c r="B3" s="45"/>
       <c r="C3" s="45" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E3" s="45" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F3" s="45"/>
     </row>
@@ -14424,112 +18223,112 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="44" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="48" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F5" s="49" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="48" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D6" s="49" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E6" s="49" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F6" s="49" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="48" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D7" s="49" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E7" s="49" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F7" s="49" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="48" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D8" s="49" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E8" s="49" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F8" s="49" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -14560,23 +18359,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="50" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B4" s="51" t="n">
         <v>0.25</v>
@@ -14587,7 +18386,7 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="50" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B5" s="51" t="n">
         <v>0.3</v>
@@ -14598,76 +18397,76 @@
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="50" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B6" s="51" t="n">
         <v>0.25</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="50" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B7" s="51" t="n">
         <v>0.2</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="53" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B8" s="54" t="n">
         <f aca="false">SUM(B4:B7)</f>
         <v>1</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="52" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D10" s="52" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D11" s="52" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D12" s="52" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D13" s="52" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="52" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D15" s="52" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D16" s="52" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
